--- a/data/hex_xlsx/INVEST.HE.xlsx
+++ b/data/hex_xlsx/INVEST.HE.xlsx
@@ -1131,7 +1131,7 @@
     <numFmt numFmtId="165" formatCode="#,##0.0"/>
     <numFmt numFmtId="166" formatCode="[&gt;=100]#,###0.0\%;[&lt;=-100]-#,###0.0\%;#,###0.0\%"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11.0"/>
       <color rgb="FF000000"/>
@@ -1174,6 +1174,12 @@
     <font>
       <sz val="10.0"/>
       <color rgb="FFF5475B"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="10.0"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -1245,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1312,6 +1318,9 @@
     <xf borderId="3" fillId="0" fontId="8" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="3" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
@@ -1324,7 +1333,7 @@
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="3" fillId="0" fontId="8" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+    <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="3" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFill="1" applyFont="1">
@@ -2910,20 +2919,48 @@
       <c r="M30" s="15">
         <v>2.26</v>
       </c>
-      <c r="N30" s="16"/>
-      <c r="O30" s="16"/>
-      <c r="P30" s="16"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
+      <c r="N30" s="21">
+        <v>3.27</v>
+      </c>
+      <c r="O30" s="21">
+        <v>2.81</v>
+      </c>
+      <c r="P30" s="21">
+        <v>3.2</v>
+      </c>
+      <c r="Q30" s="21">
+        <v>3.13</v>
+      </c>
+      <c r="R30" s="21">
+        <v>2.84</v>
+      </c>
+      <c r="S30" s="21">
+        <v>2.58</v>
+      </c>
+      <c r="T30" s="21">
+        <v>2.49</v>
+      </c>
+      <c r="U30" s="21">
+        <v>2.5</v>
+      </c>
+      <c r="V30" s="21">
+        <v>2.43</v>
+      </c>
+      <c r="W30" s="21">
+        <v>1.78</v>
+      </c>
+      <c r="X30" s="21">
+        <v>1.94</v>
+      </c>
+      <c r="Y30" s="21">
+        <v>1.91</v>
+      </c>
+      <c r="Z30" s="21">
+        <v>2.0</v>
+      </c>
+      <c r="AA30" s="21">
+        <v>3.44</v>
+      </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
@@ -3271,7 +3308,9 @@
       <c r="X36" s="16"/>
       <c r="Y36" s="16"/>
       <c r="Z36" s="16"/>
-      <c r="AA36" s="16"/>
+      <c r="AA36" s="15">
+        <v>0.24</v>
+      </c>
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
@@ -3488,7 +3527,9 @@
       <c r="X41" s="16"/>
       <c r="Y41" s="16"/>
       <c r="Z41" s="16"/>
-      <c r="AA41" s="16"/>
+      <c r="AA41" s="15">
+        <v>0.79</v>
+      </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
@@ -3563,7 +3604,7 @@
       <c r="B44" s="18">
         <v>38.86</v>
       </c>
-      <c r="C44" s="21">
+      <c r="C44" s="22">
         <v>-23.24</v>
       </c>
       <c r="D44" s="18">
@@ -3587,13 +3628,13 @@
       <c r="J44" s="18">
         <v>4.37</v>
       </c>
-      <c r="K44" s="21">
+      <c r="K44" s="22">
         <v>-12.73</v>
       </c>
-      <c r="L44" s="21">
+      <c r="L44" s="22">
         <v>-25.82</v>
       </c>
-      <c r="M44" s="21">
+      <c r="M44" s="22">
         <v>-0.09</v>
       </c>
       <c r="N44" s="18">
@@ -3655,10 +3696,10 @@
       <c r="E45" s="18">
         <v>42.96</v>
       </c>
-      <c r="F45" s="21">
+      <c r="F45" s="22">
         <v>-8.38</v>
       </c>
-      <c r="G45" s="21">
+      <c r="G45" s="22">
         <v>-11.2</v>
       </c>
       <c r="H45" s="18">
@@ -4041,7 +4082,7 @@
       <c r="L52" s="16"/>
       <c r="M52" s="16"/>
       <c r="N52" s="16"/>
-      <c r="O52" s="22">
+      <c r="O52" s="23">
         <v>0.0</v>
       </c>
       <c r="P52" s="16"/>
@@ -4130,7 +4171,7 @@
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
-      <c r="N54" s="22">
+      <c r="N54" s="23">
         <v>0.0</v>
       </c>
       <c r="O54" s="16">
@@ -4290,7 +4331,7 @@
       <c r="P57" s="20">
         <v>-0.14</v>
       </c>
-      <c r="Q57" s="22">
+      <c r="Q57" s="23">
         <v>0.0</v>
       </c>
       <c r="R57" s="16">
@@ -4371,34 +4412,34 @@
       <c r="A59" s="17" t="s">
         <v>118</v>
       </c>
-      <c r="B59" s="21">
+      <c r="B59" s="22">
         <v>-8.39</v>
       </c>
-      <c r="C59" s="21">
+      <c r="C59" s="22">
         <v>-16.05</v>
       </c>
-      <c r="D59" s="21">
+      <c r="D59" s="22">
         <v>-4.35</v>
       </c>
-      <c r="E59" s="21">
+      <c r="E59" s="22">
         <v>-2.41</v>
       </c>
-      <c r="F59" s="21">
+      <c r="F59" s="22">
         <v>-6.25</v>
       </c>
-      <c r="G59" s="21">
+      <c r="G59" s="22">
         <v>-11.97</v>
       </c>
-      <c r="H59" s="21">
+      <c r="H59" s="22">
         <v>-11.94</v>
       </c>
-      <c r="I59" s="21">
+      <c r="I59" s="22">
         <v>-5.67</v>
       </c>
-      <c r="J59" s="21">
+      <c r="J59" s="22">
         <v>-3.94</v>
       </c>
-      <c r="K59" s="21">
+      <c r="K59" s="22">
         <v>-2.6</v>
       </c>
       <c r="L59" s="18">
@@ -4413,7 +4454,7 @@
       <c r="O59" s="18">
         <v>1.67</v>
       </c>
-      <c r="P59" s="21">
+      <c r="P59" s="22">
         <v>-1.44</v>
       </c>
       <c r="Q59" s="18">
@@ -4437,16 +4478,16 @@
       <c r="W59" s="18">
         <v>0.62</v>
       </c>
-      <c r="X59" s="21">
+      <c r="X59" s="22">
         <v>-0.06</v>
       </c>
-      <c r="Y59" s="21">
+      <c r="Y59" s="22">
         <v>-0.23</v>
       </c>
-      <c r="Z59" s="21">
+      <c r="Z59" s="22">
         <v>-0.3</v>
       </c>
-      <c r="AA59" s="21">
+      <c r="AA59" s="22">
         <v>-0.64</v>
       </c>
     </row>
@@ -4466,10 +4507,10 @@
       <c r="E60" s="18">
         <v>40.55</v>
       </c>
-      <c r="F60" s="21">
+      <c r="F60" s="22">
         <v>-14.63</v>
       </c>
-      <c r="G60" s="21">
+      <c r="G60" s="22">
         <v>-23.16</v>
       </c>
       <c r="H60" s="18">
@@ -4496,7 +4537,7 @@
       <c r="O60" s="18">
         <v>2.1</v>
       </c>
-      <c r="P60" s="21">
+      <c r="P60" s="22">
         <v>-1.09</v>
       </c>
       <c r="Q60" s="18">
@@ -4645,7 +4686,7 @@
       <c r="P62" s="16">
         <v>0.0</v>
       </c>
-      <c r="Q62" s="22">
+      <c r="Q62" s="23">
         <v>0.0</v>
       </c>
       <c r="R62" s="16"/>
@@ -4824,7 +4865,7 @@
       <c r="A66" s="17" t="s">
         <v>125</v>
       </c>
-      <c r="B66" s="21">
+      <c r="B66" s="22">
         <v>-3.19</v>
       </c>
       <c r="C66" s="18">
@@ -4836,10 +4877,10 @@
       <c r="E66" s="18">
         <v>8.02</v>
       </c>
-      <c r="F66" s="21">
+      <c r="F66" s="22">
         <v>-3.33</v>
       </c>
-      <c r="G66" s="21">
+      <c r="G66" s="22">
         <v>-2.13</v>
       </c>
       <c r="H66" s="18">
@@ -4860,13 +4901,13 @@
       <c r="M66" s="18">
         <v>0.89</v>
       </c>
-      <c r="N66" s="21">
+      <c r="N66" s="22">
         <v>-0.11</v>
       </c>
       <c r="O66" s="18">
         <v>0.39</v>
       </c>
-      <c r="P66" s="21">
+      <c r="P66" s="22">
         <v>-0.36</v>
       </c>
       <c r="Q66" s="18">
@@ -4881,7 +4922,7 @@
       <c r="T66" s="18">
         <v>0.54</v>
       </c>
-      <c r="U66" s="21">
+      <c r="U66" s="22">
         <v>-0.28</v>
       </c>
       <c r="V66" s="18">
@@ -4919,10 +4960,10 @@
       <c r="E67" s="18">
         <v>32.52</v>
       </c>
-      <c r="F67" s="21">
+      <c r="F67" s="22">
         <v>-11.3</v>
       </c>
-      <c r="G67" s="21">
+      <c r="G67" s="22">
         <v>-21.03</v>
       </c>
       <c r="H67" s="18">
@@ -4949,7 +4990,7 @@
       <c r="O67" s="18">
         <v>1.71</v>
       </c>
-      <c r="P67" s="21">
+      <c r="P67" s="22">
         <v>-0.73</v>
       </c>
       <c r="Q67" s="18">
@@ -5002,10 +5043,10 @@
       <c r="E68" s="18">
         <v>32.52</v>
       </c>
-      <c r="F68" s="21">
+      <c r="F68" s="22">
         <v>-11.3</v>
       </c>
-      <c r="G68" s="21">
+      <c r="G68" s="22">
         <v>-21.03</v>
       </c>
       <c r="H68" s="18">
@@ -5032,7 +5073,7 @@
       <c r="O68" s="18">
         <v>1.71</v>
       </c>
-      <c r="P68" s="21">
+      <c r="P68" s="22">
         <v>-0.73</v>
       </c>
       <c r="Q68" s="18">
@@ -5128,13 +5169,13 @@
       <c r="C70" s="18">
         <v>20.29</v>
       </c>
-      <c r="D70" s="21">
+      <c r="D70" s="22">
         <v>-0.64</v>
       </c>
       <c r="E70" s="18">
         <v>0.09</v>
       </c>
-      <c r="F70" s="21">
+      <c r="F70" s="22">
         <v>-1.39</v>
       </c>
       <c r="G70" s="18">
@@ -5143,29 +5184,29 @@
       <c r="H70" s="18">
         <v>4.26</v>
       </c>
-      <c r="I70" s="21">
+      <c r="I70" s="22">
         <v>-1.08</v>
       </c>
-      <c r="J70" s="21">
+      <c r="J70" s="22">
         <v>-0.01</v>
       </c>
-      <c r="K70" s="23"/>
-      <c r="L70" s="23"/>
-      <c r="M70" s="23"/>
-      <c r="N70" s="23"/>
-      <c r="O70" s="23"/>
-      <c r="P70" s="23"/>
-      <c r="Q70" s="23"/>
-      <c r="R70" s="23"/>
-      <c r="S70" s="23"/>
-      <c r="T70" s="23"/>
-      <c r="U70" s="23"/>
-      <c r="V70" s="23"/>
-      <c r="W70" s="23"/>
-      <c r="X70" s="23"/>
-      <c r="Y70" s="23"/>
-      <c r="Z70" s="23"/>
-      <c r="AA70" s="23"/>
+      <c r="K70" s="24"/>
+      <c r="L70" s="24"/>
+      <c r="M70" s="24"/>
+      <c r="N70" s="24"/>
+      <c r="O70" s="24"/>
+      <c r="P70" s="24"/>
+      <c r="Q70" s="24"/>
+      <c r="R70" s="24"/>
+      <c r="S70" s="24"/>
+      <c r="T70" s="24"/>
+      <c r="U70" s="24"/>
+      <c r="V70" s="24"/>
+      <c r="W70" s="24"/>
+      <c r="X70" s="24"/>
+      <c r="Y70" s="24"/>
+      <c r="Z70" s="24"/>
+      <c r="AA70" s="24"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="17" t="s">
@@ -5183,10 +5224,10 @@
       <c r="E71" s="18">
         <v>32.43</v>
       </c>
-      <c r="F71" s="21">
+      <c r="F71" s="22">
         <v>-9.91</v>
       </c>
-      <c r="G71" s="21">
+      <c r="G71" s="22">
         <v>-23.54</v>
       </c>
       <c r="H71" s="18">
@@ -5213,7 +5254,7 @@
       <c r="O71" s="18">
         <v>1.71</v>
       </c>
-      <c r="P71" s="21">
+      <c r="P71" s="22">
         <v>-0.73</v>
       </c>
       <c r="Q71" s="18">
@@ -5266,10 +5307,10 @@
       <c r="E72" s="18">
         <v>32.43</v>
       </c>
-      <c r="F72" s="21">
+      <c r="F72" s="22">
         <v>-9.91</v>
       </c>
-      <c r="G72" s="21">
+      <c r="G72" s="22">
         <v>-23.54</v>
       </c>
       <c r="H72" s="18">
@@ -5296,7 +5337,7 @@
       <c r="O72" s="18">
         <v>1.71</v>
       </c>
-      <c r="P72" s="21">
+      <c r="P72" s="22">
         <v>-0.73</v>
       </c>
       <c r="Q72" s="18">
@@ -5349,10 +5390,10 @@
       <c r="E73" s="18">
         <v>32.43</v>
       </c>
-      <c r="F73" s="21">
+      <c r="F73" s="22">
         <v>-9.91</v>
       </c>
-      <c r="G73" s="21">
+      <c r="G73" s="22">
         <v>-23.54</v>
       </c>
       <c r="H73" s="18">
@@ -5379,7 +5420,7 @@
       <c r="O73" s="18">
         <v>1.71</v>
       </c>
-      <c r="P73" s="21">
+      <c r="P73" s="22">
         <v>-0.73</v>
       </c>
       <c r="Q73" s="18">
@@ -9450,7 +9491,7 @@
       <c r="E27" s="15">
         <v>68.6</v>
       </c>
-      <c r="F27" s="24">
+      <c r="F27" s="25">
         <v>174.19</v>
       </c>
       <c r="G27" s="15">
@@ -9867,28 +9908,28 @@
       <c r="L35" s="16"/>
       <c r="M35" s="16"/>
       <c r="N35" s="16"/>
-      <c r="O35" s="24">
+      <c r="O35" s="25">
         <v>119.97</v>
       </c>
-      <c r="P35" s="24">
+      <c r="P35" s="25">
         <v>122.38</v>
       </c>
-      <c r="Q35" s="24">
+      <c r="Q35" s="25">
         <v>113.46</v>
       </c>
-      <c r="R35" s="24">
+      <c r="R35" s="25">
         <v>117.47</v>
       </c>
-      <c r="S35" s="24">
+      <c r="S35" s="25">
         <v>137.51</v>
       </c>
-      <c r="T35" s="24">
+      <c r="T35" s="25">
         <v>112.21</v>
       </c>
-      <c r="U35" s="24">
+      <c r="U35" s="25">
         <v>116.39</v>
       </c>
-      <c r="V35" s="24">
+      <c r="V35" s="25">
         <v>112.99</v>
       </c>
       <c r="W35" s="16"/>
@@ -9963,10 +10004,10 @@
       <c r="T37" s="16"/>
       <c r="U37" s="16"/>
       <c r="V37" s="16"/>
-      <c r="W37" s="24">
+      <c r="W37" s="25">
         <v>102.11</v>
       </c>
-      <c r="X37" s="24">
+      <c r="X37" s="25">
         <v>104.04</v>
       </c>
       <c r="Y37" s="15">
@@ -9975,7 +10016,7 @@
       <c r="Z37" s="15">
         <v>98.73</v>
       </c>
-      <c r="AA37" s="24">
+      <c r="AA37" s="25">
         <v>102.4</v>
       </c>
     </row>
@@ -10090,7 +10131,7 @@
       <c r="R40" s="20">
         <v>-97.33</v>
       </c>
-      <c r="S40" s="25">
+      <c r="S40" s="26">
         <v>-112.71</v>
       </c>
       <c r="T40" s="20">
@@ -10155,37 +10196,37 @@
       <c r="A42" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="B42" s="24">
+      <c r="B42" s="25">
         <v>326.59</v>
       </c>
-      <c r="C42" s="24">
+      <c r="C42" s="25">
         <v>950.63</v>
       </c>
-      <c r="D42" s="24">
+      <c r="D42" s="25">
         <v>311.83</v>
       </c>
-      <c r="E42" s="24">
+      <c r="E42" s="25">
         <v>302.8</v>
       </c>
-      <c r="F42" s="24">
+      <c r="F42" s="25">
         <v>260.19</v>
       </c>
-      <c r="G42" s="24">
+      <c r="G42" s="25">
         <v>413.73</v>
       </c>
-      <c r="H42" s="24">
+      <c r="H42" s="25">
         <v>1022.36</v>
       </c>
-      <c r="I42" s="24">
+      <c r="I42" s="25">
         <v>675.75</v>
       </c>
-      <c r="J42" s="24">
+      <c r="J42" s="25">
         <v>539.39</v>
       </c>
-      <c r="K42" s="24">
+      <c r="K42" s="25">
         <v>324.5</v>
       </c>
-      <c r="L42" s="24">
+      <c r="L42" s="25">
         <v>257.23</v>
       </c>
       <c r="M42" s="15">
@@ -10428,7 +10469,7 @@
       <c r="M47" s="16"/>
       <c r="N47" s="16"/>
       <c r="O47" s="16"/>
-      <c r="P47" s="22">
+      <c r="P47" s="23">
         <v>0.0</v>
       </c>
       <c r="Q47" s="16"/>
@@ -10462,16 +10503,16 @@
       <c r="F48" s="15">
         <v>7.46</v>
       </c>
-      <c r="G48" s="24">
+      <c r="G48" s="25">
         <v>166.06</v>
       </c>
-      <c r="H48" s="24">
+      <c r="H48" s="25">
         <v>115.97</v>
       </c>
-      <c r="I48" s="24">
+      <c r="I48" s="25">
         <v>141.64</v>
       </c>
-      <c r="J48" s="24">
+      <c r="J48" s="25">
         <v>133.73</v>
       </c>
       <c r="K48" s="15">
@@ -11220,7 +11261,7 @@
       <c r="B62" s="15">
         <v>9.5</v>
       </c>
-      <c r="C62" s="24">
+      <c r="C62" s="25">
         <v>289.98</v>
       </c>
       <c r="D62" s="15">
@@ -11318,7 +11359,7 @@
         <v>211</v>
       </c>
       <c r="B64" s="16"/>
-      <c r="C64" s="24">
+      <c r="C64" s="25">
         <v>287.91</v>
       </c>
       <c r="D64" s="15">
@@ -11611,34 +11652,34 @@
       <c r="A70" s="14" t="s">
         <v>200</v>
       </c>
-      <c r="B70" s="24">
+      <c r="B70" s="25">
         <v>161.71</v>
       </c>
-      <c r="C70" s="24">
+      <c r="C70" s="25">
         <v>168.82</v>
       </c>
-      <c r="D70" s="24">
+      <c r="D70" s="25">
         <v>101.1</v>
       </c>
-      <c r="E70" s="24">
+      <c r="E70" s="25">
         <v>173.55</v>
       </c>
-      <c r="F70" s="24">
+      <c r="F70" s="25">
         <v>185.33</v>
       </c>
-      <c r="G70" s="24">
+      <c r="G70" s="25">
         <v>192.38</v>
       </c>
-      <c r="H70" s="24">
+      <c r="H70" s="25">
         <v>460.1</v>
       </c>
-      <c r="I70" s="24">
+      <c r="I70" s="25">
         <v>283.77</v>
       </c>
-      <c r="J70" s="24">
+      <c r="J70" s="25">
         <v>210.76</v>
       </c>
-      <c r="K70" s="24">
+      <c r="K70" s="25">
         <v>165.92</v>
       </c>
       <c r="L70" s="15">
@@ -11720,22 +11761,22 @@
         <v>218</v>
       </c>
       <c r="B72" s="16"/>
-      <c r="C72" s="24">
+      <c r="C72" s="25">
         <v>148.51</v>
       </c>
       <c r="D72" s="15">
         <v>81.18</v>
       </c>
-      <c r="E72" s="24">
+      <c r="E72" s="25">
         <v>156.17</v>
       </c>
-      <c r="F72" s="24">
+      <c r="F72" s="25">
         <v>167.69</v>
       </c>
-      <c r="G72" s="24">
+      <c r="G72" s="25">
         <v>191.17</v>
       </c>
-      <c r="H72" s="24">
+      <c r="H72" s="25">
         <v>454.33</v>
       </c>
       <c r="I72" s="16"/>
@@ -11910,7 +11951,7 @@
       <c r="O75" s="16">
         <v>0.0</v>
       </c>
-      <c r="P75" s="22">
+      <c r="P75" s="23">
         <v>0.0</v>
       </c>
       <c r="Q75" s="16"/>
@@ -12029,7 +12070,7 @@
       <c r="L77" s="16"/>
       <c r="M77" s="16"/>
       <c r="N77" s="16"/>
-      <c r="O77" s="22">
+      <c r="O77" s="23">
         <v>0.0</v>
       </c>
       <c r="P77" s="16">
@@ -12342,28 +12383,28 @@
         <v>227</v>
       </c>
       <c r="B82" s="16"/>
-      <c r="C82" s="24">
+      <c r="C82" s="25">
         <v>232.21</v>
       </c>
-      <c r="D82" s="24">
+      <c r="D82" s="25">
         <v>221.42</v>
       </c>
-      <c r="E82" s="24">
+      <c r="E82" s="25">
         <v>208.3</v>
       </c>
-      <c r="F82" s="24">
+      <c r="F82" s="25">
         <v>250.25</v>
       </c>
-      <c r="G82" s="24">
+      <c r="G82" s="25">
         <v>247.94</v>
       </c>
-      <c r="H82" s="24">
+      <c r="H82" s="25">
         <v>267.7</v>
       </c>
-      <c r="I82" s="24">
+      <c r="I82" s="25">
         <v>290.49</v>
       </c>
-      <c r="J82" s="24">
+      <c r="J82" s="25">
         <v>289.12</v>
       </c>
       <c r="K82" s="15">
@@ -12395,28 +12436,28 @@
         <v>228</v>
       </c>
       <c r="B83" s="16"/>
-      <c r="C83" s="24">
+      <c r="C83" s="25">
         <v>188.64</v>
       </c>
-      <c r="D83" s="24">
+      <c r="D83" s="25">
         <v>125.94</v>
       </c>
-      <c r="E83" s="24">
+      <c r="E83" s="25">
         <v>101.51</v>
       </c>
       <c r="F83" s="15">
         <v>83.47</v>
       </c>
-      <c r="G83" s="24">
+      <c r="G83" s="25">
         <v>115.48</v>
       </c>
-      <c r="H83" s="24">
+      <c r="H83" s="25">
         <v>149.57</v>
       </c>
-      <c r="I83" s="24">
+      <c r="I83" s="25">
         <v>147.94</v>
       </c>
-      <c r="J83" s="24">
+      <c r="J83" s="25">
         <v>139.78</v>
       </c>
       <c r="K83" s="15">
@@ -12475,7 +12516,7 @@
       <c r="A84" s="14" t="s">
         <v>229</v>
       </c>
-      <c r="B84" s="24">
+      <c r="B84" s="25">
         <v>211.36</v>
       </c>
       <c r="C84" s="16"/>
@@ -12652,7 +12693,7 @@
         <v>0.0</v>
       </c>
       <c r="L88" s="16"/>
-      <c r="M88" s="22">
+      <c r="M88" s="23">
         <v>0.0</v>
       </c>
       <c r="N88" s="16"/>
@@ -12760,7 +12801,7 @@
       <c r="B90" s="16">
         <v>0.0</v>
       </c>
-      <c r="C90" s="24">
+      <c r="C90" s="25">
         <v>106.71</v>
       </c>
       <c r="D90" s="15">
@@ -12775,7 +12816,7 @@
       <c r="G90" s="15">
         <v>10.65</v>
       </c>
-      <c r="H90" s="24">
+      <c r="H90" s="25">
         <v>168.83</v>
       </c>
       <c r="I90" s="15">
@@ -12806,7 +12847,7 @@
       <c r="A91" s="17" t="s">
         <v>236</v>
       </c>
-      <c r="B91" s="23">
+      <c r="B91" s="24">
         <v>0.0</v>
       </c>
       <c r="C91" s="19">
@@ -12833,23 +12874,23 @@
       <c r="J91" s="18">
         <v>0.19</v>
       </c>
-      <c r="K91" s="23"/>
-      <c r="L91" s="23"/>
-      <c r="M91" s="23"/>
-      <c r="N91" s="23"/>
-      <c r="O91" s="23"/>
-      <c r="P91" s="23"/>
-      <c r="Q91" s="23"/>
-      <c r="R91" s="23"/>
-      <c r="S91" s="23"/>
-      <c r="T91" s="23"/>
-      <c r="U91" s="23"/>
-      <c r="V91" s="23"/>
-      <c r="W91" s="23"/>
-      <c r="X91" s="23"/>
-      <c r="Y91" s="23"/>
-      <c r="Z91" s="23"/>
-      <c r="AA91" s="23"/>
+      <c r="K91" s="24"/>
+      <c r="L91" s="24"/>
+      <c r="M91" s="24"/>
+      <c r="N91" s="24"/>
+      <c r="O91" s="24"/>
+      <c r="P91" s="24"/>
+      <c r="Q91" s="24"/>
+      <c r="R91" s="24"/>
+      <c r="S91" s="24"/>
+      <c r="T91" s="24"/>
+      <c r="U91" s="24"/>
+      <c r="V91" s="24"/>
+      <c r="W91" s="24"/>
+      <c r="X91" s="24"/>
+      <c r="Y91" s="24"/>
+      <c r="Z91" s="24"/>
+      <c r="AA91" s="24"/>
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="17" t="s">
@@ -13271,22 +13312,22 @@
         <v>242</v>
       </c>
       <c r="B97" s="16"/>
-      <c r="C97" s="24">
+      <c r="C97" s="25">
         <v>436.42</v>
       </c>
-      <c r="D97" s="24">
+      <c r="D97" s="25">
         <v>189.28</v>
       </c>
-      <c r="E97" s="24">
+      <c r="E97" s="25">
         <v>167.6</v>
       </c>
-      <c r="F97" s="24">
+      <c r="F97" s="25">
         <v>178.42</v>
       </c>
-      <c r="G97" s="24">
+      <c r="G97" s="25">
         <v>204.24</v>
       </c>
-      <c r="H97" s="24">
+      <c r="H97" s="25">
         <v>480.48</v>
       </c>
       <c r="I97" s="16"/>
@@ -13314,7 +13355,7 @@
         <v>243</v>
       </c>
       <c r="B98" s="16"/>
-      <c r="C98" s="24">
+      <c r="C98" s="25">
         <v>287.91</v>
       </c>
       <c r="D98" s="15">
@@ -13542,22 +13583,22 @@
         <v>249</v>
       </c>
       <c r="B104" s="16"/>
-      <c r="C104" s="24">
+      <c r="C104" s="25">
         <v>115.12</v>
       </c>
       <c r="D104" s="15">
         <v>62.21</v>
       </c>
-      <c r="E104" s="24">
+      <c r="E104" s="25">
         <v>103.72</v>
       </c>
-      <c r="F104" s="24">
+      <c r="F104" s="25">
         <v>104.0</v>
       </c>
-      <c r="G104" s="24">
+      <c r="G104" s="25">
         <v>154.05</v>
       </c>
-      <c r="H104" s="24">
+      <c r="H104" s="25">
         <v>393.52</v>
       </c>
       <c r="I104" s="16"/>
@@ -14423,39 +14464,39 @@
       <c r="L121" s="16"/>
       <c r="M121" s="16"/>
       <c r="N121" s="16"/>
-      <c r="O121" s="24">
+      <c r="O121" s="25">
         <v>247.0</v>
       </c>
-      <c r="P121" s="24">
+      <c r="P121" s="25">
         <v>253.0</v>
       </c>
       <c r="Q121" s="16"/>
-      <c r="R121" s="24">
+      <c r="R121" s="25">
         <v>268.0</v>
       </c>
-      <c r="S121" s="24">
+      <c r="S121" s="25">
         <v>252.0</v>
       </c>
-      <c r="T121" s="24">
+      <c r="T121" s="25">
         <v>248.0</v>
       </c>
-      <c r="U121" s="24">
+      <c r="U121" s="25">
         <v>252.0</v>
       </c>
-      <c r="V121" s="24">
+      <c r="V121" s="25">
         <v>252.0</v>
       </c>
-      <c r="W121" s="24">
+      <c r="W121" s="25">
         <v>239.0</v>
       </c>
-      <c r="X121" s="24">
+      <c r="X121" s="25">
         <v>243.0</v>
       </c>
-      <c r="Y121" s="24">
+      <c r="Y121" s="25">
         <v>243.0</v>
       </c>
       <c r="Z121" s="16"/>
-      <c r="AA121" s="24">
+      <c r="AA121" s="25">
         <v>247.0</v>
       </c>
     </row>
@@ -16077,7 +16118,7 @@
         <v>270</v>
       </c>
       <c r="B20" s="16"/>
-      <c r="C20" s="24">
+      <c r="C20" s="25">
         <v>123.11</v>
       </c>
       <c r="D20" s="15">
@@ -17108,7 +17149,7 @@
       <c r="D39" s="18">
         <v>0.94</v>
       </c>
-      <c r="E39" s="21">
+      <c r="E39" s="22">
         <v>-5.64</v>
       </c>
       <c r="F39" s="18">
@@ -17132,7 +17173,7 @@
       <c r="L39" s="18">
         <v>4.18</v>
       </c>
-      <c r="M39" s="21">
+      <c r="M39" s="22">
         <v>-0.24</v>
       </c>
       <c r="N39" s="18">
@@ -17174,7 +17215,7 @@
       <c r="Z39" s="18">
         <v>1.29</v>
       </c>
-      <c r="AA39" s="21">
+      <c r="AA39" s="22">
         <v>-1.5</v>
       </c>
     </row>
@@ -17267,7 +17308,7 @@
       <c r="G41" s="20">
         <v>-29.48</v>
       </c>
-      <c r="H41" s="25">
+      <c r="H41" s="26">
         <v>-280.96</v>
       </c>
       <c r="I41" s="20">
@@ -17384,7 +17425,7 @@
       <c r="A44" s="14" t="s">
         <v>291</v>
       </c>
-      <c r="B44" s="24">
+      <c r="B44" s="25">
         <v>334.01</v>
       </c>
       <c r="C44" s="15">
@@ -17396,13 +17437,13 @@
       <c r="E44" s="15">
         <v>8.22</v>
       </c>
-      <c r="F44" s="24">
+      <c r="F44" s="25">
         <v>330.18</v>
       </c>
       <c r="G44" s="15">
         <v>15.86</v>
       </c>
-      <c r="H44" s="24">
+      <c r="H44" s="25">
         <v>152.4</v>
       </c>
       <c r="I44" s="15">
@@ -17925,76 +17966,76 @@
       <c r="B56" s="19">
         <v>306.69</v>
       </c>
-      <c r="C56" s="21">
+      <c r="C56" s="22">
         <v>-37.95</v>
       </c>
       <c r="D56" s="18">
         <v>69.32</v>
       </c>
-      <c r="E56" s="21">
+      <c r="E56" s="22">
         <v>-2.96</v>
       </c>
       <c r="F56" s="19">
         <v>240.03</v>
       </c>
-      <c r="G56" s="21">
+      <c r="G56" s="22">
         <v>-16.72</v>
       </c>
-      <c r="H56" s="26">
+      <c r="H56" s="27">
         <v>-127.19</v>
       </c>
-      <c r="I56" s="21">
+      <c r="I56" s="22">
         <v>-64.5</v>
       </c>
       <c r="J56" s="18">
         <v>1.0</v>
       </c>
-      <c r="K56" s="21">
+      <c r="K56" s="22">
         <v>-46.97</v>
       </c>
-      <c r="L56" s="21">
+      <c r="L56" s="22">
         <v>-31.29</v>
       </c>
       <c r="M56" s="18">
         <v>3.2</v>
       </c>
-      <c r="N56" s="21">
+      <c r="N56" s="22">
         <v>-7.14</v>
       </c>
       <c r="O56" s="18">
         <v>0.06</v>
       </c>
-      <c r="P56" s="21">
+      <c r="P56" s="22">
         <v>-5.92</v>
       </c>
-      <c r="Q56" s="21">
+      <c r="Q56" s="22">
         <v>-3.2</v>
       </c>
-      <c r="R56" s="21">
+      <c r="R56" s="22">
         <v>-8.07</v>
       </c>
-      <c r="S56" s="21">
+      <c r="S56" s="22">
         <v>-0.1</v>
       </c>
-      <c r="T56" s="23">
+      <c r="T56" s="24">
         <v>0.0</v>
       </c>
       <c r="U56" s="18">
         <v>4.29</v>
       </c>
-      <c r="V56" s="21">
+      <c r="V56" s="22">
         <v>-0.15</v>
       </c>
-      <c r="W56" s="21">
+      <c r="W56" s="22">
         <v>-0.37</v>
       </c>
-      <c r="X56" s="21">
+      <c r="X56" s="22">
         <v>-0.05</v>
       </c>
-      <c r="Y56" s="21">
+      <c r="Y56" s="22">
         <v>-1.91</v>
       </c>
-      <c r="Z56" s="21">
+      <c r="Z56" s="22">
         <v>-0.05</v>
       </c>
       <c r="AA56" s="18">
@@ -18017,16 +18058,16 @@
       <c r="E57" s="15">
         <v>45.11</v>
       </c>
-      <c r="F57" s="24">
+      <c r="F57" s="25">
         <v>140.51</v>
       </c>
       <c r="G57" s="15">
         <v>86.05</v>
       </c>
-      <c r="H57" s="24">
+      <c r="H57" s="25">
         <v>259.05</v>
       </c>
-      <c r="I57" s="24">
+      <c r="I57" s="25">
         <v>208.25</v>
       </c>
       <c r="J57" s="15">
@@ -18092,16 +18133,16 @@
       <c r="E58" s="20">
         <v>-70.17</v>
       </c>
-      <c r="F58" s="25">
+      <c r="F58" s="26">
         <v>-245.11</v>
       </c>
-      <c r="G58" s="25">
+      <c r="G58" s="26">
         <v>-145.3</v>
       </c>
-      <c r="H58" s="25">
+      <c r="H58" s="26">
         <v>-205.01</v>
       </c>
-      <c r="I58" s="25">
+      <c r="I58" s="26">
         <v>-137.3</v>
       </c>
       <c r="J58" s="20">
@@ -18157,7 +18198,7 @@
       <c r="A59" s="14" t="s">
         <v>230</v>
       </c>
-      <c r="B59" s="25">
+      <c r="B59" s="26">
         <v>-260.15</v>
       </c>
       <c r="C59" s="20">
@@ -18336,7 +18377,7 @@
       <c r="G62" s="15">
         <v>11.6</v>
       </c>
-      <c r="H62" s="24">
+      <c r="H62" s="25">
         <v>134.76</v>
       </c>
       <c r="I62" s="15">
@@ -18449,22 +18490,22 @@
       <c r="A65" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="B65" s="26">
+      <c r="B65" s="27">
         <v>-286.77</v>
       </c>
-      <c r="C65" s="21">
+      <c r="C65" s="22">
         <v>-59.09</v>
       </c>
-      <c r="D65" s="21">
+      <c r="D65" s="22">
         <v>-47.75</v>
       </c>
-      <c r="E65" s="26">
+      <c r="E65" s="27">
         <v>-100.98</v>
       </c>
-      <c r="F65" s="26">
+      <c r="F65" s="27">
         <v>-117.36</v>
       </c>
-      <c r="G65" s="21">
+      <c r="G65" s="22">
         <v>-68.76</v>
       </c>
       <c r="H65" s="19">
@@ -18473,7 +18514,7 @@
       <c r="I65" s="18">
         <v>59.58</v>
       </c>
-      <c r="J65" s="21">
+      <c r="J65" s="22">
         <v>-5.6</v>
       </c>
       <c r="K65" s="18">
@@ -18482,13 +18523,13 @@
       <c r="L65" s="18">
         <v>28.66</v>
       </c>
-      <c r="M65" s="21">
+      <c r="M65" s="22">
         <v>-3.15</v>
       </c>
       <c r="N65" s="18">
         <v>5.11</v>
       </c>
-      <c r="O65" s="21">
+      <c r="O65" s="22">
         <v>-1.88</v>
       </c>
       <c r="P65" s="18">
@@ -18497,31 +18538,31 @@
       <c r="Q65" s="18">
         <v>1.18</v>
       </c>
-      <c r="R65" s="21">
+      <c r="R65" s="22">
         <v>-1.99</v>
       </c>
-      <c r="S65" s="21">
+      <c r="S65" s="22">
         <v>-1.88</v>
       </c>
-      <c r="T65" s="21">
+      <c r="T65" s="22">
         <v>-1.83</v>
       </c>
-      <c r="U65" s="21">
+      <c r="U65" s="22">
         <v>-3.86</v>
       </c>
-      <c r="V65" s="21">
+      <c r="V65" s="22">
         <v>-3.84</v>
       </c>
-      <c r="W65" s="21">
+      <c r="W65" s="22">
         <v>-1.34</v>
       </c>
-      <c r="X65" s="21">
+      <c r="X65" s="22">
         <v>-2.08</v>
       </c>
-      <c r="Y65" s="21">
+      <c r="Y65" s="22">
         <v>-0.45</v>
       </c>
-      <c r="Z65" s="21">
+      <c r="Z65" s="22">
         <v>-1.21</v>
       </c>
       <c r="AA65" s="18">
@@ -18533,13 +18574,13 @@
         <v>310</v>
       </c>
       <c r="B66" s="16"/>
-      <c r="C66" s="24">
+      <c r="C66" s="25">
         <v>100.21</v>
       </c>
       <c r="D66" s="15">
         <v>73.18</v>
       </c>
-      <c r="E66" s="24">
+      <c r="E66" s="25">
         <v>182.42</v>
       </c>
       <c r="F66" s="15">
@@ -18623,7 +18664,7 @@
       <c r="E67" s="15">
         <v>68.6</v>
       </c>
-      <c r="F67" s="24">
+      <c r="F67" s="25">
         <v>174.19</v>
       </c>
       <c r="G67" s="15">
@@ -18730,19 +18771,19 @@
       <c r="B69" s="18">
         <v>32.03</v>
       </c>
-      <c r="C69" s="21">
+      <c r="C69" s="22">
         <v>-73.58</v>
       </c>
       <c r="D69" s="18">
         <v>22.51</v>
       </c>
-      <c r="E69" s="26">
+      <c r="E69" s="27">
         <v>-109.58</v>
       </c>
       <c r="F69" s="19">
         <v>144.47</v>
       </c>
-      <c r="G69" s="21">
+      <c r="G69" s="22">
         <v>-55.55</v>
       </c>
       <c r="H69" s="18">
@@ -18760,22 +18801,22 @@
       <c r="L69" s="18">
         <v>1.55</v>
       </c>
-      <c r="M69" s="21">
+      <c r="M69" s="22">
         <v>-0.19</v>
       </c>
-      <c r="N69" s="21">
+      <c r="N69" s="22">
         <v>-0.69</v>
       </c>
-      <c r="O69" s="21">
+      <c r="O69" s="22">
         <v>-0.24</v>
       </c>
-      <c r="P69" s="21">
+      <c r="P69" s="22">
         <v>-1.87</v>
       </c>
       <c r="Q69" s="18">
         <v>0.96</v>
       </c>
-      <c r="R69" s="21">
+      <c r="R69" s="22">
         <v>-6.89</v>
       </c>
       <c r="S69" s="18">
@@ -18796,7 +18837,7 @@
       <c r="X69" s="18">
         <v>1.98</v>
       </c>
-      <c r="Y69" s="21">
+      <c r="Y69" s="22">
         <v>-0.51</v>
       </c>
       <c r="Z69" s="18">
@@ -20449,3062 +20490,3062 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="28" t="s">
         <v>316</v>
       </c>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
-      <c r="K20" s="28"/>
-      <c r="L20" s="28"/>
-      <c r="M20" s="28"/>
-      <c r="N20" s="28"/>
-      <c r="O20" s="28"/>
-      <c r="P20" s="28"/>
-      <c r="Q20" s="28"/>
-      <c r="R20" s="28"/>
-      <c r="S20" s="28"/>
-      <c r="T20" s="28"/>
-      <c r="U20" s="28"/>
-      <c r="V20" s="28"/>
-      <c r="W20" s="28"/>
-      <c r="X20" s="28"/>
-      <c r="Y20" s="28"/>
-      <c r="Z20" s="28"/>
+      <c r="B20" s="29"/>
+      <c r="C20" s="29"/>
+      <c r="D20" s="29"/>
+      <c r="E20" s="29"/>
+      <c r="F20" s="29"/>
+      <c r="G20" s="29"/>
+      <c r="H20" s="29"/>
+      <c r="I20" s="29"/>
+      <c r="J20" s="29"/>
+      <c r="K20" s="29"/>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="29"/>
+      <c r="V20" s="29"/>
+      <c r="W20" s="29"/>
+      <c r="X20" s="29"/>
+      <c r="Y20" s="29"/>
+      <c r="Z20" s="29"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="29" t="s">
+      <c r="A21" s="30" t="s">
         <v>316</v>
       </c>
-      <c r="B21" s="30">
+      <c r="B21" s="31">
         <v>782.57</v>
       </c>
-      <c r="C21" s="30">
+      <c r="C21" s="31">
         <v>323.49</v>
       </c>
-      <c r="D21" s="30">
+      <c r="D21" s="31">
         <v>329.11</v>
       </c>
-      <c r="E21" s="30">
+      <c r="E21" s="31">
         <v>259.95</v>
       </c>
-      <c r="F21" s="30">
+      <c r="F21" s="31">
         <v>440.7</v>
       </c>
-      <c r="G21" s="30">
+      <c r="G21" s="31">
         <v>862.03</v>
       </c>
-      <c r="H21" s="30">
+      <c r="H21" s="31">
         <v>568.33</v>
       </c>
-      <c r="I21" s="30">
+      <c r="I21" s="31">
         <v>479.79</v>
       </c>
-      <c r="J21" s="30">
+      <c r="J21" s="31">
         <v>274.68</v>
       </c>
-      <c r="K21" s="30">
+      <c r="K21" s="31">
         <v>189.59</v>
       </c>
-      <c r="L21" s="31">
+      <c r="L21" s="32">
         <v>41.71</v>
       </c>
-      <c r="M21" s="31">
+      <c r="M21" s="32">
         <v>24.6</v>
       </c>
-      <c r="N21" s="31">
+      <c r="N21" s="32">
         <v>11.79</v>
       </c>
-      <c r="O21" s="31">
+      <c r="O21" s="32">
         <v>12.88</v>
       </c>
-      <c r="P21" s="31">
+      <c r="P21" s="32">
         <v>6.69</v>
       </c>
-      <c r="Q21" s="31">
+      <c r="Q21" s="32">
         <v>7.24</v>
       </c>
-      <c r="R21" s="32">
+      <c r="R21" s="33">
         <v>-0.33</v>
       </c>
-      <c r="S21" s="31">
+      <c r="S21" s="32">
         <v>14.87</v>
       </c>
-      <c r="T21" s="31">
+      <c r="T21" s="32">
         <v>15.61</v>
       </c>
-      <c r="U21" s="31">
+      <c r="U21" s="32">
         <v>19.73</v>
       </c>
-      <c r="V21" s="31">
+      <c r="V21" s="32">
         <v>15.6</v>
       </c>
-      <c r="W21" s="31">
+      <c r="W21" s="32">
         <v>14.8</v>
       </c>
-      <c r="X21" s="31">
+      <c r="X21" s="32">
         <v>12.86</v>
       </c>
-      <c r="Y21" s="31">
+      <c r="Y21" s="32">
         <v>14.22</v>
       </c>
-      <c r="Z21" s="31">
+      <c r="Z21" s="32">
         <v>9.86</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="29" t="s">
+      <c r="A22" s="30" t="s">
         <v>317</v>
       </c>
-      <c r="B22" s="30">
+      <c r="B22" s="31">
         <v>458.56</v>
       </c>
-      <c r="C22" s="30">
+      <c r="C22" s="31">
         <v>483.07</v>
       </c>
-      <c r="D22" s="30">
+      <c r="D22" s="31">
         <v>512.44</v>
       </c>
-      <c r="E22" s="30">
+      <c r="E22" s="31">
         <v>524.05</v>
       </c>
-      <c r="F22" s="30">
+      <c r="F22" s="31">
         <v>557.36</v>
       </c>
-      <c r="G22" s="30">
+      <c r="G22" s="31">
         <v>479.62</v>
       </c>
-      <c r="H22" s="30">
+      <c r="H22" s="31">
         <v>318.45</v>
       </c>
-      <c r="I22" s="30">
+      <c r="I22" s="31">
         <v>209.3</v>
       </c>
-      <c r="J22" s="30">
+      <c r="J22" s="31">
         <v>107.46</v>
       </c>
-      <c r="K22" s="31">
+      <c r="K22" s="32">
         <v>58.72</v>
       </c>
-      <c r="L22" s="31">
+      <c r="L22" s="32">
         <v>21.14</v>
       </c>
-      <c r="M22" s="31">
+      <c r="M22" s="32">
         <v>13.26</v>
       </c>
-      <c r="N22" s="31">
+      <c r="N22" s="32">
         <v>7.29</v>
       </c>
-      <c r="O22" s="31">
+      <c r="O22" s="32">
         <v>8.1</v>
       </c>
-      <c r="P22" s="31">
+      <c r="P22" s="32">
         <v>8.52</v>
       </c>
-      <c r="Q22" s="31">
+      <c r="Q22" s="32">
         <v>11.75</v>
       </c>
-      <c r="R22" s="31">
+      <c r="R22" s="32">
         <v>15.73</v>
       </c>
-      <c r="S22" s="31">
+      <c r="S22" s="32">
         <v>15.7</v>
       </c>
-      <c r="T22" s="31">
+      <c r="T22" s="32">
         <v>16.11</v>
       </c>
-      <c r="U22" s="31">
+      <c r="U22" s="32">
         <v>15.46</v>
       </c>
-      <c r="V22" s="31">
+      <c r="V22" s="32">
         <v>13.84</v>
       </c>
-      <c r="W22" s="33"/>
-      <c r="X22" s="33"/>
-      <c r="Y22" s="33"/>
-      <c r="Z22" s="33"/>
+      <c r="W22" s="34"/>
+      <c r="X22" s="34"/>
+      <c r="Y22" s="34"/>
+      <c r="Z22" s="34"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="28" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
-      <c r="K23" s="28"/>
-      <c r="L23" s="28"/>
-      <c r="M23" s="28"/>
-      <c r="N23" s="28"/>
-      <c r="O23" s="28"/>
-      <c r="P23" s="28"/>
-      <c r="Q23" s="28"/>
-      <c r="R23" s="28"/>
-      <c r="S23" s="28"/>
-      <c r="T23" s="28"/>
-      <c r="U23" s="28"/>
-      <c r="V23" s="28"/>
-      <c r="W23" s="28"/>
-      <c r="X23" s="28"/>
-      <c r="Y23" s="28"/>
-      <c r="Z23" s="28"/>
+      <c r="B23" s="29"/>
+      <c r="C23" s="29"/>
+      <c r="D23" s="29"/>
+      <c r="E23" s="29"/>
+      <c r="F23" s="29"/>
+      <c r="G23" s="29"/>
+      <c r="H23" s="29"/>
+      <c r="I23" s="29"/>
+      <c r="J23" s="29"/>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29"/>
+      <c r="N23" s="29"/>
+      <c r="O23" s="29"/>
+      <c r="P23" s="29"/>
+      <c r="Q23" s="29"/>
+      <c r="R23" s="29"/>
+      <c r="S23" s="29"/>
+      <c r="T23" s="29"/>
+      <c r="U23" s="29"/>
+      <c r="V23" s="29"/>
+      <c r="W23" s="29"/>
+      <c r="X23" s="29"/>
+      <c r="Y23" s="29"/>
+      <c r="Z23" s="29"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="29" t="s">
+      <c r="A24" s="30" t="s">
         <v>318</v>
       </c>
-      <c r="B24" s="30">
+      <c r="B24" s="31">
         <v>243.77</v>
       </c>
-      <c r="C24" s="30">
+      <c r="C24" s="31">
         <v>228.2</v>
       </c>
-      <c r="D24" s="30">
+      <c r="D24" s="31">
         <v>197.45</v>
       </c>
-      <c r="E24" s="30">
+      <c r="E24" s="31">
         <v>212.09</v>
       </c>
-      <c r="F24" s="30">
+      <c r="F24" s="31">
         <v>226.71</v>
       </c>
-      <c r="G24" s="30">
+      <c r="G24" s="31">
         <v>220.16</v>
       </c>
-      <c r="H24" s="30">
+      <c r="H24" s="31">
         <v>196.4</v>
       </c>
-      <c r="I24" s="30">
+      <c r="I24" s="31">
         <v>240.7</v>
       </c>
-      <c r="J24" s="30">
+      <c r="J24" s="31">
         <v>101.96</v>
       </c>
-      <c r="K24" s="31">
+      <c r="K24" s="32">
         <v>98.04</v>
       </c>
-      <c r="L24" s="31">
+      <c r="L24" s="32">
         <v>35.82</v>
       </c>
-      <c r="M24" s="31">
+      <c r="M24" s="32">
         <v>20.04</v>
       </c>
-      <c r="N24" s="31">
+      <c r="N24" s="32">
         <v>16.93</v>
       </c>
-      <c r="O24" s="31">
+      <c r="O24" s="32">
         <v>19.91</v>
       </c>
-      <c r="P24" s="31">
+      <c r="P24" s="32">
         <v>25.36</v>
       </c>
-      <c r="Q24" s="31">
+      <c r="Q24" s="32">
         <v>25.52</v>
       </c>
-      <c r="R24" s="31">
+      <c r="R24" s="32">
         <v>16.16</v>
       </c>
-      <c r="S24" s="31">
+      <c r="S24" s="32">
         <v>27.3</v>
       </c>
-      <c r="T24" s="31">
+      <c r="T24" s="32">
         <v>27.52</v>
       </c>
-      <c r="U24" s="31">
+      <c r="U24" s="32">
         <v>23.73</v>
       </c>
-      <c r="V24" s="31">
+      <c r="V24" s="32">
         <v>17.39</v>
       </c>
-      <c r="W24" s="31">
+      <c r="W24" s="32">
         <v>12.27</v>
       </c>
-      <c r="X24" s="31">
+      <c r="X24" s="32">
         <v>8.27</v>
       </c>
-      <c r="Y24" s="31">
+      <c r="Y24" s="32">
         <v>9.06</v>
       </c>
-      <c r="Z24" s="31">
+      <c r="Z24" s="32">
         <v>10.73</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="29" t="s">
+      <c r="A25" s="30" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="30">
+      <c r="B25" s="31">
         <v>241.88</v>
       </c>
-      <c r="C25" s="30">
+      <c r="C25" s="31">
         <v>233.62</v>
       </c>
-      <c r="D25" s="30">
+      <c r="D25" s="31">
         <v>217.77</v>
       </c>
-      <c r="E25" s="30">
+      <c r="E25" s="31">
         <v>219.19</v>
       </c>
-      <c r="F25" s="30">
+      <c r="F25" s="31">
         <v>208.5</v>
       </c>
-      <c r="G25" s="30">
+      <c r="G25" s="31">
         <v>173.36</v>
       </c>
-      <c r="H25" s="30">
+      <c r="H25" s="31">
         <v>138.06</v>
       </c>
-      <c r="I25" s="30">
+      <c r="I25" s="31">
         <v>102.89</v>
       </c>
-      <c r="J25" s="31">
+      <c r="J25" s="32">
         <v>54.69</v>
       </c>
-      <c r="K25" s="31">
+      <c r="K25" s="32">
         <v>41.2</v>
       </c>
-      <c r="L25" s="31">
+      <c r="L25" s="32">
         <v>26.22</v>
       </c>
-      <c r="M25" s="31">
+      <c r="M25" s="32">
         <v>22.71</v>
       </c>
-      <c r="N25" s="31">
+      <c r="N25" s="32">
         <v>18.91</v>
       </c>
-      <c r="O25" s="31">
+      <c r="O25" s="32">
         <v>21.69</v>
       </c>
-      <c r="P25" s="31">
+      <c r="P25" s="32">
         <v>23.03</v>
       </c>
-      <c r="Q25" s="31">
+      <c r="Q25" s="32">
         <v>24.06</v>
       </c>
-      <c r="R25" s="31">
+      <c r="R25" s="32">
         <v>26.28</v>
       </c>
-      <c r="S25" s="31">
+      <c r="S25" s="32">
         <v>21.14</v>
       </c>
-      <c r="T25" s="31">
+      <c r="T25" s="32">
         <v>18.14</v>
       </c>
-      <c r="U25" s="31">
+      <c r="U25" s="32">
         <v>14.08</v>
       </c>
-      <c r="V25" s="31">
+      <c r="V25" s="32">
         <v>11.77</v>
       </c>
-      <c r="W25" s="33"/>
-      <c r="X25" s="33"/>
-      <c r="Y25" s="33"/>
-      <c r="Z25" s="33"/>
+      <c r="W25" s="34"/>
+      <c r="X25" s="34"/>
+      <c r="Y25" s="34"/>
+      <c r="Z25" s="34"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="27" t="s">
+      <c r="A26" s="28" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
-      <c r="K26" s="28"/>
-      <c r="L26" s="28"/>
-      <c r="M26" s="28"/>
-      <c r="N26" s="28"/>
-      <c r="O26" s="28"/>
-      <c r="P26" s="28"/>
-      <c r="Q26" s="28"/>
-      <c r="R26" s="28"/>
-      <c r="S26" s="28"/>
-      <c r="T26" s="28"/>
-      <c r="U26" s="28"/>
-      <c r="V26" s="28"/>
-      <c r="W26" s="28"/>
-      <c r="X26" s="28"/>
-      <c r="Y26" s="28"/>
-      <c r="Z26" s="28"/>
+      <c r="B26" s="29"/>
+      <c r="C26" s="29"/>
+      <c r="D26" s="29"/>
+      <c r="E26" s="29"/>
+      <c r="F26" s="29"/>
+      <c r="G26" s="29"/>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29"/>
+      <c r="J26" s="29"/>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29"/>
+      <c r="N26" s="29"/>
+      <c r="O26" s="29"/>
+      <c r="P26" s="29"/>
+      <c r="Q26" s="29"/>
+      <c r="R26" s="29"/>
+      <c r="S26" s="29"/>
+      <c r="T26" s="29"/>
+      <c r="U26" s="29"/>
+      <c r="V26" s="29"/>
+      <c r="W26" s="29"/>
+      <c r="X26" s="29"/>
+      <c r="Y26" s="29"/>
+      <c r="Z26" s="29"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="29" t="s">
+      <c r="A27" s="30" t="s">
         <v>321</v>
       </c>
-      <c r="B27" s="31">
+      <c r="B27" s="32">
         <v>38.15</v>
       </c>
-      <c r="C27" s="31">
+      <c r="C27" s="32">
         <v>35.72</v>
       </c>
-      <c r="D27" s="31">
+      <c r="D27" s="32">
         <v>30.9</v>
       </c>
-      <c r="E27" s="31">
+      <c r="E27" s="32">
         <v>34.31</v>
       </c>
-      <c r="F27" s="31">
+      <c r="F27" s="32">
         <v>36.67</v>
       </c>
-      <c r="G27" s="31">
+      <c r="G27" s="32">
         <v>35.61</v>
       </c>
-      <c r="H27" s="31">
+      <c r="H27" s="32">
         <v>31.77</v>
       </c>
-      <c r="I27" s="31">
+      <c r="I27" s="32">
         <v>38.93</v>
       </c>
-      <c r="J27" s="31">
+      <c r="J27" s="32">
         <v>28.97</v>
       </c>
-      <c r="K27" s="31">
+      <c r="K27" s="32">
         <v>27.86</v>
       </c>
-      <c r="L27" s="31">
+      <c r="L27" s="32">
         <v>23.57</v>
       </c>
-      <c r="M27" s="31">
+      <c r="M27" s="32">
         <v>13.19</v>
       </c>
-      <c r="N27" s="31">
+      <c r="N27" s="32">
         <v>11.14</v>
       </c>
-      <c r="O27" s="31">
+      <c r="O27" s="32">
         <v>13.11</v>
       </c>
-      <c r="P27" s="31">
+      <c r="P27" s="32">
         <v>16.69</v>
       </c>
-      <c r="Q27" s="31">
+      <c r="Q27" s="32">
         <v>16.8</v>
       </c>
-      <c r="R27" s="31">
+      <c r="R27" s="32">
         <v>10.64</v>
       </c>
-      <c r="S27" s="31">
+      <c r="S27" s="32">
         <v>17.97</v>
       </c>
-      <c r="T27" s="31">
+      <c r="T27" s="32">
         <v>18.11</v>
       </c>
-      <c r="U27" s="31">
+      <c r="U27" s="32">
         <v>15.62</v>
       </c>
-      <c r="V27" s="31">
+      <c r="V27" s="32">
         <v>11.45</v>
       </c>
-      <c r="W27" s="31">
+      <c r="W27" s="32">
         <v>8.07</v>
       </c>
-      <c r="X27" s="31">
+      <c r="X27" s="32">
         <v>5.44</v>
       </c>
-      <c r="Y27" s="31">
+      <c r="Y27" s="32">
         <v>5.96</v>
       </c>
-      <c r="Z27" s="31">
+      <c r="Z27" s="32">
         <v>7.06</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="30" t="s">
         <v>322</v>
       </c>
-      <c r="B28" s="31">
+      <c r="B28" s="32">
         <v>38.39</v>
       </c>
-      <c r="C28" s="31">
+      <c r="C28" s="32">
         <v>37.33</v>
       </c>
-      <c r="D28" s="31">
+      <c r="D28" s="32">
         <v>35.02</v>
       </c>
-      <c r="E28" s="31">
+      <c r="E28" s="32">
         <v>35.45</v>
       </c>
-      <c r="F28" s="31">
+      <c r="F28" s="32">
         <v>36.61</v>
       </c>
-      <c r="G28" s="31">
+      <c r="G28" s="32">
         <v>33.21</v>
       </c>
-      <c r="H28" s="31">
+      <c r="H28" s="32">
         <v>31.43</v>
       </c>
-      <c r="I28" s="31">
+      <c r="I28" s="32">
         <v>28.03</v>
       </c>
-      <c r="J28" s="31">
+      <c r="J28" s="32">
         <v>21.43</v>
       </c>
-      <c r="K28" s="31">
+      <c r="K28" s="32">
         <v>19.78</v>
       </c>
-      <c r="L28" s="31">
+      <c r="L28" s="32">
         <v>17.25</v>
       </c>
-      <c r="M28" s="31">
+      <c r="M28" s="32">
         <v>14.95</v>
       </c>
-      <c r="N28" s="31">
+      <c r="N28" s="32">
         <v>12.44</v>
       </c>
-      <c r="O28" s="31">
+      <c r="O28" s="32">
         <v>14.27</v>
       </c>
-      <c r="P28" s="31">
+      <c r="P28" s="32">
         <v>15.16</v>
       </c>
-      <c r="Q28" s="31">
+      <c r="Q28" s="32">
         <v>15.83</v>
       </c>
-      <c r="R28" s="31">
+      <c r="R28" s="32">
         <v>17.3</v>
       </c>
-      <c r="S28" s="31">
+      <c r="S28" s="32">
         <v>13.91</v>
       </c>
-      <c r="T28" s="31">
+      <c r="T28" s="32">
         <v>11.94</v>
       </c>
-      <c r="U28" s="31">
+      <c r="U28" s="32">
         <v>9.27</v>
       </c>
-      <c r="V28" s="31">
+      <c r="V28" s="32">
         <v>7.75</v>
       </c>
-      <c r="W28" s="33"/>
-      <c r="X28" s="33"/>
-      <c r="Y28" s="33"/>
-      <c r="Z28" s="33"/>
+      <c r="W28" s="34"/>
+      <c r="X28" s="34"/>
+      <c r="Y28" s="34"/>
+      <c r="Z28" s="34"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="27" t="s">
+      <c r="A29" s="28" t="s">
         <v>323</v>
       </c>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
-      <c r="N29" s="28"/>
-      <c r="O29" s="28"/>
-      <c r="P29" s="28"/>
-      <c r="Q29" s="28"/>
-      <c r="R29" s="28"/>
-      <c r="S29" s="28"/>
-      <c r="T29" s="28"/>
-      <c r="U29" s="28"/>
-      <c r="V29" s="28"/>
-      <c r="W29" s="28"/>
-      <c r="X29" s="28"/>
-      <c r="Y29" s="28"/>
-      <c r="Z29" s="28"/>
+      <c r="B29" s="29"/>
+      <c r="C29" s="29"/>
+      <c r="D29" s="29"/>
+      <c r="E29" s="29"/>
+      <c r="F29" s="29"/>
+      <c r="G29" s="29"/>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29"/>
+      <c r="J29" s="29"/>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="29"/>
+      <c r="V29" s="29"/>
+      <c r="W29" s="29"/>
+      <c r="X29" s="29"/>
+      <c r="Y29" s="29"/>
+      <c r="Z29" s="29"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="29" t="s">
+      <c r="A30" s="30" t="s">
         <v>324</v>
       </c>
-      <c r="B30" s="34">
+      <c r="B30" s="35">
         <v>9.82</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C30" s="36">
         <v>-4.59</v>
       </c>
-      <c r="D30" s="35">
+      <c r="D30" s="36">
         <v>-2.97</v>
       </c>
-      <c r="E30" s="35">
+      <c r="E30" s="36">
         <v>-11.39</v>
       </c>
-      <c r="F30" s="35">
+      <c r="F30" s="36">
         <v>-1.05</v>
       </c>
-      <c r="G30" s="35">
+      <c r="G30" s="36">
         <v>-124.79</v>
       </c>
-      <c r="H30" s="35">
+      <c r="H30" s="36">
         <v>-23.92</v>
       </c>
-      <c r="I30" s="34">
+      <c r="I30" s="35">
         <v>0.38</v>
       </c>
-      <c r="J30" s="35">
+      <c r="J30" s="36">
         <v>-42.87</v>
       </c>
-      <c r="K30" s="35">
+      <c r="K30" s="36">
         <v>-41.71</v>
       </c>
-      <c r="L30" s="34">
+      <c r="L30" s="35">
         <v>0.19</v>
       </c>
-      <c r="M30" s="35">
+      <c r="M30" s="36">
         <v>-46.98</v>
       </c>
-      <c r="N30" s="35">
+      <c r="N30" s="36">
         <v>-13.66</v>
       </c>
-      <c r="O30" s="35">
+      <c r="O30" s="36">
         <v>-45.79</v>
       </c>
-      <c r="P30" s="35">
+      <c r="P30" s="36">
         <v>-1.02</v>
       </c>
-      <c r="Q30" s="34">
+      <c r="Q30" s="35">
         <v>11.83</v>
       </c>
-      <c r="R30" s="34">
+      <c r="R30" s="35">
         <v>23.67</v>
       </c>
-      <c r="S30" s="34">
+      <c r="S30" s="35">
         <v>9.76</v>
       </c>
-      <c r="T30" s="34">
+      <c r="T30" s="35">
         <v>12.32</v>
       </c>
-      <c r="U30" s="34">
+      <c r="U30" s="35">
         <v>17.19</v>
       </c>
-      <c r="V30" s="34">
+      <c r="V30" s="35">
         <v>27.99</v>
       </c>
-      <c r="W30" s="34">
+      <c r="W30" s="35">
         <v>34.69</v>
       </c>
-      <c r="X30" s="34">
+      <c r="X30" s="35">
         <v>21.29</v>
       </c>
-      <c r="Y30" s="34">
+      <c r="Y30" s="35">
         <v>13.55</v>
       </c>
-      <c r="Z30" s="35">
+      <c r="Z30" s="36">
         <v>-32.47</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="29" t="s">
+      <c r="A31" s="30" t="s">
         <v>325</v>
       </c>
-      <c r="B31" s="35">
+      <c r="B31" s="36">
         <v>-2.1</v>
       </c>
-      <c r="C31" s="35">
+      <c r="C31" s="36">
         <v>-31.03</v>
       </c>
-      <c r="D31" s="35">
+      <c r="D31" s="36">
         <v>-34.72</v>
       </c>
-      <c r="E31" s="35">
+      <c r="E31" s="36">
         <v>-32.16</v>
       </c>
-      <c r="F31" s="35">
+      <c r="F31" s="36">
         <v>-38.19</v>
       </c>
-      <c r="G31" s="35">
+      <c r="G31" s="36">
         <v>-46.5</v>
       </c>
-      <c r="H31" s="35">
+      <c r="H31" s="36">
         <v>-20.96</v>
       </c>
-      <c r="I31" s="35">
+      <c r="I31" s="36">
         <v>-23.19</v>
       </c>
-      <c r="J31" s="35">
+      <c r="J31" s="36">
         <v>-29.86</v>
       </c>
-      <c r="K31" s="35">
+      <c r="K31" s="36">
         <v>-28.45</v>
       </c>
-      <c r="L31" s="35">
+      <c r="L31" s="36">
         <v>-18.26</v>
       </c>
-      <c r="M31" s="35">
+      <c r="M31" s="36">
         <v>-16.83</v>
       </c>
-      <c r="N31" s="35">
+      <c r="N31" s="36">
         <v>-5.97</v>
       </c>
-      <c r="O31" s="35">
+      <c r="O31" s="36">
         <v>-0.84</v>
       </c>
-      <c r="P31" s="34">
+      <c r="P31" s="35">
         <v>9.96</v>
       </c>
-      <c r="Q31" s="34">
+      <c r="Q31" s="35">
         <v>13.91</v>
       </c>
-      <c r="R31" s="34">
+      <c r="R31" s="35">
         <v>16.58</v>
       </c>
-      <c r="S31" s="34">
+      <c r="S31" s="35">
         <v>17.68</v>
       </c>
-      <c r="T31" s="34">
+      <c r="T31" s="35">
         <v>20.52</v>
       </c>
-      <c r="U31" s="34">
+      <c r="U31" s="35">
         <v>22.74</v>
       </c>
-      <c r="V31" s="34">
+      <c r="V31" s="35">
         <v>15.0</v>
       </c>
-      <c r="W31" s="34"/>
-      <c r="X31" s="34"/>
-      <c r="Y31" s="34"/>
-      <c r="Z31" s="34"/>
+      <c r="W31" s="35"/>
+      <c r="X31" s="35"/>
+      <c r="Y31" s="35"/>
+      <c r="Z31" s="35"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="27" t="s">
+      <c r="A32" s="28" t="s">
         <v>326</v>
       </c>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
-      <c r="K32" s="28"/>
-      <c r="L32" s="28"/>
-      <c r="M32" s="28"/>
-      <c r="N32" s="28"/>
-      <c r="O32" s="28"/>
-      <c r="P32" s="28"/>
-      <c r="Q32" s="28"/>
-      <c r="R32" s="28"/>
-      <c r="S32" s="28"/>
-      <c r="T32" s="28"/>
-      <c r="U32" s="28"/>
-      <c r="V32" s="28"/>
-      <c r="W32" s="28"/>
-      <c r="X32" s="28"/>
-      <c r="Y32" s="28"/>
-      <c r="Z32" s="28"/>
+      <c r="B32" s="29"/>
+      <c r="C32" s="29"/>
+      <c r="D32" s="29"/>
+      <c r="E32" s="29"/>
+      <c r="F32" s="29"/>
+      <c r="G32" s="29"/>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29"/>
+      <c r="J32" s="29"/>
+      <c r="K32" s="29"/>
+      <c r="L32" s="29"/>
+      <c r="M32" s="29"/>
+      <c r="N32" s="29"/>
+      <c r="O32" s="29"/>
+      <c r="P32" s="29"/>
+      <c r="Q32" s="29"/>
+      <c r="R32" s="29"/>
+      <c r="S32" s="29"/>
+      <c r="T32" s="29"/>
+      <c r="U32" s="29"/>
+      <c r="V32" s="29"/>
+      <c r="W32" s="29"/>
+      <c r="X32" s="29"/>
+      <c r="Y32" s="29"/>
+      <c r="Z32" s="29"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="29" t="s">
+      <c r="A33" s="30" t="s">
         <v>327</v>
       </c>
-      <c r="B33" s="34">
+      <c r="B33" s="35">
         <v>10.18</v>
       </c>
-      <c r="C33" s="34">
+      <c r="C33" s="35">
         <v>9.71</v>
       </c>
-      <c r="D33" s="34">
+      <c r="D33" s="35">
         <v>9.84</v>
       </c>
-      <c r="E33" s="34">
+      <c r="E33" s="35">
         <v>37.06</v>
       </c>
-      <c r="F33" s="34">
+      <c r="F33" s="35">
         <v>7.14</v>
       </c>
-      <c r="G33" s="34">
+      <c r="G33" s="35">
         <v>6.36</v>
       </c>
-      <c r="H33" s="34">
+      <c r="H33" s="35">
         <v>6.55</v>
       </c>
-      <c r="I33" s="34">
+      <c r="I33" s="35">
         <v>4.8</v>
       </c>
-      <c r="J33" s="34">
+      <c r="J33" s="35">
         <v>5.33</v>
       </c>
-      <c r="K33" s="34">
+      <c r="K33" s="35">
         <v>3.45</v>
       </c>
-      <c r="L33" s="34">
+      <c r="L33" s="35">
         <v>3.83</v>
       </c>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34">
+      <c r="M33" s="35"/>
+      <c r="N33" s="35">
         <v>6.59</v>
       </c>
-      <c r="O33" s="34">
+      <c r="O33" s="35">
         <v>4.75</v>
       </c>
-      <c r="P33" s="34">
+      <c r="P33" s="35">
         <v>3.75</v>
       </c>
-      <c r="Q33" s="34">
+      <c r="Q33" s="35">
         <v>5.95</v>
       </c>
-      <c r="R33" s="34">
+      <c r="R33" s="35">
         <v>11.01</v>
       </c>
-      <c r="S33" s="34">
+      <c r="S33" s="35">
         <v>5.32</v>
       </c>
-      <c r="T33" s="34">
+      <c r="T33" s="35">
         <v>5.48</v>
       </c>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34">
+      <c r="U33" s="35"/>
+      <c r="V33" s="35">
         <v>10.8</v>
       </c>
-      <c r="W33" s="34">
+      <c r="W33" s="35">
         <v>5.2</v>
       </c>
-      <c r="X33" s="34">
+      <c r="X33" s="35">
         <v>6.68</v>
       </c>
-      <c r="Y33" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Z33" s="34">
+      <c r="Y33" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Z33" s="35">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="29" t="s">
+      <c r="A34" s="30" t="s">
         <v>328</v>
       </c>
-      <c r="B34" s="34">
+      <c r="B34" s="35">
         <v>15.02</v>
       </c>
-      <c r="C34" s="34">
+      <c r="C34" s="35">
         <v>14.08</v>
       </c>
-      <c r="D34" s="34">
+      <c r="D34" s="35">
         <v>13.47</v>
       </c>
-      <c r="E34" s="34">
+      <c r="E34" s="35">
         <v>12.14</v>
       </c>
-      <c r="F34" s="34">
+      <c r="F34" s="35">
         <v>6.01</v>
       </c>
-      <c r="G34" s="34">
+      <c r="G34" s="35">
         <v>5.33</v>
       </c>
-      <c r="H34" s="34">
+      <c r="H34" s="35">
         <v>4.85</v>
       </c>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34">
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35">
         <v>5.92</v>
       </c>
-      <c r="O34" s="34">
+      <c r="O34" s="35">
         <v>5.67</v>
       </c>
-      <c r="P34" s="34">
+      <c r="P34" s="35">
         <v>5.78</v>
       </c>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34">
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35">
         <v>5.32</v>
       </c>
-      <c r="W34" s="34"/>
-      <c r="X34" s="34"/>
-      <c r="Y34" s="34"/>
-      <c r="Z34" s="34"/>
+      <c r="W34" s="35"/>
+      <c r="X34" s="35"/>
+      <c r="Y34" s="35"/>
+      <c r="Z34" s="35"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="29" t="s">
+      <c r="A35" s="30" t="s">
         <v>329</v>
       </c>
-      <c r="B35" s="34">
+      <c r="B35" s="35">
         <v>10.18</v>
       </c>
-      <c r="C35" s="34">
+      <c r="C35" s="35">
         <v>9.71</v>
       </c>
-      <c r="D35" s="34">
+      <c r="D35" s="35">
         <v>9.84</v>
       </c>
-      <c r="E35" s="34">
+      <c r="E35" s="35">
         <v>37.06</v>
       </c>
-      <c r="F35" s="34">
+      <c r="F35" s="35">
         <v>7.14</v>
       </c>
-      <c r="G35" s="34">
+      <c r="G35" s="35">
         <v>6.36</v>
       </c>
-      <c r="H35" s="34">
+      <c r="H35" s="35">
         <v>6.55</v>
       </c>
-      <c r="I35" s="34">
+      <c r="I35" s="35">
         <v>4.8</v>
       </c>
-      <c r="J35" s="34">
+      <c r="J35" s="35">
         <v>5.33</v>
       </c>
-      <c r="K35" s="34">
+      <c r="K35" s="35">
         <v>3.45</v>
       </c>
-      <c r="L35" s="34">
+      <c r="L35" s="35">
         <v>3.83</v>
       </c>
-      <c r="M35" s="34">
+      <c r="M35" s="35">
         <v>6.32</v>
       </c>
-      <c r="N35" s="34">
+      <c r="N35" s="35">
         <v>6.59</v>
       </c>
-      <c r="O35" s="34">
+      <c r="O35" s="35">
         <v>5.9</v>
       </c>
-      <c r="P35" s="34">
+      <c r="P35" s="35">
         <v>4.67</v>
       </c>
-      <c r="Q35" s="34">
+      <c r="Q35" s="35">
         <v>7.41</v>
       </c>
-      <c r="R35" s="34">
+      <c r="R35" s="35">
         <v>13.69</v>
       </c>
-      <c r="S35" s="34">
+      <c r="S35" s="35">
         <v>6.62</v>
       </c>
-      <c r="T35" s="34">
+      <c r="T35" s="35">
         <v>6.81</v>
       </c>
-      <c r="U35" s="34">
+      <c r="U35" s="35">
         <v>7.67</v>
       </c>
-      <c r="V35" s="34">
+      <c r="V35" s="35">
         <v>3.6</v>
       </c>
-      <c r="W35" s="34">
+      <c r="W35" s="35">
         <v>5.2</v>
       </c>
-      <c r="X35" s="34">
+      <c r="X35" s="35">
         <v>6.68</v>
       </c>
-      <c r="Y35" s="34">
-        <v>0.0</v>
-      </c>
-      <c r="Z35" s="34">
+      <c r="Y35" s="35">
+        <v>0.0</v>
+      </c>
+      <c r="Z35" s="35">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="29" t="s">
+      <c r="A36" s="30" t="s">
         <v>330</v>
       </c>
-      <c r="B36" s="34">
+      <c r="B36" s="35">
         <v>15.02</v>
       </c>
-      <c r="C36" s="34">
+      <c r="C36" s="35">
         <v>14.08</v>
       </c>
-      <c r="D36" s="34">
+      <c r="D36" s="35">
         <v>13.47</v>
       </c>
-      <c r="E36" s="34">
+      <c r="E36" s="35">
         <v>12.14</v>
       </c>
-      <c r="F36" s="34">
+      <c r="F36" s="35">
         <v>6.01</v>
       </c>
-      <c r="G36" s="34">
+      <c r="G36" s="35">
         <v>5.33</v>
       </c>
-      <c r="H36" s="34">
+      <c r="H36" s="35">
         <v>4.85</v>
       </c>
-      <c r="I36" s="34">
+      <c r="I36" s="35">
         <v>4.64</v>
       </c>
-      <c r="J36" s="34">
+      <c r="J36" s="35">
         <v>4.83</v>
       </c>
-      <c r="K36" s="34">
+      <c r="K36" s="35">
         <v>4.85</v>
       </c>
-      <c r="L36" s="34">
+      <c r="L36" s="35">
         <v>5.24</v>
       </c>
-      <c r="M36" s="34">
+      <c r="M36" s="35">
         <v>6.14</v>
       </c>
-      <c r="N36" s="34">
+      <c r="N36" s="35">
         <v>7.08</v>
       </c>
-      <c r="O36" s="34">
+      <c r="O36" s="35">
         <v>7.05</v>
       </c>
-      <c r="P36" s="34">
+      <c r="P36" s="35">
         <v>7.19</v>
       </c>
-      <c r="Q36" s="34">
+      <c r="Q36" s="35">
         <v>7.86</v>
       </c>
-      <c r="R36" s="34">
+      <c r="R36" s="35">
         <v>7.3</v>
       </c>
-      <c r="S36" s="34">
+      <c r="S36" s="35">
         <v>6.27</v>
       </c>
-      <c r="T36" s="34">
+      <c r="T36" s="35">
         <v>6.2</v>
       </c>
-      <c r="U36" s="34">
+      <c r="U36" s="35">
         <v>5.17</v>
       </c>
-      <c r="V36" s="34">
+      <c r="V36" s="35">
         <v>3.19</v>
       </c>
-      <c r="W36" s="34"/>
-      <c r="X36" s="34"/>
-      <c r="Y36" s="34"/>
-      <c r="Z36" s="34"/>
+      <c r="W36" s="35"/>
+      <c r="X36" s="35"/>
+      <c r="Y36" s="35"/>
+      <c r="Z36" s="35"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="27" t="s">
+      <c r="A37" s="28" t="s">
         <v>331</v>
       </c>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
-      <c r="F37" s="28"/>
-      <c r="G37" s="28"/>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28"/>
-      <c r="J37" s="28"/>
-      <c r="K37" s="28"/>
-      <c r="L37" s="28"/>
-      <c r="M37" s="28"/>
-      <c r="N37" s="28"/>
-      <c r="O37" s="28"/>
-      <c r="P37" s="28"/>
-      <c r="Q37" s="28"/>
-      <c r="R37" s="28"/>
-      <c r="S37" s="28"/>
-      <c r="T37" s="28"/>
-      <c r="U37" s="28"/>
-      <c r="V37" s="28"/>
-      <c r="W37" s="28"/>
-      <c r="X37" s="28"/>
-      <c r="Y37" s="28"/>
-      <c r="Z37" s="28"/>
+      <c r="B37" s="29"/>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="29"/>
+      <c r="F37" s="29"/>
+      <c r="G37" s="29"/>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29"/>
+      <c r="J37" s="29"/>
+      <c r="K37" s="29"/>
+      <c r="L37" s="29"/>
+      <c r="M37" s="29"/>
+      <c r="N37" s="29"/>
+      <c r="O37" s="29"/>
+      <c r="P37" s="29"/>
+      <c r="Q37" s="29"/>
+      <c r="R37" s="29"/>
+      <c r="S37" s="29"/>
+      <c r="T37" s="29"/>
+      <c r="U37" s="29"/>
+      <c r="V37" s="29"/>
+      <c r="W37" s="29"/>
+      <c r="X37" s="29"/>
+      <c r="Y37" s="29"/>
+      <c r="Z37" s="29"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="29" t="s">
+      <c r="A38" s="30" t="s">
         <v>332</v>
       </c>
-      <c r="B38" s="31">
+      <c r="B38" s="32">
         <v>0.54</v>
       </c>
-      <c r="C38" s="31">
+      <c r="C38" s="32">
         <v>0.61</v>
       </c>
-      <c r="D38" s="31">
+      <c r="D38" s="32">
         <v>0.59</v>
       </c>
-      <c r="E38" s="31">
+      <c r="E38" s="32">
         <v>0.59</v>
       </c>
-      <c r="F38" s="31">
+      <c r="F38" s="32">
         <v>0.56</v>
       </c>
-      <c r="G38" s="31">
+      <c r="G38" s="32">
         <v>0.48</v>
       </c>
-      <c r="H38" s="31">
+      <c r="H38" s="32">
         <v>0.41</v>
       </c>
-      <c r="I38" s="31">
+      <c r="I38" s="32">
         <v>0.52</v>
       </c>
-      <c r="J38" s="31">
+      <c r="J38" s="32">
         <v>0.49</v>
       </c>
-      <c r="K38" s="31">
+      <c r="K38" s="32">
         <v>0.52</v>
       </c>
-      <c r="L38" s="31">
+      <c r="L38" s="32">
         <v>0.67</v>
       </c>
-      <c r="M38" s="31">
+      <c r="M38" s="32">
         <v>0.52</v>
       </c>
-      <c r="N38" s="31">
+      <c r="N38" s="32">
         <v>0.49</v>
       </c>
-      <c r="O38" s="31">
+      <c r="O38" s="32">
         <v>0.55</v>
       </c>
-      <c r="P38" s="31">
+      <c r="P38" s="32">
         <v>0.66</v>
       </c>
-      <c r="Q38" s="31">
+      <c r="Q38" s="32">
         <v>0.66</v>
       </c>
-      <c r="R38" s="31">
+      <c r="R38" s="32">
         <v>0.38</v>
       </c>
-      <c r="S38" s="31">
+      <c r="S38" s="32">
         <v>0.78</v>
       </c>
-      <c r="T38" s="31">
+      <c r="T38" s="32">
         <v>0.76</v>
       </c>
-      <c r="U38" s="31">
+      <c r="U38" s="32">
         <v>0.81</v>
       </c>
-      <c r="V38" s="31">
+      <c r="V38" s="32">
         <v>0.58</v>
       </c>
-      <c r="W38" s="31">
+      <c r="W38" s="32">
         <v>0.47</v>
       </c>
-      <c r="X38" s="31">
+      <c r="X38" s="32">
         <v>0.4</v>
       </c>
-      <c r="Y38" s="31">
+      <c r="Y38" s="32">
         <v>0.42</v>
       </c>
-      <c r="Z38" s="31">
+      <c r="Z38" s="32">
         <v>0.4</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="29" t="s">
+      <c r="A39" s="30" t="s">
         <v>333</v>
       </c>
-      <c r="B39" s="31">
+      <c r="B39" s="32">
         <v>0.57</v>
       </c>
-      <c r="C39" s="31">
+      <c r="C39" s="32">
         <v>0.56</v>
       </c>
-      <c r="D39" s="31">
+      <c r="D39" s="32">
         <v>0.52</v>
       </c>
-      <c r="E39" s="31">
+      <c r="E39" s="32">
         <v>0.51</v>
       </c>
-      <c r="F39" s="31">
+      <c r="F39" s="32">
         <v>0.49</v>
       </c>
-      <c r="G39" s="31">
+      <c r="G39" s="32">
         <v>0.48</v>
       </c>
-      <c r="H39" s="31">
+      <c r="H39" s="32">
         <v>0.5</v>
       </c>
-      <c r="I39" s="31">
+      <c r="I39" s="32">
         <v>0.53</v>
       </c>
-      <c r="J39" s="31">
+      <c r="J39" s="32">
         <v>0.53</v>
       </c>
-      <c r="K39" s="31">
+      <c r="K39" s="32">
         <v>0.55</v>
       </c>
-      <c r="L39" s="31">
+      <c r="L39" s="32">
         <v>0.58</v>
       </c>
-      <c r="M39" s="31">
+      <c r="M39" s="32">
         <v>0.58</v>
       </c>
-      <c r="N39" s="31">
+      <c r="N39" s="32">
         <v>0.55</v>
       </c>
-      <c r="O39" s="31">
+      <c r="O39" s="32">
         <v>0.61</v>
       </c>
-      <c r="P39" s="31">
+      <c r="P39" s="32">
         <v>0.65</v>
       </c>
-      <c r="Q39" s="31">
+      <c r="Q39" s="32">
         <v>0.67</v>
       </c>
-      <c r="R39" s="31">
+      <c r="R39" s="32">
         <v>0.66</v>
       </c>
-      <c r="S39" s="31">
+      <c r="S39" s="32">
         <v>0.69</v>
       </c>
-      <c r="T39" s="31">
+      <c r="T39" s="32">
         <v>0.62</v>
       </c>
-      <c r="U39" s="31">
+      <c r="U39" s="32">
         <v>0.55</v>
       </c>
-      <c r="V39" s="31">
+      <c r="V39" s="32">
         <v>0.46</v>
       </c>
-      <c r="W39" s="33"/>
-      <c r="X39" s="33"/>
-      <c r="Y39" s="33"/>
-      <c r="Z39" s="33"/>
+      <c r="W39" s="34"/>
+      <c r="X39" s="34"/>
+      <c r="Y39" s="34"/>
+      <c r="Z39" s="34"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="27" t="s">
+      <c r="A40" s="28" t="s">
         <v>334</v>
       </c>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
-      <c r="F40" s="28"/>
-      <c r="G40" s="28"/>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
-      <c r="K40" s="28"/>
-      <c r="L40" s="28"/>
-      <c r="M40" s="28"/>
-      <c r="N40" s="28"/>
-      <c r="O40" s="28"/>
-      <c r="P40" s="28"/>
-      <c r="Q40" s="28"/>
-      <c r="R40" s="28"/>
-      <c r="S40" s="28"/>
-      <c r="T40" s="28"/>
-      <c r="U40" s="28"/>
-      <c r="V40" s="28"/>
-      <c r="W40" s="28"/>
-      <c r="X40" s="28"/>
-      <c r="Y40" s="28"/>
-      <c r="Z40" s="28"/>
+      <c r="B40" s="29"/>
+      <c r="C40" s="29"/>
+      <c r="D40" s="29"/>
+      <c r="E40" s="29"/>
+      <c r="F40" s="29"/>
+      <c r="G40" s="29"/>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29"/>
+      <c r="J40" s="29"/>
+      <c r="K40" s="29"/>
+      <c r="L40" s="29"/>
+      <c r="M40" s="29"/>
+      <c r="N40" s="29"/>
+      <c r="O40" s="29"/>
+      <c r="P40" s="29"/>
+      <c r="Q40" s="29"/>
+      <c r="R40" s="29"/>
+      <c r="S40" s="29"/>
+      <c r="T40" s="29"/>
+      <c r="U40" s="29"/>
+      <c r="V40" s="29"/>
+      <c r="W40" s="29"/>
+      <c r="X40" s="29"/>
+      <c r="Y40" s="29"/>
+      <c r="Z40" s="29"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="30" t="s">
         <v>335</v>
       </c>
-      <c r="B41" s="31">
+      <c r="B41" s="32">
         <v>0.61</v>
       </c>
-      <c r="C41" s="31">
+      <c r="C41" s="32">
         <v>0.74</v>
       </c>
-      <c r="D41" s="31">
+      <c r="D41" s="32">
         <v>0.75</v>
       </c>
-      <c r="E41" s="31">
+      <c r="E41" s="32">
         <v>0.69</v>
       </c>
-      <c r="F41" s="31">
+      <c r="F41" s="32">
         <v>0.61</v>
       </c>
-      <c r="G41" s="31">
+      <c r="G41" s="32">
         <v>0.52</v>
       </c>
-      <c r="H41" s="31">
+      <c r="H41" s="32">
         <v>0.44</v>
       </c>
-      <c r="I41" s="31">
+      <c r="I41" s="32">
         <v>0.53</v>
       </c>
-      <c r="J41" s="31">
+      <c r="J41" s="32">
         <v>0.52</v>
       </c>
-      <c r="K41" s="31">
+      <c r="K41" s="32">
         <v>0.53</v>
       </c>
-      <c r="L41" s="31">
+      <c r="L41" s="32">
         <v>0.67</v>
       </c>
-      <c r="M41" s="31">
+      <c r="M41" s="32">
         <v>0.52</v>
       </c>
-      <c r="N41" s="31">
+      <c r="N41" s="32">
         <v>0.49</v>
       </c>
-      <c r="O41" s="31">
+      <c r="O41" s="32">
         <v>0.55</v>
       </c>
-      <c r="P41" s="31">
+      <c r="P41" s="32">
         <v>0.66</v>
       </c>
-      <c r="Q41" s="31">
+      <c r="Q41" s="32">
         <v>0.66</v>
       </c>
-      <c r="R41" s="31">
+      <c r="R41" s="32">
         <v>0.38</v>
       </c>
-      <c r="S41" s="31">
+      <c r="S41" s="32">
         <v>0.78</v>
       </c>
-      <c r="T41" s="31">
+      <c r="T41" s="32">
         <v>0.76</v>
       </c>
-      <c r="U41" s="31">
+      <c r="U41" s="32">
         <v>0.86</v>
       </c>
-      <c r="V41" s="31">
+      <c r="V41" s="32">
         <v>0.6</v>
       </c>
-      <c r="W41" s="31">
+      <c r="W41" s="32">
         <v>0.48</v>
       </c>
-      <c r="X41" s="31">
+      <c r="X41" s="32">
         <v>0.41</v>
       </c>
-      <c r="Y41" s="31">
+      <c r="Y41" s="32">
         <v>0.43</v>
       </c>
-      <c r="Z41" s="31">
+      <c r="Z41" s="32">
         <v>0.41</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="29" t="s">
+      <c r="A42" s="30" t="s">
         <v>336</v>
       </c>
-      <c r="B42" s="31">
+      <c r="B42" s="32">
         <v>0.67</v>
       </c>
-      <c r="C42" s="31">
+      <c r="C42" s="32">
         <v>0.64</v>
       </c>
-      <c r="D42" s="31">
+      <c r="D42" s="32">
         <v>0.58</v>
       </c>
-      <c r="E42" s="31">
+      <c r="E42" s="32">
         <v>0.55</v>
       </c>
-      <c r="F42" s="31">
+      <c r="F42" s="32">
         <v>0.52</v>
       </c>
-      <c r="G42" s="31">
+      <c r="G42" s="32">
         <v>0.51</v>
       </c>
-      <c r="H42" s="31">
+      <c r="H42" s="32">
         <v>0.52</v>
       </c>
-      <c r="I42" s="31">
+      <c r="I42" s="32">
         <v>0.55</v>
       </c>
-      <c r="J42" s="31">
+      <c r="J42" s="32">
         <v>0.54</v>
       </c>
-      <c r="K42" s="31">
+      <c r="K42" s="32">
         <v>0.55</v>
       </c>
-      <c r="L42" s="31">
+      <c r="L42" s="32">
         <v>0.58</v>
       </c>
-      <c r="M42" s="31">
+      <c r="M42" s="32">
         <v>0.58</v>
       </c>
-      <c r="N42" s="31">
+      <c r="N42" s="32">
         <v>0.55</v>
       </c>
-      <c r="O42" s="31">
+      <c r="O42" s="32">
         <v>0.61</v>
       </c>
-      <c r="P42" s="31">
+      <c r="P42" s="32">
         <v>0.65</v>
       </c>
-      <c r="Q42" s="31">
+      <c r="Q42" s="32">
         <v>0.68</v>
       </c>
-      <c r="R42" s="31">
+      <c r="R42" s="32">
         <v>0.67</v>
       </c>
-      <c r="S42" s="31">
+      <c r="S42" s="32">
         <v>0.71</v>
       </c>
-      <c r="T42" s="31">
+      <c r="T42" s="32">
         <v>0.64</v>
       </c>
-      <c r="U42" s="31">
+      <c r="U42" s="32">
         <v>0.57</v>
       </c>
-      <c r="V42" s="31">
+      <c r="V42" s="32">
         <v>0.47</v>
       </c>
-      <c r="W42" s="33"/>
-      <c r="X42" s="33"/>
-      <c r="Y42" s="33"/>
-      <c r="Z42" s="33"/>
+      <c r="W42" s="34"/>
+      <c r="X42" s="34"/>
+      <c r="Y42" s="34"/>
+      <c r="Z42" s="34"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="27" t="s">
+      <c r="A43" s="28" t="s">
         <v>337</v>
       </c>
-      <c r="B43" s="28"/>
-      <c r="C43" s="28"/>
-      <c r="D43" s="28"/>
-      <c r="E43" s="28"/>
-      <c r="F43" s="28"/>
-      <c r="G43" s="28"/>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
-      <c r="K43" s="28"/>
-      <c r="L43" s="28"/>
-      <c r="M43" s="28"/>
-      <c r="N43" s="28"/>
-      <c r="O43" s="28"/>
-      <c r="P43" s="28"/>
-      <c r="Q43" s="28"/>
-      <c r="R43" s="28"/>
-      <c r="S43" s="28"/>
-      <c r="T43" s="28"/>
-      <c r="U43" s="28"/>
-      <c r="V43" s="28"/>
-      <c r="W43" s="28"/>
-      <c r="X43" s="28"/>
-      <c r="Y43" s="28"/>
-      <c r="Z43" s="28"/>
+      <c r="B43" s="29"/>
+      <c r="C43" s="29"/>
+      <c r="D43" s="29"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29"/>
+      <c r="J43" s="29"/>
+      <c r="K43" s="29"/>
+      <c r="L43" s="29"/>
+      <c r="M43" s="29"/>
+      <c r="N43" s="29"/>
+      <c r="O43" s="29"/>
+      <c r="P43" s="29"/>
+      <c r="Q43" s="29"/>
+      <c r="R43" s="29"/>
+      <c r="S43" s="29"/>
+      <c r="T43" s="29"/>
+      <c r="U43" s="29"/>
+      <c r="V43" s="29"/>
+      <c r="W43" s="29"/>
+      <c r="X43" s="29"/>
+      <c r="Y43" s="29"/>
+      <c r="Z43" s="29"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="29" t="s">
+      <c r="A44" s="30" t="s">
         <v>338</v>
       </c>
-      <c r="B44" s="31">
+      <c r="B44" s="32">
         <v>2.06</v>
       </c>
-      <c r="C44" s="31">
+      <c r="C44" s="32">
         <v>2.96</v>
       </c>
-      <c r="D44" s="31">
+      <c r="D44" s="32">
         <v>2.48</v>
       </c>
-      <c r="E44" s="31">
+      <c r="E44" s="32">
         <v>2.13</v>
       </c>
-      <c r="F44" s="31">
+      <c r="F44" s="32">
         <v>2.21</v>
       </c>
-      <c r="G44" s="31">
+      <c r="G44" s="32">
         <v>1.9</v>
       </c>
-      <c r="H44" s="31">
+      <c r="H44" s="32">
         <v>2.33</v>
       </c>
-      <c r="I44" s="31">
+      <c r="I44" s="32">
         <v>3.79</v>
       </c>
-      <c r="J44" s="31">
+      <c r="J44" s="32">
         <v>3.37</v>
       </c>
-      <c r="K44" s="31">
+      <c r="K44" s="32">
         <v>6.42</v>
       </c>
-      <c r="L44" s="31">
+      <c r="L44" s="32">
         <v>5.23</v>
       </c>
-      <c r="M44" s="31">
+      <c r="M44" s="32">
         <v>3.63</v>
       </c>
-      <c r="N44" s="31">
+      <c r="N44" s="32">
         <v>3.56</v>
       </c>
-      <c r="O44" s="31">
+      <c r="O44" s="32">
         <v>4.23</v>
       </c>
-      <c r="P44" s="31">
+      <c r="P44" s="32">
         <v>4.68</v>
       </c>
-      <c r="Q44" s="31">
+      <c r="Q44" s="32">
         <v>4.26</v>
       </c>
-      <c r="R44" s="31">
+      <c r="R44" s="32">
         <v>2.31</v>
       </c>
-      <c r="S44" s="31">
+      <c r="S44" s="32">
         <v>4.94</v>
       </c>
-      <c r="T44" s="31">
+      <c r="T44" s="32">
         <v>2.61</v>
       </c>
-      <c r="U44" s="31">
+      <c r="U44" s="32">
         <v>3.73</v>
       </c>
-      <c r="V44" s="31">
+      <c r="V44" s="32">
         <v>2.54</v>
       </c>
-      <c r="W44" s="31">
+      <c r="W44" s="32">
         <v>1.83</v>
       </c>
-      <c r="X44" s="31">
+      <c r="X44" s="32">
         <v>1.81</v>
       </c>
-      <c r="Y44" s="31">
+      <c r="Y44" s="32">
         <v>2.07</v>
       </c>
-      <c r="Z44" s="31">
+      <c r="Z44" s="32">
         <v>1.01</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="29" t="s">
+      <c r="A45" s="30" t="s">
         <v>339</v>
       </c>
-      <c r="B45" s="31">
+      <c r="B45" s="32">
         <v>2.32</v>
       </c>
-      <c r="C45" s="31">
+      <c r="C45" s="32">
         <v>2.26</v>
       </c>
-      <c r="D45" s="31">
+      <c r="D45" s="32">
         <v>2.18</v>
       </c>
-      <c r="E45" s="31">
+      <c r="E45" s="32">
         <v>2.36</v>
       </c>
-      <c r="F45" s="31">
+      <c r="F45" s="32">
         <v>2.55</v>
       </c>
-      <c r="G45" s="31">
+      <c r="G45" s="32">
         <v>2.95</v>
       </c>
-      <c r="H45" s="31">
+      <c r="H45" s="32">
         <v>3.68</v>
       </c>
-      <c r="I45" s="31">
+      <c r="I45" s="32">
         <v>4.22</v>
       </c>
-      <c r="J45" s="31">
+      <c r="J45" s="32">
         <v>4.28</v>
       </c>
-      <c r="K45" s="31">
+      <c r="K45" s="32">
         <v>4.65</v>
       </c>
-      <c r="L45" s="31">
+      <c r="L45" s="32">
         <v>4.3</v>
       </c>
-      <c r="M45" s="31">
+      <c r="M45" s="32">
         <v>4.08</v>
       </c>
-      <c r="N45" s="31">
+      <c r="N45" s="32">
         <v>3.79</v>
       </c>
-      <c r="O45" s="31">
+      <c r="O45" s="32">
         <v>4.07</v>
       </c>
-      <c r="P45" s="31">
+      <c r="P45" s="32">
         <v>3.59</v>
       </c>
-      <c r="Q45" s="31">
+      <c r="Q45" s="32">
         <v>3.44</v>
       </c>
-      <c r="R45" s="31">
+      <c r="R45" s="32">
         <v>3.13</v>
       </c>
-      <c r="S45" s="31">
+      <c r="S45" s="32">
         <v>3.03</v>
       </c>
-      <c r="T45" s="31">
+      <c r="T45" s="32">
         <v>2.54</v>
       </c>
-      <c r="U45" s="31">
+      <c r="U45" s="32">
         <v>2.45</v>
       </c>
-      <c r="V45" s="31">
+      <c r="V45" s="32">
         <v>1.75</v>
       </c>
-      <c r="W45" s="33"/>
-      <c r="X45" s="33"/>
-      <c r="Y45" s="33"/>
-      <c r="Z45" s="33"/>
+      <c r="W45" s="34"/>
+      <c r="X45" s="34"/>
+      <c r="Y45" s="34"/>
+      <c r="Z45" s="34"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="27" t="s">
+      <c r="A46" s="28" t="s">
         <v>340</v>
       </c>
-      <c r="B46" s="28"/>
-      <c r="C46" s="28"/>
-      <c r="D46" s="28"/>
-      <c r="E46" s="28"/>
-      <c r="F46" s="28"/>
-      <c r="G46" s="28"/>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
-      <c r="K46" s="28"/>
-      <c r="L46" s="28"/>
-      <c r="M46" s="28"/>
-      <c r="N46" s="28"/>
-      <c r="O46" s="28"/>
-      <c r="P46" s="28"/>
-      <c r="Q46" s="28"/>
-      <c r="R46" s="28"/>
-      <c r="S46" s="28"/>
-      <c r="T46" s="28"/>
-      <c r="U46" s="28"/>
-      <c r="V46" s="28"/>
-      <c r="W46" s="28"/>
-      <c r="X46" s="28"/>
-      <c r="Y46" s="28"/>
-      <c r="Z46" s="28"/>
+      <c r="B46" s="29"/>
+      <c r="C46" s="29"/>
+      <c r="D46" s="29"/>
+      <c r="E46" s="29"/>
+      <c r="F46" s="29"/>
+      <c r="G46" s="29"/>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
+      <c r="K46" s="29"/>
+      <c r="L46" s="29"/>
+      <c r="M46" s="29"/>
+      <c r="N46" s="29"/>
+      <c r="O46" s="29"/>
+      <c r="P46" s="29"/>
+      <c r="Q46" s="29"/>
+      <c r="R46" s="29"/>
+      <c r="S46" s="29"/>
+      <c r="T46" s="29"/>
+      <c r="U46" s="29"/>
+      <c r="V46" s="29"/>
+      <c r="W46" s="29"/>
+      <c r="X46" s="29"/>
+      <c r="Y46" s="29"/>
+      <c r="Z46" s="29"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="29" t="s">
+      <c r="A47" s="30" t="s">
         <v>341</v>
       </c>
-      <c r="B47" s="31">
+      <c r="B47" s="32">
         <v>10.19</v>
       </c>
-      <c r="C47" s="33"/>
-      <c r="D47" s="30">
+      <c r="C47" s="34"/>
+      <c r="D47" s="31">
         <v>118.75</v>
       </c>
-      <c r="E47" s="33"/>
-      <c r="F47" s="33"/>
-      <c r="G47" s="33"/>
-      <c r="H47" s="33"/>
-      <c r="I47" s="30">
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="31">
         <v>260.09</v>
       </c>
-      <c r="J47" s="33"/>
-      <c r="K47" s="33"/>
-      <c r="L47" s="30">
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="31">
         <v>531.79</v>
       </c>
-      <c r="M47" s="33"/>
-      <c r="N47" s="33"/>
-      <c r="O47" s="33"/>
-      <c r="P47" s="33"/>
-      <c r="Q47" s="31">
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="32">
         <v>8.45</v>
       </c>
-      <c r="R47" s="31">
+      <c r="R47" s="32">
         <v>4.22</v>
       </c>
-      <c r="S47" s="31">
+      <c r="S47" s="32">
         <v>10.25</v>
       </c>
-      <c r="T47" s="31">
+      <c r="T47" s="32">
         <v>8.12</v>
       </c>
-      <c r="U47" s="31">
+      <c r="U47" s="32">
         <v>5.82</v>
       </c>
-      <c r="V47" s="31">
+      <c r="V47" s="32">
         <v>3.57</v>
       </c>
-      <c r="W47" s="31">
+      <c r="W47" s="32">
         <v>2.88</v>
       </c>
-      <c r="X47" s="31">
+      <c r="X47" s="32">
         <v>4.7</v>
       </c>
-      <c r="Y47" s="31">
+      <c r="Y47" s="32">
         <v>7.38</v>
       </c>
-      <c r="Z47" s="33"/>
+      <c r="Z47" s="34"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="29" t="s">
+      <c r="A48" s="30" t="s">
         <v>342</v>
       </c>
-      <c r="B48" s="33"/>
-      <c r="C48" s="33"/>
-      <c r="D48" s="33"/>
-      <c r="E48" s="33"/>
-      <c r="F48" s="33"/>
-      <c r="G48" s="33"/>
-      <c r="H48" s="33"/>
-      <c r="I48" s="33"/>
-      <c r="J48" s="33"/>
-      <c r="K48" s="33"/>
-      <c r="L48" s="33"/>
-      <c r="M48" s="33"/>
-      <c r="N48" s="33"/>
-      <c r="O48" s="33"/>
-      <c r="P48" s="31">
+      <c r="B48" s="34"/>
+      <c r="C48" s="34"/>
+      <c r="D48" s="34"/>
+      <c r="E48" s="34"/>
+      <c r="F48" s="34"/>
+      <c r="G48" s="34"/>
+      <c r="H48" s="34"/>
+      <c r="I48" s="34"/>
+      <c r="J48" s="34"/>
+      <c r="K48" s="34"/>
+      <c r="L48" s="34"/>
+      <c r="M48" s="34"/>
+      <c r="N48" s="34"/>
+      <c r="O48" s="34"/>
+      <c r="P48" s="32">
         <v>10.04</v>
       </c>
-      <c r="Q48" s="31">
+      <c r="Q48" s="32">
         <v>7.19</v>
       </c>
-      <c r="R48" s="31">
+      <c r="R48" s="32">
         <v>6.03</v>
       </c>
-      <c r="S48" s="31">
+      <c r="S48" s="32">
         <v>5.66</v>
       </c>
-      <c r="T48" s="31">
+      <c r="T48" s="32">
         <v>4.87</v>
       </c>
-      <c r="U48" s="31">
+      <c r="U48" s="32">
         <v>4.4</v>
       </c>
-      <c r="V48" s="31">
+      <c r="V48" s="32">
         <v>6.66</v>
       </c>
-      <c r="W48" s="33"/>
-      <c r="X48" s="33"/>
-      <c r="Y48" s="33"/>
-      <c r="Z48" s="33"/>
+      <c r="W48" s="34"/>
+      <c r="X48" s="34"/>
+      <c r="Y48" s="34"/>
+      <c r="Z48" s="34"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="27" t="s">
+      <c r="A49" s="28" t="s">
         <v>343</v>
       </c>
-      <c r="B49" s="28"/>
-      <c r="C49" s="28"/>
-      <c r="D49" s="28"/>
-      <c r="E49" s="28"/>
-      <c r="F49" s="28"/>
-      <c r="G49" s="28"/>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
-      <c r="K49" s="28"/>
-      <c r="L49" s="28"/>
-      <c r="M49" s="28"/>
-      <c r="N49" s="28"/>
-      <c r="O49" s="28"/>
-      <c r="P49" s="28"/>
-      <c r="Q49" s="28"/>
-      <c r="R49" s="28"/>
-      <c r="S49" s="28"/>
-      <c r="T49" s="28"/>
-      <c r="U49" s="28"/>
-      <c r="V49" s="28"/>
-      <c r="W49" s="28"/>
-      <c r="X49" s="28"/>
-      <c r="Y49" s="28"/>
-      <c r="Z49" s="28"/>
+      <c r="B49" s="29"/>
+      <c r="C49" s="29"/>
+      <c r="D49" s="29"/>
+      <c r="E49" s="29"/>
+      <c r="F49" s="29"/>
+      <c r="G49" s="29"/>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29"/>
+      <c r="J49" s="29"/>
+      <c r="K49" s="29"/>
+      <c r="L49" s="29"/>
+      <c r="M49" s="29"/>
+      <c r="N49" s="29"/>
+      <c r="O49" s="29"/>
+      <c r="P49" s="29"/>
+      <c r="Q49" s="29"/>
+      <c r="R49" s="29"/>
+      <c r="S49" s="29"/>
+      <c r="T49" s="29"/>
+      <c r="U49" s="29"/>
+      <c r="V49" s="29"/>
+      <c r="W49" s="29"/>
+      <c r="X49" s="29"/>
+      <c r="Y49" s="29"/>
+      <c r="Z49" s="29"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="29" t="s">
+      <c r="A50" s="30" t="s">
         <v>344</v>
       </c>
-      <c r="B50" s="31">
+      <c r="B50" s="32">
         <v>2.3</v>
       </c>
-      <c r="C50" s="31">
+      <c r="C50" s="32">
         <v>4.95</v>
       </c>
-      <c r="D50" s="31">
+      <c r="D50" s="32">
         <v>5.2</v>
       </c>
-      <c r="E50" s="30">
+      <c r="E50" s="31">
         <v>156.04</v>
       </c>
-      <c r="F50" s="33"/>
-      <c r="G50" s="31">
+      <c r="F50" s="34"/>
+      <c r="G50" s="32">
         <v>10.22</v>
       </c>
-      <c r="H50" s="33"/>
-      <c r="I50" s="33"/>
-      <c r="J50" s="33"/>
-      <c r="K50" s="33"/>
-      <c r="L50" s="33"/>
-      <c r="M50" s="31">
+      <c r="H50" s="34"/>
+      <c r="I50" s="34"/>
+      <c r="J50" s="34"/>
+      <c r="K50" s="34"/>
+      <c r="L50" s="34"/>
+      <c r="M50" s="32">
         <v>8.91</v>
       </c>
-      <c r="N50" s="31">
+      <c r="N50" s="32">
         <v>5.58</v>
       </c>
-      <c r="O50" s="31">
+      <c r="O50" s="32">
         <v>47.27</v>
       </c>
-      <c r="P50" s="31">
+      <c r="P50" s="32">
         <v>6.09</v>
       </c>
-      <c r="Q50" s="31">
+      <c r="Q50" s="32">
         <v>5.07</v>
       </c>
-      <c r="R50" s="31">
+      <c r="R50" s="32">
         <v>4.87</v>
       </c>
-      <c r="S50" s="31">
+      <c r="S50" s="32">
         <v>9.89</v>
       </c>
-      <c r="T50" s="31">
+      <c r="T50" s="32">
         <v>3.11</v>
       </c>
-      <c r="U50" s="31">
+      <c r="U50" s="32">
         <v>7.32</v>
       </c>
-      <c r="V50" s="31">
+      <c r="V50" s="32">
         <v>3.15</v>
       </c>
-      <c r="W50" s="31">
+      <c r="W50" s="32">
         <v>2.84</v>
       </c>
-      <c r="X50" s="31">
+      <c r="X50" s="32">
         <v>3.85</v>
       </c>
-      <c r="Y50" s="31">
+      <c r="Y50" s="32">
         <v>4.32</v>
       </c>
-      <c r="Z50" s="31">
+      <c r="Z50" s="32">
         <v>5.59</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="29" t="s">
+      <c r="A51" s="30" t="s">
         <v>345</v>
       </c>
-      <c r="B51" s="31">
+      <c r="B51" s="32">
         <v>7.24</v>
       </c>
-      <c r="C51" s="31">
+      <c r="C51" s="32">
         <v>13.91</v>
       </c>
-      <c r="D51" s="33"/>
-      <c r="E51" s="33"/>
-      <c r="F51" s="33"/>
-      <c r="G51" s="33"/>
-      <c r="H51" s="33"/>
-      <c r="I51" s="33"/>
-      <c r="J51" s="33"/>
-      <c r="K51" s="33"/>
-      <c r="L51" s="33"/>
-      <c r="M51" s="31">
+      <c r="D51" s="34"/>
+      <c r="E51" s="34"/>
+      <c r="F51" s="34"/>
+      <c r="G51" s="34"/>
+      <c r="H51" s="34"/>
+      <c r="I51" s="34"/>
+      <c r="J51" s="34"/>
+      <c r="K51" s="34"/>
+      <c r="L51" s="34"/>
+      <c r="M51" s="32">
         <v>7.25</v>
       </c>
-      <c r="N51" s="31">
+      <c r="N51" s="32">
         <v>6.6</v>
       </c>
-      <c r="O51" s="31">
+      <c r="O51" s="32">
         <v>7.43</v>
       </c>
-      <c r="P51" s="31">
+      <c r="P51" s="32">
         <v>5.08</v>
       </c>
-      <c r="Q51" s="31">
+      <c r="Q51" s="32">
         <v>5.22</v>
       </c>
-      <c r="R51" s="31">
+      <c r="R51" s="32">
         <v>4.76</v>
       </c>
-      <c r="S51" s="31">
+      <c r="S51" s="32">
         <v>4.42</v>
       </c>
-      <c r="T51" s="31">
+      <c r="T51" s="32">
         <v>3.72</v>
       </c>
-      <c r="U51" s="31">
+      <c r="U51" s="32">
         <v>4.11</v>
       </c>
-      <c r="V51" s="31">
+      <c r="V51" s="32">
         <v>3.62</v>
       </c>
-      <c r="W51" s="33"/>
-      <c r="X51" s="33"/>
-      <c r="Y51" s="33"/>
-      <c r="Z51" s="33"/>
+      <c r="W51" s="34"/>
+      <c r="X51" s="34"/>
+      <c r="Y51" s="34"/>
+      <c r="Z51" s="34"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="27" t="s">
+      <c r="A52" s="28" t="s">
         <v>346</v>
       </c>
-      <c r="B52" s="28"/>
-      <c r="C52" s="28"/>
-      <c r="D52" s="28"/>
-      <c r="E52" s="28"/>
-      <c r="F52" s="28"/>
-      <c r="G52" s="28"/>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
-      <c r="K52" s="28"/>
-      <c r="L52" s="28"/>
-      <c r="M52" s="28"/>
-      <c r="N52" s="28"/>
-      <c r="O52" s="28"/>
-      <c r="P52" s="28"/>
-      <c r="Q52" s="28"/>
-      <c r="R52" s="28"/>
-      <c r="S52" s="28"/>
-      <c r="T52" s="28"/>
-      <c r="U52" s="28"/>
-      <c r="V52" s="28"/>
-      <c r="W52" s="28"/>
-      <c r="X52" s="28"/>
-      <c r="Y52" s="28"/>
-      <c r="Z52" s="28"/>
+      <c r="B52" s="29"/>
+      <c r="C52" s="29"/>
+      <c r="D52" s="29"/>
+      <c r="E52" s="29"/>
+      <c r="F52" s="29"/>
+      <c r="G52" s="29"/>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29"/>
+      <c r="J52" s="29"/>
+      <c r="K52" s="29"/>
+      <c r="L52" s="29"/>
+      <c r="M52" s="29"/>
+      <c r="N52" s="29"/>
+      <c r="O52" s="29"/>
+      <c r="P52" s="29"/>
+      <c r="Q52" s="29"/>
+      <c r="R52" s="29"/>
+      <c r="S52" s="29"/>
+      <c r="T52" s="29"/>
+      <c r="U52" s="29"/>
+      <c r="V52" s="29"/>
+      <c r="W52" s="29"/>
+      <c r="X52" s="29"/>
+      <c r="Y52" s="29"/>
+      <c r="Z52" s="29"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="29" t="s">
+      <c r="A53" s="30" t="s">
         <v>347</v>
       </c>
-      <c r="B53" s="31">
+      <c r="B53" s="32">
         <v>3.0</v>
       </c>
-      <c r="C53" s="31">
+      <c r="C53" s="32">
         <v>5.7</v>
       </c>
-      <c r="D53" s="31">
+      <c r="D53" s="32">
         <v>5.86</v>
       </c>
-      <c r="E53" s="33"/>
-      <c r="F53" s="33"/>
-      <c r="G53" s="31">
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="32">
         <v>13.19</v>
       </c>
-      <c r="H53" s="31">
+      <c r="H53" s="32">
         <v>7.73</v>
       </c>
-      <c r="I53" s="31">
+      <c r="I53" s="32">
         <v>4.84</v>
       </c>
-      <c r="J53" s="31">
+      <c r="J53" s="32">
         <v>2.8</v>
       </c>
-      <c r="K53" s="31">
+      <c r="K53" s="32">
         <v>2.65</v>
       </c>
-      <c r="L53" s="31">
+      <c r="L53" s="32">
         <v>5.67</v>
       </c>
-      <c r="M53" s="31">
+      <c r="M53" s="32">
         <v>35.44</v>
       </c>
-      <c r="N53" s="31">
+      <c r="N53" s="32">
         <v>10.06</v>
       </c>
-      <c r="O53" s="33"/>
-      <c r="P53" s="31">
+      <c r="O53" s="34"/>
+      <c r="P53" s="32">
         <v>7.86</v>
       </c>
-      <c r="Q53" s="31">
+      <c r="Q53" s="32">
         <v>6.38</v>
       </c>
-      <c r="R53" s="31">
+      <c r="R53" s="32">
         <v>7.67</v>
       </c>
-      <c r="S53" s="31">
+      <c r="S53" s="32">
         <v>15.37</v>
       </c>
-      <c r="T53" s="31">
+      <c r="T53" s="32">
         <v>3.51</v>
       </c>
-      <c r="U53" s="31">
+      <c r="U53" s="32">
         <v>10.5</v>
       </c>
-      <c r="V53" s="31">
+      <c r="V53" s="32">
         <v>3.84</v>
       </c>
-      <c r="W53" s="31">
+      <c r="W53" s="32">
         <v>3.68</v>
       </c>
-      <c r="X53" s="31">
+      <c r="X53" s="32">
         <v>6.38</v>
       </c>
-      <c r="Y53" s="31">
+      <c r="Y53" s="32">
         <v>7.73</v>
       </c>
-      <c r="Z53" s="31">
+      <c r="Z53" s="32">
         <v>19.84</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="29" t="s">
+      <c r="A54" s="30" t="s">
         <v>348</v>
       </c>
-      <c r="B54" s="31">
+      <c r="B54" s="32">
         <v>10.1</v>
       </c>
-      <c r="C54" s="31">
+      <c r="C54" s="32">
         <v>20.63</v>
       </c>
-      <c r="D54" s="31">
+      <c r="D54" s="32">
         <v>25.16</v>
       </c>
-      <c r="E54" s="31">
+      <c r="E54" s="32">
         <v>18.12</v>
       </c>
-      <c r="F54" s="31">
+      <c r="F54" s="32">
         <v>7.68</v>
       </c>
-      <c r="G54" s="31">
+      <c r="G54" s="32">
         <v>4.51</v>
       </c>
-      <c r="H54" s="31">
+      <c r="H54" s="32">
         <v>4.04</v>
       </c>
-      <c r="I54" s="31">
+      <c r="I54" s="32">
         <v>4.0</v>
       </c>
-      <c r="J54" s="31">
+      <c r="J54" s="32">
         <v>4.08</v>
       </c>
-      <c r="K54" s="31">
+      <c r="K54" s="32">
         <v>6.1</v>
       </c>
-      <c r="L54" s="31">
+      <c r="L54" s="32">
         <v>11.02</v>
       </c>
-      <c r="M54" s="31">
+      <c r="M54" s="32">
         <v>12.39</v>
       </c>
-      <c r="N54" s="31">
+      <c r="N54" s="32">
         <v>10.32</v>
       </c>
-      <c r="O54" s="31">
+      <c r="O54" s="32">
         <v>11.28</v>
       </c>
-      <c r="P54" s="31">
+      <c r="P54" s="32">
         <v>6.46</v>
       </c>
-      <c r="Q54" s="31">
+      <c r="Q54" s="32">
         <v>6.72</v>
       </c>
-      <c r="R54" s="31">
+      <c r="R54" s="32">
         <v>6.08</v>
       </c>
-      <c r="S54" s="31">
+      <c r="S54" s="32">
         <v>5.54</v>
       </c>
-      <c r="T54" s="31">
+      <c r="T54" s="32">
         <v>4.67</v>
       </c>
-      <c r="U54" s="31">
+      <c r="U54" s="32">
         <v>5.67</v>
       </c>
-      <c r="V54" s="31">
+      <c r="V54" s="32">
         <v>5.34</v>
       </c>
-      <c r="W54" s="33"/>
-      <c r="X54" s="33"/>
-      <c r="Y54" s="33"/>
-      <c r="Z54" s="33"/>
+      <c r="W54" s="34"/>
+      <c r="X54" s="34"/>
+      <c r="Y54" s="34"/>
+      <c r="Z54" s="34"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="27" t="s">
+      <c r="A55" s="28" t="s">
         <v>349</v>
       </c>
-      <c r="B55" s="28"/>
-      <c r="C55" s="28"/>
-      <c r="D55" s="28"/>
-      <c r="E55" s="28"/>
-      <c r="F55" s="28"/>
-      <c r="G55" s="28"/>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
-      <c r="K55" s="28"/>
-      <c r="L55" s="28"/>
-      <c r="M55" s="28"/>
-      <c r="N55" s="28"/>
-      <c r="O55" s="28"/>
-      <c r="P55" s="28"/>
-      <c r="Q55" s="28"/>
-      <c r="R55" s="28"/>
-      <c r="S55" s="28"/>
-      <c r="T55" s="28"/>
-      <c r="U55" s="28"/>
-      <c r="V55" s="28"/>
-      <c r="W55" s="28"/>
-      <c r="X55" s="28"/>
-      <c r="Y55" s="28"/>
-      <c r="Z55" s="28"/>
+      <c r="B55" s="29"/>
+      <c r="C55" s="29"/>
+      <c r="D55" s="29"/>
+      <c r="E55" s="29"/>
+      <c r="F55" s="29"/>
+      <c r="G55" s="29"/>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29"/>
+      <c r="J55" s="29"/>
+      <c r="K55" s="29"/>
+      <c r="L55" s="29"/>
+      <c r="M55" s="29"/>
+      <c r="N55" s="29"/>
+      <c r="O55" s="29"/>
+      <c r="P55" s="29"/>
+      <c r="Q55" s="29"/>
+      <c r="R55" s="29"/>
+      <c r="S55" s="29"/>
+      <c r="T55" s="29"/>
+      <c r="U55" s="29"/>
+      <c r="V55" s="29"/>
+      <c r="W55" s="29"/>
+      <c r="X55" s="29"/>
+      <c r="Y55" s="29"/>
+      <c r="Z55" s="29"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="29" t="s">
+      <c r="A56" s="30" t="s">
         <v>350</v>
       </c>
-      <c r="B56" s="31">
+      <c r="B56" s="32">
         <v>5.71</v>
       </c>
-      <c r="C56" s="31">
+      <c r="C56" s="32">
         <v>4.27</v>
       </c>
-      <c r="D56" s="31">
+      <c r="D56" s="32">
         <v>19.47</v>
       </c>
-      <c r="E56" s="31">
+      <c r="E56" s="32">
         <v>11.33</v>
       </c>
-      <c r="F56" s="33"/>
-      <c r="G56" s="31">
+      <c r="F56" s="34"/>
+      <c r="G56" s="32">
         <v>9.18</v>
       </c>
-      <c r="H56" s="31">
+      <c r="H56" s="32">
         <v>12.31</v>
       </c>
-      <c r="I56" s="31">
+      <c r="I56" s="32">
         <v>9.87</v>
       </c>
-      <c r="J56" s="31">
+      <c r="J56" s="32">
         <v>5.31</v>
       </c>
-      <c r="K56" s="30">
+      <c r="K56" s="31">
         <v>322.07</v>
       </c>
-      <c r="L56" s="31">
+      <c r="L56" s="32">
         <v>46.67</v>
       </c>
-      <c r="M56" s="31">
+      <c r="M56" s="32">
         <v>35.44</v>
       </c>
-      <c r="N56" s="31">
+      <c r="N56" s="32">
         <v>10.06</v>
       </c>
-      <c r="O56" s="33"/>
-      <c r="P56" s="31">
+      <c r="O56" s="34"/>
+      <c r="P56" s="32">
         <v>7.86</v>
       </c>
-      <c r="Q56" s="31">
+      <c r="Q56" s="32">
         <v>6.38</v>
       </c>
-      <c r="R56" s="31">
+      <c r="R56" s="32">
         <v>6.63</v>
       </c>
-      <c r="S56" s="31">
+      <c r="S56" s="32">
         <v>15.58</v>
       </c>
-      <c r="T56" s="31">
+      <c r="T56" s="32">
         <v>3.55</v>
       </c>
-      <c r="U56" s="31">
+      <c r="U56" s="32">
         <v>10.5</v>
       </c>
-      <c r="V56" s="31">
+      <c r="V56" s="32">
         <v>3.84</v>
       </c>
-      <c r="W56" s="31">
+      <c r="W56" s="32">
         <v>3.68</v>
       </c>
-      <c r="X56" s="31">
+      <c r="X56" s="32">
         <v>6.39</v>
       </c>
-      <c r="Y56" s="31">
+      <c r="Y56" s="32">
         <v>7.74</v>
       </c>
-      <c r="Z56" s="31">
+      <c r="Z56" s="32">
         <v>19.84</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="29" t="s">
+      <c r="A57" s="30" t="s">
         <v>351</v>
       </c>
-      <c r="B57" s="31">
+      <c r="B57" s="32">
         <v>0.57</v>
       </c>
-      <c r="C57" s="31">
+      <c r="C57" s="32">
         <v>0.56</v>
       </c>
-      <c r="D57" s="31">
+      <c r="D57" s="32">
         <v>0.52</v>
       </c>
-      <c r="E57" s="31">
+      <c r="E57" s="32">
         <v>0.51</v>
       </c>
-      <c r="F57" s="31">
+      <c r="F57" s="32">
         <v>0.49</v>
       </c>
-      <c r="G57" s="31">
+      <c r="G57" s="32">
         <v>0.48</v>
       </c>
-      <c r="H57" s="31">
+      <c r="H57" s="32">
         <v>0.5</v>
       </c>
-      <c r="I57" s="31">
+      <c r="I57" s="32">
         <v>0.53</v>
       </c>
-      <c r="J57" s="31">
+      <c r="J57" s="32">
         <v>0.53</v>
       </c>
-      <c r="K57" s="31">
+      <c r="K57" s="32">
         <v>0.55</v>
       </c>
-      <c r="L57" s="31">
+      <c r="L57" s="32">
         <v>0.58</v>
       </c>
-      <c r="M57" s="31">
+      <c r="M57" s="32">
         <v>0.58</v>
       </c>
-      <c r="N57" s="31">
+      <c r="N57" s="32">
         <v>0.55</v>
       </c>
-      <c r="O57" s="31">
+      <c r="O57" s="32">
         <v>0.61</v>
       </c>
-      <c r="P57" s="31">
+      <c r="P57" s="32">
         <v>0.65</v>
       </c>
-      <c r="Q57" s="31">
+      <c r="Q57" s="32">
         <v>0.67</v>
       </c>
-      <c r="R57" s="31">
+      <c r="R57" s="32">
         <v>0.66</v>
       </c>
-      <c r="S57" s="31">
+      <c r="S57" s="32">
         <v>0.69</v>
       </c>
-      <c r="T57" s="31">
+      <c r="T57" s="32">
         <v>0.62</v>
       </c>
-      <c r="U57" s="31">
+      <c r="U57" s="32">
         <v>0.55</v>
       </c>
-      <c r="V57" s="31">
+      <c r="V57" s="32">
         <v>0.46</v>
       </c>
-      <c r="W57" s="33"/>
-      <c r="X57" s="33"/>
-      <c r="Y57" s="33"/>
-      <c r="Z57" s="33"/>
+      <c r="W57" s="34"/>
+      <c r="X57" s="34"/>
+      <c r="Y57" s="34"/>
+      <c r="Z57" s="34"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="27" t="s">
+      <c r="A58" s="28" t="s">
         <v>352</v>
       </c>
-      <c r="B58" s="28"/>
-      <c r="C58" s="28"/>
-      <c r="D58" s="28"/>
-      <c r="E58" s="28"/>
-      <c r="F58" s="28"/>
-      <c r="G58" s="28"/>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
-      <c r="K58" s="28"/>
-      <c r="L58" s="28"/>
-      <c r="M58" s="28"/>
-      <c r="N58" s="28"/>
-      <c r="O58" s="28"/>
-      <c r="P58" s="28"/>
-      <c r="Q58" s="28"/>
-      <c r="R58" s="28"/>
-      <c r="S58" s="28"/>
-      <c r="T58" s="28"/>
-      <c r="U58" s="28"/>
-      <c r="V58" s="28"/>
-      <c r="W58" s="28"/>
-      <c r="X58" s="28"/>
-      <c r="Y58" s="28"/>
-      <c r="Z58" s="28"/>
+      <c r="B58" s="29"/>
+      <c r="C58" s="29"/>
+      <c r="D58" s="29"/>
+      <c r="E58" s="29"/>
+      <c r="F58" s="29"/>
+      <c r="G58" s="29"/>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29"/>
+      <c r="J58" s="29"/>
+      <c r="K58" s="29"/>
+      <c r="L58" s="29"/>
+      <c r="M58" s="29"/>
+      <c r="N58" s="29"/>
+      <c r="O58" s="29"/>
+      <c r="P58" s="29"/>
+      <c r="Q58" s="29"/>
+      <c r="R58" s="29"/>
+      <c r="S58" s="29"/>
+      <c r="T58" s="29"/>
+      <c r="U58" s="29"/>
+      <c r="V58" s="29"/>
+      <c r="W58" s="29"/>
+      <c r="X58" s="29"/>
+      <c r="Y58" s="29"/>
+      <c r="Z58" s="29"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="29" t="s">
+      <c r="A59" s="30" t="s">
         <v>353</v>
       </c>
-      <c r="B59" s="31">
+      <c r="B59" s="32">
         <v>0.03</v>
       </c>
-      <c r="C59" s="31">
+      <c r="C59" s="32">
         <v>0.5</v>
       </c>
-      <c r="D59" s="31">
+      <c r="D59" s="32">
         <v>0.01</v>
       </c>
-      <c r="E59" s="33"/>
-      <c r="F59" s="33"/>
-      <c r="G59" s="32">
+      <c r="E59" s="34"/>
+      <c r="F59" s="34"/>
+      <c r="G59" s="33">
         <v>-0.39</v>
       </c>
-      <c r="H59" s="32">
+      <c r="H59" s="33">
         <v>-0.16</v>
       </c>
-      <c r="I59" s="32">
+      <c r="I59" s="33">
         <v>-0.17</v>
       </c>
-      <c r="J59" s="31">
+      <c r="J59" s="32">
         <v>0.74</v>
       </c>
-      <c r="K59" s="31">
+      <c r="K59" s="32">
         <v>0.02</v>
       </c>
-      <c r="L59" s="31">
+      <c r="L59" s="32">
         <v>0.01</v>
       </c>
-      <c r="M59" s="32">
+      <c r="M59" s="33">
         <v>-0.5</v>
       </c>
-      <c r="N59" s="31">
+      <c r="N59" s="32">
         <v>0.03</v>
       </c>
-      <c r="O59" s="33"/>
-      <c r="P59" s="32">
+      <c r="O59" s="34"/>
+      <c r="P59" s="33">
         <v>-0.56</v>
       </c>
-      <c r="Q59" s="31">
+      <c r="Q59" s="32">
         <v>0.05</v>
       </c>
-      <c r="R59" s="32">
+      <c r="R59" s="33">
         <v>-2.45</v>
       </c>
-      <c r="S59" s="32">
+      <c r="S59" s="33">
         <v>-0.2</v>
       </c>
-      <c r="T59" s="31">
+      <c r="T59" s="32">
         <v>0.01</v>
       </c>
-      <c r="U59" s="32">
+      <c r="U59" s="33">
         <v>-0.22</v>
       </c>
-      <c r="V59" s="31">
+      <c r="V59" s="32">
         <v>0.1</v>
       </c>
-      <c r="W59" s="31">
+      <c r="W59" s="32">
         <v>0.03</v>
       </c>
-      <c r="X59" s="31">
+      <c r="X59" s="32">
         <v>0.3</v>
       </c>
-      <c r="Y59" s="31">
+      <c r="Y59" s="32">
         <v>0.06</v>
       </c>
-      <c r="Z59" s="33"/>
+      <c r="Z59" s="34"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="29" t="s">
+      <c r="A60" s="30" t="s">
         <v>354</v>
       </c>
-      <c r="B60" s="31">
+      <c r="B60" s="32">
         <v>0.32</v>
       </c>
-      <c r="C60" s="31">
+      <c r="C60" s="32">
         <v>3.33</v>
       </c>
-      <c r="D60" s="32">
+      <c r="D60" s="33">
         <v>-2.72</v>
       </c>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="32">
+      <c r="E60" s="34"/>
+      <c r="F60" s="34"/>
+      <c r="G60" s="33">
         <v>-0.46</v>
       </c>
-      <c r="H60" s="31">
+      <c r="H60" s="32">
         <v>0.07</v>
       </c>
-      <c r="I60" s="31">
+      <c r="I60" s="32">
         <v>0.1</v>
       </c>
-      <c r="J60" s="33"/>
-      <c r="K60" s="31">
+      <c r="J60" s="34"/>
+      <c r="K60" s="32">
         <v>0.19</v>
       </c>
-      <c r="L60" s="31">
+      <c r="L60" s="32">
         <v>1.43</v>
       </c>
-      <c r="M60" s="32">
+      <c r="M60" s="33">
         <v>-0.6</v>
       </c>
-      <c r="N60" s="31">
+      <c r="N60" s="32">
         <v>21.87</v>
       </c>
-      <c r="O60" s="33"/>
-      <c r="P60" s="31">
+      <c r="O60" s="34"/>
+      <c r="P60" s="32">
         <v>0.82</v>
       </c>
-      <c r="Q60" s="32">
+      <c r="Q60" s="33">
         <v>-2.58</v>
       </c>
-      <c r="R60" s="32">
+      <c r="R60" s="33">
         <v>-0.53</v>
       </c>
-      <c r="S60" s="31">
+      <c r="S60" s="32">
         <v>1.18</v>
       </c>
-      <c r="T60" s="31">
+      <c r="T60" s="32">
         <v>0.1</v>
       </c>
-      <c r="U60" s="31">
+      <c r="U60" s="32">
         <v>0.17</v>
       </c>
-      <c r="V60" s="33"/>
-      <c r="W60" s="33"/>
-      <c r="X60" s="33"/>
-      <c r="Y60" s="33"/>
-      <c r="Z60" s="33"/>
+      <c r="V60" s="34"/>
+      <c r="W60" s="34"/>
+      <c r="X60" s="34"/>
+      <c r="Y60" s="34"/>
+      <c r="Z60" s="34"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="27" t="s">
+      <c r="A61" s="28" t="s">
         <v>355</v>
       </c>
-      <c r="B61" s="28"/>
-      <c r="C61" s="28"/>
-      <c r="D61" s="28"/>
-      <c r="E61" s="28"/>
-      <c r="F61" s="28"/>
-      <c r="G61" s="28"/>
-      <c r="H61" s="28"/>
-      <c r="I61" s="28"/>
-      <c r="J61" s="28"/>
-      <c r="K61" s="28"/>
-      <c r="L61" s="28"/>
-      <c r="M61" s="28"/>
-      <c r="N61" s="28"/>
-      <c r="O61" s="28"/>
-      <c r="P61" s="28"/>
-      <c r="Q61" s="28"/>
-      <c r="R61" s="28"/>
-      <c r="S61" s="28"/>
-      <c r="T61" s="28"/>
-      <c r="U61" s="28"/>
-      <c r="V61" s="28"/>
-      <c r="W61" s="28"/>
-      <c r="X61" s="28"/>
-      <c r="Y61" s="28"/>
-      <c r="Z61" s="28"/>
+      <c r="B61" s="29"/>
+      <c r="C61" s="29"/>
+      <c r="D61" s="29"/>
+      <c r="E61" s="29"/>
+      <c r="F61" s="29"/>
+      <c r="G61" s="29"/>
+      <c r="H61" s="29"/>
+      <c r="I61" s="29"/>
+      <c r="J61" s="29"/>
+      <c r="K61" s="29"/>
+      <c r="L61" s="29"/>
+      <c r="M61" s="29"/>
+      <c r="N61" s="29"/>
+      <c r="O61" s="29"/>
+      <c r="P61" s="29"/>
+      <c r="Q61" s="29"/>
+      <c r="R61" s="29"/>
+      <c r="S61" s="29"/>
+      <c r="T61" s="29"/>
+      <c r="U61" s="29"/>
+      <c r="V61" s="29"/>
+      <c r="W61" s="29"/>
+      <c r="X61" s="29"/>
+      <c r="Y61" s="29"/>
+      <c r="Z61" s="29"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="29" t="s">
+      <c r="A62" s="30" t="s">
         <v>356</v>
       </c>
-      <c r="B62" s="31">
+      <c r="B62" s="32">
         <v>6.67</v>
       </c>
-      <c r="C62" s="31">
+      <c r="C62" s="32">
         <v>4.22</v>
       </c>
-      <c r="D62" s="31">
+      <c r="D62" s="32">
         <v>4.13</v>
       </c>
-      <c r="E62" s="31">
+      <c r="E62" s="32">
         <v>2.66</v>
       </c>
-      <c r="F62" s="31">
+      <c r="F62" s="32">
         <v>4.44</v>
       </c>
-      <c r="G62" s="31">
+      <c r="G62" s="32">
         <v>7.64</v>
       </c>
-      <c r="H62" s="31">
+      <c r="H62" s="32">
         <v>6.93</v>
       </c>
-      <c r="I62" s="31">
+      <c r="I62" s="32">
         <v>7.56</v>
       </c>
-      <c r="J62" s="31">
+      <c r="J62" s="32">
         <v>9.65</v>
       </c>
-      <c r="K62" s="31">
+      <c r="K62" s="32">
         <v>13.73</v>
       </c>
-      <c r="L62" s="31">
+      <c r="L62" s="32">
         <v>6.14</v>
       </c>
-      <c r="M62" s="31">
+      <c r="M62" s="32">
         <v>4.45</v>
       </c>
-      <c r="N62" s="31">
+      <c r="N62" s="32">
         <v>2.48</v>
       </c>
-      <c r="O62" s="31">
+      <c r="O62" s="32">
         <v>2.73</v>
       </c>
-      <c r="P62" s="31">
+      <c r="P62" s="32">
         <v>1.23</v>
       </c>
-      <c r="Q62" s="31">
+      <c r="Q62" s="32">
         <v>1.21</v>
       </c>
-      <c r="R62" s="32">
+      <c r="R62" s="33">
         <v>-0.05</v>
       </c>
-      <c r="S62" s="31">
+      <c r="S62" s="32">
         <v>2.69</v>
       </c>
-      <c r="T62" s="31">
+      <c r="T62" s="32">
         <v>1.48</v>
       </c>
-      <c r="U62" s="31">
+      <c r="U62" s="32">
         <v>3.1</v>
       </c>
-      <c r="V62" s="31">
+      <c r="V62" s="32">
         <v>2.28</v>
       </c>
-      <c r="W62" s="31">
+      <c r="W62" s="32">
         <v>2.21</v>
       </c>
-      <c r="X62" s="31">
+      <c r="X62" s="32">
         <v>2.82</v>
       </c>
-      <c r="Y62" s="31">
+      <c r="Y62" s="32">
         <v>3.25</v>
       </c>
-      <c r="Z62" s="31">
+      <c r="Z62" s="32">
         <v>1.29</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="29" t="s">
+      <c r="A63" s="30" t="s">
         <v>357</v>
       </c>
-      <c r="B63" s="31">
+      <c r="B63" s="32">
         <v>4.46</v>
       </c>
-      <c r="C63" s="31">
+      <c r="C63" s="32">
         <v>4.78</v>
       </c>
-      <c r="D63" s="31">
+      <c r="D63" s="32">
         <v>5.25</v>
       </c>
-      <c r="E63" s="31">
+      <c r="E63" s="32">
         <v>5.76</v>
       </c>
-      <c r="F63" s="31">
+      <c r="F63" s="32">
         <v>6.86</v>
       </c>
-      <c r="G63" s="31">
+      <c r="G63" s="32">
         <v>7.92</v>
       </c>
-      <c r="H63" s="31">
+      <c r="H63" s="32">
         <v>8.02</v>
       </c>
-      <c r="I63" s="31">
+      <c r="I63" s="32">
         <v>8.55</v>
       </c>
-      <c r="J63" s="31">
+      <c r="J63" s="32">
         <v>8.92</v>
       </c>
-      <c r="K63" s="31">
+      <c r="K63" s="32">
         <v>7.44</v>
       </c>
-      <c r="L63" s="31">
+      <c r="L63" s="32">
         <v>3.47</v>
       </c>
-      <c r="M63" s="31">
+      <c r="M63" s="32">
         <v>2.38</v>
       </c>
-      <c r="N63" s="31">
+      <c r="N63" s="32">
         <v>1.46</v>
       </c>
-      <c r="O63" s="31">
+      <c r="O63" s="32">
         <v>1.52</v>
       </c>
-      <c r="P63" s="31">
+      <c r="P63" s="32">
         <v>1.33</v>
       </c>
-      <c r="Q63" s="31">
+      <c r="Q63" s="32">
         <v>1.68</v>
       </c>
-      <c r="R63" s="31">
+      <c r="R63" s="32">
         <v>1.87</v>
       </c>
-      <c r="S63" s="31">
+      <c r="S63" s="32">
         <v>2.25</v>
       </c>
-      <c r="T63" s="31">
+      <c r="T63" s="32">
         <v>2.26</v>
       </c>
-      <c r="U63" s="31">
+      <c r="U63" s="32">
         <v>2.69</v>
       </c>
-      <c r="V63" s="31">
+      <c r="V63" s="32">
         <v>2.25</v>
       </c>
-      <c r="W63" s="33"/>
-      <c r="X63" s="33"/>
-      <c r="Y63" s="33"/>
-      <c r="Z63" s="33"/>
+      <c r="W63" s="34"/>
+      <c r="X63" s="34"/>
+      <c r="Y63" s="34"/>
+      <c r="Z63" s="34"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="27" t="s">
+      <c r="A64" s="28" t="s">
         <v>358</v>
       </c>
-      <c r="B64" s="28"/>
-      <c r="C64" s="28"/>
-      <c r="D64" s="28"/>
-      <c r="E64" s="28"/>
-      <c r="F64" s="28"/>
-      <c r="G64" s="28"/>
-      <c r="H64" s="28"/>
-      <c r="I64" s="28"/>
-      <c r="J64" s="28"/>
-      <c r="K64" s="28"/>
-      <c r="L64" s="28"/>
-      <c r="M64" s="28"/>
-      <c r="N64" s="28"/>
-      <c r="O64" s="28"/>
-      <c r="P64" s="28"/>
-      <c r="Q64" s="28"/>
-      <c r="R64" s="28"/>
-      <c r="S64" s="28"/>
-      <c r="T64" s="28"/>
-      <c r="U64" s="28"/>
-      <c r="V64" s="28"/>
-      <c r="W64" s="28"/>
-      <c r="X64" s="28"/>
-      <c r="Y64" s="28"/>
-      <c r="Z64" s="28"/>
+      <c r="B64" s="29"/>
+      <c r="C64" s="29"/>
+      <c r="D64" s="29"/>
+      <c r="E64" s="29"/>
+      <c r="F64" s="29"/>
+      <c r="G64" s="29"/>
+      <c r="H64" s="29"/>
+      <c r="I64" s="29"/>
+      <c r="J64" s="29"/>
+      <c r="K64" s="29"/>
+      <c r="L64" s="29"/>
+      <c r="M64" s="29"/>
+      <c r="N64" s="29"/>
+      <c r="O64" s="29"/>
+      <c r="P64" s="29"/>
+      <c r="Q64" s="29"/>
+      <c r="R64" s="29"/>
+      <c r="S64" s="29"/>
+      <c r="T64" s="29"/>
+      <c r="U64" s="29"/>
+      <c r="V64" s="29"/>
+      <c r="W64" s="29"/>
+      <c r="X64" s="29"/>
+      <c r="Y64" s="29"/>
+      <c r="Z64" s="29"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="29" t="s">
+      <c r="A65" s="30" t="s">
         <v>359</v>
       </c>
-      <c r="B65" s="31">
+      <c r="B65" s="32">
         <v>23.84</v>
       </c>
-      <c r="C65" s="31">
+      <c r="C65" s="32">
         <v>32.98</v>
       </c>
-      <c r="D65" s="31">
+      <c r="D65" s="32">
         <v>15.43</v>
       </c>
-      <c r="E65" s="31">
+      <c r="E65" s="32">
         <v>9.94</v>
       </c>
-      <c r="F65" s="31">
+      <c r="F65" s="32">
         <v>12.9</v>
       </c>
-      <c r="G65" s="31">
+      <c r="G65" s="32">
         <v>16.47</v>
       </c>
-      <c r="H65" s="31">
+      <c r="H65" s="32">
         <v>16.97</v>
       </c>
-      <c r="I65" s="31">
+      <c r="I65" s="32">
         <v>21.01</v>
       </c>
-      <c r="J65" s="31">
+      <c r="J65" s="32">
         <v>22.51</v>
       </c>
-      <c r="K65" s="31">
+      <c r="K65" s="32">
         <v>22.75</v>
       </c>
-      <c r="L65" s="31">
+      <c r="L65" s="32">
         <v>29.97</v>
       </c>
-      <c r="M65" s="31">
+      <c r="M65" s="32">
         <v>13.85</v>
       </c>
-      <c r="N65" s="31">
+      <c r="N65" s="32">
         <v>6.64</v>
       </c>
-      <c r="O65" s="31">
+      <c r="O65" s="32">
         <v>8.65</v>
       </c>
-      <c r="P65" s="31">
+      <c r="P65" s="32">
         <v>2.88</v>
       </c>
-      <c r="Q65" s="31">
+      <c r="Q65" s="32">
         <v>2.2</v>
       </c>
-      <c r="R65" s="32">
+      <c r="R65" s="33">
         <v>-0.08</v>
       </c>
-      <c r="S65" s="31">
+      <c r="S65" s="32">
         <v>4.86</v>
       </c>
-      <c r="T65" s="31">
+      <c r="T65" s="32">
         <v>1.95</v>
       </c>
-      <c r="U65" s="31">
+      <c r="U65" s="32">
         <v>5.01</v>
       </c>
-      <c r="V65" s="31">
+      <c r="V65" s="32">
         <v>3.06</v>
       </c>
-      <c r="W65" s="31">
+      <c r="W65" s="32">
         <v>3.18</v>
       </c>
-      <c r="X65" s="31">
+      <c r="X65" s="32">
         <v>4.74</v>
       </c>
-      <c r="Y65" s="31">
+      <c r="Y65" s="32">
         <v>5.93</v>
       </c>
-      <c r="Z65" s="31">
+      <c r="Z65" s="32">
         <v>4.83</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="29" t="s">
+      <c r="A66" s="30" t="s">
         <v>360</v>
       </c>
-      <c r="B66" s="31">
+      <c r="B66" s="32">
         <v>16.84</v>
       </c>
-      <c r="C66" s="31">
+      <c r="C66" s="32">
         <v>15.31</v>
       </c>
-      <c r="D66" s="31">
+      <c r="D66" s="32">
         <v>14.72</v>
       </c>
-      <c r="E66" s="31">
+      <c r="E66" s="32">
         <v>15.49</v>
       </c>
-      <c r="F66" s="31">
+      <c r="F66" s="32">
         <v>17.03</v>
       </c>
-      <c r="G66" s="31">
+      <c r="G66" s="32">
         <v>18.42</v>
       </c>
-      <c r="H66" s="31">
+      <c r="H66" s="32">
         <v>19.92</v>
       </c>
-      <c r="I66" s="31">
+      <c r="I66" s="32">
         <v>21.7</v>
       </c>
-      <c r="J66" s="31">
+      <c r="J66" s="32">
         <v>20.98</v>
       </c>
-      <c r="K66" s="31">
+      <c r="K66" s="32">
         <v>18.32</v>
       </c>
-      <c r="L66" s="31">
+      <c r="L66" s="32">
         <v>10.64</v>
       </c>
-      <c r="M66" s="31">
+      <c r="M66" s="32">
         <v>5.93</v>
       </c>
-      <c r="N66" s="31">
+      <c r="N66" s="32">
         <v>3.23</v>
       </c>
-      <c r="O66" s="31">
+      <c r="O66" s="32">
         <v>3.11</v>
       </c>
-      <c r="P66" s="31">
+      <c r="P66" s="32">
         <v>2.22</v>
       </c>
-      <c r="Q66" s="31">
+      <c r="Q66" s="32">
         <v>2.67</v>
       </c>
-      <c r="R66" s="31">
+      <c r="R66" s="32">
         <v>2.81</v>
       </c>
-      <c r="S66" s="31">
+      <c r="S66" s="32">
         <v>3.27</v>
       </c>
-      <c r="T66" s="31">
+      <c r="T66" s="32">
         <v>3.25</v>
       </c>
-      <c r="U66" s="31">
+      <c r="U66" s="32">
         <v>4.14</v>
       </c>
-      <c r="V66" s="31">
+      <c r="V66" s="32">
         <v>4.01</v>
       </c>
-      <c r="W66" s="33"/>
-      <c r="X66" s="33"/>
-      <c r="Y66" s="33"/>
-      <c r="Z66" s="33"/>
+      <c r="W66" s="34"/>
+      <c r="X66" s="34"/>
+      <c r="Y66" s="34"/>
+      <c r="Z66" s="34"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="27" t="s">
+      <c r="A67" s="28" t="s">
         <v>361</v>
       </c>
-      <c r="B67" s="28"/>
-      <c r="C67" s="28"/>
-      <c r="D67" s="28"/>
-      <c r="E67" s="28"/>
-      <c r="F67" s="28"/>
-      <c r="G67" s="28"/>
-      <c r="H67" s="28"/>
-      <c r="I67" s="28"/>
-      <c r="J67" s="28"/>
-      <c r="K67" s="28"/>
-      <c r="L67" s="28"/>
-      <c r="M67" s="28"/>
-      <c r="N67" s="28"/>
-      <c r="O67" s="28"/>
-      <c r="P67" s="28"/>
-      <c r="Q67" s="28"/>
-      <c r="R67" s="28"/>
-      <c r="S67" s="28"/>
-      <c r="T67" s="28"/>
-      <c r="U67" s="28"/>
-      <c r="V67" s="28"/>
-      <c r="W67" s="28"/>
-      <c r="X67" s="28"/>
-      <c r="Y67" s="28"/>
-      <c r="Z67" s="28"/>
+      <c r="B67" s="29"/>
+      <c r="C67" s="29"/>
+      <c r="D67" s="29"/>
+      <c r="E67" s="29"/>
+      <c r="F67" s="29"/>
+      <c r="G67" s="29"/>
+      <c r="H67" s="29"/>
+      <c r="I67" s="29"/>
+      <c r="J67" s="29"/>
+      <c r="K67" s="29"/>
+      <c r="L67" s="29"/>
+      <c r="M67" s="29"/>
+      <c r="N67" s="29"/>
+      <c r="O67" s="29"/>
+      <c r="P67" s="29"/>
+      <c r="Q67" s="29"/>
+      <c r="R67" s="29"/>
+      <c r="S67" s="29"/>
+      <c r="T67" s="29"/>
+      <c r="U67" s="29"/>
+      <c r="V67" s="29"/>
+      <c r="W67" s="29"/>
+      <c r="X67" s="29"/>
+      <c r="Y67" s="29"/>
+      <c r="Z67" s="29"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="29" t="s">
+      <c r="A68" s="30" t="s">
         <v>362</v>
       </c>
-      <c r="B68" s="31">
+      <c r="B68" s="32">
         <v>32.94</v>
       </c>
-      <c r="C68" s="30">
+      <c r="C68" s="31">
         <v>352.7</v>
       </c>
-      <c r="D68" s="30">
+      <c r="D68" s="31">
         <v>111.44</v>
       </c>
-      <c r="E68" s="31">
+      <c r="E68" s="32">
         <v>12.1</v>
       </c>
-      <c r="F68" s="31">
+      <c r="F68" s="32">
         <v>15.07</v>
       </c>
-      <c r="G68" s="31">
+      <c r="G68" s="32">
         <v>63.52</v>
       </c>
-      <c r="H68" s="31">
+      <c r="H68" s="32">
         <v>41.84</v>
       </c>
-      <c r="I68" s="31">
+      <c r="I68" s="32">
         <v>33.66</v>
       </c>
-      <c r="J68" s="31">
+      <c r="J68" s="32">
         <v>46.79</v>
       </c>
-      <c r="K68" s="31">
+      <c r="K68" s="32">
         <v>42.3</v>
       </c>
-      <c r="L68" s="30">
+      <c r="L68" s="31">
         <v>624.41</v>
       </c>
-      <c r="M68" s="31">
+      <c r="M68" s="32">
         <v>13.83</v>
       </c>
-      <c r="N68" s="31">
+      <c r="N68" s="32">
         <v>7.55</v>
       </c>
-      <c r="O68" s="31">
+      <c r="O68" s="32">
         <v>23.35</v>
       </c>
-      <c r="P68" s="31">
+      <c r="P68" s="32">
         <v>2.31</v>
       </c>
-      <c r="Q68" s="31">
+      <c r="Q68" s="32">
         <v>2.4</v>
       </c>
-      <c r="R68" s="32">
+      <c r="R68" s="33">
         <v>-0.08</v>
       </c>
-      <c r="S68" s="31">
+      <c r="S68" s="32">
         <v>5.58</v>
       </c>
-      <c r="T68" s="31">
+      <c r="T68" s="32">
         <v>4.61</v>
       </c>
-      <c r="U68" s="31">
+      <c r="U68" s="32">
         <v>4.66</v>
       </c>
-      <c r="V68" s="31">
+      <c r="V68" s="32">
         <v>2.97</v>
       </c>
-      <c r="W68" s="31">
+      <c r="W68" s="32">
         <v>3.44</v>
       </c>
-      <c r="X68" s="31">
+      <c r="X68" s="32">
         <v>7.19</v>
       </c>
-      <c r="Y68" s="31">
+      <c r="Y68" s="32">
         <v>11.16</v>
       </c>
-      <c r="Z68" s="33"/>
+      <c r="Z68" s="34"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="29" t="s">
+      <c r="A69" s="30" t="s">
         <v>363</v>
       </c>
-      <c r="B69" s="31">
+      <c r="B69" s="32">
         <v>30.08</v>
       </c>
-      <c r="C69" s="31">
+      <c r="C69" s="32">
         <v>36.99</v>
       </c>
-      <c r="D69" s="31">
+      <c r="D69" s="32">
         <v>34.29</v>
       </c>
-      <c r="E69" s="31">
+      <c r="E69" s="32">
         <v>28.65</v>
       </c>
-      <c r="F69" s="31">
+      <c r="F69" s="32">
         <v>34.84</v>
       </c>
-      <c r="G69" s="31">
+      <c r="G69" s="32">
         <v>45.88</v>
       </c>
-      <c r="H69" s="31">
+      <c r="H69" s="32">
         <v>40.79</v>
       </c>
-      <c r="I69" s="31">
+      <c r="I69" s="32">
         <v>38.21</v>
       </c>
-      <c r="J69" s="31">
+      <c r="J69" s="32">
         <v>38.26</v>
       </c>
-      <c r="K69" s="31">
+      <c r="K69" s="32">
         <v>31.48</v>
       </c>
-      <c r="L69" s="31">
+      <c r="L69" s="32">
         <v>13.35</v>
       </c>
-      <c r="M69" s="31">
+      <c r="M69" s="32">
         <v>6.45</v>
       </c>
-      <c r="N69" s="31">
+      <c r="N69" s="32">
         <v>3.49</v>
       </c>
-      <c r="O69" s="31">
+      <c r="O69" s="32">
         <v>3.38</v>
       </c>
-      <c r="P69" s="31">
+      <c r="P69" s="32">
         <v>2.9</v>
       </c>
-      <c r="Q69" s="31">
+      <c r="Q69" s="32">
         <v>3.46</v>
       </c>
-      <c r="R69" s="31">
+      <c r="R69" s="32">
         <v>3.49</v>
       </c>
-      <c r="S69" s="31">
+      <c r="S69" s="32">
         <v>4.08</v>
       </c>
-      <c r="T69" s="31">
+      <c r="T69" s="32">
         <v>4.19</v>
       </c>
-      <c r="U69" s="31">
+      <c r="U69" s="32">
         <v>4.64</v>
       </c>
-      <c r="V69" s="31">
+      <c r="V69" s="32">
         <v>6.12</v>
       </c>
-      <c r="W69" s="33"/>
-      <c r="X69" s="33"/>
-      <c r="Y69" s="33"/>
-      <c r="Z69" s="33"/>
+      <c r="W69" s="34"/>
+      <c r="X69" s="34"/>
+      <c r="Y69" s="34"/>
+      <c r="Z69" s="34"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="27" t="s">
+      <c r="A70" s="28" t="s">
         <v>364</v>
       </c>
-      <c r="B70" s="28"/>
-      <c r="C70" s="28"/>
-      <c r="D70" s="28"/>
-      <c r="E70" s="28"/>
-      <c r="F70" s="28"/>
-      <c r="G70" s="28"/>
-      <c r="H70" s="28"/>
-      <c r="I70" s="28"/>
-      <c r="J70" s="28"/>
-      <c r="K70" s="28"/>
-      <c r="L70" s="28"/>
-      <c r="M70" s="28"/>
-      <c r="N70" s="28"/>
-      <c r="O70" s="28"/>
-      <c r="P70" s="28"/>
-      <c r="Q70" s="28"/>
-      <c r="R70" s="28"/>
-      <c r="S70" s="28"/>
-      <c r="T70" s="28"/>
-      <c r="U70" s="28"/>
-      <c r="V70" s="28"/>
-      <c r="W70" s="28"/>
-      <c r="X70" s="28"/>
-      <c r="Y70" s="28"/>
-      <c r="Z70" s="28"/>
+      <c r="B70" s="29"/>
+      <c r="C70" s="29"/>
+      <c r="D70" s="29"/>
+      <c r="E70" s="29"/>
+      <c r="F70" s="29"/>
+      <c r="G70" s="29"/>
+      <c r="H70" s="29"/>
+      <c r="I70" s="29"/>
+      <c r="J70" s="29"/>
+      <c r="K70" s="29"/>
+      <c r="L70" s="29"/>
+      <c r="M70" s="29"/>
+      <c r="N70" s="29"/>
+      <c r="O70" s="29"/>
+      <c r="P70" s="29"/>
+      <c r="Q70" s="29"/>
+      <c r="R70" s="29"/>
+      <c r="S70" s="29"/>
+      <c r="T70" s="29"/>
+      <c r="U70" s="29"/>
+      <c r="V70" s="29"/>
+      <c r="W70" s="29"/>
+      <c r="X70" s="29"/>
+      <c r="Y70" s="29"/>
+      <c r="Z70" s="29"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="29" t="s">
+      <c r="A71" s="30" t="s">
         <v>365</v>
       </c>
-      <c r="B71" s="31">
+      <c r="B71" s="32">
         <v>32.94</v>
       </c>
-      <c r="C71" s="33"/>
-      <c r="D71" s="30">
+      <c r="C71" s="34"/>
+      <c r="D71" s="31">
         <v>121.6</v>
       </c>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="30">
+      <c r="E71" s="34"/>
+      <c r="F71" s="34"/>
+      <c r="G71" s="34"/>
+      <c r="H71" s="34"/>
+      <c r="I71" s="31">
         <v>518.44</v>
       </c>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="30">
+      <c r="J71" s="34"/>
+      <c r="K71" s="34"/>
+      <c r="L71" s="31">
         <v>624.41</v>
       </c>
-      <c r="M71" s="33"/>
-      <c r="N71" s="33"/>
-      <c r="O71" s="33"/>
-      <c r="P71" s="33"/>
-      <c r="Q71" s="31">
+      <c r="M71" s="34"/>
+      <c r="N71" s="34"/>
+      <c r="O71" s="34"/>
+      <c r="P71" s="34"/>
+      <c r="Q71" s="32">
         <v>2.4</v>
       </c>
-      <c r="R71" s="32">
+      <c r="R71" s="33">
         <v>-0.09</v>
       </c>
-      <c r="S71" s="31">
+      <c r="S71" s="32">
         <v>5.58</v>
       </c>
-      <c r="T71" s="31">
+      <c r="T71" s="32">
         <v>4.61</v>
       </c>
-      <c r="U71" s="31">
+      <c r="U71" s="32">
         <v>4.84</v>
       </c>
-      <c r="V71" s="31">
+      <c r="V71" s="32">
         <v>3.2</v>
       </c>
-      <c r="W71" s="31">
+      <c r="W71" s="32">
         <v>3.48</v>
       </c>
-      <c r="X71" s="31">
+      <c r="X71" s="32">
         <v>7.31</v>
       </c>
-      <c r="Y71" s="31">
+      <c r="Y71" s="32">
         <v>11.59</v>
       </c>
-      <c r="Z71" s="33"/>
+      <c r="Z71" s="34"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="29" t="s">
+      <c r="A72" s="30" t="s">
         <v>366</v>
       </c>
-      <c r="B72" s="33"/>
-      <c r="C72" s="33"/>
-      <c r="D72" s="33"/>
-      <c r="E72" s="33"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="33"/>
-      <c r="J72" s="33"/>
-      <c r="K72" s="33"/>
-      <c r="L72" s="33"/>
-      <c r="M72" s="33"/>
-      <c r="N72" s="33"/>
-      <c r="O72" s="33"/>
-      <c r="P72" s="31">
+      <c r="B72" s="34"/>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="34"/>
+      <c r="M72" s="34"/>
+      <c r="N72" s="34"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="32">
         <v>3.71</v>
       </c>
-      <c r="Q72" s="31">
+      <c r="Q72" s="32">
         <v>3.51</v>
       </c>
-      <c r="R72" s="31">
+      <c r="R72" s="32">
         <v>3.61</v>
       </c>
-      <c r="S72" s="31">
+      <c r="S72" s="32">
         <v>4.2</v>
       </c>
-      <c r="T72" s="31">
+      <c r="T72" s="32">
         <v>4.33</v>
       </c>
-      <c r="U72" s="31">
+      <c r="U72" s="32">
         <v>4.83</v>
       </c>
-      <c r="V72" s="31">
+      <c r="V72" s="32">
         <v>7.06</v>
       </c>
-      <c r="W72" s="33"/>
-      <c r="X72" s="33"/>
-      <c r="Y72" s="33"/>
-      <c r="Z72" s="33"/>
+      <c r="W72" s="34"/>
+      <c r="X72" s="34"/>
+      <c r="Y72" s="34"/>
+      <c r="Z72" s="34"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/hex_xlsx/INVEST.HE.xlsx
+++ b/data/hex_xlsx/INVEST.HE.xlsx
@@ -1251,7 +1251,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="38">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1332,6 +1332,9 @@
     </xf>
     <xf borderId="3" fillId="0" fontId="7" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
@@ -10235,21 +10238,56 @@
       <c r="N42" s="15">
         <v>44.17</v>
       </c>
-      <c r="O42" s="16"/>
-      <c r="P42" s="16">
-        <v>0.0</v>
-      </c>
-      <c r="Q42" s="16"/>
-      <c r="R42" s="16"/>
-      <c r="S42" s="16"/>
-      <c r="T42" s="16"/>
-      <c r="U42" s="16"/>
-      <c r="V42" s="16"/>
-      <c r="W42" s="16"/>
-      <c r="X42" s="16"/>
-      <c r="Y42" s="16"/>
-      <c r="Z42" s="16"/>
-      <c r="AA42" s="16"/>
+      <c r="O42" s="15">
+        <f t="shared" ref="O42:R42" si="1">SUM(O40,O35)</f>
+        <v>30.51</v>
+      </c>
+      <c r="P42" s="15">
+        <f t="shared" si="1"/>
+        <v>29.51</v>
+      </c>
+      <c r="Q42" s="15">
+        <f t="shared" si="1"/>
+        <v>21.13</v>
+      </c>
+      <c r="R42" s="15">
+        <f t="shared" si="1"/>
+        <v>20.14</v>
+      </c>
+      <c r="S42" s="27">
+        <v>24.79</v>
+      </c>
+      <c r="T42" s="15">
+        <f t="shared" ref="T42:U42" si="2">SUM(T40,T35)</f>
+        <v>21.15</v>
+      </c>
+      <c r="U42" s="15">
+        <f t="shared" si="2"/>
+        <v>22.95</v>
+      </c>
+      <c r="V42" s="27">
+        <v>23.27</v>
+      </c>
+      <c r="W42" s="15">
+        <f t="shared" ref="W42:AA42" si="3">SUM(W36:W40)</f>
+        <v>24.22</v>
+      </c>
+      <c r="X42" s="15">
+        <f t="shared" si="3"/>
+        <v>25.27</v>
+      </c>
+      <c r="Y42" s="15">
+        <f t="shared" si="3"/>
+        <v>22.7</v>
+      </c>
+      <c r="Z42" s="15">
+        <f t="shared" si="3"/>
+        <v>25.78</v>
+      </c>
+      <c r="AA42" s="15">
+        <f t="shared" si="3"/>
+        <v>27.65</v>
+      </c>
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
@@ -11262,22 +11300,28 @@
         <v>9.5</v>
       </c>
       <c r="C62" s="25">
-        <v>289.98</v>
+        <f> 289.98 - C63</f>
+        <v>287.91</v>
       </c>
       <c r="D62" s="15">
-        <v>86.68</v>
+        <f> 86.68 - D63</f>
+        <v>85.2</v>
       </c>
       <c r="E62" s="15">
-        <v>23.01</v>
+        <f> 23.01 - E63</f>
+        <v>21.85</v>
       </c>
       <c r="F62" s="15">
-        <v>32.74</v>
+        <f> 32.74 - F63</f>
+        <v>30.7</v>
       </c>
       <c r="G62" s="15">
-        <v>45.38</v>
+        <f> 45.38 - G63</f>
+        <v>44.41</v>
       </c>
       <c r="H62" s="15">
-        <v>95.23</v>
+        <f> 95.23 -H63</f>
+        <v>94.9</v>
       </c>
       <c r="I62" s="15">
         <v>86.19</v>
@@ -17981,7 +18025,7 @@
       <c r="G56" s="22">
         <v>-16.72</v>
       </c>
-      <c r="H56" s="27">
+      <c r="H56" s="28">
         <v>-127.19</v>
       </c>
       <c r="I56" s="22">
@@ -18490,7 +18534,7 @@
       <c r="A65" s="17" t="s">
         <v>309</v>
       </c>
-      <c r="B65" s="27">
+      <c r="B65" s="28">
         <v>-286.77</v>
       </c>
       <c r="C65" s="22">
@@ -18499,10 +18543,10 @@
       <c r="D65" s="22">
         <v>-47.75</v>
       </c>
-      <c r="E65" s="27">
+      <c r="E65" s="28">
         <v>-100.98</v>
       </c>
-      <c r="F65" s="27">
+      <c r="F65" s="28">
         <v>-117.36</v>
       </c>
       <c r="G65" s="22">
@@ -18777,7 +18821,7 @@
       <c r="D69" s="18">
         <v>22.51</v>
       </c>
-      <c r="E69" s="27">
+      <c r="E69" s="28">
         <v>-109.58</v>
       </c>
       <c r="F69" s="19">
@@ -20490,3062 +20534,3062 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="28" t="s">
+      <c r="A20" s="29" t="s">
         <v>316</v>
       </c>
-      <c r="B20" s="29"/>
-      <c r="C20" s="29"/>
-      <c r="D20" s="29"/>
-      <c r="E20" s="29"/>
-      <c r="F20" s="29"/>
-      <c r="G20" s="29"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="29"/>
-      <c r="J20" s="29"/>
-      <c r="K20" s="29"/>
-      <c r="L20" s="29"/>
-      <c r="M20" s="29"/>
-      <c r="N20" s="29"/>
-      <c r="O20" s="29"/>
-      <c r="P20" s="29"/>
-      <c r="Q20" s="29"/>
-      <c r="R20" s="29"/>
-      <c r="S20" s="29"/>
-      <c r="T20" s="29"/>
-      <c r="U20" s="29"/>
-      <c r="V20" s="29"/>
-      <c r="W20" s="29"/>
-      <c r="X20" s="29"/>
-      <c r="Y20" s="29"/>
-      <c r="Z20" s="29"/>
+      <c r="B20" s="30"/>
+      <c r="C20" s="30"/>
+      <c r="D20" s="30"/>
+      <c r="E20" s="30"/>
+      <c r="F20" s="30"/>
+      <c r="G20" s="30"/>
+      <c r="H20" s="30"/>
+      <c r="I20" s="30"/>
+      <c r="J20" s="30"/>
+      <c r="K20" s="30"/>
+      <c r="L20" s="30"/>
+      <c r="M20" s="30"/>
+      <c r="N20" s="30"/>
+      <c r="O20" s="30"/>
+      <c r="P20" s="30"/>
+      <c r="Q20" s="30"/>
+      <c r="R20" s="30"/>
+      <c r="S20" s="30"/>
+      <c r="T20" s="30"/>
+      <c r="U20" s="30"/>
+      <c r="V20" s="30"/>
+      <c r="W20" s="30"/>
+      <c r="X20" s="30"/>
+      <c r="Y20" s="30"/>
+      <c r="Z20" s="30"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="30" t="s">
+      <c r="A21" s="31" t="s">
         <v>316</v>
       </c>
-      <c r="B21" s="31">
+      <c r="B21" s="32">
         <v>782.57</v>
       </c>
-      <c r="C21" s="31">
+      <c r="C21" s="32">
         <v>323.49</v>
       </c>
-      <c r="D21" s="31">
+      <c r="D21" s="32">
         <v>329.11</v>
       </c>
-      <c r="E21" s="31">
+      <c r="E21" s="32">
         <v>259.95</v>
       </c>
-      <c r="F21" s="31">
+      <c r="F21" s="32">
         <v>440.7</v>
       </c>
-      <c r="G21" s="31">
+      <c r="G21" s="32">
         <v>862.03</v>
       </c>
-      <c r="H21" s="31">
+      <c r="H21" s="32">
         <v>568.33</v>
       </c>
-      <c r="I21" s="31">
+      <c r="I21" s="32">
         <v>479.79</v>
       </c>
-      <c r="J21" s="31">
+      <c r="J21" s="32">
         <v>274.68</v>
       </c>
-      <c r="K21" s="31">
+      <c r="K21" s="32">
         <v>189.59</v>
       </c>
-      <c r="L21" s="32">
+      <c r="L21" s="33">
         <v>41.71</v>
       </c>
-      <c r="M21" s="32">
+      <c r="M21" s="33">
         <v>24.6</v>
       </c>
-      <c r="N21" s="32">
+      <c r="N21" s="33">
         <v>11.79</v>
       </c>
-      <c r="O21" s="32">
+      <c r="O21" s="33">
         <v>12.88</v>
       </c>
-      <c r="P21" s="32">
+      <c r="P21" s="33">
         <v>6.69</v>
       </c>
-      <c r="Q21" s="32">
+      <c r="Q21" s="33">
         <v>7.24</v>
       </c>
-      <c r="R21" s="33">
+      <c r="R21" s="34">
         <v>-0.33</v>
       </c>
-      <c r="S21" s="32">
+      <c r="S21" s="33">
         <v>14.87</v>
       </c>
-      <c r="T21" s="32">
+      <c r="T21" s="33">
         <v>15.61</v>
       </c>
-      <c r="U21" s="32">
+      <c r="U21" s="33">
         <v>19.73</v>
       </c>
-      <c r="V21" s="32">
+      <c r="V21" s="33">
         <v>15.6</v>
       </c>
-      <c r="W21" s="32">
+      <c r="W21" s="33">
         <v>14.8</v>
       </c>
-      <c r="X21" s="32">
+      <c r="X21" s="33">
         <v>12.86</v>
       </c>
-      <c r="Y21" s="32">
+      <c r="Y21" s="33">
         <v>14.22</v>
       </c>
-      <c r="Z21" s="32">
+      <c r="Z21" s="33">
         <v>9.86</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="30" t="s">
+      <c r="A22" s="31" t="s">
         <v>317</v>
       </c>
-      <c r="B22" s="31">
+      <c r="B22" s="32">
         <v>458.56</v>
       </c>
-      <c r="C22" s="31">
+      <c r="C22" s="32">
         <v>483.07</v>
       </c>
-      <c r="D22" s="31">
+      <c r="D22" s="32">
         <v>512.44</v>
       </c>
-      <c r="E22" s="31">
+      <c r="E22" s="32">
         <v>524.05</v>
       </c>
-      <c r="F22" s="31">
+      <c r="F22" s="32">
         <v>557.36</v>
       </c>
-      <c r="G22" s="31">
+      <c r="G22" s="32">
         <v>479.62</v>
       </c>
-      <c r="H22" s="31">
+      <c r="H22" s="32">
         <v>318.45</v>
       </c>
-      <c r="I22" s="31">
+      <c r="I22" s="32">
         <v>209.3</v>
       </c>
-      <c r="J22" s="31">
+      <c r="J22" s="32">
         <v>107.46</v>
       </c>
-      <c r="K22" s="32">
+      <c r="K22" s="33">
         <v>58.72</v>
       </c>
-      <c r="L22" s="32">
+      <c r="L22" s="33">
         <v>21.14</v>
       </c>
-      <c r="M22" s="32">
+      <c r="M22" s="33">
         <v>13.26</v>
       </c>
-      <c r="N22" s="32">
+      <c r="N22" s="33">
         <v>7.29</v>
       </c>
-      <c r="O22" s="32">
+      <c r="O22" s="33">
         <v>8.1</v>
       </c>
-      <c r="P22" s="32">
+      <c r="P22" s="33">
         <v>8.52</v>
       </c>
-      <c r="Q22" s="32">
+      <c r="Q22" s="33">
         <v>11.75</v>
       </c>
-      <c r="R22" s="32">
+      <c r="R22" s="33">
         <v>15.73</v>
       </c>
-      <c r="S22" s="32">
+      <c r="S22" s="33">
         <v>15.7</v>
       </c>
-      <c r="T22" s="32">
+      <c r="T22" s="33">
         <v>16.11</v>
       </c>
-      <c r="U22" s="32">
+      <c r="U22" s="33">
         <v>15.46</v>
       </c>
-      <c r="V22" s="32">
+      <c r="V22" s="33">
         <v>13.84</v>
       </c>
-      <c r="W22" s="34"/>
-      <c r="X22" s="34"/>
-      <c r="Y22" s="34"/>
-      <c r="Z22" s="34"/>
+      <c r="W22" s="35"/>
+      <c r="X22" s="35"/>
+      <c r="Y22" s="35"/>
+      <c r="Z22" s="35"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="28" t="s">
+      <c r="A23" s="29" t="s">
         <v>318</v>
       </c>
-      <c r="B23" s="29"/>
-      <c r="C23" s="29"/>
-      <c r="D23" s="29"/>
-      <c r="E23" s="29"/>
-      <c r="F23" s="29"/>
-      <c r="G23" s="29"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="29"/>
-      <c r="J23" s="29"/>
-      <c r="K23" s="29"/>
-      <c r="L23" s="29"/>
-      <c r="M23" s="29"/>
-      <c r="N23" s="29"/>
-      <c r="O23" s="29"/>
-      <c r="P23" s="29"/>
-      <c r="Q23" s="29"/>
-      <c r="R23" s="29"/>
-      <c r="S23" s="29"/>
-      <c r="T23" s="29"/>
-      <c r="U23" s="29"/>
-      <c r="V23" s="29"/>
-      <c r="W23" s="29"/>
-      <c r="X23" s="29"/>
-      <c r="Y23" s="29"/>
-      <c r="Z23" s="29"/>
+      <c r="B23" s="30"/>
+      <c r="C23" s="30"/>
+      <c r="D23" s="30"/>
+      <c r="E23" s="30"/>
+      <c r="F23" s="30"/>
+      <c r="G23" s="30"/>
+      <c r="H23" s="30"/>
+      <c r="I23" s="30"/>
+      <c r="J23" s="30"/>
+      <c r="K23" s="30"/>
+      <c r="L23" s="30"/>
+      <c r="M23" s="30"/>
+      <c r="N23" s="30"/>
+      <c r="O23" s="30"/>
+      <c r="P23" s="30"/>
+      <c r="Q23" s="30"/>
+      <c r="R23" s="30"/>
+      <c r="S23" s="30"/>
+      <c r="T23" s="30"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="30"/>
+      <c r="W23" s="30"/>
+      <c r="X23" s="30"/>
+      <c r="Y23" s="30"/>
+      <c r="Z23" s="30"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="30" t="s">
+      <c r="A24" s="31" t="s">
         <v>318</v>
       </c>
-      <c r="B24" s="31">
+      <c r="B24" s="32">
         <v>243.77</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C24" s="32">
         <v>228.2</v>
       </c>
-      <c r="D24" s="31">
+      <c r="D24" s="32">
         <v>197.45</v>
       </c>
-      <c r="E24" s="31">
+      <c r="E24" s="32">
         <v>212.09</v>
       </c>
-      <c r="F24" s="31">
+      <c r="F24" s="32">
         <v>226.71</v>
       </c>
-      <c r="G24" s="31">
+      <c r="G24" s="32">
         <v>220.16</v>
       </c>
-      <c r="H24" s="31">
+      <c r="H24" s="32">
         <v>196.4</v>
       </c>
-      <c r="I24" s="31">
+      <c r="I24" s="32">
         <v>240.7</v>
       </c>
-      <c r="J24" s="31">
+      <c r="J24" s="32">
         <v>101.96</v>
       </c>
-      <c r="K24" s="32">
+      <c r="K24" s="33">
         <v>98.04</v>
       </c>
-      <c r="L24" s="32">
+      <c r="L24" s="33">
         <v>35.82</v>
       </c>
-      <c r="M24" s="32">
+      <c r="M24" s="33">
         <v>20.04</v>
       </c>
-      <c r="N24" s="32">
+      <c r="N24" s="33">
         <v>16.93</v>
       </c>
-      <c r="O24" s="32">
+      <c r="O24" s="33">
         <v>19.91</v>
       </c>
-      <c r="P24" s="32">
+      <c r="P24" s="33">
         <v>25.36</v>
       </c>
-      <c r="Q24" s="32">
+      <c r="Q24" s="33">
         <v>25.52</v>
       </c>
-      <c r="R24" s="32">
+      <c r="R24" s="33">
         <v>16.16</v>
       </c>
-      <c r="S24" s="32">
+      <c r="S24" s="33">
         <v>27.3</v>
       </c>
-      <c r="T24" s="32">
+      <c r="T24" s="33">
         <v>27.52</v>
       </c>
-      <c r="U24" s="32">
+      <c r="U24" s="33">
         <v>23.73</v>
       </c>
-      <c r="V24" s="32">
+      <c r="V24" s="33">
         <v>17.39</v>
       </c>
-      <c r="W24" s="32">
+      <c r="W24" s="33">
         <v>12.27</v>
       </c>
-      <c r="X24" s="32">
+      <c r="X24" s="33">
         <v>8.27</v>
       </c>
-      <c r="Y24" s="32">
+      <c r="Y24" s="33">
         <v>9.06</v>
       </c>
-      <c r="Z24" s="32">
+      <c r="Z24" s="33">
         <v>10.73</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="30" t="s">
+      <c r="A25" s="31" t="s">
         <v>319</v>
       </c>
-      <c r="B25" s="31">
+      <c r="B25" s="32">
         <v>241.88</v>
       </c>
-      <c r="C25" s="31">
+      <c r="C25" s="32">
         <v>233.62</v>
       </c>
-      <c r="D25" s="31">
+      <c r="D25" s="32">
         <v>217.77</v>
       </c>
-      <c r="E25" s="31">
+      <c r="E25" s="32">
         <v>219.19</v>
       </c>
-      <c r="F25" s="31">
+      <c r="F25" s="32">
         <v>208.5</v>
       </c>
-      <c r="G25" s="31">
+      <c r="G25" s="32">
         <v>173.36</v>
       </c>
-      <c r="H25" s="31">
+      <c r="H25" s="32">
         <v>138.06</v>
       </c>
-      <c r="I25" s="31">
+      <c r="I25" s="32">
         <v>102.89</v>
       </c>
-      <c r="J25" s="32">
+      <c r="J25" s="33">
         <v>54.69</v>
       </c>
-      <c r="K25" s="32">
+      <c r="K25" s="33">
         <v>41.2</v>
       </c>
-      <c r="L25" s="32">
+      <c r="L25" s="33">
         <v>26.22</v>
       </c>
-      <c r="M25" s="32">
+      <c r="M25" s="33">
         <v>22.71</v>
       </c>
-      <c r="N25" s="32">
+      <c r="N25" s="33">
         <v>18.91</v>
       </c>
-      <c r="O25" s="32">
+      <c r="O25" s="33">
         <v>21.69</v>
       </c>
-      <c r="P25" s="32">
+      <c r="P25" s="33">
         <v>23.03</v>
       </c>
-      <c r="Q25" s="32">
+      <c r="Q25" s="33">
         <v>24.06</v>
       </c>
-      <c r="R25" s="32">
+      <c r="R25" s="33">
         <v>26.28</v>
       </c>
-      <c r="S25" s="32">
+      <c r="S25" s="33">
         <v>21.14</v>
       </c>
-      <c r="T25" s="32">
+      <c r="T25" s="33">
         <v>18.14</v>
       </c>
-      <c r="U25" s="32">
+      <c r="U25" s="33">
         <v>14.08</v>
       </c>
-      <c r="V25" s="32">
+      <c r="V25" s="33">
         <v>11.77</v>
       </c>
-      <c r="W25" s="34"/>
-      <c r="X25" s="34"/>
-      <c r="Y25" s="34"/>
-      <c r="Z25" s="34"/>
+      <c r="W25" s="35"/>
+      <c r="X25" s="35"/>
+      <c r="Y25" s="35"/>
+      <c r="Z25" s="35"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="29" t="s">
         <v>320</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="29"/>
-      <c r="D26" s="29"/>
-      <c r="E26" s="29"/>
-      <c r="F26" s="29"/>
-      <c r="G26" s="29"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="29"/>
-      <c r="J26" s="29"/>
-      <c r="K26" s="29"/>
-      <c r="L26" s="29"/>
-      <c r="M26" s="29"/>
-      <c r="N26" s="29"/>
-      <c r="O26" s="29"/>
-      <c r="P26" s="29"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" s="29"/>
-      <c r="S26" s="29"/>
-      <c r="T26" s="29"/>
-      <c r="U26" s="29"/>
-      <c r="V26" s="29"/>
-      <c r="W26" s="29"/>
-      <c r="X26" s="29"/>
-      <c r="Y26" s="29"/>
-      <c r="Z26" s="29"/>
+      <c r="B26" s="30"/>
+      <c r="C26" s="30"/>
+      <c r="D26" s="30"/>
+      <c r="E26" s="30"/>
+      <c r="F26" s="30"/>
+      <c r="G26" s="30"/>
+      <c r="H26" s="30"/>
+      <c r="I26" s="30"/>
+      <c r="J26" s="30"/>
+      <c r="K26" s="30"/>
+      <c r="L26" s="30"/>
+      <c r="M26" s="30"/>
+      <c r="N26" s="30"/>
+      <c r="O26" s="30"/>
+      <c r="P26" s="30"/>
+      <c r="Q26" s="30"/>
+      <c r="R26" s="30"/>
+      <c r="S26" s="30"/>
+      <c r="T26" s="30"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="30"/>
+      <c r="W26" s="30"/>
+      <c r="X26" s="30"/>
+      <c r="Y26" s="30"/>
+      <c r="Z26" s="30"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="30" t="s">
+      <c r="A27" s="31" t="s">
         <v>321</v>
       </c>
-      <c r="B27" s="32">
+      <c r="B27" s="33">
         <v>38.15</v>
       </c>
-      <c r="C27" s="32">
+      <c r="C27" s="33">
         <v>35.72</v>
       </c>
-      <c r="D27" s="32">
+      <c r="D27" s="33">
         <v>30.9</v>
       </c>
-      <c r="E27" s="32">
+      <c r="E27" s="33">
         <v>34.31</v>
       </c>
-      <c r="F27" s="32">
+      <c r="F27" s="33">
         <v>36.67</v>
       </c>
-      <c r="G27" s="32">
+      <c r="G27" s="33">
         <v>35.61</v>
       </c>
-      <c r="H27" s="32">
+      <c r="H27" s="33">
         <v>31.77</v>
       </c>
-      <c r="I27" s="32">
+      <c r="I27" s="33">
         <v>38.93</v>
       </c>
-      <c r="J27" s="32">
+      <c r="J27" s="33">
         <v>28.97</v>
       </c>
-      <c r="K27" s="32">
+      <c r="K27" s="33">
         <v>27.86</v>
       </c>
-      <c r="L27" s="32">
+      <c r="L27" s="33">
         <v>23.57</v>
       </c>
-      <c r="M27" s="32">
+      <c r="M27" s="33">
         <v>13.19</v>
       </c>
-      <c r="N27" s="32">
+      <c r="N27" s="33">
         <v>11.14</v>
       </c>
-      <c r="O27" s="32">
+      <c r="O27" s="33">
         <v>13.11</v>
       </c>
-      <c r="P27" s="32">
+      <c r="P27" s="33">
         <v>16.69</v>
       </c>
-      <c r="Q27" s="32">
+      <c r="Q27" s="33">
         <v>16.8</v>
       </c>
-      <c r="R27" s="32">
+      <c r="R27" s="33">
         <v>10.64</v>
       </c>
-      <c r="S27" s="32">
+      <c r="S27" s="33">
         <v>17.97</v>
       </c>
-      <c r="T27" s="32">
+      <c r="T27" s="33">
         <v>18.11</v>
       </c>
-      <c r="U27" s="32">
+      <c r="U27" s="33">
         <v>15.62</v>
       </c>
-      <c r="V27" s="32">
+      <c r="V27" s="33">
         <v>11.45</v>
       </c>
-      <c r="W27" s="32">
+      <c r="W27" s="33">
         <v>8.07</v>
       </c>
-      <c r="X27" s="32">
+      <c r="X27" s="33">
         <v>5.44</v>
       </c>
-      <c r="Y27" s="32">
+      <c r="Y27" s="33">
         <v>5.96</v>
       </c>
-      <c r="Z27" s="32">
+      <c r="Z27" s="33">
         <v>7.06</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="30" t="s">
+      <c r="A28" s="31" t="s">
         <v>322</v>
       </c>
-      <c r="B28" s="32">
+      <c r="B28" s="33">
         <v>38.39</v>
       </c>
-      <c r="C28" s="32">
+      <c r="C28" s="33">
         <v>37.33</v>
       </c>
-      <c r="D28" s="32">
+      <c r="D28" s="33">
         <v>35.02</v>
       </c>
-      <c r="E28" s="32">
+      <c r="E28" s="33">
         <v>35.45</v>
       </c>
-      <c r="F28" s="32">
+      <c r="F28" s="33">
         <v>36.61</v>
       </c>
-      <c r="G28" s="32">
+      <c r="G28" s="33">
         <v>33.21</v>
       </c>
-      <c r="H28" s="32">
+      <c r="H28" s="33">
         <v>31.43</v>
       </c>
-      <c r="I28" s="32">
+      <c r="I28" s="33">
         <v>28.03</v>
       </c>
-      <c r="J28" s="32">
+      <c r="J28" s="33">
         <v>21.43</v>
       </c>
-      <c r="K28" s="32">
+      <c r="K28" s="33">
         <v>19.78</v>
       </c>
-      <c r="L28" s="32">
+      <c r="L28" s="33">
         <v>17.25</v>
       </c>
-      <c r="M28" s="32">
+      <c r="M28" s="33">
         <v>14.95</v>
       </c>
-      <c r="N28" s="32">
+      <c r="N28" s="33">
         <v>12.44</v>
       </c>
-      <c r="O28" s="32">
+      <c r="O28" s="33">
         <v>14.27</v>
       </c>
-      <c r="P28" s="32">
+      <c r="P28" s="33">
         <v>15.16</v>
       </c>
-      <c r="Q28" s="32">
+      <c r="Q28" s="33">
         <v>15.83</v>
       </c>
-      <c r="R28" s="32">
+      <c r="R28" s="33">
         <v>17.3</v>
       </c>
-      <c r="S28" s="32">
+      <c r="S28" s="33">
         <v>13.91</v>
       </c>
-      <c r="T28" s="32">
+      <c r="T28" s="33">
         <v>11.94</v>
       </c>
-      <c r="U28" s="32">
+      <c r="U28" s="33">
         <v>9.27</v>
       </c>
-      <c r="V28" s="32">
+      <c r="V28" s="33">
         <v>7.75</v>
       </c>
-      <c r="W28" s="34"/>
-      <c r="X28" s="34"/>
-      <c r="Y28" s="34"/>
-      <c r="Z28" s="34"/>
+      <c r="W28" s="35"/>
+      <c r="X28" s="35"/>
+      <c r="Y28" s="35"/>
+      <c r="Z28" s="35"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="28" t="s">
+      <c r="A29" s="29" t="s">
         <v>323</v>
       </c>
-      <c r="B29" s="29"/>
-      <c r="C29" s="29"/>
-      <c r="D29" s="29"/>
-      <c r="E29" s="29"/>
-      <c r="F29" s="29"/>
-      <c r="G29" s="29"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="29"/>
-      <c r="J29" s="29"/>
-      <c r="K29" s="29"/>
-      <c r="L29" s="29"/>
-      <c r="M29" s="29"/>
-      <c r="N29" s="29"/>
-      <c r="O29" s="29"/>
-      <c r="P29" s="29"/>
-      <c r="Q29" s="29"/>
-      <c r="R29" s="29"/>
-      <c r="S29" s="29"/>
-      <c r="T29" s="29"/>
-      <c r="U29" s="29"/>
-      <c r="V29" s="29"/>
-      <c r="W29" s="29"/>
-      <c r="X29" s="29"/>
-      <c r="Y29" s="29"/>
-      <c r="Z29" s="29"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="30"/>
+      <c r="D29" s="30"/>
+      <c r="E29" s="30"/>
+      <c r="F29" s="30"/>
+      <c r="G29" s="30"/>
+      <c r="H29" s="30"/>
+      <c r="I29" s="30"/>
+      <c r="J29" s="30"/>
+      <c r="K29" s="30"/>
+      <c r="L29" s="30"/>
+      <c r="M29" s="30"/>
+      <c r="N29" s="30"/>
+      <c r="O29" s="30"/>
+      <c r="P29" s="30"/>
+      <c r="Q29" s="30"/>
+      <c r="R29" s="30"/>
+      <c r="S29" s="30"/>
+      <c r="T29" s="30"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="30"/>
+      <c r="W29" s="30"/>
+      <c r="X29" s="30"/>
+      <c r="Y29" s="30"/>
+      <c r="Z29" s="30"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="30" t="s">
+      <c r="A30" s="31" t="s">
         <v>324</v>
       </c>
-      <c r="B30" s="35">
+      <c r="B30" s="36">
         <v>9.82</v>
       </c>
-      <c r="C30" s="36">
+      <c r="C30" s="37">
         <v>-4.59</v>
       </c>
-      <c r="D30" s="36">
+      <c r="D30" s="37">
         <v>-2.97</v>
       </c>
-      <c r="E30" s="36">
+      <c r="E30" s="37">
         <v>-11.39</v>
       </c>
-      <c r="F30" s="36">
+      <c r="F30" s="37">
         <v>-1.05</v>
       </c>
-      <c r="G30" s="36">
+      <c r="G30" s="37">
         <v>-124.79</v>
       </c>
-      <c r="H30" s="36">
+      <c r="H30" s="37">
         <v>-23.92</v>
       </c>
-      <c r="I30" s="35">
+      <c r="I30" s="36">
         <v>0.38</v>
       </c>
-      <c r="J30" s="36">
+      <c r="J30" s="37">
         <v>-42.87</v>
       </c>
-      <c r="K30" s="36">
+      <c r="K30" s="37">
         <v>-41.71</v>
       </c>
-      <c r="L30" s="35">
+      <c r="L30" s="36">
         <v>0.19</v>
       </c>
-      <c r="M30" s="36">
+      <c r="M30" s="37">
         <v>-46.98</v>
       </c>
-      <c r="N30" s="36">
+      <c r="N30" s="37">
         <v>-13.66</v>
       </c>
-      <c r="O30" s="36">
+      <c r="O30" s="37">
         <v>-45.79</v>
       </c>
-      <c r="P30" s="36">
+      <c r="P30" s="37">
         <v>-1.02</v>
       </c>
-      <c r="Q30" s="35">
+      <c r="Q30" s="36">
         <v>11.83</v>
       </c>
-      <c r="R30" s="35">
+      <c r="R30" s="36">
         <v>23.67</v>
       </c>
-      <c r="S30" s="35">
+      <c r="S30" s="36">
         <v>9.76</v>
       </c>
-      <c r="T30" s="35">
+      <c r="T30" s="36">
         <v>12.32</v>
       </c>
-      <c r="U30" s="35">
+      <c r="U30" s="36">
         <v>17.19</v>
       </c>
-      <c r="V30" s="35">
+      <c r="V30" s="36">
         <v>27.99</v>
       </c>
-      <c r="W30" s="35">
+      <c r="W30" s="36">
         <v>34.69</v>
       </c>
-      <c r="X30" s="35">
+      <c r="X30" s="36">
         <v>21.29</v>
       </c>
-      <c r="Y30" s="35">
+      <c r="Y30" s="36">
         <v>13.55</v>
       </c>
-      <c r="Z30" s="36">
+      <c r="Z30" s="37">
         <v>-32.47</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="30" t="s">
+      <c r="A31" s="31" t="s">
         <v>325</v>
       </c>
-      <c r="B31" s="36">
+      <c r="B31" s="37">
         <v>-2.1</v>
       </c>
-      <c r="C31" s="36">
+      <c r="C31" s="37">
         <v>-31.03</v>
       </c>
-      <c r="D31" s="36">
+      <c r="D31" s="37">
         <v>-34.72</v>
       </c>
-      <c r="E31" s="36">
+      <c r="E31" s="37">
         <v>-32.16</v>
       </c>
-      <c r="F31" s="36">
+      <c r="F31" s="37">
         <v>-38.19</v>
       </c>
-      <c r="G31" s="36">
+      <c r="G31" s="37">
         <v>-46.5</v>
       </c>
-      <c r="H31" s="36">
+      <c r="H31" s="37">
         <v>-20.96</v>
       </c>
-      <c r="I31" s="36">
+      <c r="I31" s="37">
         <v>-23.19</v>
       </c>
-      <c r="J31" s="36">
+      <c r="J31" s="37">
         <v>-29.86</v>
       </c>
-      <c r="K31" s="36">
+      <c r="K31" s="37">
         <v>-28.45</v>
       </c>
-      <c r="L31" s="36">
+      <c r="L31" s="37">
         <v>-18.26</v>
       </c>
-      <c r="M31" s="36">
+      <c r="M31" s="37">
         <v>-16.83</v>
       </c>
-      <c r="N31" s="36">
+      <c r="N31" s="37">
         <v>-5.97</v>
       </c>
-      <c r="O31" s="36">
+      <c r="O31" s="37">
         <v>-0.84</v>
       </c>
-      <c r="P31" s="35">
+      <c r="P31" s="36">
         <v>9.96</v>
       </c>
-      <c r="Q31" s="35">
+      <c r="Q31" s="36">
         <v>13.91</v>
       </c>
-      <c r="R31" s="35">
+      <c r="R31" s="36">
         <v>16.58</v>
       </c>
-      <c r="S31" s="35">
+      <c r="S31" s="36">
         <v>17.68</v>
       </c>
-      <c r="T31" s="35">
+      <c r="T31" s="36">
         <v>20.52</v>
       </c>
-      <c r="U31" s="35">
+      <c r="U31" s="36">
         <v>22.74</v>
       </c>
-      <c r="V31" s="35">
+      <c r="V31" s="36">
         <v>15.0</v>
       </c>
-      <c r="W31" s="35"/>
-      <c r="X31" s="35"/>
-      <c r="Y31" s="35"/>
-      <c r="Z31" s="35"/>
+      <c r="W31" s="36"/>
+      <c r="X31" s="36"/>
+      <c r="Y31" s="36"/>
+      <c r="Z31" s="36"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="28" t="s">
+      <c r="A32" s="29" t="s">
         <v>326</v>
       </c>
-      <c r="B32" s="29"/>
-      <c r="C32" s="29"/>
-      <c r="D32" s="29"/>
-      <c r="E32" s="29"/>
-      <c r="F32" s="29"/>
-      <c r="G32" s="29"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="29"/>
-      <c r="J32" s="29"/>
-      <c r="K32" s="29"/>
-      <c r="L32" s="29"/>
-      <c r="M32" s="29"/>
-      <c r="N32" s="29"/>
-      <c r="O32" s="29"/>
-      <c r="P32" s="29"/>
-      <c r="Q32" s="29"/>
-      <c r="R32" s="29"/>
-      <c r="S32" s="29"/>
-      <c r="T32" s="29"/>
-      <c r="U32" s="29"/>
-      <c r="V32" s="29"/>
-      <c r="W32" s="29"/>
-      <c r="X32" s="29"/>
-      <c r="Y32" s="29"/>
-      <c r="Z32" s="29"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="30"/>
+      <c r="D32" s="30"/>
+      <c r="E32" s="30"/>
+      <c r="F32" s="30"/>
+      <c r="G32" s="30"/>
+      <c r="H32" s="30"/>
+      <c r="I32" s="30"/>
+      <c r="J32" s="30"/>
+      <c r="K32" s="30"/>
+      <c r="L32" s="30"/>
+      <c r="M32" s="30"/>
+      <c r="N32" s="30"/>
+      <c r="O32" s="30"/>
+      <c r="P32" s="30"/>
+      <c r="Q32" s="30"/>
+      <c r="R32" s="30"/>
+      <c r="S32" s="30"/>
+      <c r="T32" s="30"/>
+      <c r="U32" s="30"/>
+      <c r="V32" s="30"/>
+      <c r="W32" s="30"/>
+      <c r="X32" s="30"/>
+      <c r="Y32" s="30"/>
+      <c r="Z32" s="30"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="30" t="s">
+      <c r="A33" s="31" t="s">
         <v>327</v>
       </c>
-      <c r="B33" s="35">
+      <c r="B33" s="36">
         <v>10.18</v>
       </c>
-      <c r="C33" s="35">
+      <c r="C33" s="36">
         <v>9.71</v>
       </c>
-      <c r="D33" s="35">
+      <c r="D33" s="36">
         <v>9.84</v>
       </c>
-      <c r="E33" s="35">
+      <c r="E33" s="36">
         <v>37.06</v>
       </c>
-      <c r="F33" s="35">
+      <c r="F33" s="36">
         <v>7.14</v>
       </c>
-      <c r="G33" s="35">
+      <c r="G33" s="36">
         <v>6.36</v>
       </c>
-      <c r="H33" s="35">
+      <c r="H33" s="36">
         <v>6.55</v>
       </c>
-      <c r="I33" s="35">
+      <c r="I33" s="36">
         <v>4.8</v>
       </c>
-      <c r="J33" s="35">
+      <c r="J33" s="36">
         <v>5.33</v>
       </c>
-      <c r="K33" s="35">
+      <c r="K33" s="36">
         <v>3.45</v>
       </c>
-      <c r="L33" s="35">
+      <c r="L33" s="36">
         <v>3.83</v>
       </c>
-      <c r="M33" s="35"/>
-      <c r="N33" s="35">
+      <c r="M33" s="36"/>
+      <c r="N33" s="36">
         <v>6.59</v>
       </c>
-      <c r="O33" s="35">
+      <c r="O33" s="36">
         <v>4.75</v>
       </c>
-      <c r="P33" s="35">
+      <c r="P33" s="36">
         <v>3.75</v>
       </c>
-      <c r="Q33" s="35">
+      <c r="Q33" s="36">
         <v>5.95</v>
       </c>
-      <c r="R33" s="35">
+      <c r="R33" s="36">
         <v>11.01</v>
       </c>
-      <c r="S33" s="35">
+      <c r="S33" s="36">
         <v>5.32</v>
       </c>
-      <c r="T33" s="35">
+      <c r="T33" s="36">
         <v>5.48</v>
       </c>
-      <c r="U33" s="35"/>
-      <c r="V33" s="35">
+      <c r="U33" s="36"/>
+      <c r="V33" s="36">
         <v>10.8</v>
       </c>
-      <c r="W33" s="35">
+      <c r="W33" s="36">
         <v>5.2</v>
       </c>
-      <c r="X33" s="35">
+      <c r="X33" s="36">
         <v>6.68</v>
       </c>
-      <c r="Y33" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Z33" s="35">
+      <c r="Y33" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="Z33" s="36">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="30" t="s">
+      <c r="A34" s="31" t="s">
         <v>328</v>
       </c>
-      <c r="B34" s="35">
+      <c r="B34" s="36">
         <v>15.02</v>
       </c>
-      <c r="C34" s="35">
+      <c r="C34" s="36">
         <v>14.08</v>
       </c>
-      <c r="D34" s="35">
+      <c r="D34" s="36">
         <v>13.47</v>
       </c>
-      <c r="E34" s="35">
+      <c r="E34" s="36">
         <v>12.14</v>
       </c>
-      <c r="F34" s="35">
+      <c r="F34" s="36">
         <v>6.01</v>
       </c>
-      <c r="G34" s="35">
+      <c r="G34" s="36">
         <v>5.33</v>
       </c>
-      <c r="H34" s="35">
+      <c r="H34" s="36">
         <v>4.85</v>
       </c>
-      <c r="I34" s="35"/>
-      <c r="J34" s="35"/>
-      <c r="K34" s="35"/>
-      <c r="L34" s="35"/>
-      <c r="M34" s="35"/>
-      <c r="N34" s="35">
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
+      <c r="K34" s="36"/>
+      <c r="L34" s="36"/>
+      <c r="M34" s="36"/>
+      <c r="N34" s="36">
         <v>5.92</v>
       </c>
-      <c r="O34" s="35">
+      <c r="O34" s="36">
         <v>5.67</v>
       </c>
-      <c r="P34" s="35">
+      <c r="P34" s="36">
         <v>5.78</v>
       </c>
-      <c r="Q34" s="35"/>
-      <c r="R34" s="35"/>
-      <c r="S34" s="35"/>
-      <c r="T34" s="35"/>
-      <c r="U34" s="35"/>
-      <c r="V34" s="35">
+      <c r="Q34" s="36"/>
+      <c r="R34" s="36"/>
+      <c r="S34" s="36"/>
+      <c r="T34" s="36"/>
+      <c r="U34" s="36"/>
+      <c r="V34" s="36">
         <v>5.32</v>
       </c>
-      <c r="W34" s="35"/>
-      <c r="X34" s="35"/>
-      <c r="Y34" s="35"/>
-      <c r="Z34" s="35"/>
+      <c r="W34" s="36"/>
+      <c r="X34" s="36"/>
+      <c r="Y34" s="36"/>
+      <c r="Z34" s="36"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="30" t="s">
+      <c r="A35" s="31" t="s">
         <v>329</v>
       </c>
-      <c r="B35" s="35">
+      <c r="B35" s="36">
         <v>10.18</v>
       </c>
-      <c r="C35" s="35">
+      <c r="C35" s="36">
         <v>9.71</v>
       </c>
-      <c r="D35" s="35">
+      <c r="D35" s="36">
         <v>9.84</v>
       </c>
-      <c r="E35" s="35">
+      <c r="E35" s="36">
         <v>37.06</v>
       </c>
-      <c r="F35" s="35">
+      <c r="F35" s="36">
         <v>7.14</v>
       </c>
-      <c r="G35" s="35">
+      <c r="G35" s="36">
         <v>6.36</v>
       </c>
-      <c r="H35" s="35">
+      <c r="H35" s="36">
         <v>6.55</v>
       </c>
-      <c r="I35" s="35">
+      <c r="I35" s="36">
         <v>4.8</v>
       </c>
-      <c r="J35" s="35">
+      <c r="J35" s="36">
         <v>5.33</v>
       </c>
-      <c r="K35" s="35">
+      <c r="K35" s="36">
         <v>3.45</v>
       </c>
-      <c r="L35" s="35">
+      <c r="L35" s="36">
         <v>3.83</v>
       </c>
-      <c r="M35" s="35">
+      <c r="M35" s="36">
         <v>6.32</v>
       </c>
-      <c r="N35" s="35">
+      <c r="N35" s="36">
         <v>6.59</v>
       </c>
-      <c r="O35" s="35">
+      <c r="O35" s="36">
         <v>5.9</v>
       </c>
-      <c r="P35" s="35">
+      <c r="P35" s="36">
         <v>4.67</v>
       </c>
-      <c r="Q35" s="35">
+      <c r="Q35" s="36">
         <v>7.41</v>
       </c>
-      <c r="R35" s="35">
+      <c r="R35" s="36">
         <v>13.69</v>
       </c>
-      <c r="S35" s="35">
+      <c r="S35" s="36">
         <v>6.62</v>
       </c>
-      <c r="T35" s="35">
+      <c r="T35" s="36">
         <v>6.81</v>
       </c>
-      <c r="U35" s="35">
+      <c r="U35" s="36">
         <v>7.67</v>
       </c>
-      <c r="V35" s="35">
+      <c r="V35" s="36">
         <v>3.6</v>
       </c>
-      <c r="W35" s="35">
+      <c r="W35" s="36">
         <v>5.2</v>
       </c>
-      <c r="X35" s="35">
+      <c r="X35" s="36">
         <v>6.68</v>
       </c>
-      <c r="Y35" s="35">
-        <v>0.0</v>
-      </c>
-      <c r="Z35" s="35">
+      <c r="Y35" s="36">
+        <v>0.0</v>
+      </c>
+      <c r="Z35" s="36">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="30" t="s">
+      <c r="A36" s="31" t="s">
         <v>330</v>
       </c>
-      <c r="B36" s="35">
+      <c r="B36" s="36">
         <v>15.02</v>
       </c>
-      <c r="C36" s="35">
+      <c r="C36" s="36">
         <v>14.08</v>
       </c>
-      <c r="D36" s="35">
+      <c r="D36" s="36">
         <v>13.47</v>
       </c>
-      <c r="E36" s="35">
+      <c r="E36" s="36">
         <v>12.14</v>
       </c>
-      <c r="F36" s="35">
+      <c r="F36" s="36">
         <v>6.01</v>
       </c>
-      <c r="G36" s="35">
+      <c r="G36" s="36">
         <v>5.33</v>
       </c>
-      <c r="H36" s="35">
+      <c r="H36" s="36">
         <v>4.85</v>
       </c>
-      <c r="I36" s="35">
+      <c r="I36" s="36">
         <v>4.64</v>
       </c>
-      <c r="J36" s="35">
+      <c r="J36" s="36">
         <v>4.83</v>
       </c>
-      <c r="K36" s="35">
+      <c r="K36" s="36">
         <v>4.85</v>
       </c>
-      <c r="L36" s="35">
+      <c r="L36" s="36">
         <v>5.24</v>
       </c>
-      <c r="M36" s="35">
+      <c r="M36" s="36">
         <v>6.14</v>
       </c>
-      <c r="N36" s="35">
+      <c r="N36" s="36">
         <v>7.08</v>
       </c>
-      <c r="O36" s="35">
+      <c r="O36" s="36">
         <v>7.05</v>
       </c>
-      <c r="P36" s="35">
+      <c r="P36" s="36">
         <v>7.19</v>
       </c>
-      <c r="Q36" s="35">
+      <c r="Q36" s="36">
         <v>7.86</v>
       </c>
-      <c r="R36" s="35">
+      <c r="R36" s="36">
         <v>7.3</v>
       </c>
-      <c r="S36" s="35">
+      <c r="S36" s="36">
         <v>6.27</v>
       </c>
-      <c r="T36" s="35">
+      <c r="T36" s="36">
         <v>6.2</v>
       </c>
-      <c r="U36" s="35">
+      <c r="U36" s="36">
         <v>5.17</v>
       </c>
-      <c r="V36" s="35">
+      <c r="V36" s="36">
         <v>3.19</v>
       </c>
-      <c r="W36" s="35"/>
-      <c r="X36" s="35"/>
-      <c r="Y36" s="35"/>
-      <c r="Z36" s="35"/>
+      <c r="W36" s="36"/>
+      <c r="X36" s="36"/>
+      <c r="Y36" s="36"/>
+      <c r="Z36" s="36"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="28" t="s">
+      <c r="A37" s="29" t="s">
         <v>331</v>
       </c>
-      <c r="B37" s="29"/>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="29"/>
-      <c r="F37" s="29"/>
-      <c r="G37" s="29"/>
-      <c r="H37" s="29"/>
-      <c r="I37" s="29"/>
-      <c r="J37" s="29"/>
-      <c r="K37" s="29"/>
-      <c r="L37" s="29"/>
-      <c r="M37" s="29"/>
-      <c r="N37" s="29"/>
-      <c r="O37" s="29"/>
-      <c r="P37" s="29"/>
-      <c r="Q37" s="29"/>
-      <c r="R37" s="29"/>
-      <c r="S37" s="29"/>
-      <c r="T37" s="29"/>
-      <c r="U37" s="29"/>
-      <c r="V37" s="29"/>
-      <c r="W37" s="29"/>
-      <c r="X37" s="29"/>
-      <c r="Y37" s="29"/>
-      <c r="Z37" s="29"/>
+      <c r="B37" s="30"/>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="30"/>
+      <c r="F37" s="30"/>
+      <c r="G37" s="30"/>
+      <c r="H37" s="30"/>
+      <c r="I37" s="30"/>
+      <c r="J37" s="30"/>
+      <c r="K37" s="30"/>
+      <c r="L37" s="30"/>
+      <c r="M37" s="30"/>
+      <c r="N37" s="30"/>
+      <c r="O37" s="30"/>
+      <c r="P37" s="30"/>
+      <c r="Q37" s="30"/>
+      <c r="R37" s="30"/>
+      <c r="S37" s="30"/>
+      <c r="T37" s="30"/>
+      <c r="U37" s="30"/>
+      <c r="V37" s="30"/>
+      <c r="W37" s="30"/>
+      <c r="X37" s="30"/>
+      <c r="Y37" s="30"/>
+      <c r="Z37" s="30"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="30" t="s">
+      <c r="A38" s="31" t="s">
         <v>332</v>
       </c>
-      <c r="B38" s="32">
+      <c r="B38" s="33">
         <v>0.54</v>
       </c>
-      <c r="C38" s="32">
+      <c r="C38" s="33">
         <v>0.61</v>
       </c>
-      <c r="D38" s="32">
+      <c r="D38" s="33">
         <v>0.59</v>
       </c>
-      <c r="E38" s="32">
+      <c r="E38" s="33">
         <v>0.59</v>
       </c>
-      <c r="F38" s="32">
+      <c r="F38" s="33">
         <v>0.56</v>
       </c>
-      <c r="G38" s="32">
+      <c r="G38" s="33">
         <v>0.48</v>
       </c>
-      <c r="H38" s="32">
+      <c r="H38" s="33">
         <v>0.41</v>
       </c>
-      <c r="I38" s="32">
+      <c r="I38" s="33">
         <v>0.52</v>
       </c>
-      <c r="J38" s="32">
+      <c r="J38" s="33">
         <v>0.49</v>
       </c>
-      <c r="K38" s="32">
+      <c r="K38" s="33">
         <v>0.52</v>
       </c>
-      <c r="L38" s="32">
+      <c r="L38" s="33">
         <v>0.67</v>
       </c>
-      <c r="M38" s="32">
+      <c r="M38" s="33">
         <v>0.52</v>
       </c>
-      <c r="N38" s="32">
+      <c r="N38" s="33">
         <v>0.49</v>
       </c>
-      <c r="O38" s="32">
+      <c r="O38" s="33">
         <v>0.55</v>
       </c>
-      <c r="P38" s="32">
+      <c r="P38" s="33">
         <v>0.66</v>
       </c>
-      <c r="Q38" s="32">
+      <c r="Q38" s="33">
         <v>0.66</v>
       </c>
-      <c r="R38" s="32">
+      <c r="R38" s="33">
         <v>0.38</v>
       </c>
-      <c r="S38" s="32">
+      <c r="S38" s="33">
         <v>0.78</v>
       </c>
-      <c r="T38" s="32">
+      <c r="T38" s="33">
         <v>0.76</v>
       </c>
-      <c r="U38" s="32">
+      <c r="U38" s="33">
         <v>0.81</v>
       </c>
-      <c r="V38" s="32">
+      <c r="V38" s="33">
         <v>0.58</v>
       </c>
-      <c r="W38" s="32">
+      <c r="W38" s="33">
         <v>0.47</v>
       </c>
-      <c r="X38" s="32">
+      <c r="X38" s="33">
         <v>0.4</v>
       </c>
-      <c r="Y38" s="32">
+      <c r="Y38" s="33">
         <v>0.42</v>
       </c>
-      <c r="Z38" s="32">
+      <c r="Z38" s="33">
         <v>0.4</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="30" t="s">
+      <c r="A39" s="31" t="s">
         <v>333</v>
       </c>
-      <c r="B39" s="32">
+      <c r="B39" s="33">
         <v>0.57</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="33">
         <v>0.56</v>
       </c>
-      <c r="D39" s="32">
+      <c r="D39" s="33">
         <v>0.52</v>
       </c>
-      <c r="E39" s="32">
+      <c r="E39" s="33">
         <v>0.51</v>
       </c>
-      <c r="F39" s="32">
+      <c r="F39" s="33">
         <v>0.49</v>
       </c>
-      <c r="G39" s="32">
+      <c r="G39" s="33">
         <v>0.48</v>
       </c>
-      <c r="H39" s="32">
+      <c r="H39" s="33">
         <v>0.5</v>
       </c>
-      <c r="I39" s="32">
+      <c r="I39" s="33">
         <v>0.53</v>
       </c>
-      <c r="J39" s="32">
+      <c r="J39" s="33">
         <v>0.53</v>
       </c>
-      <c r="K39" s="32">
+      <c r="K39" s="33">
         <v>0.55</v>
       </c>
-      <c r="L39" s="32">
+      <c r="L39" s="33">
         <v>0.58</v>
       </c>
-      <c r="M39" s="32">
+      <c r="M39" s="33">
         <v>0.58</v>
       </c>
-      <c r="N39" s="32">
+      <c r="N39" s="33">
         <v>0.55</v>
       </c>
-      <c r="O39" s="32">
+      <c r="O39" s="33">
         <v>0.61</v>
       </c>
-      <c r="P39" s="32">
+      <c r="P39" s="33">
         <v>0.65</v>
       </c>
-      <c r="Q39" s="32">
+      <c r="Q39" s="33">
         <v>0.67</v>
       </c>
-      <c r="R39" s="32">
+      <c r="R39" s="33">
         <v>0.66</v>
       </c>
-      <c r="S39" s="32">
+      <c r="S39" s="33">
         <v>0.69</v>
       </c>
-      <c r="T39" s="32">
+      <c r="T39" s="33">
         <v>0.62</v>
       </c>
-      <c r="U39" s="32">
+      <c r="U39" s="33">
         <v>0.55</v>
       </c>
-      <c r="V39" s="32">
+      <c r="V39" s="33">
         <v>0.46</v>
       </c>
-      <c r="W39" s="34"/>
-      <c r="X39" s="34"/>
-      <c r="Y39" s="34"/>
-      <c r="Z39" s="34"/>
+      <c r="W39" s="35"/>
+      <c r="X39" s="35"/>
+      <c r="Y39" s="35"/>
+      <c r="Z39" s="35"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="28" t="s">
+      <c r="A40" s="29" t="s">
         <v>334</v>
       </c>
-      <c r="B40" s="29"/>
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="29"/>
-      <c r="G40" s="29"/>
-      <c r="H40" s="29"/>
-      <c r="I40" s="29"/>
-      <c r="J40" s="29"/>
-      <c r="K40" s="29"/>
-      <c r="L40" s="29"/>
-      <c r="M40" s="29"/>
-      <c r="N40" s="29"/>
-      <c r="O40" s="29"/>
-      <c r="P40" s="29"/>
-      <c r="Q40" s="29"/>
-      <c r="R40" s="29"/>
-      <c r="S40" s="29"/>
-      <c r="T40" s="29"/>
-      <c r="U40" s="29"/>
-      <c r="V40" s="29"/>
-      <c r="W40" s="29"/>
-      <c r="X40" s="29"/>
-      <c r="Y40" s="29"/>
-      <c r="Z40" s="29"/>
+      <c r="B40" s="30"/>
+      <c r="C40" s="30"/>
+      <c r="D40" s="30"/>
+      <c r="E40" s="30"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="30"/>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30"/>
+      <c r="J40" s="30"/>
+      <c r="K40" s="30"/>
+      <c r="L40" s="30"/>
+      <c r="M40" s="30"/>
+      <c r="N40" s="30"/>
+      <c r="O40" s="30"/>
+      <c r="P40" s="30"/>
+      <c r="Q40" s="30"/>
+      <c r="R40" s="30"/>
+      <c r="S40" s="30"/>
+      <c r="T40" s="30"/>
+      <c r="U40" s="30"/>
+      <c r="V40" s="30"/>
+      <c r="W40" s="30"/>
+      <c r="X40" s="30"/>
+      <c r="Y40" s="30"/>
+      <c r="Z40" s="30"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="30" t="s">
+      <c r="A41" s="31" t="s">
         <v>335</v>
       </c>
-      <c r="B41" s="32">
+      <c r="B41" s="33">
         <v>0.61</v>
       </c>
-      <c r="C41" s="32">
+      <c r="C41" s="33">
         <v>0.74</v>
       </c>
-      <c r="D41" s="32">
+      <c r="D41" s="33">
         <v>0.75</v>
       </c>
-      <c r="E41" s="32">
+      <c r="E41" s="33">
         <v>0.69</v>
       </c>
-      <c r="F41" s="32">
+      <c r="F41" s="33">
         <v>0.61</v>
       </c>
-      <c r="G41" s="32">
+      <c r="G41" s="33">
         <v>0.52</v>
       </c>
-      <c r="H41" s="32">
+      <c r="H41" s="33">
         <v>0.44</v>
       </c>
-      <c r="I41" s="32">
+      <c r="I41" s="33">
         <v>0.53</v>
       </c>
-      <c r="J41" s="32">
+      <c r="J41" s="33">
         <v>0.52</v>
       </c>
-      <c r="K41" s="32">
+      <c r="K41" s="33">
         <v>0.53</v>
       </c>
-      <c r="L41" s="32">
+      <c r="L41" s="33">
         <v>0.67</v>
       </c>
-      <c r="M41" s="32">
+      <c r="M41" s="33">
         <v>0.52</v>
       </c>
-      <c r="N41" s="32">
+      <c r="N41" s="33">
         <v>0.49</v>
       </c>
-      <c r="O41" s="32">
+      <c r="O41" s="33">
         <v>0.55</v>
       </c>
-      <c r="P41" s="32">
+      <c r="P41" s="33">
         <v>0.66</v>
       </c>
-      <c r="Q41" s="32">
+      <c r="Q41" s="33">
         <v>0.66</v>
       </c>
-      <c r="R41" s="32">
+      <c r="R41" s="33">
         <v>0.38</v>
       </c>
-      <c r="S41" s="32">
+      <c r="S41" s="33">
         <v>0.78</v>
       </c>
-      <c r="T41" s="32">
+      <c r="T41" s="33">
         <v>0.76</v>
       </c>
-      <c r="U41" s="32">
+      <c r="U41" s="33">
         <v>0.86</v>
       </c>
-      <c r="V41" s="32">
+      <c r="V41" s="33">
         <v>0.6</v>
       </c>
-      <c r="W41" s="32">
+      <c r="W41" s="33">
         <v>0.48</v>
       </c>
-      <c r="X41" s="32">
+      <c r="X41" s="33">
         <v>0.41</v>
       </c>
-      <c r="Y41" s="32">
+      <c r="Y41" s="33">
         <v>0.43</v>
       </c>
-      <c r="Z41" s="32">
+      <c r="Z41" s="33">
         <v>0.41</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="30" t="s">
+      <c r="A42" s="31" t="s">
         <v>336</v>
       </c>
-      <c r="B42" s="32">
+      <c r="B42" s="33">
         <v>0.67</v>
       </c>
-      <c r="C42" s="32">
+      <c r="C42" s="33">
         <v>0.64</v>
       </c>
-      <c r="D42" s="32">
+      <c r="D42" s="33">
         <v>0.58</v>
       </c>
-      <c r="E42" s="32">
+      <c r="E42" s="33">
         <v>0.55</v>
       </c>
-      <c r="F42" s="32">
+      <c r="F42" s="33">
         <v>0.52</v>
       </c>
-      <c r="G42" s="32">
+      <c r="G42" s="33">
         <v>0.51</v>
       </c>
-      <c r="H42" s="32">
+      <c r="H42" s="33">
         <v>0.52</v>
       </c>
-      <c r="I42" s="32">
+      <c r="I42" s="33">
         <v>0.55</v>
       </c>
-      <c r="J42" s="32">
+      <c r="J42" s="33">
         <v>0.54</v>
       </c>
-      <c r="K42" s="32">
+      <c r="K42" s="33">
         <v>0.55</v>
       </c>
-      <c r="L42" s="32">
+      <c r="L42" s="33">
         <v>0.58</v>
       </c>
-      <c r="M42" s="32">
+      <c r="M42" s="33">
         <v>0.58</v>
       </c>
-      <c r="N42" s="32">
+      <c r="N42" s="33">
         <v>0.55</v>
       </c>
-      <c r="O42" s="32">
+      <c r="O42" s="33">
         <v>0.61</v>
       </c>
-      <c r="P42" s="32">
+      <c r="P42" s="33">
         <v>0.65</v>
       </c>
-      <c r="Q42" s="32">
+      <c r="Q42" s="33">
         <v>0.68</v>
       </c>
-      <c r="R42" s="32">
+      <c r="R42" s="33">
         <v>0.67</v>
       </c>
-      <c r="S42" s="32">
+      <c r="S42" s="33">
         <v>0.71</v>
       </c>
-      <c r="T42" s="32">
+      <c r="T42" s="33">
         <v>0.64</v>
       </c>
-      <c r="U42" s="32">
+      <c r="U42" s="33">
         <v>0.57</v>
       </c>
-      <c r="V42" s="32">
+      <c r="V42" s="33">
         <v>0.47</v>
       </c>
-      <c r="W42" s="34"/>
-      <c r="X42" s="34"/>
-      <c r="Y42" s="34"/>
-      <c r="Z42" s="34"/>
+      <c r="W42" s="35"/>
+      <c r="X42" s="35"/>
+      <c r="Y42" s="35"/>
+      <c r="Z42" s="35"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="28" t="s">
+      <c r="A43" s="29" t="s">
         <v>337</v>
       </c>
-      <c r="B43" s="29"/>
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
-      <c r="F43" s="29"/>
-      <c r="G43" s="29"/>
-      <c r="H43" s="29"/>
-      <c r="I43" s="29"/>
-      <c r="J43" s="29"/>
-      <c r="K43" s="29"/>
-      <c r="L43" s="29"/>
-      <c r="M43" s="29"/>
-      <c r="N43" s="29"/>
-      <c r="O43" s="29"/>
-      <c r="P43" s="29"/>
-      <c r="Q43" s="29"/>
-      <c r="R43" s="29"/>
-      <c r="S43" s="29"/>
-      <c r="T43" s="29"/>
-      <c r="U43" s="29"/>
-      <c r="V43" s="29"/>
-      <c r="W43" s="29"/>
-      <c r="X43" s="29"/>
-      <c r="Y43" s="29"/>
-      <c r="Z43" s="29"/>
+      <c r="B43" s="30"/>
+      <c r="C43" s="30"/>
+      <c r="D43" s="30"/>
+      <c r="E43" s="30"/>
+      <c r="F43" s="30"/>
+      <c r="G43" s="30"/>
+      <c r="H43" s="30"/>
+      <c r="I43" s="30"/>
+      <c r="J43" s="30"/>
+      <c r="K43" s="30"/>
+      <c r="L43" s="30"/>
+      <c r="M43" s="30"/>
+      <c r="N43" s="30"/>
+      <c r="O43" s="30"/>
+      <c r="P43" s="30"/>
+      <c r="Q43" s="30"/>
+      <c r="R43" s="30"/>
+      <c r="S43" s="30"/>
+      <c r="T43" s="30"/>
+      <c r="U43" s="30"/>
+      <c r="V43" s="30"/>
+      <c r="W43" s="30"/>
+      <c r="X43" s="30"/>
+      <c r="Y43" s="30"/>
+      <c r="Z43" s="30"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="30" t="s">
+      <c r="A44" s="31" t="s">
         <v>338</v>
       </c>
-      <c r="B44" s="32">
+      <c r="B44" s="33">
         <v>2.06</v>
       </c>
-      <c r="C44" s="32">
+      <c r="C44" s="33">
         <v>2.96</v>
       </c>
-      <c r="D44" s="32">
+      <c r="D44" s="33">
         <v>2.48</v>
       </c>
-      <c r="E44" s="32">
+      <c r="E44" s="33">
         <v>2.13</v>
       </c>
-      <c r="F44" s="32">
+      <c r="F44" s="33">
         <v>2.21</v>
       </c>
-      <c r="G44" s="32">
+      <c r="G44" s="33">
         <v>1.9</v>
       </c>
-      <c r="H44" s="32">
+      <c r="H44" s="33">
         <v>2.33</v>
       </c>
-      <c r="I44" s="32">
+      <c r="I44" s="33">
         <v>3.79</v>
       </c>
-      <c r="J44" s="32">
+      <c r="J44" s="33">
         <v>3.37</v>
       </c>
-      <c r="K44" s="32">
+      <c r="K44" s="33">
         <v>6.42</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="33">
         <v>5.23</v>
       </c>
-      <c r="M44" s="32">
+      <c r="M44" s="33">
         <v>3.63</v>
       </c>
-      <c r="N44" s="32">
+      <c r="N44" s="33">
         <v>3.56</v>
       </c>
-      <c r="O44" s="32">
+      <c r="O44" s="33">
         <v>4.23</v>
       </c>
-      <c r="P44" s="32">
+      <c r="P44" s="33">
         <v>4.68</v>
       </c>
-      <c r="Q44" s="32">
+      <c r="Q44" s="33">
         <v>4.26</v>
       </c>
-      <c r="R44" s="32">
+      <c r="R44" s="33">
         <v>2.31</v>
       </c>
-      <c r="S44" s="32">
+      <c r="S44" s="33">
         <v>4.94</v>
       </c>
-      <c r="T44" s="32">
+      <c r="T44" s="33">
         <v>2.61</v>
       </c>
-      <c r="U44" s="32">
+      <c r="U44" s="33">
         <v>3.73</v>
       </c>
-      <c r="V44" s="32">
+      <c r="V44" s="33">
         <v>2.54</v>
       </c>
-      <c r="W44" s="32">
+      <c r="W44" s="33">
         <v>1.83</v>
       </c>
-      <c r="X44" s="32">
+      <c r="X44" s="33">
         <v>1.81</v>
       </c>
-      <c r="Y44" s="32">
+      <c r="Y44" s="33">
         <v>2.07</v>
       </c>
-      <c r="Z44" s="32">
+      <c r="Z44" s="33">
         <v>1.01</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="30" t="s">
+      <c r="A45" s="31" t="s">
         <v>339</v>
       </c>
-      <c r="B45" s="32">
+      <c r="B45" s="33">
         <v>2.32</v>
       </c>
-      <c r="C45" s="32">
+      <c r="C45" s="33">
         <v>2.26</v>
       </c>
-      <c r="D45" s="32">
+      <c r="D45" s="33">
         <v>2.18</v>
       </c>
-      <c r="E45" s="32">
+      <c r="E45" s="33">
         <v>2.36</v>
       </c>
-      <c r="F45" s="32">
+      <c r="F45" s="33">
         <v>2.55</v>
       </c>
-      <c r="G45" s="32">
+      <c r="G45" s="33">
         <v>2.95</v>
       </c>
-      <c r="H45" s="32">
+      <c r="H45" s="33">
         <v>3.68</v>
       </c>
-      <c r="I45" s="32">
+      <c r="I45" s="33">
         <v>4.22</v>
       </c>
-      <c r="J45" s="32">
+      <c r="J45" s="33">
         <v>4.28</v>
       </c>
-      <c r="K45" s="32">
+      <c r="K45" s="33">
         <v>4.65</v>
       </c>
-      <c r="L45" s="32">
+      <c r="L45" s="33">
         <v>4.3</v>
       </c>
-      <c r="M45" s="32">
+      <c r="M45" s="33">
         <v>4.08</v>
       </c>
-      <c r="N45" s="32">
+      <c r="N45" s="33">
         <v>3.79</v>
       </c>
-      <c r="O45" s="32">
+      <c r="O45" s="33">
         <v>4.07</v>
       </c>
-      <c r="P45" s="32">
+      <c r="P45" s="33">
         <v>3.59</v>
       </c>
-      <c r="Q45" s="32">
+      <c r="Q45" s="33">
         <v>3.44</v>
       </c>
-      <c r="R45" s="32">
+      <c r="R45" s="33">
         <v>3.13</v>
       </c>
-      <c r="S45" s="32">
+      <c r="S45" s="33">
         <v>3.03</v>
       </c>
-      <c r="T45" s="32">
+      <c r="T45" s="33">
         <v>2.54</v>
       </c>
-      <c r="U45" s="32">
+      <c r="U45" s="33">
         <v>2.45</v>
       </c>
-      <c r="V45" s="32">
+      <c r="V45" s="33">
         <v>1.75</v>
       </c>
-      <c r="W45" s="34"/>
-      <c r="X45" s="34"/>
-      <c r="Y45" s="34"/>
-      <c r="Z45" s="34"/>
+      <c r="W45" s="35"/>
+      <c r="X45" s="35"/>
+      <c r="Y45" s="35"/>
+      <c r="Z45" s="35"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="28" t="s">
+      <c r="A46" s="29" t="s">
         <v>340</v>
       </c>
-      <c r="B46" s="29"/>
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
-      <c r="F46" s="29"/>
-      <c r="G46" s="29"/>
-      <c r="H46" s="29"/>
-      <c r="I46" s="29"/>
-      <c r="J46" s="29"/>
-      <c r="K46" s="29"/>
-      <c r="L46" s="29"/>
-      <c r="M46" s="29"/>
-      <c r="N46" s="29"/>
-      <c r="O46" s="29"/>
-      <c r="P46" s="29"/>
-      <c r="Q46" s="29"/>
-      <c r="R46" s="29"/>
-      <c r="S46" s="29"/>
-      <c r="T46" s="29"/>
-      <c r="U46" s="29"/>
-      <c r="V46" s="29"/>
-      <c r="W46" s="29"/>
-      <c r="X46" s="29"/>
-      <c r="Y46" s="29"/>
-      <c r="Z46" s="29"/>
+      <c r="B46" s="30"/>
+      <c r="C46" s="30"/>
+      <c r="D46" s="30"/>
+      <c r="E46" s="30"/>
+      <c r="F46" s="30"/>
+      <c r="G46" s="30"/>
+      <c r="H46" s="30"/>
+      <c r="I46" s="30"/>
+      <c r="J46" s="30"/>
+      <c r="K46" s="30"/>
+      <c r="L46" s="30"/>
+      <c r="M46" s="30"/>
+      <c r="N46" s="30"/>
+      <c r="O46" s="30"/>
+      <c r="P46" s="30"/>
+      <c r="Q46" s="30"/>
+      <c r="R46" s="30"/>
+      <c r="S46" s="30"/>
+      <c r="T46" s="30"/>
+      <c r="U46" s="30"/>
+      <c r="V46" s="30"/>
+      <c r="W46" s="30"/>
+      <c r="X46" s="30"/>
+      <c r="Y46" s="30"/>
+      <c r="Z46" s="30"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="30" t="s">
+      <c r="A47" s="31" t="s">
         <v>341</v>
       </c>
-      <c r="B47" s="32">
+      <c r="B47" s="33">
         <v>10.19</v>
       </c>
-      <c r="C47" s="34"/>
-      <c r="D47" s="31">
+      <c r="C47" s="35"/>
+      <c r="D47" s="32">
         <v>118.75</v>
       </c>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="31">
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="32">
         <v>260.09</v>
       </c>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="31">
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="32">
         <v>531.79</v>
       </c>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="32">
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="33">
         <v>8.45</v>
       </c>
-      <c r="R47" s="32">
+      <c r="R47" s="33">
         <v>4.22</v>
       </c>
-      <c r="S47" s="32">
+      <c r="S47" s="33">
         <v>10.25</v>
       </c>
-      <c r="T47" s="32">
+      <c r="T47" s="33">
         <v>8.12</v>
       </c>
-      <c r="U47" s="32">
+      <c r="U47" s="33">
         <v>5.82</v>
       </c>
-      <c r="V47" s="32">
+      <c r="V47" s="33">
         <v>3.57</v>
       </c>
-      <c r="W47" s="32">
+      <c r="W47" s="33">
         <v>2.88</v>
       </c>
-      <c r="X47" s="32">
+      <c r="X47" s="33">
         <v>4.7</v>
       </c>
-      <c r="Y47" s="32">
+      <c r="Y47" s="33">
         <v>7.38</v>
       </c>
-      <c r="Z47" s="34"/>
+      <c r="Z47" s="35"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="30" t="s">
+      <c r="A48" s="31" t="s">
         <v>342</v>
       </c>
-      <c r="B48" s="34"/>
-      <c r="C48" s="34"/>
-      <c r="D48" s="34"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="34"/>
-      <c r="J48" s="34"/>
-      <c r="K48" s="34"/>
-      <c r="L48" s="34"/>
-      <c r="M48" s="34"/>
-      <c r="N48" s="34"/>
-      <c r="O48" s="34"/>
-      <c r="P48" s="32">
+      <c r="B48" s="35"/>
+      <c r="C48" s="35"/>
+      <c r="D48" s="35"/>
+      <c r="E48" s="35"/>
+      <c r="F48" s="35"/>
+      <c r="G48" s="35"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="33">
         <v>10.04</v>
       </c>
-      <c r="Q48" s="32">
+      <c r="Q48" s="33">
         <v>7.19</v>
       </c>
-      <c r="R48" s="32">
+      <c r="R48" s="33">
         <v>6.03</v>
       </c>
-      <c r="S48" s="32">
+      <c r="S48" s="33">
         <v>5.66</v>
       </c>
-      <c r="T48" s="32">
+      <c r="T48" s="33">
         <v>4.87</v>
       </c>
-      <c r="U48" s="32">
+      <c r="U48" s="33">
         <v>4.4</v>
       </c>
-      <c r="V48" s="32">
+      <c r="V48" s="33">
         <v>6.66</v>
       </c>
-      <c r="W48" s="34"/>
-      <c r="X48" s="34"/>
-      <c r="Y48" s="34"/>
-      <c r="Z48" s="34"/>
+      <c r="W48" s="35"/>
+      <c r="X48" s="35"/>
+      <c r="Y48" s="35"/>
+      <c r="Z48" s="35"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="28" t="s">
+      <c r="A49" s="29" t="s">
         <v>343</v>
       </c>
-      <c r="B49" s="29"/>
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
-      <c r="F49" s="29"/>
-      <c r="G49" s="29"/>
-      <c r="H49" s="29"/>
-      <c r="I49" s="29"/>
-      <c r="J49" s="29"/>
-      <c r="K49" s="29"/>
-      <c r="L49" s="29"/>
-      <c r="M49" s="29"/>
-      <c r="N49" s="29"/>
-      <c r="O49" s="29"/>
-      <c r="P49" s="29"/>
-      <c r="Q49" s="29"/>
-      <c r="R49" s="29"/>
-      <c r="S49" s="29"/>
-      <c r="T49" s="29"/>
-      <c r="U49" s="29"/>
-      <c r="V49" s="29"/>
-      <c r="W49" s="29"/>
-      <c r="X49" s="29"/>
-      <c r="Y49" s="29"/>
-      <c r="Z49" s="29"/>
+      <c r="B49" s="30"/>
+      <c r="C49" s="30"/>
+      <c r="D49" s="30"/>
+      <c r="E49" s="30"/>
+      <c r="F49" s="30"/>
+      <c r="G49" s="30"/>
+      <c r="H49" s="30"/>
+      <c r="I49" s="30"/>
+      <c r="J49" s="30"/>
+      <c r="K49" s="30"/>
+      <c r="L49" s="30"/>
+      <c r="M49" s="30"/>
+      <c r="N49" s="30"/>
+      <c r="O49" s="30"/>
+      <c r="P49" s="30"/>
+      <c r="Q49" s="30"/>
+      <c r="R49" s="30"/>
+      <c r="S49" s="30"/>
+      <c r="T49" s="30"/>
+      <c r="U49" s="30"/>
+      <c r="V49" s="30"/>
+      <c r="W49" s="30"/>
+      <c r="X49" s="30"/>
+      <c r="Y49" s="30"/>
+      <c r="Z49" s="30"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="30" t="s">
+      <c r="A50" s="31" t="s">
         <v>344</v>
       </c>
-      <c r="B50" s="32">
+      <c r="B50" s="33">
         <v>2.3</v>
       </c>
-      <c r="C50" s="32">
+      <c r="C50" s="33">
         <v>4.95</v>
       </c>
-      <c r="D50" s="32">
+      <c r="D50" s="33">
         <v>5.2</v>
       </c>
-      <c r="E50" s="31">
+      <c r="E50" s="32">
         <v>156.04</v>
       </c>
-      <c r="F50" s="34"/>
-      <c r="G50" s="32">
+      <c r="F50" s="35"/>
+      <c r="G50" s="33">
         <v>10.22</v>
       </c>
-      <c r="H50" s="34"/>
-      <c r="I50" s="34"/>
-      <c r="J50" s="34"/>
-      <c r="K50" s="34"/>
-      <c r="L50" s="34"/>
-      <c r="M50" s="32">
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="33">
         <v>8.91</v>
       </c>
-      <c r="N50" s="32">
+      <c r="N50" s="33">
         <v>5.58</v>
       </c>
-      <c r="O50" s="32">
+      <c r="O50" s="33">
         <v>47.27</v>
       </c>
-      <c r="P50" s="32">
+      <c r="P50" s="33">
         <v>6.09</v>
       </c>
-      <c r="Q50" s="32">
+      <c r="Q50" s="33">
         <v>5.07</v>
       </c>
-      <c r="R50" s="32">
+      <c r="R50" s="33">
         <v>4.87</v>
       </c>
-      <c r="S50" s="32">
+      <c r="S50" s="33">
         <v>9.89</v>
       </c>
-      <c r="T50" s="32">
+      <c r="T50" s="33">
         <v>3.11</v>
       </c>
-      <c r="U50" s="32">
+      <c r="U50" s="33">
         <v>7.32</v>
       </c>
-      <c r="V50" s="32">
+      <c r="V50" s="33">
         <v>3.15</v>
       </c>
-      <c r="W50" s="32">
+      <c r="W50" s="33">
         <v>2.84</v>
       </c>
-      <c r="X50" s="32">
+      <c r="X50" s="33">
         <v>3.85</v>
       </c>
-      <c r="Y50" s="32">
+      <c r="Y50" s="33">
         <v>4.32</v>
       </c>
-      <c r="Z50" s="32">
+      <c r="Z50" s="33">
         <v>5.59</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="30" t="s">
+      <c r="A51" s="31" t="s">
         <v>345</v>
       </c>
-      <c r="B51" s="32">
+      <c r="B51" s="33">
         <v>7.24</v>
       </c>
-      <c r="C51" s="32">
+      <c r="C51" s="33">
         <v>13.91</v>
       </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="34"/>
-      <c r="F51" s="34"/>
-      <c r="G51" s="34"/>
-      <c r="H51" s="34"/>
-      <c r="I51" s="34"/>
-      <c r="J51" s="34"/>
-      <c r="K51" s="34"/>
-      <c r="L51" s="34"/>
-      <c r="M51" s="32">
+      <c r="D51" s="35"/>
+      <c r="E51" s="35"/>
+      <c r="F51" s="35"/>
+      <c r="G51" s="35"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="33">
         <v>7.25</v>
       </c>
-      <c r="N51" s="32">
+      <c r="N51" s="33">
         <v>6.6</v>
       </c>
-      <c r="O51" s="32">
+      <c r="O51" s="33">
         <v>7.43</v>
       </c>
-      <c r="P51" s="32">
+      <c r="P51" s="33">
         <v>5.08</v>
       </c>
-      <c r="Q51" s="32">
+      <c r="Q51" s="33">
         <v>5.22</v>
       </c>
-      <c r="R51" s="32">
+      <c r="R51" s="33">
         <v>4.76</v>
       </c>
-      <c r="S51" s="32">
+      <c r="S51" s="33">
         <v>4.42</v>
       </c>
-      <c r="T51" s="32">
+      <c r="T51" s="33">
         <v>3.72</v>
       </c>
-      <c r="U51" s="32">
+      <c r="U51" s="33">
         <v>4.11</v>
       </c>
-      <c r="V51" s="32">
+      <c r="V51" s="33">
         <v>3.62</v>
       </c>
-      <c r="W51" s="34"/>
-      <c r="X51" s="34"/>
-      <c r="Y51" s="34"/>
-      <c r="Z51" s="34"/>
+      <c r="W51" s="35"/>
+      <c r="X51" s="35"/>
+      <c r="Y51" s="35"/>
+      <c r="Z51" s="35"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="28" t="s">
+      <c r="A52" s="29" t="s">
         <v>346</v>
       </c>
-      <c r="B52" s="29"/>
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
-      <c r="F52" s="29"/>
-      <c r="G52" s="29"/>
-      <c r="H52" s="29"/>
-      <c r="I52" s="29"/>
-      <c r="J52" s="29"/>
-      <c r="K52" s="29"/>
-      <c r="L52" s="29"/>
-      <c r="M52" s="29"/>
-      <c r="N52" s="29"/>
-      <c r="O52" s="29"/>
-      <c r="P52" s="29"/>
-      <c r="Q52" s="29"/>
-      <c r="R52" s="29"/>
-      <c r="S52" s="29"/>
-      <c r="T52" s="29"/>
-      <c r="U52" s="29"/>
-      <c r="V52" s="29"/>
-      <c r="W52" s="29"/>
-      <c r="X52" s="29"/>
-      <c r="Y52" s="29"/>
-      <c r="Z52" s="29"/>
+      <c r="B52" s="30"/>
+      <c r="C52" s="30"/>
+      <c r="D52" s="30"/>
+      <c r="E52" s="30"/>
+      <c r="F52" s="30"/>
+      <c r="G52" s="30"/>
+      <c r="H52" s="30"/>
+      <c r="I52" s="30"/>
+      <c r="J52" s="30"/>
+      <c r="K52" s="30"/>
+      <c r="L52" s="30"/>
+      <c r="M52" s="30"/>
+      <c r="N52" s="30"/>
+      <c r="O52" s="30"/>
+      <c r="P52" s="30"/>
+      <c r="Q52" s="30"/>
+      <c r="R52" s="30"/>
+      <c r="S52" s="30"/>
+      <c r="T52" s="30"/>
+      <c r="U52" s="30"/>
+      <c r="V52" s="30"/>
+      <c r="W52" s="30"/>
+      <c r="X52" s="30"/>
+      <c r="Y52" s="30"/>
+      <c r="Z52" s="30"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="30" t="s">
+      <c r="A53" s="31" t="s">
         <v>347</v>
       </c>
-      <c r="B53" s="32">
+      <c r="B53" s="33">
         <v>3.0</v>
       </c>
-      <c r="C53" s="32">
+      <c r="C53" s="33">
         <v>5.7</v>
       </c>
-      <c r="D53" s="32">
+      <c r="D53" s="33">
         <v>5.86</v>
       </c>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="32">
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="33">
         <v>13.19</v>
       </c>
-      <c r="H53" s="32">
+      <c r="H53" s="33">
         <v>7.73</v>
       </c>
-      <c r="I53" s="32">
+      <c r="I53" s="33">
         <v>4.84</v>
       </c>
-      <c r="J53" s="32">
+      <c r="J53" s="33">
         <v>2.8</v>
       </c>
-      <c r="K53" s="32">
+      <c r="K53" s="33">
         <v>2.65</v>
       </c>
-      <c r="L53" s="32">
+      <c r="L53" s="33">
         <v>5.67</v>
       </c>
-      <c r="M53" s="32">
+      <c r="M53" s="33">
         <v>35.44</v>
       </c>
-      <c r="N53" s="32">
+      <c r="N53" s="33">
         <v>10.06</v>
       </c>
-      <c r="O53" s="34"/>
-      <c r="P53" s="32">
+      <c r="O53" s="35"/>
+      <c r="P53" s="33">
         <v>7.86</v>
       </c>
-      <c r="Q53" s="32">
+      <c r="Q53" s="33">
         <v>6.38</v>
       </c>
-      <c r="R53" s="32">
+      <c r="R53" s="33">
         <v>7.67</v>
       </c>
-      <c r="S53" s="32">
+      <c r="S53" s="33">
         <v>15.37</v>
       </c>
-      <c r="T53" s="32">
+      <c r="T53" s="33">
         <v>3.51</v>
       </c>
-      <c r="U53" s="32">
+      <c r="U53" s="33">
         <v>10.5</v>
       </c>
-      <c r="V53" s="32">
+      <c r="V53" s="33">
         <v>3.84</v>
       </c>
-      <c r="W53" s="32">
+      <c r="W53" s="33">
         <v>3.68</v>
       </c>
-      <c r="X53" s="32">
+      <c r="X53" s="33">
         <v>6.38</v>
       </c>
-      <c r="Y53" s="32">
+      <c r="Y53" s="33">
         <v>7.73</v>
       </c>
-      <c r="Z53" s="32">
+      <c r="Z53" s="33">
         <v>19.84</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="30" t="s">
+      <c r="A54" s="31" t="s">
         <v>348</v>
       </c>
-      <c r="B54" s="32">
+      <c r="B54" s="33">
         <v>10.1</v>
       </c>
-      <c r="C54" s="32">
+      <c r="C54" s="33">
         <v>20.63</v>
       </c>
-      <c r="D54" s="32">
+      <c r="D54" s="33">
         <v>25.16</v>
       </c>
-      <c r="E54" s="32">
+      <c r="E54" s="33">
         <v>18.12</v>
       </c>
-      <c r="F54" s="32">
+      <c r="F54" s="33">
         <v>7.68</v>
       </c>
-      <c r="G54" s="32">
+      <c r="G54" s="33">
         <v>4.51</v>
       </c>
-      <c r="H54" s="32">
+      <c r="H54" s="33">
         <v>4.04</v>
       </c>
-      <c r="I54" s="32">
+      <c r="I54" s="33">
         <v>4.0</v>
       </c>
-      <c r="J54" s="32">
+      <c r="J54" s="33">
         <v>4.08</v>
       </c>
-      <c r="K54" s="32">
+      <c r="K54" s="33">
         <v>6.1</v>
       </c>
-      <c r="L54" s="32">
+      <c r="L54" s="33">
         <v>11.02</v>
       </c>
-      <c r="M54" s="32">
+      <c r="M54" s="33">
         <v>12.39</v>
       </c>
-      <c r="N54" s="32">
+      <c r="N54" s="33">
         <v>10.32</v>
       </c>
-      <c r="O54" s="32">
+      <c r="O54" s="33">
         <v>11.28</v>
       </c>
-      <c r="P54" s="32">
+      <c r="P54" s="33">
         <v>6.46</v>
       </c>
-      <c r="Q54" s="32">
+      <c r="Q54" s="33">
         <v>6.72</v>
       </c>
-      <c r="R54" s="32">
+      <c r="R54" s="33">
         <v>6.08</v>
       </c>
-      <c r="S54" s="32">
+      <c r="S54" s="33">
         <v>5.54</v>
       </c>
-      <c r="T54" s="32">
+      <c r="T54" s="33">
         <v>4.67</v>
       </c>
-      <c r="U54" s="32">
+      <c r="U54" s="33">
         <v>5.67</v>
       </c>
-      <c r="V54" s="32">
+      <c r="V54" s="33">
         <v>5.34</v>
       </c>
-      <c r="W54" s="34"/>
-      <c r="X54" s="34"/>
-      <c r="Y54" s="34"/>
-      <c r="Z54" s="34"/>
+      <c r="W54" s="35"/>
+      <c r="X54" s="35"/>
+      <c r="Y54" s="35"/>
+      <c r="Z54" s="35"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="28" t="s">
+      <c r="A55" s="29" t="s">
         <v>349</v>
       </c>
-      <c r="B55" s="29"/>
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
-      <c r="F55" s="29"/>
-      <c r="G55" s="29"/>
-      <c r="H55" s="29"/>
-      <c r="I55" s="29"/>
-      <c r="J55" s="29"/>
-      <c r="K55" s="29"/>
-      <c r="L55" s="29"/>
-      <c r="M55" s="29"/>
-      <c r="N55" s="29"/>
-      <c r="O55" s="29"/>
-      <c r="P55" s="29"/>
-      <c r="Q55" s="29"/>
-      <c r="R55" s="29"/>
-      <c r="S55" s="29"/>
-      <c r="T55" s="29"/>
-      <c r="U55" s="29"/>
-      <c r="V55" s="29"/>
-      <c r="W55" s="29"/>
-      <c r="X55" s="29"/>
-      <c r="Y55" s="29"/>
-      <c r="Z55" s="29"/>
+      <c r="B55" s="30"/>
+      <c r="C55" s="30"/>
+      <c r="D55" s="30"/>
+      <c r="E55" s="30"/>
+      <c r="F55" s="30"/>
+      <c r="G55" s="30"/>
+      <c r="H55" s="30"/>
+      <c r="I55" s="30"/>
+      <c r="J55" s="30"/>
+      <c r="K55" s="30"/>
+      <c r="L55" s="30"/>
+      <c r="M55" s="30"/>
+      <c r="N55" s="30"/>
+      <c r="O55" s="30"/>
+      <c r="P55" s="30"/>
+      <c r="Q55" s="30"/>
+      <c r="R55" s="30"/>
+      <c r="S55" s="30"/>
+      <c r="T55" s="30"/>
+      <c r="U55" s="30"/>
+      <c r="V55" s="30"/>
+      <c r="W55" s="30"/>
+      <c r="X55" s="30"/>
+      <c r="Y55" s="30"/>
+      <c r="Z55" s="30"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="30" t="s">
+      <c r="A56" s="31" t="s">
         <v>350</v>
       </c>
-      <c r="B56" s="32">
+      <c r="B56" s="33">
         <v>5.71</v>
       </c>
-      <c r="C56" s="32">
+      <c r="C56" s="33">
         <v>4.27</v>
       </c>
-      <c r="D56" s="32">
+      <c r="D56" s="33">
         <v>19.47</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="33">
         <v>11.33</v>
       </c>
-      <c r="F56" s="34"/>
-      <c r="G56" s="32">
+      <c r="F56" s="35"/>
+      <c r="G56" s="33">
         <v>9.18</v>
       </c>
-      <c r="H56" s="32">
+      <c r="H56" s="33">
         <v>12.31</v>
       </c>
-      <c r="I56" s="32">
+      <c r="I56" s="33">
         <v>9.87</v>
       </c>
-      <c r="J56" s="32">
+      <c r="J56" s="33">
         <v>5.31</v>
       </c>
-      <c r="K56" s="31">
+      <c r="K56" s="32">
         <v>322.07</v>
       </c>
-      <c r="L56" s="32">
+      <c r="L56" s="33">
         <v>46.67</v>
       </c>
-      <c r="M56" s="32">
+      <c r="M56" s="33">
         <v>35.44</v>
       </c>
-      <c r="N56" s="32">
+      <c r="N56" s="33">
         <v>10.06</v>
       </c>
-      <c r="O56" s="34"/>
-      <c r="P56" s="32">
+      <c r="O56" s="35"/>
+      <c r="P56" s="33">
         <v>7.86</v>
       </c>
-      <c r="Q56" s="32">
+      <c r="Q56" s="33">
         <v>6.38</v>
       </c>
-      <c r="R56" s="32">
+      <c r="R56" s="33">
         <v>6.63</v>
       </c>
-      <c r="S56" s="32">
+      <c r="S56" s="33">
         <v>15.58</v>
       </c>
-      <c r="T56" s="32">
+      <c r="T56" s="33">
         <v>3.55</v>
       </c>
-      <c r="U56" s="32">
+      <c r="U56" s="33">
         <v>10.5</v>
       </c>
-      <c r="V56" s="32">
+      <c r="V56" s="33">
         <v>3.84</v>
       </c>
-      <c r="W56" s="32">
+      <c r="W56" s="33">
         <v>3.68</v>
       </c>
-      <c r="X56" s="32">
+      <c r="X56" s="33">
         <v>6.39</v>
       </c>
-      <c r="Y56" s="32">
+      <c r="Y56" s="33">
         <v>7.74</v>
       </c>
-      <c r="Z56" s="32">
+      <c r="Z56" s="33">
         <v>19.84</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="30" t="s">
+      <c r="A57" s="31" t="s">
         <v>351</v>
       </c>
-      <c r="B57" s="32">
+      <c r="B57" s="33">
         <v>0.57</v>
       </c>
-      <c r="C57" s="32">
+      <c r="C57" s="33">
         <v>0.56</v>
       </c>
-      <c r="D57" s="32">
+      <c r="D57" s="33">
         <v>0.52</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="33">
         <v>0.51</v>
       </c>
-      <c r="F57" s="32">
+      <c r="F57" s="33">
         <v>0.49</v>
       </c>
-      <c r="G57" s="32">
+      <c r="G57" s="33">
         <v>0.48</v>
       </c>
-      <c r="H57" s="32">
+      <c r="H57" s="33">
         <v>0.5</v>
       </c>
-      <c r="I57" s="32">
+      <c r="I57" s="33">
         <v>0.53</v>
       </c>
-      <c r="J57" s="32">
+      <c r="J57" s="33">
         <v>0.53</v>
       </c>
-      <c r="K57" s="32">
+      <c r="K57" s="33">
         <v>0.55</v>
       </c>
-      <c r="L57" s="32">
+      <c r="L57" s="33">
         <v>0.58</v>
       </c>
-      <c r="M57" s="32">
+      <c r="M57" s="33">
         <v>0.58</v>
       </c>
-      <c r="N57" s="32">
+      <c r="N57" s="33">
         <v>0.55</v>
       </c>
-      <c r="O57" s="32">
+      <c r="O57" s="33">
         <v>0.61</v>
       </c>
-      <c r="P57" s="32">
+      <c r="P57" s="33">
         <v>0.65</v>
       </c>
-      <c r="Q57" s="32">
+      <c r="Q57" s="33">
         <v>0.67</v>
       </c>
-      <c r="R57" s="32">
+      <c r="R57" s="33">
         <v>0.66</v>
       </c>
-      <c r="S57" s="32">
+      <c r="S57" s="33">
         <v>0.69</v>
       </c>
-      <c r="T57" s="32">
+      <c r="T57" s="33">
         <v>0.62</v>
       </c>
-      <c r="U57" s="32">
+      <c r="U57" s="33">
         <v>0.55</v>
       </c>
-      <c r="V57" s="32">
+      <c r="V57" s="33">
         <v>0.46</v>
       </c>
-      <c r="W57" s="34"/>
-      <c r="X57" s="34"/>
-      <c r="Y57" s="34"/>
-      <c r="Z57" s="34"/>
+      <c r="W57" s="35"/>
+      <c r="X57" s="35"/>
+      <c r="Y57" s="35"/>
+      <c r="Z57" s="35"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="28" t="s">
+      <c r="A58" s="29" t="s">
         <v>352</v>
       </c>
-      <c r="B58" s="29"/>
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
-      <c r="F58" s="29"/>
-      <c r="G58" s="29"/>
-      <c r="H58" s="29"/>
-      <c r="I58" s="29"/>
-      <c r="J58" s="29"/>
-      <c r="K58" s="29"/>
-      <c r="L58" s="29"/>
-      <c r="M58" s="29"/>
-      <c r="N58" s="29"/>
-      <c r="O58" s="29"/>
-      <c r="P58" s="29"/>
-      <c r="Q58" s="29"/>
-      <c r="R58" s="29"/>
-      <c r="S58" s="29"/>
-      <c r="T58" s="29"/>
-      <c r="U58" s="29"/>
-      <c r="V58" s="29"/>
-      <c r="W58" s="29"/>
-      <c r="X58" s="29"/>
-      <c r="Y58" s="29"/>
-      <c r="Z58" s="29"/>
+      <c r="B58" s="30"/>
+      <c r="C58" s="30"/>
+      <c r="D58" s="30"/>
+      <c r="E58" s="30"/>
+      <c r="F58" s="30"/>
+      <c r="G58" s="30"/>
+      <c r="H58" s="30"/>
+      <c r="I58" s="30"/>
+      <c r="J58" s="30"/>
+      <c r="K58" s="30"/>
+      <c r="L58" s="30"/>
+      <c r="M58" s="30"/>
+      <c r="N58" s="30"/>
+      <c r="O58" s="30"/>
+      <c r="P58" s="30"/>
+      <c r="Q58" s="30"/>
+      <c r="R58" s="30"/>
+      <c r="S58" s="30"/>
+      <c r="T58" s="30"/>
+      <c r="U58" s="30"/>
+      <c r="V58" s="30"/>
+      <c r="W58" s="30"/>
+      <c r="X58" s="30"/>
+      <c r="Y58" s="30"/>
+      <c r="Z58" s="30"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="30" t="s">
+      <c r="A59" s="31" t="s">
         <v>353</v>
       </c>
-      <c r="B59" s="32">
+      <c r="B59" s="33">
         <v>0.03</v>
       </c>
-      <c r="C59" s="32">
+      <c r="C59" s="33">
         <v>0.5</v>
       </c>
-      <c r="D59" s="32">
+      <c r="D59" s="33">
         <v>0.01</v>
       </c>
-      <c r="E59" s="34"/>
-      <c r="F59" s="34"/>
-      <c r="G59" s="33">
+      <c r="E59" s="35"/>
+      <c r="F59" s="35"/>
+      <c r="G59" s="34">
         <v>-0.39</v>
       </c>
-      <c r="H59" s="33">
+      <c r="H59" s="34">
         <v>-0.16</v>
       </c>
-      <c r="I59" s="33">
+      <c r="I59" s="34">
         <v>-0.17</v>
       </c>
-      <c r="J59" s="32">
+      <c r="J59" s="33">
         <v>0.74</v>
       </c>
-      <c r="K59" s="32">
+      <c r="K59" s="33">
         <v>0.02</v>
       </c>
-      <c r="L59" s="32">
+      <c r="L59" s="33">
         <v>0.01</v>
       </c>
-      <c r="M59" s="33">
+      <c r="M59" s="34">
         <v>-0.5</v>
       </c>
-      <c r="N59" s="32">
+      <c r="N59" s="33">
         <v>0.03</v>
       </c>
-      <c r="O59" s="34"/>
-      <c r="P59" s="33">
+      <c r="O59" s="35"/>
+      <c r="P59" s="34">
         <v>-0.56</v>
       </c>
-      <c r="Q59" s="32">
+      <c r="Q59" s="33">
         <v>0.05</v>
       </c>
-      <c r="R59" s="33">
+      <c r="R59" s="34">
         <v>-2.45</v>
       </c>
-      <c r="S59" s="33">
+      <c r="S59" s="34">
         <v>-0.2</v>
       </c>
-      <c r="T59" s="32">
+      <c r="T59" s="33">
         <v>0.01</v>
       </c>
-      <c r="U59" s="33">
+      <c r="U59" s="34">
         <v>-0.22</v>
       </c>
-      <c r="V59" s="32">
+      <c r="V59" s="33">
         <v>0.1</v>
       </c>
-      <c r="W59" s="32">
+      <c r="W59" s="33">
         <v>0.03</v>
       </c>
-      <c r="X59" s="32">
+      <c r="X59" s="33">
         <v>0.3</v>
       </c>
-      <c r="Y59" s="32">
+      <c r="Y59" s="33">
         <v>0.06</v>
       </c>
-      <c r="Z59" s="34"/>
+      <c r="Z59" s="35"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="30" t="s">
+      <c r="A60" s="31" t="s">
         <v>354</v>
       </c>
-      <c r="B60" s="32">
+      <c r="B60" s="33">
         <v>0.32</v>
       </c>
-      <c r="C60" s="32">
+      <c r="C60" s="33">
         <v>3.33</v>
       </c>
-      <c r="D60" s="33">
+      <c r="D60" s="34">
         <v>-2.72</v>
       </c>
-      <c r="E60" s="34"/>
-      <c r="F60" s="34"/>
-      <c r="G60" s="33">
+      <c r="E60" s="35"/>
+      <c r="F60" s="35"/>
+      <c r="G60" s="34">
         <v>-0.46</v>
       </c>
-      <c r="H60" s="32">
+      <c r="H60" s="33">
         <v>0.07</v>
       </c>
-      <c r="I60" s="32">
+      <c r="I60" s="33">
         <v>0.1</v>
       </c>
-      <c r="J60" s="34"/>
-      <c r="K60" s="32">
+      <c r="J60" s="35"/>
+      <c r="K60" s="33">
         <v>0.19</v>
       </c>
-      <c r="L60" s="32">
+      <c r="L60" s="33">
         <v>1.43</v>
       </c>
-      <c r="M60" s="33">
+      <c r="M60" s="34">
         <v>-0.6</v>
       </c>
-      <c r="N60" s="32">
+      <c r="N60" s="33">
         <v>21.87</v>
       </c>
-      <c r="O60" s="34"/>
-      <c r="P60" s="32">
+      <c r="O60" s="35"/>
+      <c r="P60" s="33">
         <v>0.82</v>
       </c>
-      <c r="Q60" s="33">
+      <c r="Q60" s="34">
         <v>-2.58</v>
       </c>
-      <c r="R60" s="33">
+      <c r="R60" s="34">
         <v>-0.53</v>
       </c>
-      <c r="S60" s="32">
+      <c r="S60" s="33">
         <v>1.18</v>
       </c>
-      <c r="T60" s="32">
+      <c r="T60" s="33">
         <v>0.1</v>
       </c>
-      <c r="U60" s="32">
+      <c r="U60" s="33">
         <v>0.17</v>
       </c>
-      <c r="V60" s="34"/>
-      <c r="W60" s="34"/>
-      <c r="X60" s="34"/>
-      <c r="Y60" s="34"/>
-      <c r="Z60" s="34"/>
+      <c r="V60" s="35"/>
+      <c r="W60" s="35"/>
+      <c r="X60" s="35"/>
+      <c r="Y60" s="35"/>
+      <c r="Z60" s="35"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="28" t="s">
+      <c r="A61" s="29" t="s">
         <v>355</v>
       </c>
-      <c r="B61" s="29"/>
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
-      <c r="F61" s="29"/>
-      <c r="G61" s="29"/>
-      <c r="H61" s="29"/>
-      <c r="I61" s="29"/>
-      <c r="J61" s="29"/>
-      <c r="K61" s="29"/>
-      <c r="L61" s="29"/>
-      <c r="M61" s="29"/>
-      <c r="N61" s="29"/>
-      <c r="O61" s="29"/>
-      <c r="P61" s="29"/>
-      <c r="Q61" s="29"/>
-      <c r="R61" s="29"/>
-      <c r="S61" s="29"/>
-      <c r="T61" s="29"/>
-      <c r="U61" s="29"/>
-      <c r="V61" s="29"/>
-      <c r="W61" s="29"/>
-      <c r="X61" s="29"/>
-      <c r="Y61" s="29"/>
-      <c r="Z61" s="29"/>
+      <c r="B61" s="30"/>
+      <c r="C61" s="30"/>
+      <c r="D61" s="30"/>
+      <c r="E61" s="30"/>
+      <c r="F61" s="30"/>
+      <c r="G61" s="30"/>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30"/>
+      <c r="J61" s="30"/>
+      <c r="K61" s="30"/>
+      <c r="L61" s="30"/>
+      <c r="M61" s="30"/>
+      <c r="N61" s="30"/>
+      <c r="O61" s="30"/>
+      <c r="P61" s="30"/>
+      <c r="Q61" s="30"/>
+      <c r="R61" s="30"/>
+      <c r="S61" s="30"/>
+      <c r="T61" s="30"/>
+      <c r="U61" s="30"/>
+      <c r="V61" s="30"/>
+      <c r="W61" s="30"/>
+      <c r="X61" s="30"/>
+      <c r="Y61" s="30"/>
+      <c r="Z61" s="30"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="30" t="s">
+      <c r="A62" s="31" t="s">
         <v>356</v>
       </c>
-      <c r="B62" s="32">
+      <c r="B62" s="33">
         <v>6.67</v>
       </c>
-      <c r="C62" s="32">
+      <c r="C62" s="33">
         <v>4.22</v>
       </c>
-      <c r="D62" s="32">
+      <c r="D62" s="33">
         <v>4.13</v>
       </c>
-      <c r="E62" s="32">
+      <c r="E62" s="33">
         <v>2.66</v>
       </c>
-      <c r="F62" s="32">
+      <c r="F62" s="33">
         <v>4.44</v>
       </c>
-      <c r="G62" s="32">
+      <c r="G62" s="33">
         <v>7.64</v>
       </c>
-      <c r="H62" s="32">
+      <c r="H62" s="33">
         <v>6.93</v>
       </c>
-      <c r="I62" s="32">
+      <c r="I62" s="33">
         <v>7.56</v>
       </c>
-      <c r="J62" s="32">
+      <c r="J62" s="33">
         <v>9.65</v>
       </c>
-      <c r="K62" s="32">
+      <c r="K62" s="33">
         <v>13.73</v>
       </c>
-      <c r="L62" s="32">
+      <c r="L62" s="33">
         <v>6.14</v>
       </c>
-      <c r="M62" s="32">
+      <c r="M62" s="33">
         <v>4.45</v>
       </c>
-      <c r="N62" s="32">
+      <c r="N62" s="33">
         <v>2.48</v>
       </c>
-      <c r="O62" s="32">
+      <c r="O62" s="33">
         <v>2.73</v>
       </c>
-      <c r="P62" s="32">
+      <c r="P62" s="33">
         <v>1.23</v>
       </c>
-      <c r="Q62" s="32">
+      <c r="Q62" s="33">
         <v>1.21</v>
       </c>
-      <c r="R62" s="33">
+      <c r="R62" s="34">
         <v>-0.05</v>
       </c>
-      <c r="S62" s="32">
+      <c r="S62" s="33">
         <v>2.69</v>
       </c>
-      <c r="T62" s="32">
+      <c r="T62" s="33">
         <v>1.48</v>
       </c>
-      <c r="U62" s="32">
+      <c r="U62" s="33">
         <v>3.1</v>
       </c>
-      <c r="V62" s="32">
+      <c r="V62" s="33">
         <v>2.28</v>
       </c>
-      <c r="W62" s="32">
+      <c r="W62" s="33">
         <v>2.21</v>
       </c>
-      <c r="X62" s="32">
+      <c r="X62" s="33">
         <v>2.82</v>
       </c>
-      <c r="Y62" s="32">
+      <c r="Y62" s="33">
         <v>3.25</v>
       </c>
-      <c r="Z62" s="32">
+      <c r="Z62" s="33">
         <v>1.29</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="30" t="s">
+      <c r="A63" s="31" t="s">
         <v>357</v>
       </c>
-      <c r="B63" s="32">
+      <c r="B63" s="33">
         <v>4.46</v>
       </c>
-      <c r="C63" s="32">
+      <c r="C63" s="33">
         <v>4.78</v>
       </c>
-      <c r="D63" s="32">
+      <c r="D63" s="33">
         <v>5.25</v>
       </c>
-      <c r="E63" s="32">
+      <c r="E63" s="33">
         <v>5.76</v>
       </c>
-      <c r="F63" s="32">
+      <c r="F63" s="33">
         <v>6.86</v>
       </c>
-      <c r="G63" s="32">
+      <c r="G63" s="33">
         <v>7.92</v>
       </c>
-      <c r="H63" s="32">
+      <c r="H63" s="33">
         <v>8.02</v>
       </c>
-      <c r="I63" s="32">
+      <c r="I63" s="33">
         <v>8.55</v>
       </c>
-      <c r="J63" s="32">
+      <c r="J63" s="33">
         <v>8.92</v>
       </c>
-      <c r="K63" s="32">
+      <c r="K63" s="33">
         <v>7.44</v>
       </c>
-      <c r="L63" s="32">
+      <c r="L63" s="33">
         <v>3.47</v>
       </c>
-      <c r="M63" s="32">
+      <c r="M63" s="33">
         <v>2.38</v>
       </c>
-      <c r="N63" s="32">
+      <c r="N63" s="33">
         <v>1.46</v>
       </c>
-      <c r="O63" s="32">
+      <c r="O63" s="33">
         <v>1.52</v>
       </c>
-      <c r="P63" s="32">
+      <c r="P63" s="33">
         <v>1.33</v>
       </c>
-      <c r="Q63" s="32">
+      <c r="Q63" s="33">
         <v>1.68</v>
       </c>
-      <c r="R63" s="32">
+      <c r="R63" s="33">
         <v>1.87</v>
       </c>
-      <c r="S63" s="32">
+      <c r="S63" s="33">
         <v>2.25</v>
       </c>
-      <c r="T63" s="32">
+      <c r="T63" s="33">
         <v>2.26</v>
       </c>
-      <c r="U63" s="32">
+      <c r="U63" s="33">
         <v>2.69</v>
       </c>
-      <c r="V63" s="32">
+      <c r="V63" s="33">
         <v>2.25</v>
       </c>
-      <c r="W63" s="34"/>
-      <c r="X63" s="34"/>
-      <c r="Y63" s="34"/>
-      <c r="Z63" s="34"/>
+      <c r="W63" s="35"/>
+      <c r="X63" s="35"/>
+      <c r="Y63" s="35"/>
+      <c r="Z63" s="35"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="28" t="s">
+      <c r="A64" s="29" t="s">
         <v>358</v>
       </c>
-      <c r="B64" s="29"/>
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
-      <c r="F64" s="29"/>
-      <c r="G64" s="29"/>
-      <c r="H64" s="29"/>
-      <c r="I64" s="29"/>
-      <c r="J64" s="29"/>
-      <c r="K64" s="29"/>
-      <c r="L64" s="29"/>
-      <c r="M64" s="29"/>
-      <c r="N64" s="29"/>
-      <c r="O64" s="29"/>
-      <c r="P64" s="29"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="29"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-      <c r="X64" s="29"/>
-      <c r="Y64" s="29"/>
-      <c r="Z64" s="29"/>
+      <c r="B64" s="30"/>
+      <c r="C64" s="30"/>
+      <c r="D64" s="30"/>
+      <c r="E64" s="30"/>
+      <c r="F64" s="30"/>
+      <c r="G64" s="30"/>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30"/>
+      <c r="J64" s="30"/>
+      <c r="K64" s="30"/>
+      <c r="L64" s="30"/>
+      <c r="M64" s="30"/>
+      <c r="N64" s="30"/>
+      <c r="O64" s="30"/>
+      <c r="P64" s="30"/>
+      <c r="Q64" s="30"/>
+      <c r="R64" s="30"/>
+      <c r="S64" s="30"/>
+      <c r="T64" s="30"/>
+      <c r="U64" s="30"/>
+      <c r="V64" s="30"/>
+      <c r="W64" s="30"/>
+      <c r="X64" s="30"/>
+      <c r="Y64" s="30"/>
+      <c r="Z64" s="30"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="30" t="s">
+      <c r="A65" s="31" t="s">
         <v>359</v>
       </c>
-      <c r="B65" s="32">
+      <c r="B65" s="33">
         <v>23.84</v>
       </c>
-      <c r="C65" s="32">
+      <c r="C65" s="33">
         <v>32.98</v>
       </c>
-      <c r="D65" s="32">
+      <c r="D65" s="33">
         <v>15.43</v>
       </c>
-      <c r="E65" s="32">
+      <c r="E65" s="33">
         <v>9.94</v>
       </c>
-      <c r="F65" s="32">
+      <c r="F65" s="33">
         <v>12.9</v>
       </c>
-      <c r="G65" s="32">
+      <c r="G65" s="33">
         <v>16.47</v>
       </c>
-      <c r="H65" s="32">
+      <c r="H65" s="33">
         <v>16.97</v>
       </c>
-      <c r="I65" s="32">
+      <c r="I65" s="33">
         <v>21.01</v>
       </c>
-      <c r="J65" s="32">
+      <c r="J65" s="33">
         <v>22.51</v>
       </c>
-      <c r="K65" s="32">
+      <c r="K65" s="33">
         <v>22.75</v>
       </c>
-      <c r="L65" s="32">
+      <c r="L65" s="33">
         <v>29.97</v>
       </c>
-      <c r="M65" s="32">
+      <c r="M65" s="33">
         <v>13.85</v>
       </c>
-      <c r="N65" s="32">
+      <c r="N65" s="33">
         <v>6.64</v>
       </c>
-      <c r="O65" s="32">
+      <c r="O65" s="33">
         <v>8.65</v>
       </c>
-      <c r="P65" s="32">
+      <c r="P65" s="33">
         <v>2.88</v>
       </c>
-      <c r="Q65" s="32">
+      <c r="Q65" s="33">
         <v>2.2</v>
       </c>
-      <c r="R65" s="33">
+      <c r="R65" s="34">
         <v>-0.08</v>
       </c>
-      <c r="S65" s="32">
+      <c r="S65" s="33">
         <v>4.86</v>
       </c>
-      <c r="T65" s="32">
+      <c r="T65" s="33">
         <v>1.95</v>
       </c>
-      <c r="U65" s="32">
+      <c r="U65" s="33">
         <v>5.01</v>
       </c>
-      <c r="V65" s="32">
+      <c r="V65" s="33">
         <v>3.06</v>
       </c>
-      <c r="W65" s="32">
+      <c r="W65" s="33">
         <v>3.18</v>
       </c>
-      <c r="X65" s="32">
+      <c r="X65" s="33">
         <v>4.74</v>
       </c>
-      <c r="Y65" s="32">
+      <c r="Y65" s="33">
         <v>5.93</v>
       </c>
-      <c r="Z65" s="32">
+      <c r="Z65" s="33">
         <v>4.83</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="30" t="s">
+      <c r="A66" s="31" t="s">
         <v>360</v>
       </c>
-      <c r="B66" s="32">
+      <c r="B66" s="33">
         <v>16.84</v>
       </c>
-      <c r="C66" s="32">
+      <c r="C66" s="33">
         <v>15.31</v>
       </c>
-      <c r="D66" s="32">
+      <c r="D66" s="33">
         <v>14.72</v>
       </c>
-      <c r="E66" s="32">
+      <c r="E66" s="33">
         <v>15.49</v>
       </c>
-      <c r="F66" s="32">
+      <c r="F66" s="33">
         <v>17.03</v>
       </c>
-      <c r="G66" s="32">
+      <c r="G66" s="33">
         <v>18.42</v>
       </c>
-      <c r="H66" s="32">
+      <c r="H66" s="33">
         <v>19.92</v>
       </c>
-      <c r="I66" s="32">
+      <c r="I66" s="33">
         <v>21.7</v>
       </c>
-      <c r="J66" s="32">
+      <c r="J66" s="33">
         <v>20.98</v>
       </c>
-      <c r="K66" s="32">
+      <c r="K66" s="33">
         <v>18.32</v>
       </c>
-      <c r="L66" s="32">
+      <c r="L66" s="33">
         <v>10.64</v>
       </c>
-      <c r="M66" s="32">
+      <c r="M66" s="33">
         <v>5.93</v>
       </c>
-      <c r="N66" s="32">
+      <c r="N66" s="33">
         <v>3.23</v>
       </c>
-      <c r="O66" s="32">
+      <c r="O66" s="33">
         <v>3.11</v>
       </c>
-      <c r="P66" s="32">
+      <c r="P66" s="33">
         <v>2.22</v>
       </c>
-      <c r="Q66" s="32">
+      <c r="Q66" s="33">
         <v>2.67</v>
       </c>
-      <c r="R66" s="32">
+      <c r="R66" s="33">
         <v>2.81</v>
       </c>
-      <c r="S66" s="32">
+      <c r="S66" s="33">
         <v>3.27</v>
       </c>
-      <c r="T66" s="32">
+      <c r="T66" s="33">
         <v>3.25</v>
       </c>
-      <c r="U66" s="32">
+      <c r="U66" s="33">
         <v>4.14</v>
       </c>
-      <c r="V66" s="32">
+      <c r="V66" s="33">
         <v>4.01</v>
       </c>
-      <c r="W66" s="34"/>
-      <c r="X66" s="34"/>
-      <c r="Y66" s="34"/>
-      <c r="Z66" s="34"/>
+      <c r="W66" s="35"/>
+      <c r="X66" s="35"/>
+      <c r="Y66" s="35"/>
+      <c r="Z66" s="35"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="28" t="s">
+      <c r="A67" s="29" t="s">
         <v>361</v>
       </c>
-      <c r="B67" s="29"/>
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
-      <c r="F67" s="29"/>
-      <c r="G67" s="29"/>
-      <c r="H67" s="29"/>
-      <c r="I67" s="29"/>
-      <c r="J67" s="29"/>
-      <c r="K67" s="29"/>
-      <c r="L67" s="29"/>
-      <c r="M67" s="29"/>
-      <c r="N67" s="29"/>
-      <c r="O67" s="29"/>
-      <c r="P67" s="29"/>
-      <c r="Q67" s="29"/>
-      <c r="R67" s="29"/>
-      <c r="S67" s="29"/>
-      <c r="T67" s="29"/>
-      <c r="U67" s="29"/>
-      <c r="V67" s="29"/>
-      <c r="W67" s="29"/>
-      <c r="X67" s="29"/>
-      <c r="Y67" s="29"/>
-      <c r="Z67" s="29"/>
+      <c r="B67" s="30"/>
+      <c r="C67" s="30"/>
+      <c r="D67" s="30"/>
+      <c r="E67" s="30"/>
+      <c r="F67" s="30"/>
+      <c r="G67" s="30"/>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30"/>
+      <c r="J67" s="30"/>
+      <c r="K67" s="30"/>
+      <c r="L67" s="30"/>
+      <c r="M67" s="30"/>
+      <c r="N67" s="30"/>
+      <c r="O67" s="30"/>
+      <c r="P67" s="30"/>
+      <c r="Q67" s="30"/>
+      <c r="R67" s="30"/>
+      <c r="S67" s="30"/>
+      <c r="T67" s="30"/>
+      <c r="U67" s="30"/>
+      <c r="V67" s="30"/>
+      <c r="W67" s="30"/>
+      <c r="X67" s="30"/>
+      <c r="Y67" s="30"/>
+      <c r="Z67" s="30"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="30" t="s">
+      <c r="A68" s="31" t="s">
         <v>362</v>
       </c>
-      <c r="B68" s="32">
+      <c r="B68" s="33">
         <v>32.94</v>
       </c>
-      <c r="C68" s="31">
+      <c r="C68" s="32">
         <v>352.7</v>
       </c>
-      <c r="D68" s="31">
+      <c r="D68" s="32">
         <v>111.44</v>
       </c>
-      <c r="E68" s="32">
+      <c r="E68" s="33">
         <v>12.1</v>
       </c>
-      <c r="F68" s="32">
+      <c r="F68" s="33">
         <v>15.07</v>
       </c>
-      <c r="G68" s="32">
+      <c r="G68" s="33">
         <v>63.52</v>
       </c>
-      <c r="H68" s="32">
+      <c r="H68" s="33">
         <v>41.84</v>
       </c>
-      <c r="I68" s="32">
+      <c r="I68" s="33">
         <v>33.66</v>
       </c>
-      <c r="J68" s="32">
+      <c r="J68" s="33">
         <v>46.79</v>
       </c>
-      <c r="K68" s="32">
+      <c r="K68" s="33">
         <v>42.3</v>
       </c>
-      <c r="L68" s="31">
+      <c r="L68" s="32">
         <v>624.41</v>
       </c>
-      <c r="M68" s="32">
+      <c r="M68" s="33">
         <v>13.83</v>
       </c>
-      <c r="N68" s="32">
+      <c r="N68" s="33">
         <v>7.55</v>
       </c>
-      <c r="O68" s="32">
+      <c r="O68" s="33">
         <v>23.35</v>
       </c>
-      <c r="P68" s="32">
+      <c r="P68" s="33">
         <v>2.31</v>
       </c>
-      <c r="Q68" s="32">
+      <c r="Q68" s="33">
         <v>2.4</v>
       </c>
-      <c r="R68" s="33">
+      <c r="R68" s="34">
         <v>-0.08</v>
       </c>
-      <c r="S68" s="32">
+      <c r="S68" s="33">
         <v>5.58</v>
       </c>
-      <c r="T68" s="32">
+      <c r="T68" s="33">
         <v>4.61</v>
       </c>
-      <c r="U68" s="32">
+      <c r="U68" s="33">
         <v>4.66</v>
       </c>
-      <c r="V68" s="32">
+      <c r="V68" s="33">
         <v>2.97</v>
       </c>
-      <c r="W68" s="32">
+      <c r="W68" s="33">
         <v>3.44</v>
       </c>
-      <c r="X68" s="32">
+      <c r="X68" s="33">
         <v>7.19</v>
       </c>
-      <c r="Y68" s="32">
+      <c r="Y68" s="33">
         <v>11.16</v>
       </c>
-      <c r="Z68" s="34"/>
+      <c r="Z68" s="35"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="30" t="s">
+      <c r="A69" s="31" t="s">
         <v>363</v>
       </c>
-      <c r="B69" s="32">
+      <c r="B69" s="33">
         <v>30.08</v>
       </c>
-      <c r="C69" s="32">
+      <c r="C69" s="33">
         <v>36.99</v>
       </c>
-      <c r="D69" s="32">
+      <c r="D69" s="33">
         <v>34.29</v>
       </c>
-      <c r="E69" s="32">
+      <c r="E69" s="33">
         <v>28.65</v>
       </c>
-      <c r="F69" s="32">
+      <c r="F69" s="33">
         <v>34.84</v>
       </c>
-      <c r="G69" s="32">
+      <c r="G69" s="33">
         <v>45.88</v>
       </c>
-      <c r="H69" s="32">
+      <c r="H69" s="33">
         <v>40.79</v>
       </c>
-      <c r="I69" s="32">
+      <c r="I69" s="33">
         <v>38.21</v>
       </c>
-      <c r="J69" s="32">
+      <c r="J69" s="33">
         <v>38.26</v>
       </c>
-      <c r="K69" s="32">
+      <c r="K69" s="33">
         <v>31.48</v>
       </c>
-      <c r="L69" s="32">
+      <c r="L69" s="33">
         <v>13.35</v>
       </c>
-      <c r="M69" s="32">
+      <c r="M69" s="33">
         <v>6.45</v>
       </c>
-      <c r="N69" s="32">
+      <c r="N69" s="33">
         <v>3.49</v>
       </c>
-      <c r="O69" s="32">
+      <c r="O69" s="33">
         <v>3.38</v>
       </c>
-      <c r="P69" s="32">
+      <c r="P69" s="33">
         <v>2.9</v>
       </c>
-      <c r="Q69" s="32">
+      <c r="Q69" s="33">
         <v>3.46</v>
       </c>
-      <c r="R69" s="32">
+      <c r="R69" s="33">
         <v>3.49</v>
       </c>
-      <c r="S69" s="32">
+      <c r="S69" s="33">
         <v>4.08</v>
       </c>
-      <c r="T69" s="32">
+      <c r="T69" s="33">
         <v>4.19</v>
       </c>
-      <c r="U69" s="32">
+      <c r="U69" s="33">
         <v>4.64</v>
       </c>
-      <c r="V69" s="32">
+      <c r="V69" s="33">
         <v>6.12</v>
       </c>
-      <c r="W69" s="34"/>
-      <c r="X69" s="34"/>
-      <c r="Y69" s="34"/>
-      <c r="Z69" s="34"/>
+      <c r="W69" s="35"/>
+      <c r="X69" s="35"/>
+      <c r="Y69" s="35"/>
+      <c r="Z69" s="35"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="28" t="s">
+      <c r="A70" s="29" t="s">
         <v>364</v>
       </c>
-      <c r="B70" s="29"/>
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
-      <c r="F70" s="29"/>
-      <c r="G70" s="29"/>
-      <c r="H70" s="29"/>
-      <c r="I70" s="29"/>
-      <c r="J70" s="29"/>
-      <c r="K70" s="29"/>
-      <c r="L70" s="29"/>
-      <c r="M70" s="29"/>
-      <c r="N70" s="29"/>
-      <c r="O70" s="29"/>
-      <c r="P70" s="29"/>
-      <c r="Q70" s="29"/>
-      <c r="R70" s="29"/>
-      <c r="S70" s="29"/>
-      <c r="T70" s="29"/>
-      <c r="U70" s="29"/>
-      <c r="V70" s="29"/>
-      <c r="W70" s="29"/>
-      <c r="X70" s="29"/>
-      <c r="Y70" s="29"/>
-      <c r="Z70" s="29"/>
+      <c r="B70" s="30"/>
+      <c r="C70" s="30"/>
+      <c r="D70" s="30"/>
+      <c r="E70" s="30"/>
+      <c r="F70" s="30"/>
+      <c r="G70" s="30"/>
+      <c r="H70" s="30"/>
+      <c r="I70" s="30"/>
+      <c r="J70" s="30"/>
+      <c r="K70" s="30"/>
+      <c r="L70" s="30"/>
+      <c r="M70" s="30"/>
+      <c r="N70" s="30"/>
+      <c r="O70" s="30"/>
+      <c r="P70" s="30"/>
+      <c r="Q70" s="30"/>
+      <c r="R70" s="30"/>
+      <c r="S70" s="30"/>
+      <c r="T70" s="30"/>
+      <c r="U70" s="30"/>
+      <c r="V70" s="30"/>
+      <c r="W70" s="30"/>
+      <c r="X70" s="30"/>
+      <c r="Y70" s="30"/>
+      <c r="Z70" s="30"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="30" t="s">
+      <c r="A71" s="31" t="s">
         <v>365</v>
       </c>
-      <c r="B71" s="32">
+      <c r="B71" s="33">
         <v>32.94</v>
       </c>
-      <c r="C71" s="34"/>
-      <c r="D71" s="31">
+      <c r="C71" s="35"/>
+      <c r="D71" s="32">
         <v>121.6</v>
       </c>
-      <c r="E71" s="34"/>
-      <c r="F71" s="34"/>
-      <c r="G71" s="34"/>
-      <c r="H71" s="34"/>
-      <c r="I71" s="31">
+      <c r="E71" s="35"/>
+      <c r="F71" s="35"/>
+      <c r="G71" s="35"/>
+      <c r="H71" s="35"/>
+      <c r="I71" s="32">
         <v>518.44</v>
       </c>
-      <c r="J71" s="34"/>
-      <c r="K71" s="34"/>
-      <c r="L71" s="31">
+      <c r="J71" s="35"/>
+      <c r="K71" s="35"/>
+      <c r="L71" s="32">
         <v>624.41</v>
       </c>
-      <c r="M71" s="34"/>
-      <c r="N71" s="34"/>
-      <c r="O71" s="34"/>
-      <c r="P71" s="34"/>
-      <c r="Q71" s="32">
+      <c r="M71" s="35"/>
+      <c r="N71" s="35"/>
+      <c r="O71" s="35"/>
+      <c r="P71" s="35"/>
+      <c r="Q71" s="33">
         <v>2.4</v>
       </c>
-      <c r="R71" s="33">
+      <c r="R71" s="34">
         <v>-0.09</v>
       </c>
-      <c r="S71" s="32">
+      <c r="S71" s="33">
         <v>5.58</v>
       </c>
-      <c r="T71" s="32">
+      <c r="T71" s="33">
         <v>4.61</v>
       </c>
-      <c r="U71" s="32">
+      <c r="U71" s="33">
         <v>4.84</v>
       </c>
-      <c r="V71" s="32">
+      <c r="V71" s="33">
         <v>3.2</v>
       </c>
-      <c r="W71" s="32">
+      <c r="W71" s="33">
         <v>3.48</v>
       </c>
-      <c r="X71" s="32">
+      <c r="X71" s="33">
         <v>7.31</v>
       </c>
-      <c r="Y71" s="32">
+      <c r="Y71" s="33">
         <v>11.59</v>
       </c>
-      <c r="Z71" s="34"/>
+      <c r="Z71" s="35"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="30" t="s">
+      <c r="A72" s="31" t="s">
         <v>366</v>
       </c>
-      <c r="B72" s="34"/>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="34"/>
-      <c r="M72" s="34"/>
-      <c r="N72" s="34"/>
-      <c r="O72" s="34"/>
-      <c r="P72" s="32">
+      <c r="B72" s="35"/>
+      <c r="C72" s="35"/>
+      <c r="D72" s="35"/>
+      <c r="E72" s="35"/>
+      <c r="F72" s="35"/>
+      <c r="G72" s="35"/>
+      <c r="H72" s="35"/>
+      <c r="I72" s="35"/>
+      <c r="J72" s="35"/>
+      <c r="K72" s="35"/>
+      <c r="L72" s="35"/>
+      <c r="M72" s="35"/>
+      <c r="N72" s="35"/>
+      <c r="O72" s="35"/>
+      <c r="P72" s="33">
         <v>3.71</v>
       </c>
-      <c r="Q72" s="32">
+      <c r="Q72" s="33">
         <v>3.51</v>
       </c>
-      <c r="R72" s="32">
+      <c r="R72" s="33">
         <v>3.61</v>
       </c>
-      <c r="S72" s="32">
+      <c r="S72" s="33">
         <v>4.2</v>
       </c>
-      <c r="T72" s="32">
+      <c r="T72" s="33">
         <v>4.33</v>
       </c>
-      <c r="U72" s="32">
+      <c r="U72" s="33">
         <v>4.83</v>
       </c>
-      <c r="V72" s="32">
+      <c r="V72" s="33">
         <v>7.06</v>
       </c>
-      <c r="W72" s="34"/>
-      <c r="X72" s="34"/>
-      <c r="Y72" s="34"/>
-      <c r="Z72" s="34"/>
+      <c r="W72" s="35"/>
+      <c r="X72" s="35"/>
+      <c r="Y72" s="35"/>
+      <c r="Z72" s="35"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>

--- a/data/hex_xlsx/INVEST.HE.xlsx
+++ b/data/hex_xlsx/INVEST.HE.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="809" uniqueCount="368">
   <si>
     <t>Company Fundamentals - Income Statement</t>
   </si>
@@ -670,6 +670,9 @@
   </si>
   <si>
     <t>Total Current Liabilities</t>
+  </si>
+  <si>
+    <t>Loans LT</t>
   </si>
   <si>
     <t>Capitalized Lease Obligations - Long-Term</t>
@@ -1251,7 +1254,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -1334,6 +1337,9 @@
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="3" numFmtId="4" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="3" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="3" fillId="0" fontId="9" numFmtId="165" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
@@ -11693,8 +11699,8 @@
       </c>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="14" t="s">
-        <v>200</v>
+      <c r="A70" s="28" t="s">
+        <v>217</v>
       </c>
       <c r="B70" s="25">
         <v>161.71</v>
@@ -11759,7 +11765,7 @@
     </row>
     <row r="71" ht="15.0" customHeight="1">
       <c r="A71" s="14" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B71" s="16"/>
       <c r="C71" s="15">
@@ -11802,7 +11808,7 @@
     </row>
     <row r="72" ht="15.0" customHeight="1">
       <c r="A72" s="14" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="B72" s="16"/>
       <c r="C72" s="25">
@@ -11845,7 +11851,7 @@
     </row>
     <row r="73" ht="15.0" customHeight="1">
       <c r="A73" s="14" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="B73" s="15">
         <v>13.59</v>
@@ -11918,7 +11924,7 @@
     </row>
     <row r="74" ht="15.0" customHeight="1">
       <c r="A74" s="14" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="B74" s="16"/>
       <c r="C74" s="16"/>
@@ -12016,7 +12022,7 @@
     </row>
     <row r="76" ht="15.0" customHeight="1">
       <c r="A76" s="17" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="B76" s="19">
         <v>175.3</v>
@@ -12099,7 +12105,7 @@
     </row>
     <row r="77" ht="15.0" customHeight="1">
       <c r="A77" s="14" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="B77" s="16"/>
       <c r="C77" s="16"/>
@@ -12134,7 +12140,7 @@
     </row>
     <row r="78" ht="15.0" customHeight="1">
       <c r="A78" s="17" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="B78" s="19">
         <v>236.29</v>
@@ -12217,7 +12223,7 @@
     </row>
     <row r="79" ht="15.0" customHeight="1">
       <c r="A79" s="14" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B79" s="15">
         <v>30.2</v>
@@ -12300,7 +12306,7 @@
     </row>
     <row r="80" ht="15.0" customHeight="1">
       <c r="A80" s="14" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="B80" s="16"/>
       <c r="C80" s="15">
@@ -12381,7 +12387,7 @@
     </row>
     <row r="81" ht="15.0" customHeight="1">
       <c r="A81" s="14" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="B81" s="16"/>
       <c r="C81" s="16"/>
@@ -12424,7 +12430,7 @@
     </row>
     <row r="82" ht="15.0" customHeight="1">
       <c r="A82" s="14" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B82" s="16"/>
       <c r="C82" s="25">
@@ -12477,7 +12483,7 @@
     </row>
     <row r="83" ht="15.0" customHeight="1">
       <c r="A83" s="14" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B83" s="16"/>
       <c r="C83" s="25">
@@ -12558,7 +12564,7 @@
     </row>
     <row r="84" ht="15.0" customHeight="1">
       <c r="A84" s="14" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B84" s="25">
         <v>211.36</v>
@@ -12593,7 +12599,7 @@
     </row>
     <row r="85" ht="15.0" customHeight="1">
       <c r="A85" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B85" s="16"/>
       <c r="C85" s="16"/>
@@ -12638,7 +12644,7 @@
     </row>
     <row r="86" ht="15.0" customHeight="1">
       <c r="A86" s="14" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B86" s="16"/>
       <c r="C86" s="16"/>
@@ -12687,7 +12693,7 @@
     </row>
     <row r="87" ht="15.0" customHeight="1">
       <c r="A87" s="14" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="B87" s="16"/>
       <c r="C87" s="16"/>
@@ -12722,7 +12728,7 @@
     </row>
     <row r="88" ht="15.0" customHeight="1">
       <c r="A88" s="14" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B88" s="16"/>
       <c r="C88" s="16"/>
@@ -12757,7 +12763,7 @@
     </row>
     <row r="89" ht="15.0" customHeight="1">
       <c r="A89" s="17" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B89" s="19">
         <v>241.56</v>
@@ -12840,7 +12846,7 @@
     </row>
     <row r="90" ht="15.0" customHeight="1">
       <c r="A90" s="14" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B90" s="16">
         <v>0.0</v>
@@ -12889,7 +12895,7 @@
     </row>
     <row r="91" ht="15.0" customHeight="1">
       <c r="A91" s="17" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="B91" s="24">
         <v>0.0</v>
@@ -12938,7 +12944,7 @@
     </row>
     <row r="92" ht="15.0" customHeight="1">
       <c r="A92" s="17" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="B92" s="19">
         <v>241.56</v>
@@ -13021,7 +13027,7 @@
     </row>
     <row r="93" ht="15.0" customHeight="1">
       <c r="A93" s="17" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B93" s="19">
         <v>477.85</v>
@@ -13104,7 +13110,7 @@
     </row>
     <row r="94" ht="15.0" customHeight="1">
       <c r="A94" s="14" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="B94" s="15">
         <v>6.39</v>
@@ -13187,7 +13193,7 @@
     </row>
     <row r="95" ht="15.0" customHeight="1">
       <c r="A95" s="14" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="B95" s="15">
         <v>0.02</v>
@@ -13270,7 +13276,7 @@
     </row>
     <row r="96" ht="15.0" customHeight="1">
       <c r="A96" s="14" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="B96" s="15">
         <v>6.37</v>
@@ -13353,7 +13359,7 @@
     </row>
     <row r="97" ht="15.0" customHeight="1">
       <c r="A97" s="14" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="B97" s="16"/>
       <c r="C97" s="25">
@@ -13396,7 +13402,7 @@
     </row>
     <row r="98" ht="15.0" customHeight="1">
       <c r="A98" s="14" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="B98" s="16"/>
       <c r="C98" s="25">
@@ -13447,7 +13453,7 @@
     </row>
     <row r="99" ht="15.0" customHeight="1">
       <c r="A99" s="14" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="B99" s="16"/>
       <c r="C99" s="16"/>
@@ -13486,7 +13492,7 @@
     </row>
     <row r="100" ht="15.0" customHeight="1">
       <c r="A100" s="14" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B100" s="16"/>
       <c r="C100" s="16"/>
@@ -13521,7 +13527,7 @@
     </row>
     <row r="101" ht="15.0" customHeight="1">
       <c r="A101" s="14" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="B101" s="16"/>
       <c r="C101" s="16"/>
@@ -13556,7 +13562,7 @@
     </row>
     <row r="102" ht="15.0" customHeight="1">
       <c r="A102" s="14" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B102" s="16"/>
       <c r="C102" s="16"/>
@@ -13591,7 +13597,7 @@
     </row>
     <row r="103" ht="15.0" customHeight="1">
       <c r="A103" s="14" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="B103" s="16"/>
       <c r="C103" s="16"/>
@@ -13624,7 +13630,7 @@
     </row>
     <row r="104" ht="15.0" customHeight="1">
       <c r="A104" s="14" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="B104" s="16"/>
       <c r="C104" s="25">
@@ -13671,7 +13677,7 @@
     </row>
     <row r="105" ht="15.0" customHeight="1">
       <c r="A105" s="14" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="B105" s="16"/>
       <c r="C105" s="15">
@@ -13714,7 +13720,7 @@
     </row>
     <row r="106" ht="15.0" customHeight="1">
       <c r="A106" s="14" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B106" s="16"/>
       <c r="C106" s="16"/>
@@ -13747,7 +13753,7 @@
     </row>
     <row r="107" ht="15.0" customHeight="1">
       <c r="A107" s="14" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B107" s="16"/>
       <c r="C107" s="15">
@@ -13790,7 +13796,7 @@
     </row>
     <row r="108" ht="15.0" customHeight="1">
       <c r="A108" s="14" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="B108" s="16"/>
       <c r="C108" s="15">
@@ -13833,7 +13839,7 @@
     </row>
     <row r="109" ht="15.0" customHeight="1">
       <c r="A109" s="14" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B109" s="16"/>
       <c r="C109" s="15">
@@ -13876,7 +13882,7 @@
     </row>
     <row r="110" ht="15.0" customHeight="1">
       <c r="A110" s="14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="B110" s="16"/>
       <c r="C110" s="15">
@@ -13913,7 +13919,7 @@
     </row>
     <row r="111" ht="15.0" customHeight="1">
       <c r="A111" s="14" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="B111" s="16"/>
       <c r="C111" s="16"/>
@@ -13950,7 +13956,7 @@
     </row>
     <row r="112" ht="15.0" customHeight="1">
       <c r="A112" s="14" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B112" s="15">
         <v>1.0</v>
@@ -14033,7 +14039,7 @@
     </row>
     <row r="113" ht="15.0" customHeight="1">
       <c r="A113" s="14" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B113" s="15">
         <v>6.39</v>
@@ -14116,7 +14122,7 @@
     </row>
     <row r="114" ht="15.0" customHeight="1">
       <c r="A114" s="14" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="B114" s="15">
         <v>0.02</v>
@@ -14199,7 +14205,7 @@
     </row>
     <row r="115" ht="15.0" customHeight="1">
       <c r="A115" s="14" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B115" s="15">
         <v>6.37</v>
@@ -14282,7 +14288,7 @@
     </row>
     <row r="116" ht="15.0" customHeight="1">
       <c r="A116" s="14" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B116" s="16"/>
       <c r="C116" s="16"/>
@@ -14337,7 +14343,7 @@
     </row>
     <row r="117" ht="15.0" customHeight="1">
       <c r="A117" s="14" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="B117" s="16"/>
       <c r="C117" s="16"/>
@@ -14376,7 +14382,7 @@
     </row>
     <row r="118" ht="15.0" customHeight="1">
       <c r="A118" s="14" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B118" s="16"/>
       <c r="C118" s="16"/>
@@ -14415,7 +14421,7 @@
     </row>
     <row r="119" ht="15.0" customHeight="1">
       <c r="A119" s="14" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="B119" s="16"/>
       <c r="C119" s="16"/>
@@ -14454,7 +14460,7 @@
     </row>
     <row r="120" ht="15.0" customHeight="1">
       <c r="A120" s="14" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="B120" s="16"/>
       <c r="C120" s="16"/>
@@ -14493,7 +14499,7 @@
     </row>
     <row r="121" ht="15.0" customHeight="1">
       <c r="A121" s="14" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B121" s="16"/>
       <c r="C121" s="16"/>
@@ -15444,7 +15450,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -15882,82 +15888,82 @@
         <v>48</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="C15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="F15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="J15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="K15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="L15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="N15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="O15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="P15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="R15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="T15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="V15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="X15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="Z15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="16" ht="15.0" customHeight="1" outlineLevel="1">
@@ -16045,7 +16051,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -16159,7 +16165,7 @@
     </row>
     <row r="20" ht="15.0" customHeight="1">
       <c r="A20" s="14" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B20" s="16"/>
       <c r="C20" s="25">
@@ -16240,7 +16246,7 @@
     </row>
     <row r="21" ht="15.0" customHeight="1">
       <c r="A21" s="14" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="B21" s="16"/>
       <c r="C21" s="15">
@@ -16305,7 +16311,7 @@
     </row>
     <row r="22" ht="15.0" customHeight="1">
       <c r="A22" s="14" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B22" s="16"/>
       <c r="C22" s="20">
@@ -16438,7 +16444,7 @@
     </row>
     <row r="25" ht="15.0" customHeight="1">
       <c r="A25" s="14" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="B25" s="16"/>
       <c r="C25" s="20">
@@ -16485,7 +16491,7 @@
     </row>
     <row r="26" ht="15.0" customHeight="1">
       <c r="A26" s="14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="B26" s="16"/>
       <c r="C26" s="15">
@@ -16566,7 +16572,7 @@
     </row>
     <row r="27" ht="15.0" customHeight="1">
       <c r="A27" s="14" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B27" s="16"/>
       <c r="C27" s="20">
@@ -16647,7 +16653,7 @@
     </row>
     <row r="28" ht="15.0" customHeight="1">
       <c r="A28" s="14" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B28" s="16"/>
       <c r="C28" s="20">
@@ -16728,7 +16734,7 @@
     </row>
     <row r="29" ht="15.0" customHeight="1">
       <c r="A29" s="14" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="B29" s="16"/>
       <c r="C29" s="16"/>
@@ -16787,7 +16793,7 @@
     </row>
     <row r="30" ht="15.0" customHeight="1">
       <c r="A30" s="14" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B30" s="15">
         <v>12.11</v>
@@ -16820,7 +16826,7 @@
     </row>
     <row r="31" ht="15.0" customHeight="1">
       <c r="A31" s="14" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="B31" s="16"/>
       <c r="C31" s="16"/>
@@ -16908,7 +16914,7 @@
     </row>
     <row r="33" ht="15.0" customHeight="1">
       <c r="A33" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B33" s="16"/>
       <c r="C33" s="16"/>
@@ -16947,7 +16953,7 @@
     </row>
     <row r="34" ht="15.0" customHeight="1">
       <c r="A34" s="14" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B34" s="16"/>
       <c r="C34" s="16"/>
@@ -17002,7 +17008,7 @@
     </row>
     <row r="35" ht="15.0" customHeight="1">
       <c r="A35" s="14" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B35" s="16"/>
       <c r="C35" s="16"/>
@@ -17043,7 +17049,7 @@
     </row>
     <row r="36" ht="15.0" customHeight="1">
       <c r="A36" s="14" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B36" s="16"/>
       <c r="C36" s="16"/>
@@ -17084,7 +17090,7 @@
     </row>
     <row r="37" ht="15.0" customHeight="1">
       <c r="A37" s="14" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B37" s="16"/>
       <c r="C37" s="16"/>
@@ -17141,7 +17147,7 @@
     </row>
     <row r="38" ht="15.0" customHeight="1">
       <c r="A38" s="14" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B38" s="16"/>
       <c r="C38" s="16"/>
@@ -17182,7 +17188,7 @@
     </row>
     <row r="39" ht="15.0" customHeight="1">
       <c r="A39" s="17" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="B39" s="18">
         <v>12.11</v>
@@ -17265,7 +17271,7 @@
     </row>
     <row r="40" ht="15.0" customHeight="1">
       <c r="A40" s="14" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B40" s="16"/>
       <c r="C40" s="16"/>
@@ -17336,7 +17342,7 @@
     </row>
     <row r="41" ht="15.0" customHeight="1">
       <c r="A41" s="14" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="B41" s="16"/>
       <c r="C41" s="16">
@@ -17387,7 +17393,7 @@
     </row>
     <row r="42" ht="15.0" customHeight="1">
       <c r="A42" s="14" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="B42" s="16"/>
       <c r="C42" s="16"/>
@@ -17420,7 +17426,7 @@
     </row>
     <row r="43" ht="15.0" customHeight="1">
       <c r="A43" s="14" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="B43" s="16"/>
       <c r="C43" s="16"/>
@@ -17467,7 +17473,7 @@
     </row>
     <row r="44" ht="15.0" customHeight="1">
       <c r="A44" s="14" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B44" s="25">
         <v>334.01</v>
@@ -17518,7 +17524,7 @@
     </row>
     <row r="45" ht="15.0" customHeight="1">
       <c r="A45" s="14" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B45" s="16"/>
       <c r="C45" s="16"/>
@@ -17555,7 +17561,7 @@
     </row>
     <row r="46" ht="15.0" customHeight="1">
       <c r="A46" s="14" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="B46" s="16"/>
       <c r="C46" s="16"/>
@@ -17610,7 +17616,7 @@
     </row>
     <row r="47" ht="15.0" customHeight="1">
       <c r="A47" s="14" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="B47" s="16"/>
       <c r="C47" s="16"/>
@@ -17643,7 +17649,7 @@
     </row>
     <row r="48" ht="15.0" customHeight="1">
       <c r="A48" s="14" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B48" s="16"/>
       <c r="C48" s="16"/>
@@ -17704,7 +17710,7 @@
     </row>
     <row r="49" ht="15.0" customHeight="1">
       <c r="A49" s="14" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B49" s="16"/>
       <c r="C49" s="16">
@@ -17739,7 +17745,7 @@
     </row>
     <row r="50" ht="15.0" customHeight="1">
       <c r="A50" s="14" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="B50" s="16"/>
       <c r="C50" s="16"/>
@@ -17778,7 +17784,7 @@
     </row>
     <row r="51" ht="15.0" customHeight="1">
       <c r="A51" s="14" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="B51" s="16"/>
       <c r="C51" s="16"/>
@@ -17817,7 +17823,7 @@
     </row>
     <row r="52" ht="15.0" customHeight="1">
       <c r="A52" s="14" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B52" s="20">
         <v>-27.33</v>
@@ -17868,7 +17874,7 @@
     </row>
     <row r="53" ht="15.0" customHeight="1">
       <c r="A53" s="14" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B53" s="16"/>
       <c r="C53" s="16">
@@ -17911,7 +17917,7 @@
     </row>
     <row r="54" ht="15.0" customHeight="1">
       <c r="A54" s="14" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B54" s="16"/>
       <c r="C54" s="16"/>
@@ -18005,7 +18011,7 @@
     </row>
     <row r="56" ht="15.0" customHeight="1">
       <c r="A56" s="17" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B56" s="19">
         <v>306.69</v>
@@ -18025,7 +18031,7 @@
       <c r="G56" s="22">
         <v>-16.72</v>
       </c>
-      <c r="H56" s="28">
+      <c r="H56" s="29">
         <v>-127.19</v>
       </c>
       <c r="I56" s="22">
@@ -18088,7 +18094,7 @@
     </row>
     <row r="57" ht="15.0" customHeight="1">
       <c r="A57" s="14" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="B57" s="16">
         <v>0.0</v>
@@ -18163,7 +18169,7 @@
     </row>
     <row r="58" ht="15.0" customHeight="1">
       <c r="A58" s="14" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="B58" s="20">
         <v>-18.98</v>
@@ -18240,7 +18246,7 @@
     </row>
     <row r="59" ht="15.0" customHeight="1">
       <c r="A59" s="14" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="B59" s="26">
         <v>-260.15</v>
@@ -18319,7 +18325,7 @@
     </row>
     <row r="60" ht="15.0" customHeight="1">
       <c r="A60" s="14" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B60" s="16"/>
       <c r="C60" s="16"/>
@@ -18360,7 +18366,7 @@
     </row>
     <row r="61" ht="15.0" customHeight="1">
       <c r="A61" s="14" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B61" s="16"/>
       <c r="C61" s="16"/>
@@ -18401,7 +18407,7 @@
     </row>
     <row r="62" ht="15.0" customHeight="1">
       <c r="A62" s="14" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B62" s="20">
         <v>-7.64</v>
@@ -18448,7 +18454,7 @@
     </row>
     <row r="63" ht="15.0" customHeight="1">
       <c r="A63" s="14" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B63" s="16"/>
       <c r="C63" s="16"/>
@@ -18487,7 +18493,7 @@
     </row>
     <row r="64" ht="15.0" customHeight="1">
       <c r="A64" s="14" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B64" s="16">
         <v>0.0</v>
@@ -18532,9 +18538,9 @@
     </row>
     <row r="65" ht="15.0" customHeight="1">
       <c r="A65" s="17" t="s">
-        <v>309</v>
-      </c>
-      <c r="B65" s="28">
+        <v>310</v>
+      </c>
+      <c r="B65" s="29">
         <v>-286.77</v>
       </c>
       <c r="C65" s="22">
@@ -18543,10 +18549,10 @@
       <c r="D65" s="22">
         <v>-47.75</v>
       </c>
-      <c r="E65" s="28">
+      <c r="E65" s="29">
         <v>-100.98</v>
       </c>
-      <c r="F65" s="28">
+      <c r="F65" s="29">
         <v>-117.36</v>
       </c>
       <c r="G65" s="22">
@@ -18615,7 +18621,7 @@
     </row>
     <row r="66" ht="15.0" customHeight="1">
       <c r="A66" s="14" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B66" s="16"/>
       <c r="C66" s="25">
@@ -18696,7 +18702,7 @@
     </row>
     <row r="67" ht="15.0" customHeight="1">
       <c r="A67" s="14" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B67" s="16"/>
       <c r="C67" s="15">
@@ -18777,7 +18783,7 @@
     </row>
     <row r="68" ht="15.0" customHeight="1">
       <c r="A68" s="14" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B68" s="16"/>
       <c r="C68" s="20">
@@ -18810,7 +18816,7 @@
     </row>
     <row r="69" ht="15.0" customHeight="1">
       <c r="A69" s="17" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B69" s="18">
         <v>32.03</v>
@@ -18821,7 +18827,7 @@
       <c r="D69" s="18">
         <v>22.51</v>
       </c>
-      <c r="E69" s="28">
+      <c r="E69" s="29">
         <v>-109.58</v>
       </c>
       <c r="F69" s="19">
@@ -19843,7 +19849,7 @@
   <sheetData>
     <row r="1" ht="15.0" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
@@ -20425,7 +20431,7 @@
     </row>
     <row r="18">
       <c r="A18" s="12" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="B18" s="6"/>
       <c r="C18" s="6"/>
@@ -20534,3062 +20540,3062 @@
       </c>
     </row>
     <row r="20" ht="15.0" customHeight="1">
-      <c r="A20" s="29" t="s">
-        <v>316</v>
-      </c>
-      <c r="B20" s="30"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
-      <c r="H20" s="30"/>
-      <c r="I20" s="30"/>
-      <c r="J20" s="30"/>
-      <c r="K20" s="30"/>
-      <c r="L20" s="30"/>
-      <c r="M20" s="30"/>
-      <c r="N20" s="30"/>
-      <c r="O20" s="30"/>
-      <c r="P20" s="30"/>
-      <c r="Q20" s="30"/>
-      <c r="R20" s="30"/>
-      <c r="S20" s="30"/>
-      <c r="T20" s="30"/>
-      <c r="U20" s="30"/>
-      <c r="V20" s="30"/>
-      <c r="W20" s="30"/>
-      <c r="X20" s="30"/>
-      <c r="Y20" s="30"/>
-      <c r="Z20" s="30"/>
+      <c r="A20" s="30" t="s">
+        <v>317</v>
+      </c>
+      <c r="B20" s="31"/>
+      <c r="C20" s="31"/>
+      <c r="D20" s="31"/>
+      <c r="E20" s="31"/>
+      <c r="F20" s="31"/>
+      <c r="G20" s="31"/>
+      <c r="H20" s="31"/>
+      <c r="I20" s="31"/>
+      <c r="J20" s="31"/>
+      <c r="K20" s="31"/>
+      <c r="L20" s="31"/>
+      <c r="M20" s="31"/>
+      <c r="N20" s="31"/>
+      <c r="O20" s="31"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="31"/>
+      <c r="R20" s="31"/>
+      <c r="S20" s="31"/>
+      <c r="T20" s="31"/>
+      <c r="U20" s="31"/>
+      <c r="V20" s="31"/>
+      <c r="W20" s="31"/>
+      <c r="X20" s="31"/>
+      <c r="Y20" s="31"/>
+      <c r="Z20" s="31"/>
     </row>
     <row r="21" ht="15.0" customHeight="1">
-      <c r="A21" s="31" t="s">
-        <v>316</v>
-      </c>
-      <c r="B21" s="32">
+      <c r="A21" s="32" t="s">
+        <v>317</v>
+      </c>
+      <c r="B21" s="33">
         <v>782.57</v>
       </c>
-      <c r="C21" s="32">
+      <c r="C21" s="33">
         <v>323.49</v>
       </c>
-      <c r="D21" s="32">
+      <c r="D21" s="33">
         <v>329.11</v>
       </c>
-      <c r="E21" s="32">
+      <c r="E21" s="33">
         <v>259.95</v>
       </c>
-      <c r="F21" s="32">
+      <c r="F21" s="33">
         <v>440.7</v>
       </c>
-      <c r="G21" s="32">
+      <c r="G21" s="33">
         <v>862.03</v>
       </c>
-      <c r="H21" s="32">
+      <c r="H21" s="33">
         <v>568.33</v>
       </c>
-      <c r="I21" s="32">
+      <c r="I21" s="33">
         <v>479.79</v>
       </c>
-      <c r="J21" s="32">
+      <c r="J21" s="33">
         <v>274.68</v>
       </c>
-      <c r="K21" s="32">
+      <c r="K21" s="33">
         <v>189.59</v>
       </c>
-      <c r="L21" s="33">
+      <c r="L21" s="34">
         <v>41.71</v>
       </c>
-      <c r="M21" s="33">
+      <c r="M21" s="34">
         <v>24.6</v>
       </c>
-      <c r="N21" s="33">
+      <c r="N21" s="34">
         <v>11.79</v>
       </c>
-      <c r="O21" s="33">
+      <c r="O21" s="34">
         <v>12.88</v>
       </c>
-      <c r="P21" s="33">
+      <c r="P21" s="34">
         <v>6.69</v>
       </c>
-      <c r="Q21" s="33">
+      <c r="Q21" s="34">
         <v>7.24</v>
       </c>
-      <c r="R21" s="34">
+      <c r="R21" s="35">
         <v>-0.33</v>
       </c>
-      <c r="S21" s="33">
+      <c r="S21" s="34">
         <v>14.87</v>
       </c>
-      <c r="T21" s="33">
+      <c r="T21" s="34">
         <v>15.61</v>
       </c>
-      <c r="U21" s="33">
+      <c r="U21" s="34">
         <v>19.73</v>
       </c>
-      <c r="V21" s="33">
+      <c r="V21" s="34">
         <v>15.6</v>
       </c>
-      <c r="W21" s="33">
+      <c r="W21" s="34">
         <v>14.8</v>
       </c>
-      <c r="X21" s="33">
+      <c r="X21" s="34">
         <v>12.86</v>
       </c>
-      <c r="Y21" s="33">
+      <c r="Y21" s="34">
         <v>14.22</v>
       </c>
-      <c r="Z21" s="33">
+      <c r="Z21" s="34">
         <v>9.86</v>
       </c>
     </row>
     <row r="22" ht="15.0" customHeight="1">
-      <c r="A22" s="31" t="s">
-        <v>317</v>
-      </c>
-      <c r="B22" s="32">
+      <c r="A22" s="32" t="s">
+        <v>318</v>
+      </c>
+      <c r="B22" s="33">
         <v>458.56</v>
       </c>
-      <c r="C22" s="32">
+      <c r="C22" s="33">
         <v>483.07</v>
       </c>
-      <c r="D22" s="32">
+      <c r="D22" s="33">
         <v>512.44</v>
       </c>
-      <c r="E22" s="32">
+      <c r="E22" s="33">
         <v>524.05</v>
       </c>
-      <c r="F22" s="32">
+      <c r="F22" s="33">
         <v>557.36</v>
       </c>
-      <c r="G22" s="32">
+      <c r="G22" s="33">
         <v>479.62</v>
       </c>
-      <c r="H22" s="32">
+      <c r="H22" s="33">
         <v>318.45</v>
       </c>
-      <c r="I22" s="32">
+      <c r="I22" s="33">
         <v>209.3</v>
       </c>
-      <c r="J22" s="32">
+      <c r="J22" s="33">
         <v>107.46</v>
       </c>
-      <c r="K22" s="33">
+      <c r="K22" s="34">
         <v>58.72</v>
       </c>
-      <c r="L22" s="33">
+      <c r="L22" s="34">
         <v>21.14</v>
       </c>
-      <c r="M22" s="33">
+      <c r="M22" s="34">
         <v>13.26</v>
       </c>
-      <c r="N22" s="33">
+      <c r="N22" s="34">
         <v>7.29</v>
       </c>
-      <c r="O22" s="33">
+      <c r="O22" s="34">
         <v>8.1</v>
       </c>
-      <c r="P22" s="33">
+      <c r="P22" s="34">
         <v>8.52</v>
       </c>
-      <c r="Q22" s="33">
+      <c r="Q22" s="34">
         <v>11.75</v>
       </c>
-      <c r="R22" s="33">
+      <c r="R22" s="34">
         <v>15.73</v>
       </c>
-      <c r="S22" s="33">
+      <c r="S22" s="34">
         <v>15.7</v>
       </c>
-      <c r="T22" s="33">
+      <c r="T22" s="34">
         <v>16.11</v>
       </c>
-      <c r="U22" s="33">
+      <c r="U22" s="34">
         <v>15.46</v>
       </c>
-      <c r="V22" s="33">
+      <c r="V22" s="34">
         <v>13.84</v>
       </c>
-      <c r="W22" s="35"/>
-      <c r="X22" s="35"/>
-      <c r="Y22" s="35"/>
-      <c r="Z22" s="35"/>
+      <c r="W22" s="36"/>
+      <c r="X22" s="36"/>
+      <c r="Y22" s="36"/>
+      <c r="Z22" s="36"/>
     </row>
     <row r="23" ht="15.0" customHeight="1">
-      <c r="A23" s="29" t="s">
-        <v>318</v>
-      </c>
-      <c r="B23" s="30"/>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="30"/>
-      <c r="F23" s="30"/>
-      <c r="G23" s="30"/>
-      <c r="H23" s="30"/>
-      <c r="I23" s="30"/>
-      <c r="J23" s="30"/>
-      <c r="K23" s="30"/>
-      <c r="L23" s="30"/>
-      <c r="M23" s="30"/>
-      <c r="N23" s="30"/>
-      <c r="O23" s="30"/>
-      <c r="P23" s="30"/>
-      <c r="Q23" s="30"/>
-      <c r="R23" s="30"/>
-      <c r="S23" s="30"/>
-      <c r="T23" s="30"/>
-      <c r="U23" s="30"/>
-      <c r="V23" s="30"/>
-      <c r="W23" s="30"/>
-      <c r="X23" s="30"/>
-      <c r="Y23" s="30"/>
-      <c r="Z23" s="30"/>
+      <c r="A23" s="30" t="s">
+        <v>319</v>
+      </c>
+      <c r="B23" s="31"/>
+      <c r="C23" s="31"/>
+      <c r="D23" s="31"/>
+      <c r="E23" s="31"/>
+      <c r="F23" s="31"/>
+      <c r="G23" s="31"/>
+      <c r="H23" s="31"/>
+      <c r="I23" s="31"/>
+      <c r="J23" s="31"/>
+      <c r="K23" s="31"/>
+      <c r="L23" s="31"/>
+      <c r="M23" s="31"/>
+      <c r="N23" s="31"/>
+      <c r="O23" s="31"/>
+      <c r="P23" s="31"/>
+      <c r="Q23" s="31"/>
+      <c r="R23" s="31"/>
+      <c r="S23" s="31"/>
+      <c r="T23" s="31"/>
+      <c r="U23" s="31"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="31"/>
+      <c r="X23" s="31"/>
+      <c r="Y23" s="31"/>
+      <c r="Z23" s="31"/>
     </row>
     <row r="24" ht="15.0" customHeight="1">
-      <c r="A24" s="31" t="s">
-        <v>318</v>
-      </c>
-      <c r="B24" s="32">
+      <c r="A24" s="32" t="s">
+        <v>319</v>
+      </c>
+      <c r="B24" s="33">
         <v>243.77</v>
       </c>
-      <c r="C24" s="32">
+      <c r="C24" s="33">
         <v>228.2</v>
       </c>
-      <c r="D24" s="32">
+      <c r="D24" s="33">
         <v>197.45</v>
       </c>
-      <c r="E24" s="32">
+      <c r="E24" s="33">
         <v>212.09</v>
       </c>
-      <c r="F24" s="32">
+      <c r="F24" s="33">
         <v>226.71</v>
       </c>
-      <c r="G24" s="32">
+      <c r="G24" s="33">
         <v>220.16</v>
       </c>
-      <c r="H24" s="32">
+      <c r="H24" s="33">
         <v>196.4</v>
       </c>
-      <c r="I24" s="32">
+      <c r="I24" s="33">
         <v>240.7</v>
       </c>
-      <c r="J24" s="32">
+      <c r="J24" s="33">
         <v>101.96</v>
       </c>
-      <c r="K24" s="33">
+      <c r="K24" s="34">
         <v>98.04</v>
       </c>
-      <c r="L24" s="33">
+      <c r="L24" s="34">
         <v>35.82</v>
       </c>
-      <c r="M24" s="33">
+      <c r="M24" s="34">
         <v>20.04</v>
       </c>
-      <c r="N24" s="33">
+      <c r="N24" s="34">
         <v>16.93</v>
       </c>
-      <c r="O24" s="33">
+      <c r="O24" s="34">
         <v>19.91</v>
       </c>
-      <c r="P24" s="33">
+      <c r="P24" s="34">
         <v>25.36</v>
       </c>
-      <c r="Q24" s="33">
+      <c r="Q24" s="34">
         <v>25.52</v>
       </c>
-      <c r="R24" s="33">
+      <c r="R24" s="34">
         <v>16.16</v>
       </c>
-      <c r="S24" s="33">
+      <c r="S24" s="34">
         <v>27.3</v>
       </c>
-      <c r="T24" s="33">
+      <c r="T24" s="34">
         <v>27.52</v>
       </c>
-      <c r="U24" s="33">
+      <c r="U24" s="34">
         <v>23.73</v>
       </c>
-      <c r="V24" s="33">
+      <c r="V24" s="34">
         <v>17.39</v>
       </c>
-      <c r="W24" s="33">
+      <c r="W24" s="34">
         <v>12.27</v>
       </c>
-      <c r="X24" s="33">
+      <c r="X24" s="34">
         <v>8.27</v>
       </c>
-      <c r="Y24" s="33">
+      <c r="Y24" s="34">
         <v>9.06</v>
       </c>
-      <c r="Z24" s="33">
+      <c r="Z24" s="34">
         <v>10.73</v>
       </c>
     </row>
     <row r="25" ht="15.0" customHeight="1">
-      <c r="A25" s="31" t="s">
-        <v>319</v>
-      </c>
-      <c r="B25" s="32">
+      <c r="A25" s="32" t="s">
+        <v>320</v>
+      </c>
+      <c r="B25" s="33">
         <v>241.88</v>
       </c>
-      <c r="C25" s="32">
+      <c r="C25" s="33">
         <v>233.62</v>
       </c>
-      <c r="D25" s="32">
+      <c r="D25" s="33">
         <v>217.77</v>
       </c>
-      <c r="E25" s="32">
+      <c r="E25" s="33">
         <v>219.19</v>
       </c>
-      <c r="F25" s="32">
+      <c r="F25" s="33">
         <v>208.5</v>
       </c>
-      <c r="G25" s="32">
+      <c r="G25" s="33">
         <v>173.36</v>
       </c>
-      <c r="H25" s="32">
+      <c r="H25" s="33">
         <v>138.06</v>
       </c>
-      <c r="I25" s="32">
+      <c r="I25" s="33">
         <v>102.89</v>
       </c>
-      <c r="J25" s="33">
+      <c r="J25" s="34">
         <v>54.69</v>
       </c>
-      <c r="K25" s="33">
+      <c r="K25" s="34">
         <v>41.2</v>
       </c>
-      <c r="L25" s="33">
+      <c r="L25" s="34">
         <v>26.22</v>
       </c>
-      <c r="M25" s="33">
+      <c r="M25" s="34">
         <v>22.71</v>
       </c>
-      <c r="N25" s="33">
+      <c r="N25" s="34">
         <v>18.91</v>
       </c>
-      <c r="O25" s="33">
+      <c r="O25" s="34">
         <v>21.69</v>
       </c>
-      <c r="P25" s="33">
+      <c r="P25" s="34">
         <v>23.03</v>
       </c>
-      <c r="Q25" s="33">
+      <c r="Q25" s="34">
         <v>24.06</v>
       </c>
-      <c r="R25" s="33">
+      <c r="R25" s="34">
         <v>26.28</v>
       </c>
-      <c r="S25" s="33">
+      <c r="S25" s="34">
         <v>21.14</v>
       </c>
-      <c r="T25" s="33">
+      <c r="T25" s="34">
         <v>18.14</v>
       </c>
-      <c r="U25" s="33">
+      <c r="U25" s="34">
         <v>14.08</v>
       </c>
-      <c r="V25" s="33">
+      <c r="V25" s="34">
         <v>11.77</v>
       </c>
-      <c r="W25" s="35"/>
-      <c r="X25" s="35"/>
-      <c r="Y25" s="35"/>
-      <c r="Z25" s="35"/>
+      <c r="W25" s="36"/>
+      <c r="X25" s="36"/>
+      <c r="Y25" s="36"/>
+      <c r="Z25" s="36"/>
     </row>
     <row r="26" ht="15.0" customHeight="1">
-      <c r="A26" s="29" t="s">
-        <v>320</v>
-      </c>
-      <c r="B26" s="30"/>
-      <c r="C26" s="30"/>
-      <c r="D26" s="30"/>
-      <c r="E26" s="30"/>
-      <c r="F26" s="30"/>
-      <c r="G26" s="30"/>
-      <c r="H26" s="30"/>
-      <c r="I26" s="30"/>
-      <c r="J26" s="30"/>
-      <c r="K26" s="30"/>
-      <c r="L26" s="30"/>
-      <c r="M26" s="30"/>
-      <c r="N26" s="30"/>
-      <c r="O26" s="30"/>
-      <c r="P26" s="30"/>
-      <c r="Q26" s="30"/>
-      <c r="R26" s="30"/>
-      <c r="S26" s="30"/>
-      <c r="T26" s="30"/>
-      <c r="U26" s="30"/>
-      <c r="V26" s="30"/>
-      <c r="W26" s="30"/>
-      <c r="X26" s="30"/>
-      <c r="Y26" s="30"/>
-      <c r="Z26" s="30"/>
+      <c r="A26" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B26" s="31"/>
+      <c r="C26" s="31"/>
+      <c r="D26" s="31"/>
+      <c r="E26" s="31"/>
+      <c r="F26" s="31"/>
+      <c r="G26" s="31"/>
+      <c r="H26" s="31"/>
+      <c r="I26" s="31"/>
+      <c r="J26" s="31"/>
+      <c r="K26" s="31"/>
+      <c r="L26" s="31"/>
+      <c r="M26" s="31"/>
+      <c r="N26" s="31"/>
+      <c r="O26" s="31"/>
+      <c r="P26" s="31"/>
+      <c r="Q26" s="31"/>
+      <c r="R26" s="31"/>
+      <c r="S26" s="31"/>
+      <c r="T26" s="31"/>
+      <c r="U26" s="31"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="31"/>
+      <c r="X26" s="31"/>
+      <c r="Y26" s="31"/>
+      <c r="Z26" s="31"/>
     </row>
     <row r="27" ht="15.0" customHeight="1">
-      <c r="A27" s="31" t="s">
-        <v>321</v>
-      </c>
-      <c r="B27" s="33">
+      <c r="A27" s="32" t="s">
+        <v>322</v>
+      </c>
+      <c r="B27" s="34">
         <v>38.15</v>
       </c>
-      <c r="C27" s="33">
+      <c r="C27" s="34">
         <v>35.72</v>
       </c>
-      <c r="D27" s="33">
+      <c r="D27" s="34">
         <v>30.9</v>
       </c>
-      <c r="E27" s="33">
+      <c r="E27" s="34">
         <v>34.31</v>
       </c>
-      <c r="F27" s="33">
+      <c r="F27" s="34">
         <v>36.67</v>
       </c>
-      <c r="G27" s="33">
+      <c r="G27" s="34">
         <v>35.61</v>
       </c>
-      <c r="H27" s="33">
+      <c r="H27" s="34">
         <v>31.77</v>
       </c>
-      <c r="I27" s="33">
+      <c r="I27" s="34">
         <v>38.93</v>
       </c>
-      <c r="J27" s="33">
+      <c r="J27" s="34">
         <v>28.97</v>
       </c>
-      <c r="K27" s="33">
+      <c r="K27" s="34">
         <v>27.86</v>
       </c>
-      <c r="L27" s="33">
+      <c r="L27" s="34">
         <v>23.57</v>
       </c>
-      <c r="M27" s="33">
+      <c r="M27" s="34">
         <v>13.19</v>
       </c>
-      <c r="N27" s="33">
+      <c r="N27" s="34">
         <v>11.14</v>
       </c>
-      <c r="O27" s="33">
+      <c r="O27" s="34">
         <v>13.11</v>
       </c>
-      <c r="P27" s="33">
+      <c r="P27" s="34">
         <v>16.69</v>
       </c>
-      <c r="Q27" s="33">
+      <c r="Q27" s="34">
         <v>16.8</v>
       </c>
-      <c r="R27" s="33">
+      <c r="R27" s="34">
         <v>10.64</v>
       </c>
-      <c r="S27" s="33">
+      <c r="S27" s="34">
         <v>17.97</v>
       </c>
-      <c r="T27" s="33">
+      <c r="T27" s="34">
         <v>18.11</v>
       </c>
-      <c r="U27" s="33">
+      <c r="U27" s="34">
         <v>15.62</v>
       </c>
-      <c r="V27" s="33">
+      <c r="V27" s="34">
         <v>11.45</v>
       </c>
-      <c r="W27" s="33">
+      <c r="W27" s="34">
         <v>8.07</v>
       </c>
-      <c r="X27" s="33">
+      <c r="X27" s="34">
         <v>5.44</v>
       </c>
-      <c r="Y27" s="33">
+      <c r="Y27" s="34">
         <v>5.96</v>
       </c>
-      <c r="Z27" s="33">
+      <c r="Z27" s="34">
         <v>7.06</v>
       </c>
     </row>
     <row r="28" ht="15.0" customHeight="1">
-      <c r="A28" s="31" t="s">
-        <v>322</v>
-      </c>
-      <c r="B28" s="33">
+      <c r="A28" s="32" t="s">
+        <v>323</v>
+      </c>
+      <c r="B28" s="34">
         <v>38.39</v>
       </c>
-      <c r="C28" s="33">
+      <c r="C28" s="34">
         <v>37.33</v>
       </c>
-      <c r="D28" s="33">
+      <c r="D28" s="34">
         <v>35.02</v>
       </c>
-      <c r="E28" s="33">
+      <c r="E28" s="34">
         <v>35.45</v>
       </c>
-      <c r="F28" s="33">
+      <c r="F28" s="34">
         <v>36.61</v>
       </c>
-      <c r="G28" s="33">
+      <c r="G28" s="34">
         <v>33.21</v>
       </c>
-      <c r="H28" s="33">
+      <c r="H28" s="34">
         <v>31.43</v>
       </c>
-      <c r="I28" s="33">
+      <c r="I28" s="34">
         <v>28.03</v>
       </c>
-      <c r="J28" s="33">
+      <c r="J28" s="34">
         <v>21.43</v>
       </c>
-      <c r="K28" s="33">
+      <c r="K28" s="34">
         <v>19.78</v>
       </c>
-      <c r="L28" s="33">
+      <c r="L28" s="34">
         <v>17.25</v>
       </c>
-      <c r="M28" s="33">
+      <c r="M28" s="34">
         <v>14.95</v>
       </c>
-      <c r="N28" s="33">
+      <c r="N28" s="34">
         <v>12.44</v>
       </c>
-      <c r="O28" s="33">
+      <c r="O28" s="34">
         <v>14.27</v>
       </c>
-      <c r="P28" s="33">
+      <c r="P28" s="34">
         <v>15.16</v>
       </c>
-      <c r="Q28" s="33">
+      <c r="Q28" s="34">
         <v>15.83</v>
       </c>
-      <c r="R28" s="33">
+      <c r="R28" s="34">
         <v>17.3</v>
       </c>
-      <c r="S28" s="33">
+      <c r="S28" s="34">
         <v>13.91</v>
       </c>
-      <c r="T28" s="33">
+      <c r="T28" s="34">
         <v>11.94</v>
       </c>
-      <c r="U28" s="33">
+      <c r="U28" s="34">
         <v>9.27</v>
       </c>
-      <c r="V28" s="33">
+      <c r="V28" s="34">
         <v>7.75</v>
       </c>
-      <c r="W28" s="35"/>
-      <c r="X28" s="35"/>
-      <c r="Y28" s="35"/>
-      <c r="Z28" s="35"/>
+      <c r="W28" s="36"/>
+      <c r="X28" s="36"/>
+      <c r="Y28" s="36"/>
+      <c r="Z28" s="36"/>
     </row>
     <row r="29" ht="15.0" customHeight="1">
-      <c r="A29" s="29" t="s">
-        <v>323</v>
-      </c>
-      <c r="B29" s="30"/>
-      <c r="C29" s="30"/>
-      <c r="D29" s="30"/>
-      <c r="E29" s="30"/>
-      <c r="F29" s="30"/>
-      <c r="G29" s="30"/>
-      <c r="H29" s="30"/>
-      <c r="I29" s="30"/>
-      <c r="J29" s="30"/>
-      <c r="K29" s="30"/>
-      <c r="L29" s="30"/>
-      <c r="M29" s="30"/>
-      <c r="N29" s="30"/>
-      <c r="O29" s="30"/>
-      <c r="P29" s="30"/>
-      <c r="Q29" s="30"/>
-      <c r="R29" s="30"/>
-      <c r="S29" s="30"/>
-      <c r="T29" s="30"/>
-      <c r="U29" s="30"/>
-      <c r="V29" s="30"/>
-      <c r="W29" s="30"/>
-      <c r="X29" s="30"/>
-      <c r="Y29" s="30"/>
-      <c r="Z29" s="30"/>
+      <c r="A29" s="30" t="s">
+        <v>324</v>
+      </c>
+      <c r="B29" s="31"/>
+      <c r="C29" s="31"/>
+      <c r="D29" s="31"/>
+      <c r="E29" s="31"/>
+      <c r="F29" s="31"/>
+      <c r="G29" s="31"/>
+      <c r="H29" s="31"/>
+      <c r="I29" s="31"/>
+      <c r="J29" s="31"/>
+      <c r="K29" s="31"/>
+      <c r="L29" s="31"/>
+      <c r="M29" s="31"/>
+      <c r="N29" s="31"/>
+      <c r="O29" s="31"/>
+      <c r="P29" s="31"/>
+      <c r="Q29" s="31"/>
+      <c r="R29" s="31"/>
+      <c r="S29" s="31"/>
+      <c r="T29" s="31"/>
+      <c r="U29" s="31"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="31"/>
+      <c r="X29" s="31"/>
+      <c r="Y29" s="31"/>
+      <c r="Z29" s="31"/>
     </row>
     <row r="30" ht="15.0" customHeight="1">
-      <c r="A30" s="31" t="s">
-        <v>324</v>
-      </c>
-      <c r="B30" s="36">
+      <c r="A30" s="32" t="s">
+        <v>325</v>
+      </c>
+      <c r="B30" s="37">
         <v>9.82</v>
       </c>
-      <c r="C30" s="37">
+      <c r="C30" s="38">
         <v>-4.59</v>
       </c>
-      <c r="D30" s="37">
+      <c r="D30" s="38">
         <v>-2.97</v>
       </c>
-      <c r="E30" s="37">
+      <c r="E30" s="38">
         <v>-11.39</v>
       </c>
-      <c r="F30" s="37">
+      <c r="F30" s="38">
         <v>-1.05</v>
       </c>
-      <c r="G30" s="37">
+      <c r="G30" s="38">
         <v>-124.79</v>
       </c>
-      <c r="H30" s="37">
+      <c r="H30" s="38">
         <v>-23.92</v>
       </c>
-      <c r="I30" s="36">
+      <c r="I30" s="37">
         <v>0.38</v>
       </c>
-      <c r="J30" s="37">
+      <c r="J30" s="38">
         <v>-42.87</v>
       </c>
-      <c r="K30" s="37">
+      <c r="K30" s="38">
         <v>-41.71</v>
       </c>
-      <c r="L30" s="36">
+      <c r="L30" s="37">
         <v>0.19</v>
       </c>
-      <c r="M30" s="37">
+      <c r="M30" s="38">
         <v>-46.98</v>
       </c>
-      <c r="N30" s="37">
+      <c r="N30" s="38">
         <v>-13.66</v>
       </c>
-      <c r="O30" s="37">
+      <c r="O30" s="38">
         <v>-45.79</v>
       </c>
-      <c r="P30" s="37">
+      <c r="P30" s="38">
         <v>-1.02</v>
       </c>
-      <c r="Q30" s="36">
+      <c r="Q30" s="37">
         <v>11.83</v>
       </c>
-      <c r="R30" s="36">
+      <c r="R30" s="37">
         <v>23.67</v>
       </c>
-      <c r="S30" s="36">
+      <c r="S30" s="37">
         <v>9.76</v>
       </c>
-      <c r="T30" s="36">
+      <c r="T30" s="37">
         <v>12.32</v>
       </c>
-      <c r="U30" s="36">
+      <c r="U30" s="37">
         <v>17.19</v>
       </c>
-      <c r="V30" s="36">
+      <c r="V30" s="37">
         <v>27.99</v>
       </c>
-      <c r="W30" s="36">
+      <c r="W30" s="37">
         <v>34.69</v>
       </c>
-      <c r="X30" s="36">
+      <c r="X30" s="37">
         <v>21.29</v>
       </c>
-      <c r="Y30" s="36">
+      <c r="Y30" s="37">
         <v>13.55</v>
       </c>
-      <c r="Z30" s="37">
+      <c r="Z30" s="38">
         <v>-32.47</v>
       </c>
     </row>
     <row r="31" ht="15.0" customHeight="1">
-      <c r="A31" s="31" t="s">
-        <v>325</v>
-      </c>
-      <c r="B31" s="37">
+      <c r="A31" s="32" t="s">
+        <v>326</v>
+      </c>
+      <c r="B31" s="38">
         <v>-2.1</v>
       </c>
-      <c r="C31" s="37">
+      <c r="C31" s="38">
         <v>-31.03</v>
       </c>
-      <c r="D31" s="37">
+      <c r="D31" s="38">
         <v>-34.72</v>
       </c>
-      <c r="E31" s="37">
+      <c r="E31" s="38">
         <v>-32.16</v>
       </c>
-      <c r="F31" s="37">
+      <c r="F31" s="38">
         <v>-38.19</v>
       </c>
-      <c r="G31" s="37">
+      <c r="G31" s="38">
         <v>-46.5</v>
       </c>
-      <c r="H31" s="37">
+      <c r="H31" s="38">
         <v>-20.96</v>
       </c>
-      <c r="I31" s="37">
+      <c r="I31" s="38">
         <v>-23.19</v>
       </c>
-      <c r="J31" s="37">
+      <c r="J31" s="38">
         <v>-29.86</v>
       </c>
-      <c r="K31" s="37">
+      <c r="K31" s="38">
         <v>-28.45</v>
       </c>
-      <c r="L31" s="37">
+      <c r="L31" s="38">
         <v>-18.26</v>
       </c>
-      <c r="M31" s="37">
+      <c r="M31" s="38">
         <v>-16.83</v>
       </c>
-      <c r="N31" s="37">
+      <c r="N31" s="38">
         <v>-5.97</v>
       </c>
-      <c r="O31" s="37">
+      <c r="O31" s="38">
         <v>-0.84</v>
       </c>
-      <c r="P31" s="36">
+      <c r="P31" s="37">
         <v>9.96</v>
       </c>
-      <c r="Q31" s="36">
+      <c r="Q31" s="37">
         <v>13.91</v>
       </c>
-      <c r="R31" s="36">
+      <c r="R31" s="37">
         <v>16.58</v>
       </c>
-      <c r="S31" s="36">
+      <c r="S31" s="37">
         <v>17.68</v>
       </c>
-      <c r="T31" s="36">
+      <c r="T31" s="37">
         <v>20.52</v>
       </c>
-      <c r="U31" s="36">
+      <c r="U31" s="37">
         <v>22.74</v>
       </c>
-      <c r="V31" s="36">
+      <c r="V31" s="37">
         <v>15.0</v>
       </c>
-      <c r="W31" s="36"/>
-      <c r="X31" s="36"/>
-      <c r="Y31" s="36"/>
-      <c r="Z31" s="36"/>
+      <c r="W31" s="37"/>
+      <c r="X31" s="37"/>
+      <c r="Y31" s="37"/>
+      <c r="Z31" s="37"/>
     </row>
     <row r="32" ht="15.0" customHeight="1">
-      <c r="A32" s="29" t="s">
-        <v>326</v>
-      </c>
-      <c r="B32" s="30"/>
-      <c r="C32" s="30"/>
-      <c r="D32" s="30"/>
-      <c r="E32" s="30"/>
-      <c r="F32" s="30"/>
-      <c r="G32" s="30"/>
-      <c r="H32" s="30"/>
-      <c r="I32" s="30"/>
-      <c r="J32" s="30"/>
-      <c r="K32" s="30"/>
-      <c r="L32" s="30"/>
-      <c r="M32" s="30"/>
-      <c r="N32" s="30"/>
-      <c r="O32" s="30"/>
-      <c r="P32" s="30"/>
-      <c r="Q32" s="30"/>
-      <c r="R32" s="30"/>
-      <c r="S32" s="30"/>
-      <c r="T32" s="30"/>
-      <c r="U32" s="30"/>
-      <c r="V32" s="30"/>
-      <c r="W32" s="30"/>
-      <c r="X32" s="30"/>
-      <c r="Y32" s="30"/>
-      <c r="Z32" s="30"/>
+      <c r="A32" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="B32" s="31"/>
+      <c r="C32" s="31"/>
+      <c r="D32" s="31"/>
+      <c r="E32" s="31"/>
+      <c r="F32" s="31"/>
+      <c r="G32" s="31"/>
+      <c r="H32" s="31"/>
+      <c r="I32" s="31"/>
+      <c r="J32" s="31"/>
+      <c r="K32" s="31"/>
+      <c r="L32" s="31"/>
+      <c r="M32" s="31"/>
+      <c r="N32" s="31"/>
+      <c r="O32" s="31"/>
+      <c r="P32" s="31"/>
+      <c r="Q32" s="31"/>
+      <c r="R32" s="31"/>
+      <c r="S32" s="31"/>
+      <c r="T32" s="31"/>
+      <c r="U32" s="31"/>
+      <c r="V32" s="31"/>
+      <c r="W32" s="31"/>
+      <c r="X32" s="31"/>
+      <c r="Y32" s="31"/>
+      <c r="Z32" s="31"/>
     </row>
     <row r="33" ht="15.0" customHeight="1">
-      <c r="A33" s="31" t="s">
-        <v>327</v>
-      </c>
-      <c r="B33" s="36">
+      <c r="A33" s="32" t="s">
+        <v>328</v>
+      </c>
+      <c r="B33" s="37">
         <v>10.18</v>
       </c>
-      <c r="C33" s="36">
+      <c r="C33" s="37">
         <v>9.71</v>
       </c>
-      <c r="D33" s="36">
+      <c r="D33" s="37">
         <v>9.84</v>
       </c>
-      <c r="E33" s="36">
+      <c r="E33" s="37">
         <v>37.06</v>
       </c>
-      <c r="F33" s="36">
+      <c r="F33" s="37">
         <v>7.14</v>
       </c>
-      <c r="G33" s="36">
+      <c r="G33" s="37">
         <v>6.36</v>
       </c>
-      <c r="H33" s="36">
+      <c r="H33" s="37">
         <v>6.55</v>
       </c>
-      <c r="I33" s="36">
+      <c r="I33" s="37">
         <v>4.8</v>
       </c>
-      <c r="J33" s="36">
+      <c r="J33" s="37">
         <v>5.33</v>
       </c>
-      <c r="K33" s="36">
+      <c r="K33" s="37">
         <v>3.45</v>
       </c>
-      <c r="L33" s="36">
+      <c r="L33" s="37">
         <v>3.83</v>
       </c>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36">
+      <c r="M33" s="37"/>
+      <c r="N33" s="37">
         <v>6.59</v>
       </c>
-      <c r="O33" s="36">
+      <c r="O33" s="37">
         <v>4.75</v>
       </c>
-      <c r="P33" s="36">
+      <c r="P33" s="37">
         <v>3.75</v>
       </c>
-      <c r="Q33" s="36">
+      <c r="Q33" s="37">
         <v>5.95</v>
       </c>
-      <c r="R33" s="36">
+      <c r="R33" s="37">
         <v>11.01</v>
       </c>
-      <c r="S33" s="36">
+      <c r="S33" s="37">
         <v>5.32</v>
       </c>
-      <c r="T33" s="36">
+      <c r="T33" s="37">
         <v>5.48</v>
       </c>
-      <c r="U33" s="36"/>
-      <c r="V33" s="36">
+      <c r="U33" s="37"/>
+      <c r="V33" s="37">
         <v>10.8</v>
       </c>
-      <c r="W33" s="36">
+      <c r="W33" s="37">
         <v>5.2</v>
       </c>
-      <c r="X33" s="36">
+      <c r="X33" s="37">
         <v>6.68</v>
       </c>
-      <c r="Y33" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="Z33" s="36">
+      <c r="Y33" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Z33" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="34" ht="15.0" customHeight="1">
-      <c r="A34" s="31" t="s">
-        <v>328</v>
-      </c>
-      <c r="B34" s="36">
+      <c r="A34" s="32" t="s">
+        <v>329</v>
+      </c>
+      <c r="B34" s="37">
         <v>15.02</v>
       </c>
-      <c r="C34" s="36">
+      <c r="C34" s="37">
         <v>14.08</v>
       </c>
-      <c r="D34" s="36">
+      <c r="D34" s="37">
         <v>13.47</v>
       </c>
-      <c r="E34" s="36">
+      <c r="E34" s="37">
         <v>12.14</v>
       </c>
-      <c r="F34" s="36">
+      <c r="F34" s="37">
         <v>6.01</v>
       </c>
-      <c r="G34" s="36">
+      <c r="G34" s="37">
         <v>5.33</v>
       </c>
-      <c r="H34" s="36">
+      <c r="H34" s="37">
         <v>4.85</v>
       </c>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36">
+      <c r="I34" s="37"/>
+      <c r="J34" s="37"/>
+      <c r="K34" s="37"/>
+      <c r="L34" s="37"/>
+      <c r="M34" s="37"/>
+      <c r="N34" s="37">
         <v>5.92</v>
       </c>
-      <c r="O34" s="36">
+      <c r="O34" s="37">
         <v>5.67</v>
       </c>
-      <c r="P34" s="36">
+      <c r="P34" s="37">
         <v>5.78</v>
       </c>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="36"/>
-      <c r="V34" s="36">
+      <c r="Q34" s="37"/>
+      <c r="R34" s="37"/>
+      <c r="S34" s="37"/>
+      <c r="T34" s="37"/>
+      <c r="U34" s="37"/>
+      <c r="V34" s="37">
         <v>5.32</v>
       </c>
-      <c r="W34" s="36"/>
-      <c r="X34" s="36"/>
-      <c r="Y34" s="36"/>
-      <c r="Z34" s="36"/>
+      <c r="W34" s="37"/>
+      <c r="X34" s="37"/>
+      <c r="Y34" s="37"/>
+      <c r="Z34" s="37"/>
     </row>
     <row r="35" ht="15.0" customHeight="1">
-      <c r="A35" s="31" t="s">
-        <v>329</v>
-      </c>
-      <c r="B35" s="36">
+      <c r="A35" s="32" t="s">
+        <v>330</v>
+      </c>
+      <c r="B35" s="37">
         <v>10.18</v>
       </c>
-      <c r="C35" s="36">
+      <c r="C35" s="37">
         <v>9.71</v>
       </c>
-      <c r="D35" s="36">
+      <c r="D35" s="37">
         <v>9.84</v>
       </c>
-      <c r="E35" s="36">
+      <c r="E35" s="37">
         <v>37.06</v>
       </c>
-      <c r="F35" s="36">
+      <c r="F35" s="37">
         <v>7.14</v>
       </c>
-      <c r="G35" s="36">
+      <c r="G35" s="37">
         <v>6.36</v>
       </c>
-      <c r="H35" s="36">
+      <c r="H35" s="37">
         <v>6.55</v>
       </c>
-      <c r="I35" s="36">
+      <c r="I35" s="37">
         <v>4.8</v>
       </c>
-      <c r="J35" s="36">
+      <c r="J35" s="37">
         <v>5.33</v>
       </c>
-      <c r="K35" s="36">
+      <c r="K35" s="37">
         <v>3.45</v>
       </c>
-      <c r="L35" s="36">
+      <c r="L35" s="37">
         <v>3.83</v>
       </c>
-      <c r="M35" s="36">
+      <c r="M35" s="37">
         <v>6.32</v>
       </c>
-      <c r="N35" s="36">
+      <c r="N35" s="37">
         <v>6.59</v>
       </c>
-      <c r="O35" s="36">
+      <c r="O35" s="37">
         <v>5.9</v>
       </c>
-      <c r="P35" s="36">
+      <c r="P35" s="37">
         <v>4.67</v>
       </c>
-      <c r="Q35" s="36">
+      <c r="Q35" s="37">
         <v>7.41</v>
       </c>
-      <c r="R35" s="36">
+      <c r="R35" s="37">
         <v>13.69</v>
       </c>
-      <c r="S35" s="36">
+      <c r="S35" s="37">
         <v>6.62</v>
       </c>
-      <c r="T35" s="36">
+      <c r="T35" s="37">
         <v>6.81</v>
       </c>
-      <c r="U35" s="36">
+      <c r="U35" s="37">
         <v>7.67</v>
       </c>
-      <c r="V35" s="36">
+      <c r="V35" s="37">
         <v>3.6</v>
       </c>
-      <c r="W35" s="36">
+      <c r="W35" s="37">
         <v>5.2</v>
       </c>
-      <c r="X35" s="36">
+      <c r="X35" s="37">
         <v>6.68</v>
       </c>
-      <c r="Y35" s="36">
-        <v>0.0</v>
-      </c>
-      <c r="Z35" s="36">
+      <c r="Y35" s="37">
+        <v>0.0</v>
+      </c>
+      <c r="Z35" s="37">
         <v>0.0</v>
       </c>
     </row>
     <row r="36" ht="15.0" customHeight="1">
-      <c r="A36" s="31" t="s">
-        <v>330</v>
-      </c>
-      <c r="B36" s="36">
+      <c r="A36" s="32" t="s">
+        <v>331</v>
+      </c>
+      <c r="B36" s="37">
         <v>15.02</v>
       </c>
-      <c r="C36" s="36">
+      <c r="C36" s="37">
         <v>14.08</v>
       </c>
-      <c r="D36" s="36">
+      <c r="D36" s="37">
         <v>13.47</v>
       </c>
-      <c r="E36" s="36">
+      <c r="E36" s="37">
         <v>12.14</v>
       </c>
-      <c r="F36" s="36">
+      <c r="F36" s="37">
         <v>6.01</v>
       </c>
-      <c r="G36" s="36">
+      <c r="G36" s="37">
         <v>5.33</v>
       </c>
-      <c r="H36" s="36">
+      <c r="H36" s="37">
         <v>4.85</v>
       </c>
-      <c r="I36" s="36">
+      <c r="I36" s="37">
         <v>4.64</v>
       </c>
-      <c r="J36" s="36">
+      <c r="J36" s="37">
         <v>4.83</v>
       </c>
-      <c r="K36" s="36">
+      <c r="K36" s="37">
         <v>4.85</v>
       </c>
-      <c r="L36" s="36">
+      <c r="L36" s="37">
         <v>5.24</v>
       </c>
-      <c r="M36" s="36">
+      <c r="M36" s="37">
         <v>6.14</v>
       </c>
-      <c r="N36" s="36">
+      <c r="N36" s="37">
         <v>7.08</v>
       </c>
-      <c r="O36" s="36">
+      <c r="O36" s="37">
         <v>7.05</v>
       </c>
-      <c r="P36" s="36">
+      <c r="P36" s="37">
         <v>7.19</v>
       </c>
-      <c r="Q36" s="36">
+      <c r="Q36" s="37">
         <v>7.86</v>
       </c>
-      <c r="R36" s="36">
+      <c r="R36" s="37">
         <v>7.3</v>
       </c>
-      <c r="S36" s="36">
+      <c r="S36" s="37">
         <v>6.27</v>
       </c>
-      <c r="T36" s="36">
+      <c r="T36" s="37">
         <v>6.2</v>
       </c>
-      <c r="U36" s="36">
+      <c r="U36" s="37">
         <v>5.17</v>
       </c>
-      <c r="V36" s="36">
+      <c r="V36" s="37">
         <v>3.19</v>
       </c>
-      <c r="W36" s="36"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="36"/>
+      <c r="W36" s="37"/>
+      <c r="X36" s="37"/>
+      <c r="Y36" s="37"/>
+      <c r="Z36" s="37"/>
     </row>
     <row r="37" ht="15.0" customHeight="1">
-      <c r="A37" s="29" t="s">
-        <v>331</v>
-      </c>
-      <c r="B37" s="30"/>
-      <c r="C37" s="30"/>
-      <c r="D37" s="30"/>
-      <c r="E37" s="30"/>
-      <c r="F37" s="30"/>
-      <c r="G37" s="30"/>
-      <c r="H37" s="30"/>
-      <c r="I37" s="30"/>
-      <c r="J37" s="30"/>
-      <c r="K37" s="30"/>
-      <c r="L37" s="30"/>
-      <c r="M37" s="30"/>
-      <c r="N37" s="30"/>
-      <c r="O37" s="30"/>
-      <c r="P37" s="30"/>
-      <c r="Q37" s="30"/>
-      <c r="R37" s="30"/>
-      <c r="S37" s="30"/>
-      <c r="T37" s="30"/>
-      <c r="U37" s="30"/>
-      <c r="V37" s="30"/>
-      <c r="W37" s="30"/>
-      <c r="X37" s="30"/>
-      <c r="Y37" s="30"/>
-      <c r="Z37" s="30"/>
+      <c r="A37" s="30" t="s">
+        <v>332</v>
+      </c>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
+      <c r="K37" s="31"/>
+      <c r="L37" s="31"/>
+      <c r="M37" s="31"/>
+      <c r="N37" s="31"/>
+      <c r="O37" s="31"/>
+      <c r="P37" s="31"/>
+      <c r="Q37" s="31"/>
+      <c r="R37" s="31"/>
+      <c r="S37" s="31"/>
+      <c r="T37" s="31"/>
+      <c r="U37" s="31"/>
+      <c r="V37" s="31"/>
+      <c r="W37" s="31"/>
+      <c r="X37" s="31"/>
+      <c r="Y37" s="31"/>
+      <c r="Z37" s="31"/>
     </row>
     <row r="38" ht="15.0" customHeight="1">
-      <c r="A38" s="31" t="s">
-        <v>332</v>
-      </c>
-      <c r="B38" s="33">
+      <c r="A38" s="32" t="s">
+        <v>333</v>
+      </c>
+      <c r="B38" s="34">
         <v>0.54</v>
       </c>
-      <c r="C38" s="33">
+      <c r="C38" s="34">
         <v>0.61</v>
       </c>
-      <c r="D38" s="33">
+      <c r="D38" s="34">
         <v>0.59</v>
       </c>
-      <c r="E38" s="33">
+      <c r="E38" s="34">
         <v>0.59</v>
       </c>
-      <c r="F38" s="33">
+      <c r="F38" s="34">
         <v>0.56</v>
       </c>
-      <c r="G38" s="33">
+      <c r="G38" s="34">
         <v>0.48</v>
       </c>
-      <c r="H38" s="33">
+      <c r="H38" s="34">
         <v>0.41</v>
       </c>
-      <c r="I38" s="33">
+      <c r="I38" s="34">
         <v>0.52</v>
       </c>
-      <c r="J38" s="33">
+      <c r="J38" s="34">
         <v>0.49</v>
       </c>
-      <c r="K38" s="33">
+      <c r="K38" s="34">
         <v>0.52</v>
       </c>
-      <c r="L38" s="33">
+      <c r="L38" s="34">
         <v>0.67</v>
       </c>
-      <c r="M38" s="33">
+      <c r="M38" s="34">
         <v>0.52</v>
       </c>
-      <c r="N38" s="33">
+      <c r="N38" s="34">
         <v>0.49</v>
       </c>
-      <c r="O38" s="33">
+      <c r="O38" s="34">
         <v>0.55</v>
       </c>
-      <c r="P38" s="33">
+      <c r="P38" s="34">
         <v>0.66</v>
       </c>
-      <c r="Q38" s="33">
+      <c r="Q38" s="34">
         <v>0.66</v>
       </c>
-      <c r="R38" s="33">
+      <c r="R38" s="34">
         <v>0.38</v>
       </c>
-      <c r="S38" s="33">
+      <c r="S38" s="34">
         <v>0.78</v>
       </c>
-      <c r="T38" s="33">
+      <c r="T38" s="34">
         <v>0.76</v>
       </c>
-      <c r="U38" s="33">
+      <c r="U38" s="34">
         <v>0.81</v>
       </c>
-      <c r="V38" s="33">
+      <c r="V38" s="34">
         <v>0.58</v>
       </c>
-      <c r="W38" s="33">
+      <c r="W38" s="34">
         <v>0.47</v>
       </c>
-      <c r="X38" s="33">
+      <c r="X38" s="34">
         <v>0.4</v>
       </c>
-      <c r="Y38" s="33">
+      <c r="Y38" s="34">
         <v>0.42</v>
       </c>
-      <c r="Z38" s="33">
+      <c r="Z38" s="34">
         <v>0.4</v>
       </c>
     </row>
     <row r="39" ht="15.0" customHeight="1">
-      <c r="A39" s="31" t="s">
-        <v>333</v>
-      </c>
-      <c r="B39" s="33">
+      <c r="A39" s="32" t="s">
+        <v>334</v>
+      </c>
+      <c r="B39" s="34">
         <v>0.57</v>
       </c>
-      <c r="C39" s="33">
+      <c r="C39" s="34">
         <v>0.56</v>
       </c>
-      <c r="D39" s="33">
+      <c r="D39" s="34">
         <v>0.52</v>
       </c>
-      <c r="E39" s="33">
+      <c r="E39" s="34">
         <v>0.51</v>
       </c>
-      <c r="F39" s="33">
+      <c r="F39" s="34">
         <v>0.49</v>
       </c>
-      <c r="G39" s="33">
+      <c r="G39" s="34">
         <v>0.48</v>
       </c>
-      <c r="H39" s="33">
+      <c r="H39" s="34">
         <v>0.5</v>
       </c>
-      <c r="I39" s="33">
+      <c r="I39" s="34">
         <v>0.53</v>
       </c>
-      <c r="J39" s="33">
+      <c r="J39" s="34">
         <v>0.53</v>
       </c>
-      <c r="K39" s="33">
+      <c r="K39" s="34">
         <v>0.55</v>
       </c>
-      <c r="L39" s="33">
+      <c r="L39" s="34">
         <v>0.58</v>
       </c>
-      <c r="M39" s="33">
+      <c r="M39" s="34">
         <v>0.58</v>
       </c>
-      <c r="N39" s="33">
+      <c r="N39" s="34">
         <v>0.55</v>
       </c>
-      <c r="O39" s="33">
+      <c r="O39" s="34">
         <v>0.61</v>
       </c>
-      <c r="P39" s="33">
+      <c r="P39" s="34">
         <v>0.65</v>
       </c>
-      <c r="Q39" s="33">
+      <c r="Q39" s="34">
         <v>0.67</v>
       </c>
-      <c r="R39" s="33">
+      <c r="R39" s="34">
         <v>0.66</v>
       </c>
-      <c r="S39" s="33">
+      <c r="S39" s="34">
         <v>0.69</v>
       </c>
-      <c r="T39" s="33">
+      <c r="T39" s="34">
         <v>0.62</v>
       </c>
-      <c r="U39" s="33">
+      <c r="U39" s="34">
         <v>0.55</v>
       </c>
-      <c r="V39" s="33">
+      <c r="V39" s="34">
         <v>0.46</v>
       </c>
-      <c r="W39" s="35"/>
-      <c r="X39" s="35"/>
-      <c r="Y39" s="35"/>
-      <c r="Z39" s="35"/>
+      <c r="W39" s="36"/>
+      <c r="X39" s="36"/>
+      <c r="Y39" s="36"/>
+      <c r="Z39" s="36"/>
     </row>
     <row r="40" ht="15.0" customHeight="1">
-      <c r="A40" s="29" t="s">
-        <v>334</v>
-      </c>
-      <c r="B40" s="30"/>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-      <c r="Q40" s="30"/>
-      <c r="R40" s="30"/>
-      <c r="S40" s="30"/>
-      <c r="T40" s="30"/>
-      <c r="U40" s="30"/>
-      <c r="V40" s="30"/>
-      <c r="W40" s="30"/>
-      <c r="X40" s="30"/>
-      <c r="Y40" s="30"/>
-      <c r="Z40" s="30"/>
+      <c r="A40" s="30" t="s">
+        <v>335</v>
+      </c>
+      <c r="B40" s="31"/>
+      <c r="C40" s="31"/>
+      <c r="D40" s="31"/>
+      <c r="E40" s="31"/>
+      <c r="F40" s="31"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="31"/>
+      <c r="I40" s="31"/>
+      <c r="J40" s="31"/>
+      <c r="K40" s="31"/>
+      <c r="L40" s="31"/>
+      <c r="M40" s="31"/>
+      <c r="N40" s="31"/>
+      <c r="O40" s="31"/>
+      <c r="P40" s="31"/>
+      <c r="Q40" s="31"/>
+      <c r="R40" s="31"/>
+      <c r="S40" s="31"/>
+      <c r="T40" s="31"/>
+      <c r="U40" s="31"/>
+      <c r="V40" s="31"/>
+      <c r="W40" s="31"/>
+      <c r="X40" s="31"/>
+      <c r="Y40" s="31"/>
+      <c r="Z40" s="31"/>
     </row>
     <row r="41" ht="15.0" customHeight="1">
-      <c r="A41" s="31" t="s">
-        <v>335</v>
-      </c>
-      <c r="B41" s="33">
+      <c r="A41" s="32" t="s">
+        <v>336</v>
+      </c>
+      <c r="B41" s="34">
         <v>0.61</v>
       </c>
-      <c r="C41" s="33">
+      <c r="C41" s="34">
         <v>0.74</v>
       </c>
-      <c r="D41" s="33">
+      <c r="D41" s="34">
         <v>0.75</v>
       </c>
-      <c r="E41" s="33">
+      <c r="E41" s="34">
         <v>0.69</v>
       </c>
-      <c r="F41" s="33">
+      <c r="F41" s="34">
         <v>0.61</v>
       </c>
-      <c r="G41" s="33">
+      <c r="G41" s="34">
         <v>0.52</v>
       </c>
-      <c r="H41" s="33">
+      <c r="H41" s="34">
         <v>0.44</v>
       </c>
-      <c r="I41" s="33">
+      <c r="I41" s="34">
         <v>0.53</v>
       </c>
-      <c r="J41" s="33">
+      <c r="J41" s="34">
         <v>0.52</v>
       </c>
-      <c r="K41" s="33">
+      <c r="K41" s="34">
         <v>0.53</v>
       </c>
-      <c r="L41" s="33">
+      <c r="L41" s="34">
         <v>0.67</v>
       </c>
-      <c r="M41" s="33">
+      <c r="M41" s="34">
         <v>0.52</v>
       </c>
-      <c r="N41" s="33">
+      <c r="N41" s="34">
         <v>0.49</v>
       </c>
-      <c r="O41" s="33">
+      <c r="O41" s="34">
         <v>0.55</v>
       </c>
-      <c r="P41" s="33">
+      <c r="P41" s="34">
         <v>0.66</v>
       </c>
-      <c r="Q41" s="33">
+      <c r="Q41" s="34">
         <v>0.66</v>
       </c>
-      <c r="R41" s="33">
+      <c r="R41" s="34">
         <v>0.38</v>
       </c>
-      <c r="S41" s="33">
+      <c r="S41" s="34">
         <v>0.78</v>
       </c>
-      <c r="T41" s="33">
+      <c r="T41" s="34">
         <v>0.76</v>
       </c>
-      <c r="U41" s="33">
+      <c r="U41" s="34">
         <v>0.86</v>
       </c>
-      <c r="V41" s="33">
+      <c r="V41" s="34">
         <v>0.6</v>
       </c>
-      <c r="W41" s="33">
+      <c r="W41" s="34">
         <v>0.48</v>
       </c>
-      <c r="X41" s="33">
+      <c r="X41" s="34">
         <v>0.41</v>
       </c>
-      <c r="Y41" s="33">
+      <c r="Y41" s="34">
         <v>0.43</v>
       </c>
-      <c r="Z41" s="33">
+      <c r="Z41" s="34">
         <v>0.41</v>
       </c>
     </row>
     <row r="42" ht="15.0" customHeight="1">
-      <c r="A42" s="31" t="s">
-        <v>336</v>
-      </c>
-      <c r="B42" s="33">
+      <c r="A42" s="32" t="s">
+        <v>337</v>
+      </c>
+      <c r="B42" s="34">
         <v>0.67</v>
       </c>
-      <c r="C42" s="33">
+      <c r="C42" s="34">
         <v>0.64</v>
       </c>
-      <c r="D42" s="33">
+      <c r="D42" s="34">
         <v>0.58</v>
       </c>
-      <c r="E42" s="33">
+      <c r="E42" s="34">
         <v>0.55</v>
       </c>
-      <c r="F42" s="33">
+      <c r="F42" s="34">
         <v>0.52</v>
       </c>
-      <c r="G42" s="33">
+      <c r="G42" s="34">
         <v>0.51</v>
       </c>
-      <c r="H42" s="33">
+      <c r="H42" s="34">
         <v>0.52</v>
       </c>
-      <c r="I42" s="33">
+      <c r="I42" s="34">
         <v>0.55</v>
       </c>
-      <c r="J42" s="33">
+      <c r="J42" s="34">
         <v>0.54</v>
       </c>
-      <c r="K42" s="33">
+      <c r="K42" s="34">
         <v>0.55</v>
       </c>
-      <c r="L42" s="33">
+      <c r="L42" s="34">
         <v>0.58</v>
       </c>
-      <c r="M42" s="33">
+      <c r="M42" s="34">
         <v>0.58</v>
       </c>
-      <c r="N42" s="33">
+      <c r="N42" s="34">
         <v>0.55</v>
       </c>
-      <c r="O42" s="33">
+      <c r="O42" s="34">
         <v>0.61</v>
       </c>
-      <c r="P42" s="33">
+      <c r="P42" s="34">
         <v>0.65</v>
       </c>
-      <c r="Q42" s="33">
+      <c r="Q42" s="34">
         <v>0.68</v>
       </c>
-      <c r="R42" s="33">
+      <c r="R42" s="34">
         <v>0.67</v>
       </c>
-      <c r="S42" s="33">
+      <c r="S42" s="34">
         <v>0.71</v>
       </c>
-      <c r="T42" s="33">
+      <c r="T42" s="34">
         <v>0.64</v>
       </c>
-      <c r="U42" s="33">
+      <c r="U42" s="34">
         <v>0.57</v>
       </c>
-      <c r="V42" s="33">
+      <c r="V42" s="34">
         <v>0.47</v>
       </c>
-      <c r="W42" s="35"/>
-      <c r="X42" s="35"/>
-      <c r="Y42" s="35"/>
-      <c r="Z42" s="35"/>
+      <c r="W42" s="36"/>
+      <c r="X42" s="36"/>
+      <c r="Y42" s="36"/>
+      <c r="Z42" s="36"/>
     </row>
     <row r="43" ht="15.0" customHeight="1">
-      <c r="A43" s="29" t="s">
-        <v>337</v>
-      </c>
-      <c r="B43" s="30"/>
-      <c r="C43" s="30"/>
-      <c r="D43" s="30"/>
-      <c r="E43" s="30"/>
-      <c r="F43" s="30"/>
-      <c r="G43" s="30"/>
-      <c r="H43" s="30"/>
-      <c r="I43" s="30"/>
-      <c r="J43" s="30"/>
-      <c r="K43" s="30"/>
-      <c r="L43" s="30"/>
-      <c r="M43" s="30"/>
-      <c r="N43" s="30"/>
-      <c r="O43" s="30"/>
-      <c r="P43" s="30"/>
-      <c r="Q43" s="30"/>
-      <c r="R43" s="30"/>
-      <c r="S43" s="30"/>
-      <c r="T43" s="30"/>
-      <c r="U43" s="30"/>
-      <c r="V43" s="30"/>
-      <c r="W43" s="30"/>
-      <c r="X43" s="30"/>
-      <c r="Y43" s="30"/>
-      <c r="Z43" s="30"/>
+      <c r="A43" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B43" s="31"/>
+      <c r="C43" s="31"/>
+      <c r="D43" s="31"/>
+      <c r="E43" s="31"/>
+      <c r="F43" s="31"/>
+      <c r="G43" s="31"/>
+      <c r="H43" s="31"/>
+      <c r="I43" s="31"/>
+      <c r="J43" s="31"/>
+      <c r="K43" s="31"/>
+      <c r="L43" s="31"/>
+      <c r="M43" s="31"/>
+      <c r="N43" s="31"/>
+      <c r="O43" s="31"/>
+      <c r="P43" s="31"/>
+      <c r="Q43" s="31"/>
+      <c r="R43" s="31"/>
+      <c r="S43" s="31"/>
+      <c r="T43" s="31"/>
+      <c r="U43" s="31"/>
+      <c r="V43" s="31"/>
+      <c r="W43" s="31"/>
+      <c r="X43" s="31"/>
+      <c r="Y43" s="31"/>
+      <c r="Z43" s="31"/>
     </row>
     <row r="44" ht="15.0" customHeight="1">
-      <c r="A44" s="31" t="s">
-        <v>338</v>
-      </c>
-      <c r="B44" s="33">
+      <c r="A44" s="32" t="s">
+        <v>339</v>
+      </c>
+      <c r="B44" s="34">
         <v>2.06</v>
       </c>
-      <c r="C44" s="33">
+      <c r="C44" s="34">
         <v>2.96</v>
       </c>
-      <c r="D44" s="33">
+      <c r="D44" s="34">
         <v>2.48</v>
       </c>
-      <c r="E44" s="33">
+      <c r="E44" s="34">
         <v>2.13</v>
       </c>
-      <c r="F44" s="33">
+      <c r="F44" s="34">
         <v>2.21</v>
       </c>
-      <c r="G44" s="33">
+      <c r="G44" s="34">
         <v>1.9</v>
       </c>
-      <c r="H44" s="33">
+      <c r="H44" s="34">
         <v>2.33</v>
       </c>
-      <c r="I44" s="33">
+      <c r="I44" s="34">
         <v>3.79</v>
       </c>
-      <c r="J44" s="33">
+      <c r="J44" s="34">
         <v>3.37</v>
       </c>
-      <c r="K44" s="33">
+      <c r="K44" s="34">
         <v>6.42</v>
       </c>
-      <c r="L44" s="33">
+      <c r="L44" s="34">
         <v>5.23</v>
       </c>
-      <c r="M44" s="33">
+      <c r="M44" s="34">
         <v>3.63</v>
       </c>
-      <c r="N44" s="33">
+      <c r="N44" s="34">
         <v>3.56</v>
       </c>
-      <c r="O44" s="33">
+      <c r="O44" s="34">
         <v>4.23</v>
       </c>
-      <c r="P44" s="33">
+      <c r="P44" s="34">
         <v>4.68</v>
       </c>
-      <c r="Q44" s="33">
+      <c r="Q44" s="34">
         <v>4.26</v>
       </c>
-      <c r="R44" s="33">
+      <c r="R44" s="34">
         <v>2.31</v>
       </c>
-      <c r="S44" s="33">
+      <c r="S44" s="34">
         <v>4.94</v>
       </c>
-      <c r="T44" s="33">
+      <c r="T44" s="34">
         <v>2.61</v>
       </c>
-      <c r="U44" s="33">
+      <c r="U44" s="34">
         <v>3.73</v>
       </c>
-      <c r="V44" s="33">
+      <c r="V44" s="34">
         <v>2.54</v>
       </c>
-      <c r="W44" s="33">
+      <c r="W44" s="34">
         <v>1.83</v>
       </c>
-      <c r="X44" s="33">
+      <c r="X44" s="34">
         <v>1.81</v>
       </c>
-      <c r="Y44" s="33">
+      <c r="Y44" s="34">
         <v>2.07</v>
       </c>
-      <c r="Z44" s="33">
+      <c r="Z44" s="34">
         <v>1.01</v>
       </c>
     </row>
     <row r="45" ht="15.0" customHeight="1">
-      <c r="A45" s="31" t="s">
-        <v>339</v>
-      </c>
-      <c r="B45" s="33">
+      <c r="A45" s="32" t="s">
+        <v>340</v>
+      </c>
+      <c r="B45" s="34">
         <v>2.32</v>
       </c>
-      <c r="C45" s="33">
+      <c r="C45" s="34">
         <v>2.26</v>
       </c>
-      <c r="D45" s="33">
+      <c r="D45" s="34">
         <v>2.18</v>
       </c>
-      <c r="E45" s="33">
+      <c r="E45" s="34">
         <v>2.36</v>
       </c>
-      <c r="F45" s="33">
+      <c r="F45" s="34">
         <v>2.55</v>
       </c>
-      <c r="G45" s="33">
+      <c r="G45" s="34">
         <v>2.95</v>
       </c>
-      <c r="H45" s="33">
+      <c r="H45" s="34">
         <v>3.68</v>
       </c>
-      <c r="I45" s="33">
+      <c r="I45" s="34">
         <v>4.22</v>
       </c>
-      <c r="J45" s="33">
+      <c r="J45" s="34">
         <v>4.28</v>
       </c>
-      <c r="K45" s="33">
+      <c r="K45" s="34">
         <v>4.65</v>
       </c>
-      <c r="L45" s="33">
+      <c r="L45" s="34">
         <v>4.3</v>
       </c>
-      <c r="M45" s="33">
+      <c r="M45" s="34">
         <v>4.08</v>
       </c>
-      <c r="N45" s="33">
+      <c r="N45" s="34">
         <v>3.79</v>
       </c>
-      <c r="O45" s="33">
+      <c r="O45" s="34">
         <v>4.07</v>
       </c>
-      <c r="P45" s="33">
+      <c r="P45" s="34">
         <v>3.59</v>
       </c>
-      <c r="Q45" s="33">
+      <c r="Q45" s="34">
         <v>3.44</v>
       </c>
-      <c r="R45" s="33">
+      <c r="R45" s="34">
         <v>3.13</v>
       </c>
-      <c r="S45" s="33">
+      <c r="S45" s="34">
         <v>3.03</v>
       </c>
-      <c r="T45" s="33">
+      <c r="T45" s="34">
         <v>2.54</v>
       </c>
-      <c r="U45" s="33">
+      <c r="U45" s="34">
         <v>2.45</v>
       </c>
-      <c r="V45" s="33">
+      <c r="V45" s="34">
         <v>1.75</v>
       </c>
-      <c r="W45" s="35"/>
-      <c r="X45" s="35"/>
-      <c r="Y45" s="35"/>
-      <c r="Z45" s="35"/>
+      <c r="W45" s="36"/>
+      <c r="X45" s="36"/>
+      <c r="Y45" s="36"/>
+      <c r="Z45" s="36"/>
     </row>
     <row r="46" ht="15.0" customHeight="1">
-      <c r="A46" s="29" t="s">
-        <v>340</v>
-      </c>
-      <c r="B46" s="30"/>
-      <c r="C46" s="30"/>
-      <c r="D46" s="30"/>
-      <c r="E46" s="30"/>
-      <c r="F46" s="30"/>
-      <c r="G46" s="30"/>
-      <c r="H46" s="30"/>
-      <c r="I46" s="30"/>
-      <c r="J46" s="30"/>
-      <c r="K46" s="30"/>
-      <c r="L46" s="30"/>
-      <c r="M46" s="30"/>
-      <c r="N46" s="30"/>
-      <c r="O46" s="30"/>
-      <c r="P46" s="30"/>
-      <c r="Q46" s="30"/>
-      <c r="R46" s="30"/>
-      <c r="S46" s="30"/>
-      <c r="T46" s="30"/>
-      <c r="U46" s="30"/>
-      <c r="V46" s="30"/>
-      <c r="W46" s="30"/>
-      <c r="X46" s="30"/>
-      <c r="Y46" s="30"/>
-      <c r="Z46" s="30"/>
+      <c r="A46" s="30" t="s">
+        <v>341</v>
+      </c>
+      <c r="B46" s="31"/>
+      <c r="C46" s="31"/>
+      <c r="D46" s="31"/>
+      <c r="E46" s="31"/>
+      <c r="F46" s="31"/>
+      <c r="G46" s="31"/>
+      <c r="H46" s="31"/>
+      <c r="I46" s="31"/>
+      <c r="J46" s="31"/>
+      <c r="K46" s="31"/>
+      <c r="L46" s="31"/>
+      <c r="M46" s="31"/>
+      <c r="N46" s="31"/>
+      <c r="O46" s="31"/>
+      <c r="P46" s="31"/>
+      <c r="Q46" s="31"/>
+      <c r="R46" s="31"/>
+      <c r="S46" s="31"/>
+      <c r="T46" s="31"/>
+      <c r="U46" s="31"/>
+      <c r="V46" s="31"/>
+      <c r="W46" s="31"/>
+      <c r="X46" s="31"/>
+      <c r="Y46" s="31"/>
+      <c r="Z46" s="31"/>
     </row>
     <row r="47" ht="15.0" customHeight="1">
-      <c r="A47" s="31" t="s">
-        <v>341</v>
-      </c>
-      <c r="B47" s="33">
+      <c r="A47" s="32" t="s">
+        <v>342</v>
+      </c>
+      <c r="B47" s="34">
         <v>10.19</v>
       </c>
-      <c r="C47" s="35"/>
-      <c r="D47" s="32">
+      <c r="C47" s="36"/>
+      <c r="D47" s="33">
         <v>118.75</v>
       </c>
-      <c r="E47" s="35"/>
-      <c r="F47" s="35"/>
-      <c r="G47" s="35"/>
-      <c r="H47" s="35"/>
-      <c r="I47" s="32">
+      <c r="E47" s="36"/>
+      <c r="F47" s="36"/>
+      <c r="G47" s="36"/>
+      <c r="H47" s="36"/>
+      <c r="I47" s="33">
         <v>260.09</v>
       </c>
-      <c r="J47" s="35"/>
-      <c r="K47" s="35"/>
-      <c r="L47" s="32">
+      <c r="J47" s="36"/>
+      <c r="K47" s="36"/>
+      <c r="L47" s="33">
         <v>531.79</v>
       </c>
-      <c r="M47" s="35"/>
-      <c r="N47" s="35"/>
-      <c r="O47" s="35"/>
-      <c r="P47" s="35"/>
-      <c r="Q47" s="33">
+      <c r="M47" s="36"/>
+      <c r="N47" s="36"/>
+      <c r="O47" s="36"/>
+      <c r="P47" s="36"/>
+      <c r="Q47" s="34">
         <v>8.45</v>
       </c>
-      <c r="R47" s="33">
+      <c r="R47" s="34">
         <v>4.22</v>
       </c>
-      <c r="S47" s="33">
+      <c r="S47" s="34">
         <v>10.25</v>
       </c>
-      <c r="T47" s="33">
+      <c r="T47" s="34">
         <v>8.12</v>
       </c>
-      <c r="U47" s="33">
+      <c r="U47" s="34">
         <v>5.82</v>
       </c>
-      <c r="V47" s="33">
+      <c r="V47" s="34">
         <v>3.57</v>
       </c>
-      <c r="W47" s="33">
+      <c r="W47" s="34">
         <v>2.88</v>
       </c>
-      <c r="X47" s="33">
+      <c r="X47" s="34">
         <v>4.7</v>
       </c>
-      <c r="Y47" s="33">
+      <c r="Y47" s="34">
         <v>7.38</v>
       </c>
-      <c r="Z47" s="35"/>
+      <c r="Z47" s="36"/>
     </row>
     <row r="48" ht="15.0" customHeight="1">
-      <c r="A48" s="31" t="s">
-        <v>342</v>
-      </c>
-      <c r="B48" s="35"/>
-      <c r="C48" s="35"/>
-      <c r="D48" s="35"/>
-      <c r="E48" s="35"/>
-      <c r="F48" s="35"/>
-      <c r="G48" s="35"/>
-      <c r="H48" s="35"/>
-      <c r="I48" s="35"/>
-      <c r="J48" s="35"/>
-      <c r="K48" s="35"/>
-      <c r="L48" s="35"/>
-      <c r="M48" s="35"/>
-      <c r="N48" s="35"/>
-      <c r="O48" s="35"/>
-      <c r="P48" s="33">
+      <c r="A48" s="32" t="s">
+        <v>343</v>
+      </c>
+      <c r="B48" s="36"/>
+      <c r="C48" s="36"/>
+      <c r="D48" s="36"/>
+      <c r="E48" s="36"/>
+      <c r="F48" s="36"/>
+      <c r="G48" s="36"/>
+      <c r="H48" s="36"/>
+      <c r="I48" s="36"/>
+      <c r="J48" s="36"/>
+      <c r="K48" s="36"/>
+      <c r="L48" s="36"/>
+      <c r="M48" s="36"/>
+      <c r="N48" s="36"/>
+      <c r="O48" s="36"/>
+      <c r="P48" s="34">
         <v>10.04</v>
       </c>
-      <c r="Q48" s="33">
+      <c r="Q48" s="34">
         <v>7.19</v>
       </c>
-      <c r="R48" s="33">
+      <c r="R48" s="34">
         <v>6.03</v>
       </c>
-      <c r="S48" s="33">
+      <c r="S48" s="34">
         <v>5.66</v>
       </c>
-      <c r="T48" s="33">
+      <c r="T48" s="34">
         <v>4.87</v>
       </c>
-      <c r="U48" s="33">
+      <c r="U48" s="34">
         <v>4.4</v>
       </c>
-      <c r="V48" s="33">
+      <c r="V48" s="34">
         <v>6.66</v>
       </c>
-      <c r="W48" s="35"/>
-      <c r="X48" s="35"/>
-      <c r="Y48" s="35"/>
-      <c r="Z48" s="35"/>
+      <c r="W48" s="36"/>
+      <c r="X48" s="36"/>
+      <c r="Y48" s="36"/>
+      <c r="Z48" s="36"/>
     </row>
     <row r="49" ht="15.0" customHeight="1">
-      <c r="A49" s="29" t="s">
-        <v>343</v>
-      </c>
-      <c r="B49" s="30"/>
-      <c r="C49" s="30"/>
-      <c r="D49" s="30"/>
-      <c r="E49" s="30"/>
-      <c r="F49" s="30"/>
-      <c r="G49" s="30"/>
-      <c r="H49" s="30"/>
-      <c r="I49" s="30"/>
-      <c r="J49" s="30"/>
-      <c r="K49" s="30"/>
-      <c r="L49" s="30"/>
-      <c r="M49" s="30"/>
-      <c r="N49" s="30"/>
-      <c r="O49" s="30"/>
-      <c r="P49" s="30"/>
-      <c r="Q49" s="30"/>
-      <c r="R49" s="30"/>
-      <c r="S49" s="30"/>
-      <c r="T49" s="30"/>
-      <c r="U49" s="30"/>
-      <c r="V49" s="30"/>
-      <c r="W49" s="30"/>
-      <c r="X49" s="30"/>
-      <c r="Y49" s="30"/>
-      <c r="Z49" s="30"/>
+      <c r="A49" s="30" t="s">
+        <v>344</v>
+      </c>
+      <c r="B49" s="31"/>
+      <c r="C49" s="31"/>
+      <c r="D49" s="31"/>
+      <c r="E49" s="31"/>
+      <c r="F49" s="31"/>
+      <c r="G49" s="31"/>
+      <c r="H49" s="31"/>
+      <c r="I49" s="31"/>
+      <c r="J49" s="31"/>
+      <c r="K49" s="31"/>
+      <c r="L49" s="31"/>
+      <c r="M49" s="31"/>
+      <c r="N49" s="31"/>
+      <c r="O49" s="31"/>
+      <c r="P49" s="31"/>
+      <c r="Q49" s="31"/>
+      <c r="R49" s="31"/>
+      <c r="S49" s="31"/>
+      <c r="T49" s="31"/>
+      <c r="U49" s="31"/>
+      <c r="V49" s="31"/>
+      <c r="W49" s="31"/>
+      <c r="X49" s="31"/>
+      <c r="Y49" s="31"/>
+      <c r="Z49" s="31"/>
     </row>
     <row r="50" ht="15.0" customHeight="1">
-      <c r="A50" s="31" t="s">
-        <v>344</v>
-      </c>
-      <c r="B50" s="33">
+      <c r="A50" s="32" t="s">
+        <v>345</v>
+      </c>
+      <c r="B50" s="34">
         <v>2.3</v>
       </c>
-      <c r="C50" s="33">
+      <c r="C50" s="34">
         <v>4.95</v>
       </c>
-      <c r="D50" s="33">
+      <c r="D50" s="34">
         <v>5.2</v>
       </c>
-      <c r="E50" s="32">
+      <c r="E50" s="33">
         <v>156.04</v>
       </c>
-      <c r="F50" s="35"/>
-      <c r="G50" s="33">
+      <c r="F50" s="36"/>
+      <c r="G50" s="34">
         <v>10.22</v>
       </c>
-      <c r="H50" s="35"/>
-      <c r="I50" s="35"/>
-      <c r="J50" s="35"/>
-      <c r="K50" s="35"/>
-      <c r="L50" s="35"/>
-      <c r="M50" s="33">
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" s="36"/>
+      <c r="K50" s="36"/>
+      <c r="L50" s="36"/>
+      <c r="M50" s="34">
         <v>8.91</v>
       </c>
-      <c r="N50" s="33">
+      <c r="N50" s="34">
         <v>5.58</v>
       </c>
-      <c r="O50" s="33">
+      <c r="O50" s="34">
         <v>47.27</v>
       </c>
-      <c r="P50" s="33">
+      <c r="P50" s="34">
         <v>6.09</v>
       </c>
-      <c r="Q50" s="33">
+      <c r="Q50" s="34">
         <v>5.07</v>
       </c>
-      <c r="R50" s="33">
+      <c r="R50" s="34">
         <v>4.87</v>
       </c>
-      <c r="S50" s="33">
+      <c r="S50" s="34">
         <v>9.89</v>
       </c>
-      <c r="T50" s="33">
+      <c r="T50" s="34">
         <v>3.11</v>
       </c>
-      <c r="U50" s="33">
+      <c r="U50" s="34">
         <v>7.32</v>
       </c>
-      <c r="V50" s="33">
+      <c r="V50" s="34">
         <v>3.15</v>
       </c>
-      <c r="W50" s="33">
+      <c r="W50" s="34">
         <v>2.84</v>
       </c>
-      <c r="X50" s="33">
+      <c r="X50" s="34">
         <v>3.85</v>
       </c>
-      <c r="Y50" s="33">
+      <c r="Y50" s="34">
         <v>4.32</v>
       </c>
-      <c r="Z50" s="33">
+      <c r="Z50" s="34">
         <v>5.59</v>
       </c>
     </row>
     <row r="51" ht="15.0" customHeight="1">
-      <c r="A51" s="31" t="s">
-        <v>345</v>
-      </c>
-      <c r="B51" s="33">
+      <c r="A51" s="32" t="s">
+        <v>346</v>
+      </c>
+      <c r="B51" s="34">
         <v>7.24</v>
       </c>
-      <c r="C51" s="33">
+      <c r="C51" s="34">
         <v>13.91</v>
       </c>
-      <c r="D51" s="35"/>
-      <c r="E51" s="35"/>
-      <c r="F51" s="35"/>
-      <c r="G51" s="35"/>
-      <c r="H51" s="35"/>
-      <c r="I51" s="35"/>
-      <c r="J51" s="35"/>
-      <c r="K51" s="35"/>
-      <c r="L51" s="35"/>
-      <c r="M51" s="33">
+      <c r="D51" s="36"/>
+      <c r="E51" s="36"/>
+      <c r="F51" s="36"/>
+      <c r="G51" s="36"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="36"/>
+      <c r="J51" s="36"/>
+      <c r="K51" s="36"/>
+      <c r="L51" s="36"/>
+      <c r="M51" s="34">
         <v>7.25</v>
       </c>
-      <c r="N51" s="33">
+      <c r="N51" s="34">
         <v>6.6</v>
       </c>
-      <c r="O51" s="33">
+      <c r="O51" s="34">
         <v>7.43</v>
       </c>
-      <c r="P51" s="33">
+      <c r="P51" s="34">
         <v>5.08</v>
       </c>
-      <c r="Q51" s="33">
+      <c r="Q51" s="34">
         <v>5.22</v>
       </c>
-      <c r="R51" s="33">
+      <c r="R51" s="34">
         <v>4.76</v>
       </c>
-      <c r="S51" s="33">
+      <c r="S51" s="34">
         <v>4.42</v>
       </c>
-      <c r="T51" s="33">
+      <c r="T51" s="34">
         <v>3.72</v>
       </c>
-      <c r="U51" s="33">
+      <c r="U51" s="34">
         <v>4.11</v>
       </c>
-      <c r="V51" s="33">
+      <c r="V51" s="34">
         <v>3.62</v>
       </c>
-      <c r="W51" s="35"/>
-      <c r="X51" s="35"/>
-      <c r="Y51" s="35"/>
-      <c r="Z51" s="35"/>
+      <c r="W51" s="36"/>
+      <c r="X51" s="36"/>
+      <c r="Y51" s="36"/>
+      <c r="Z51" s="36"/>
     </row>
     <row r="52" ht="15.0" customHeight="1">
-      <c r="A52" s="29" t="s">
-        <v>346</v>
-      </c>
-      <c r="B52" s="30"/>
-      <c r="C52" s="30"/>
-      <c r="D52" s="30"/>
-      <c r="E52" s="30"/>
-      <c r="F52" s="30"/>
-      <c r="G52" s="30"/>
-      <c r="H52" s="30"/>
-      <c r="I52" s="30"/>
-      <c r="J52" s="30"/>
-      <c r="K52" s="30"/>
-      <c r="L52" s="30"/>
-      <c r="M52" s="30"/>
-      <c r="N52" s="30"/>
-      <c r="O52" s="30"/>
-      <c r="P52" s="30"/>
-      <c r="Q52" s="30"/>
-      <c r="R52" s="30"/>
-      <c r="S52" s="30"/>
-      <c r="T52" s="30"/>
-      <c r="U52" s="30"/>
-      <c r="V52" s="30"/>
-      <c r="W52" s="30"/>
-      <c r="X52" s="30"/>
-      <c r="Y52" s="30"/>
-      <c r="Z52" s="30"/>
+      <c r="A52" s="30" t="s">
+        <v>347</v>
+      </c>
+      <c r="B52" s="31"/>
+      <c r="C52" s="31"/>
+      <c r="D52" s="31"/>
+      <c r="E52" s="31"/>
+      <c r="F52" s="31"/>
+      <c r="G52" s="31"/>
+      <c r="H52" s="31"/>
+      <c r="I52" s="31"/>
+      <c r="J52" s="31"/>
+      <c r="K52" s="31"/>
+      <c r="L52" s="31"/>
+      <c r="M52" s="31"/>
+      <c r="N52" s="31"/>
+      <c r="O52" s="31"/>
+      <c r="P52" s="31"/>
+      <c r="Q52" s="31"/>
+      <c r="R52" s="31"/>
+      <c r="S52" s="31"/>
+      <c r="T52" s="31"/>
+      <c r="U52" s="31"/>
+      <c r="V52" s="31"/>
+      <c r="W52" s="31"/>
+      <c r="X52" s="31"/>
+      <c r="Y52" s="31"/>
+      <c r="Z52" s="31"/>
     </row>
     <row r="53" ht="15.0" customHeight="1">
-      <c r="A53" s="31" t="s">
-        <v>347</v>
-      </c>
-      <c r="B53" s="33">
+      <c r="A53" s="32" t="s">
+        <v>348</v>
+      </c>
+      <c r="B53" s="34">
         <v>3.0</v>
       </c>
-      <c r="C53" s="33">
+      <c r="C53" s="34">
         <v>5.7</v>
       </c>
-      <c r="D53" s="33">
+      <c r="D53" s="34">
         <v>5.86</v>
       </c>
-      <c r="E53" s="35"/>
-      <c r="F53" s="35"/>
-      <c r="G53" s="33">
+      <c r="E53" s="36"/>
+      <c r="F53" s="36"/>
+      <c r="G53" s="34">
         <v>13.19</v>
       </c>
-      <c r="H53" s="33">
+      <c r="H53" s="34">
         <v>7.73</v>
       </c>
-      <c r="I53" s="33">
+      <c r="I53" s="34">
         <v>4.84</v>
       </c>
-      <c r="J53" s="33">
+      <c r="J53" s="34">
         <v>2.8</v>
       </c>
-      <c r="K53" s="33">
+      <c r="K53" s="34">
         <v>2.65</v>
       </c>
-      <c r="L53" s="33">
+      <c r="L53" s="34">
         <v>5.67</v>
       </c>
-      <c r="M53" s="33">
+      <c r="M53" s="34">
         <v>35.44</v>
       </c>
-      <c r="N53" s="33">
+      <c r="N53" s="34">
         <v>10.06</v>
       </c>
-      <c r="O53" s="35"/>
-      <c r="P53" s="33">
+      <c r="O53" s="36"/>
+      <c r="P53" s="34">
         <v>7.86</v>
       </c>
-      <c r="Q53" s="33">
+      <c r="Q53" s="34">
         <v>6.38</v>
       </c>
-      <c r="R53" s="33">
+      <c r="R53" s="34">
         <v>7.67</v>
       </c>
-      <c r="S53" s="33">
+      <c r="S53" s="34">
         <v>15.37</v>
       </c>
-      <c r="T53" s="33">
+      <c r="T53" s="34">
         <v>3.51</v>
       </c>
-      <c r="U53" s="33">
+      <c r="U53" s="34">
         <v>10.5</v>
       </c>
-      <c r="V53" s="33">
+      <c r="V53" s="34">
         <v>3.84</v>
       </c>
-      <c r="W53" s="33">
+      <c r="W53" s="34">
         <v>3.68</v>
       </c>
-      <c r="X53" s="33">
+      <c r="X53" s="34">
         <v>6.38</v>
       </c>
-      <c r="Y53" s="33">
+      <c r="Y53" s="34">
         <v>7.73</v>
       </c>
-      <c r="Z53" s="33">
+      <c r="Z53" s="34">
         <v>19.84</v>
       </c>
     </row>
     <row r="54" ht="15.0" customHeight="1">
-      <c r="A54" s="31" t="s">
-        <v>348</v>
-      </c>
-      <c r="B54" s="33">
+      <c r="A54" s="32" t="s">
+        <v>349</v>
+      </c>
+      <c r="B54" s="34">
         <v>10.1</v>
       </c>
-      <c r="C54" s="33">
+      <c r="C54" s="34">
         <v>20.63</v>
       </c>
-      <c r="D54" s="33">
+      <c r="D54" s="34">
         <v>25.16</v>
       </c>
-      <c r="E54" s="33">
+      <c r="E54" s="34">
         <v>18.12</v>
       </c>
-      <c r="F54" s="33">
+      <c r="F54" s="34">
         <v>7.68</v>
       </c>
-      <c r="G54" s="33">
+      <c r="G54" s="34">
         <v>4.51</v>
       </c>
-      <c r="H54" s="33">
+      <c r="H54" s="34">
         <v>4.04</v>
       </c>
-      <c r="I54" s="33">
+      <c r="I54" s="34">
         <v>4.0</v>
       </c>
-      <c r="J54" s="33">
+      <c r="J54" s="34">
         <v>4.08</v>
       </c>
-      <c r="K54" s="33">
+      <c r="K54" s="34">
         <v>6.1</v>
       </c>
-      <c r="L54" s="33">
+      <c r="L54" s="34">
         <v>11.02</v>
       </c>
-      <c r="M54" s="33">
+      <c r="M54" s="34">
         <v>12.39</v>
       </c>
-      <c r="N54" s="33">
+      <c r="N54" s="34">
         <v>10.32</v>
       </c>
-      <c r="O54" s="33">
+      <c r="O54" s="34">
         <v>11.28</v>
       </c>
-      <c r="P54" s="33">
+      <c r="P54" s="34">
         <v>6.46</v>
       </c>
-      <c r="Q54" s="33">
+      <c r="Q54" s="34">
         <v>6.72</v>
       </c>
-      <c r="R54" s="33">
+      <c r="R54" s="34">
         <v>6.08</v>
       </c>
-      <c r="S54" s="33">
+      <c r="S54" s="34">
         <v>5.54</v>
       </c>
-      <c r="T54" s="33">
+      <c r="T54" s="34">
         <v>4.67</v>
       </c>
-      <c r="U54" s="33">
+      <c r="U54" s="34">
         <v>5.67</v>
       </c>
-      <c r="V54" s="33">
+      <c r="V54" s="34">
         <v>5.34</v>
       </c>
-      <c r="W54" s="35"/>
-      <c r="X54" s="35"/>
-      <c r="Y54" s="35"/>
-      <c r="Z54" s="35"/>
+      <c r="W54" s="36"/>
+      <c r="X54" s="36"/>
+      <c r="Y54" s="36"/>
+      <c r="Z54" s="36"/>
     </row>
     <row r="55" ht="15.0" customHeight="1">
-      <c r="A55" s="29" t="s">
-        <v>349</v>
-      </c>
-      <c r="B55" s="30"/>
-      <c r="C55" s="30"/>
-      <c r="D55" s="30"/>
-      <c r="E55" s="30"/>
-      <c r="F55" s="30"/>
-      <c r="G55" s="30"/>
-      <c r="H55" s="30"/>
-      <c r="I55" s="30"/>
-      <c r="J55" s="30"/>
-      <c r="K55" s="30"/>
-      <c r="L55" s="30"/>
-      <c r="M55" s="30"/>
-      <c r="N55" s="30"/>
-      <c r="O55" s="30"/>
-      <c r="P55" s="30"/>
-      <c r="Q55" s="30"/>
-      <c r="R55" s="30"/>
-      <c r="S55" s="30"/>
-      <c r="T55" s="30"/>
-      <c r="U55" s="30"/>
-      <c r="V55" s="30"/>
-      <c r="W55" s="30"/>
-      <c r="X55" s="30"/>
-      <c r="Y55" s="30"/>
-      <c r="Z55" s="30"/>
+      <c r="A55" s="30" t="s">
+        <v>350</v>
+      </c>
+      <c r="B55" s="31"/>
+      <c r="C55" s="31"/>
+      <c r="D55" s="31"/>
+      <c r="E55" s="31"/>
+      <c r="F55" s="31"/>
+      <c r="G55" s="31"/>
+      <c r="H55" s="31"/>
+      <c r="I55" s="31"/>
+      <c r="J55" s="31"/>
+      <c r="K55" s="31"/>
+      <c r="L55" s="31"/>
+      <c r="M55" s="31"/>
+      <c r="N55" s="31"/>
+      <c r="O55" s="31"/>
+      <c r="P55" s="31"/>
+      <c r="Q55" s="31"/>
+      <c r="R55" s="31"/>
+      <c r="S55" s="31"/>
+      <c r="T55" s="31"/>
+      <c r="U55" s="31"/>
+      <c r="V55" s="31"/>
+      <c r="W55" s="31"/>
+      <c r="X55" s="31"/>
+      <c r="Y55" s="31"/>
+      <c r="Z55" s="31"/>
     </row>
     <row r="56" ht="15.0" customHeight="1">
-      <c r="A56" s="31" t="s">
-        <v>350</v>
-      </c>
-      <c r="B56" s="33">
+      <c r="A56" s="32" t="s">
+        <v>351</v>
+      </c>
+      <c r="B56" s="34">
         <v>5.71</v>
       </c>
-      <c r="C56" s="33">
+      <c r="C56" s="34">
         <v>4.27</v>
       </c>
-      <c r="D56" s="33">
+      <c r="D56" s="34">
         <v>19.47</v>
       </c>
-      <c r="E56" s="33">
+      <c r="E56" s="34">
         <v>11.33</v>
       </c>
-      <c r="F56" s="35"/>
-      <c r="G56" s="33">
+      <c r="F56" s="36"/>
+      <c r="G56" s="34">
         <v>9.18</v>
       </c>
-      <c r="H56" s="33">
+      <c r="H56" s="34">
         <v>12.31</v>
       </c>
-      <c r="I56" s="33">
+      <c r="I56" s="34">
         <v>9.87</v>
       </c>
-      <c r="J56" s="33">
+      <c r="J56" s="34">
         <v>5.31</v>
       </c>
-      <c r="K56" s="32">
+      <c r="K56" s="33">
         <v>322.07</v>
       </c>
-      <c r="L56" s="33">
+      <c r="L56" s="34">
         <v>46.67</v>
       </c>
-      <c r="M56" s="33">
+      <c r="M56" s="34">
         <v>35.44</v>
       </c>
-      <c r="N56" s="33">
+      <c r="N56" s="34">
         <v>10.06</v>
       </c>
-      <c r="O56" s="35"/>
-      <c r="P56" s="33">
+      <c r="O56" s="36"/>
+      <c r="P56" s="34">
         <v>7.86</v>
       </c>
-      <c r="Q56" s="33">
+      <c r="Q56" s="34">
         <v>6.38</v>
       </c>
-      <c r="R56" s="33">
+      <c r="R56" s="34">
         <v>6.63</v>
       </c>
-      <c r="S56" s="33">
+      <c r="S56" s="34">
         <v>15.58</v>
       </c>
-      <c r="T56" s="33">
+      <c r="T56" s="34">
         <v>3.55</v>
       </c>
-      <c r="U56" s="33">
+      <c r="U56" s="34">
         <v>10.5</v>
       </c>
-      <c r="V56" s="33">
+      <c r="V56" s="34">
         <v>3.84</v>
       </c>
-      <c r="W56" s="33">
+      <c r="W56" s="34">
         <v>3.68</v>
       </c>
-      <c r="X56" s="33">
+      <c r="X56" s="34">
         <v>6.39</v>
       </c>
-      <c r="Y56" s="33">
+      <c r="Y56" s="34">
         <v>7.74</v>
       </c>
-      <c r="Z56" s="33">
+      <c r="Z56" s="34">
         <v>19.84</v>
       </c>
     </row>
     <row r="57" ht="15.0" customHeight="1">
-      <c r="A57" s="31" t="s">
-        <v>351</v>
-      </c>
-      <c r="B57" s="33">
+      <c r="A57" s="32" t="s">
+        <v>352</v>
+      </c>
+      <c r="B57" s="34">
         <v>0.57</v>
       </c>
-      <c r="C57" s="33">
+      <c r="C57" s="34">
         <v>0.56</v>
       </c>
-      <c r="D57" s="33">
+      <c r="D57" s="34">
         <v>0.52</v>
       </c>
-      <c r="E57" s="33">
+      <c r="E57" s="34">
         <v>0.51</v>
       </c>
-      <c r="F57" s="33">
+      <c r="F57" s="34">
         <v>0.49</v>
       </c>
-      <c r="G57" s="33">
+      <c r="G57" s="34">
         <v>0.48</v>
       </c>
-      <c r="H57" s="33">
+      <c r="H57" s="34">
         <v>0.5</v>
       </c>
-      <c r="I57" s="33">
+      <c r="I57" s="34">
         <v>0.53</v>
       </c>
-      <c r="J57" s="33">
+      <c r="J57" s="34">
         <v>0.53</v>
       </c>
-      <c r="K57" s="33">
+      <c r="K57" s="34">
         <v>0.55</v>
       </c>
-      <c r="L57" s="33">
+      <c r="L57" s="34">
         <v>0.58</v>
       </c>
-      <c r="M57" s="33">
+      <c r="M57" s="34">
         <v>0.58</v>
       </c>
-      <c r="N57" s="33">
+      <c r="N57" s="34">
         <v>0.55</v>
       </c>
-      <c r="O57" s="33">
+      <c r="O57" s="34">
         <v>0.61</v>
       </c>
-      <c r="P57" s="33">
+      <c r="P57" s="34">
         <v>0.65</v>
       </c>
-      <c r="Q57" s="33">
+      <c r="Q57" s="34">
         <v>0.67</v>
       </c>
-      <c r="R57" s="33">
+      <c r="R57" s="34">
         <v>0.66</v>
       </c>
-      <c r="S57" s="33">
+      <c r="S57" s="34">
         <v>0.69</v>
       </c>
-      <c r="T57" s="33">
+      <c r="T57" s="34">
         <v>0.62</v>
       </c>
-      <c r="U57" s="33">
+      <c r="U57" s="34">
         <v>0.55</v>
       </c>
-      <c r="V57" s="33">
+      <c r="V57" s="34">
         <v>0.46</v>
       </c>
-      <c r="W57" s="35"/>
-      <c r="X57" s="35"/>
-      <c r="Y57" s="35"/>
-      <c r="Z57" s="35"/>
+      <c r="W57" s="36"/>
+      <c r="X57" s="36"/>
+      <c r="Y57" s="36"/>
+      <c r="Z57" s="36"/>
     </row>
     <row r="58" ht="15.0" customHeight="1">
-      <c r="A58" s="29" t="s">
-        <v>352</v>
-      </c>
-      <c r="B58" s="30"/>
-      <c r="C58" s="30"/>
-      <c r="D58" s="30"/>
-      <c r="E58" s="30"/>
-      <c r="F58" s="30"/>
-      <c r="G58" s="30"/>
-      <c r="H58" s="30"/>
-      <c r="I58" s="30"/>
-      <c r="J58" s="30"/>
-      <c r="K58" s="30"/>
-      <c r="L58" s="30"/>
-      <c r="M58" s="30"/>
-      <c r="N58" s="30"/>
-      <c r="O58" s="30"/>
-      <c r="P58" s="30"/>
-      <c r="Q58" s="30"/>
-      <c r="R58" s="30"/>
-      <c r="S58" s="30"/>
-      <c r="T58" s="30"/>
-      <c r="U58" s="30"/>
-      <c r="V58" s="30"/>
-      <c r="W58" s="30"/>
-      <c r="X58" s="30"/>
-      <c r="Y58" s="30"/>
-      <c r="Z58" s="30"/>
+      <c r="A58" s="30" t="s">
+        <v>353</v>
+      </c>
+      <c r="B58" s="31"/>
+      <c r="C58" s="31"/>
+      <c r="D58" s="31"/>
+      <c r="E58" s="31"/>
+      <c r="F58" s="31"/>
+      <c r="G58" s="31"/>
+      <c r="H58" s="31"/>
+      <c r="I58" s="31"/>
+      <c r="J58" s="31"/>
+      <c r="K58" s="31"/>
+      <c r="L58" s="31"/>
+      <c r="M58" s="31"/>
+      <c r="N58" s="31"/>
+      <c r="O58" s="31"/>
+      <c r="P58" s="31"/>
+      <c r="Q58" s="31"/>
+      <c r="R58" s="31"/>
+      <c r="S58" s="31"/>
+      <c r="T58" s="31"/>
+      <c r="U58" s="31"/>
+      <c r="V58" s="31"/>
+      <c r="W58" s="31"/>
+      <c r="X58" s="31"/>
+      <c r="Y58" s="31"/>
+      <c r="Z58" s="31"/>
     </row>
     <row r="59" ht="15.0" customHeight="1">
-      <c r="A59" s="31" t="s">
-        <v>353</v>
-      </c>
-      <c r="B59" s="33">
+      <c r="A59" s="32" t="s">
+        <v>354</v>
+      </c>
+      <c r="B59" s="34">
         <v>0.03</v>
       </c>
-      <c r="C59" s="33">
+      <c r="C59" s="34">
         <v>0.5</v>
       </c>
-      <c r="D59" s="33">
+      <c r="D59" s="34">
         <v>0.01</v>
       </c>
-      <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
-      <c r="G59" s="34">
+      <c r="E59" s="36"/>
+      <c r="F59" s="36"/>
+      <c r="G59" s="35">
         <v>-0.39</v>
       </c>
-      <c r="H59" s="34">
+      <c r="H59" s="35">
         <v>-0.16</v>
       </c>
-      <c r="I59" s="34">
+      <c r="I59" s="35">
         <v>-0.17</v>
       </c>
-      <c r="J59" s="33">
+      <c r="J59" s="34">
         <v>0.74</v>
       </c>
-      <c r="K59" s="33">
+      <c r="K59" s="34">
         <v>0.02</v>
       </c>
-      <c r="L59" s="33">
+      <c r="L59" s="34">
         <v>0.01</v>
       </c>
-      <c r="M59" s="34">
+      <c r="M59" s="35">
         <v>-0.5</v>
       </c>
-      <c r="N59" s="33">
+      <c r="N59" s="34">
         <v>0.03</v>
       </c>
-      <c r="O59" s="35"/>
-      <c r="P59" s="34">
+      <c r="O59" s="36"/>
+      <c r="P59" s="35">
         <v>-0.56</v>
       </c>
-      <c r="Q59" s="33">
+      <c r="Q59" s="34">
         <v>0.05</v>
       </c>
-      <c r="R59" s="34">
+      <c r="R59" s="35">
         <v>-2.45</v>
       </c>
-      <c r="S59" s="34">
+      <c r="S59" s="35">
         <v>-0.2</v>
       </c>
-      <c r="T59" s="33">
+      <c r="T59" s="34">
         <v>0.01</v>
       </c>
-      <c r="U59" s="34">
+      <c r="U59" s="35">
         <v>-0.22</v>
       </c>
-      <c r="V59" s="33">
+      <c r="V59" s="34">
         <v>0.1</v>
       </c>
-      <c r="W59" s="33">
+      <c r="W59" s="34">
         <v>0.03</v>
       </c>
-      <c r="X59" s="33">
+      <c r="X59" s="34">
         <v>0.3</v>
       </c>
-      <c r="Y59" s="33">
+      <c r="Y59" s="34">
         <v>0.06</v>
       </c>
-      <c r="Z59" s="35"/>
+      <c r="Z59" s="36"/>
     </row>
     <row r="60" ht="15.0" customHeight="1">
-      <c r="A60" s="31" t="s">
-        <v>354</v>
-      </c>
-      <c r="B60" s="33">
+      <c r="A60" s="32" t="s">
+        <v>355</v>
+      </c>
+      <c r="B60" s="34">
         <v>0.32</v>
       </c>
-      <c r="C60" s="33">
+      <c r="C60" s="34">
         <v>3.33</v>
       </c>
-      <c r="D60" s="34">
+      <c r="D60" s="35">
         <v>-2.72</v>
       </c>
-      <c r="E60" s="35"/>
-      <c r="F60" s="35"/>
-      <c r="G60" s="34">
+      <c r="E60" s="36"/>
+      <c r="F60" s="36"/>
+      <c r="G60" s="35">
         <v>-0.46</v>
       </c>
-      <c r="H60" s="33">
+      <c r="H60" s="34">
         <v>0.07</v>
       </c>
-      <c r="I60" s="33">
+      <c r="I60" s="34">
         <v>0.1</v>
       </c>
-      <c r="J60" s="35"/>
-      <c r="K60" s="33">
+      <c r="J60" s="36"/>
+      <c r="K60" s="34">
         <v>0.19</v>
       </c>
-      <c r="L60" s="33">
+      <c r="L60" s="34">
         <v>1.43</v>
       </c>
-      <c r="M60" s="34">
+      <c r="M60" s="35">
         <v>-0.6</v>
       </c>
-      <c r="N60" s="33">
+      <c r="N60" s="34">
         <v>21.87</v>
       </c>
-      <c r="O60" s="35"/>
-      <c r="P60" s="33">
+      <c r="O60" s="36"/>
+      <c r="P60" s="34">
         <v>0.82</v>
       </c>
-      <c r="Q60" s="34">
+      <c r="Q60" s="35">
         <v>-2.58</v>
       </c>
-      <c r="R60" s="34">
+      <c r="R60" s="35">
         <v>-0.53</v>
       </c>
-      <c r="S60" s="33">
+      <c r="S60" s="34">
         <v>1.18</v>
       </c>
-      <c r="T60" s="33">
+      <c r="T60" s="34">
         <v>0.1</v>
       </c>
-      <c r="U60" s="33">
+      <c r="U60" s="34">
         <v>0.17</v>
       </c>
-      <c r="V60" s="35"/>
-      <c r="W60" s="35"/>
-      <c r="X60" s="35"/>
-      <c r="Y60" s="35"/>
-      <c r="Z60" s="35"/>
+      <c r="V60" s="36"/>
+      <c r="W60" s="36"/>
+      <c r="X60" s="36"/>
+      <c r="Y60" s="36"/>
+      <c r="Z60" s="36"/>
     </row>
     <row r="61" ht="15.0" customHeight="1">
-      <c r="A61" s="29" t="s">
-        <v>355</v>
-      </c>
-      <c r="B61" s="30"/>
-      <c r="C61" s="30"/>
-      <c r="D61" s="30"/>
-      <c r="E61" s="30"/>
-      <c r="F61" s="30"/>
-      <c r="G61" s="30"/>
-      <c r="H61" s="30"/>
-      <c r="I61" s="30"/>
-      <c r="J61" s="30"/>
-      <c r="K61" s="30"/>
-      <c r="L61" s="30"/>
-      <c r="M61" s="30"/>
-      <c r="N61" s="30"/>
-      <c r="O61" s="30"/>
-      <c r="P61" s="30"/>
-      <c r="Q61" s="30"/>
-      <c r="R61" s="30"/>
-      <c r="S61" s="30"/>
-      <c r="T61" s="30"/>
-      <c r="U61" s="30"/>
-      <c r="V61" s="30"/>
-      <c r="W61" s="30"/>
-      <c r="X61" s="30"/>
-      <c r="Y61" s="30"/>
-      <c r="Z61" s="30"/>
+      <c r="A61" s="30" t="s">
+        <v>356</v>
+      </c>
+      <c r="B61" s="31"/>
+      <c r="C61" s="31"/>
+      <c r="D61" s="31"/>
+      <c r="E61" s="31"/>
+      <c r="F61" s="31"/>
+      <c r="G61" s="31"/>
+      <c r="H61" s="31"/>
+      <c r="I61" s="31"/>
+      <c r="J61" s="31"/>
+      <c r="K61" s="31"/>
+      <c r="L61" s="31"/>
+      <c r="M61" s="31"/>
+      <c r="N61" s="31"/>
+      <c r="O61" s="31"/>
+      <c r="P61" s="31"/>
+      <c r="Q61" s="31"/>
+      <c r="R61" s="31"/>
+      <c r="S61" s="31"/>
+      <c r="T61" s="31"/>
+      <c r="U61" s="31"/>
+      <c r="V61" s="31"/>
+      <c r="W61" s="31"/>
+      <c r="X61" s="31"/>
+      <c r="Y61" s="31"/>
+      <c r="Z61" s="31"/>
     </row>
     <row r="62" ht="15.0" customHeight="1">
-      <c r="A62" s="31" t="s">
-        <v>356</v>
-      </c>
-      <c r="B62" s="33">
+      <c r="A62" s="32" t="s">
+        <v>357</v>
+      </c>
+      <c r="B62" s="34">
         <v>6.67</v>
       </c>
-      <c r="C62" s="33">
+      <c r="C62" s="34">
         <v>4.22</v>
       </c>
-      <c r="D62" s="33">
+      <c r="D62" s="34">
         <v>4.13</v>
       </c>
-      <c r="E62" s="33">
+      <c r="E62" s="34">
         <v>2.66</v>
       </c>
-      <c r="F62" s="33">
+      <c r="F62" s="34">
         <v>4.44</v>
       </c>
-      <c r="G62" s="33">
+      <c r="G62" s="34">
         <v>7.64</v>
       </c>
-      <c r="H62" s="33">
+      <c r="H62" s="34">
         <v>6.93</v>
       </c>
-      <c r="I62" s="33">
+      <c r="I62" s="34">
         <v>7.56</v>
       </c>
-      <c r="J62" s="33">
+      <c r="J62" s="34">
         <v>9.65</v>
       </c>
-      <c r="K62" s="33">
+      <c r="K62" s="34">
         <v>13.73</v>
       </c>
-      <c r="L62" s="33">
+      <c r="L62" s="34">
         <v>6.14</v>
       </c>
-      <c r="M62" s="33">
+      <c r="M62" s="34">
         <v>4.45</v>
       </c>
-      <c r="N62" s="33">
+      <c r="N62" s="34">
         <v>2.48</v>
       </c>
-      <c r="O62" s="33">
+      <c r="O62" s="34">
         <v>2.73</v>
       </c>
-      <c r="P62" s="33">
+      <c r="P62" s="34">
         <v>1.23</v>
       </c>
-      <c r="Q62" s="33">
+      <c r="Q62" s="34">
         <v>1.21</v>
       </c>
-      <c r="R62" s="34">
+      <c r="R62" s="35">
         <v>-0.05</v>
       </c>
-      <c r="S62" s="33">
+      <c r="S62" s="34">
         <v>2.69</v>
       </c>
-      <c r="T62" s="33">
+      <c r="T62" s="34">
         <v>1.48</v>
       </c>
-      <c r="U62" s="33">
+      <c r="U62" s="34">
         <v>3.1</v>
       </c>
-      <c r="V62" s="33">
+      <c r="V62" s="34">
         <v>2.28</v>
       </c>
-      <c r="W62" s="33">
+      <c r="W62" s="34">
         <v>2.21</v>
       </c>
-      <c r="X62" s="33">
+      <c r="X62" s="34">
         <v>2.82</v>
       </c>
-      <c r="Y62" s="33">
+      <c r="Y62" s="34">
         <v>3.25</v>
       </c>
-      <c r="Z62" s="33">
+      <c r="Z62" s="34">
         <v>1.29</v>
       </c>
     </row>
     <row r="63" ht="15.0" customHeight="1">
-      <c r="A63" s="31" t="s">
-        <v>357</v>
-      </c>
-      <c r="B63" s="33">
+      <c r="A63" s="32" t="s">
+        <v>358</v>
+      </c>
+      <c r="B63" s="34">
         <v>4.46</v>
       </c>
-      <c r="C63" s="33">
+      <c r="C63" s="34">
         <v>4.78</v>
       </c>
-      <c r="D63" s="33">
+      <c r="D63" s="34">
         <v>5.25</v>
       </c>
-      <c r="E63" s="33">
+      <c r="E63" s="34">
         <v>5.76</v>
       </c>
-      <c r="F63" s="33">
+      <c r="F63" s="34">
         <v>6.86</v>
       </c>
-      <c r="G63" s="33">
+      <c r="G63" s="34">
         <v>7.92</v>
       </c>
-      <c r="H63" s="33">
+      <c r="H63" s="34">
         <v>8.02</v>
       </c>
-      <c r="I63" s="33">
+      <c r="I63" s="34">
         <v>8.55</v>
       </c>
-      <c r="J63" s="33">
+      <c r="J63" s="34">
         <v>8.92</v>
       </c>
-      <c r="K63" s="33">
+      <c r="K63" s="34">
         <v>7.44</v>
       </c>
-      <c r="L63" s="33">
+      <c r="L63" s="34">
         <v>3.47</v>
       </c>
-      <c r="M63" s="33">
+      <c r="M63" s="34">
         <v>2.38</v>
       </c>
-      <c r="N63" s="33">
+      <c r="N63" s="34">
         <v>1.46</v>
       </c>
-      <c r="O63" s="33">
+      <c r="O63" s="34">
         <v>1.52</v>
       </c>
-      <c r="P63" s="33">
+      <c r="P63" s="34">
         <v>1.33</v>
       </c>
-      <c r="Q63" s="33">
+      <c r="Q63" s="34">
         <v>1.68</v>
       </c>
-      <c r="R63" s="33">
+      <c r="R63" s="34">
         <v>1.87</v>
       </c>
-      <c r="S63" s="33">
+      <c r="S63" s="34">
         <v>2.25</v>
       </c>
-      <c r="T63" s="33">
+      <c r="T63" s="34">
         <v>2.26</v>
       </c>
-      <c r="U63" s="33">
+      <c r="U63" s="34">
         <v>2.69</v>
       </c>
-      <c r="V63" s="33">
+      <c r="V63" s="34">
         <v>2.25</v>
       </c>
-      <c r="W63" s="35"/>
-      <c r="X63" s="35"/>
-      <c r="Y63" s="35"/>
-      <c r="Z63" s="35"/>
+      <c r="W63" s="36"/>
+      <c r="X63" s="36"/>
+      <c r="Y63" s="36"/>
+      <c r="Z63" s="36"/>
     </row>
     <row r="64" ht="15.0" customHeight="1">
-      <c r="A64" s="29" t="s">
-        <v>358</v>
-      </c>
-      <c r="B64" s="30"/>
-      <c r="C64" s="30"/>
-      <c r="D64" s="30"/>
-      <c r="E64" s="30"/>
-      <c r="F64" s="30"/>
-      <c r="G64" s="30"/>
-      <c r="H64" s="30"/>
-      <c r="I64" s="30"/>
-      <c r="J64" s="30"/>
-      <c r="K64" s="30"/>
-      <c r="L64" s="30"/>
-      <c r="M64" s="30"/>
-      <c r="N64" s="30"/>
-      <c r="O64" s="30"/>
-      <c r="P64" s="30"/>
-      <c r="Q64" s="30"/>
-      <c r="R64" s="30"/>
-      <c r="S64" s="30"/>
-      <c r="T64" s="30"/>
-      <c r="U64" s="30"/>
-      <c r="V64" s="30"/>
-      <c r="W64" s="30"/>
-      <c r="X64" s="30"/>
-      <c r="Y64" s="30"/>
-      <c r="Z64" s="30"/>
+      <c r="A64" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B64" s="31"/>
+      <c r="C64" s="31"/>
+      <c r="D64" s="31"/>
+      <c r="E64" s="31"/>
+      <c r="F64" s="31"/>
+      <c r="G64" s="31"/>
+      <c r="H64" s="31"/>
+      <c r="I64" s="31"/>
+      <c r="J64" s="31"/>
+      <c r="K64" s="31"/>
+      <c r="L64" s="31"/>
+      <c r="M64" s="31"/>
+      <c r="N64" s="31"/>
+      <c r="O64" s="31"/>
+      <c r="P64" s="31"/>
+      <c r="Q64" s="31"/>
+      <c r="R64" s="31"/>
+      <c r="S64" s="31"/>
+      <c r="T64" s="31"/>
+      <c r="U64" s="31"/>
+      <c r="V64" s="31"/>
+      <c r="W64" s="31"/>
+      <c r="X64" s="31"/>
+      <c r="Y64" s="31"/>
+      <c r="Z64" s="31"/>
     </row>
     <row r="65" ht="15.0" customHeight="1">
-      <c r="A65" s="31" t="s">
-        <v>359</v>
-      </c>
-      <c r="B65" s="33">
+      <c r="A65" s="32" t="s">
+        <v>360</v>
+      </c>
+      <c r="B65" s="34">
         <v>23.84</v>
       </c>
-      <c r="C65" s="33">
+      <c r="C65" s="34">
         <v>32.98</v>
       </c>
-      <c r="D65" s="33">
+      <c r="D65" s="34">
         <v>15.43</v>
       </c>
-      <c r="E65" s="33">
+      <c r="E65" s="34">
         <v>9.94</v>
       </c>
-      <c r="F65" s="33">
+      <c r="F65" s="34">
         <v>12.9</v>
       </c>
-      <c r="G65" s="33">
+      <c r="G65" s="34">
         <v>16.47</v>
       </c>
-      <c r="H65" s="33">
+      <c r="H65" s="34">
         <v>16.97</v>
       </c>
-      <c r="I65" s="33">
+      <c r="I65" s="34">
         <v>21.01</v>
       </c>
-      <c r="J65" s="33">
+      <c r="J65" s="34">
         <v>22.51</v>
       </c>
-      <c r="K65" s="33">
+      <c r="K65" s="34">
         <v>22.75</v>
       </c>
-      <c r="L65" s="33">
+      <c r="L65" s="34">
         <v>29.97</v>
       </c>
-      <c r="M65" s="33">
+      <c r="M65" s="34">
         <v>13.85</v>
       </c>
-      <c r="N65" s="33">
+      <c r="N65" s="34">
         <v>6.64</v>
       </c>
-      <c r="O65" s="33">
+      <c r="O65" s="34">
         <v>8.65</v>
       </c>
-      <c r="P65" s="33">
+      <c r="P65" s="34">
         <v>2.88</v>
       </c>
-      <c r="Q65" s="33">
+      <c r="Q65" s="34">
         <v>2.2</v>
       </c>
-      <c r="R65" s="34">
+      <c r="R65" s="35">
         <v>-0.08</v>
       </c>
-      <c r="S65" s="33">
+      <c r="S65" s="34">
         <v>4.86</v>
       </c>
-      <c r="T65" s="33">
+      <c r="T65" s="34">
         <v>1.95</v>
       </c>
-      <c r="U65" s="33">
+      <c r="U65" s="34">
         <v>5.01</v>
       </c>
-      <c r="V65" s="33">
+      <c r="V65" s="34">
         <v>3.06</v>
       </c>
-      <c r="W65" s="33">
+      <c r="W65" s="34">
         <v>3.18</v>
       </c>
-      <c r="X65" s="33">
+      <c r="X65" s="34">
         <v>4.74</v>
       </c>
-      <c r="Y65" s="33">
+      <c r="Y65" s="34">
         <v>5.93</v>
       </c>
-      <c r="Z65" s="33">
+      <c r="Z65" s="34">
         <v>4.83</v>
       </c>
     </row>
     <row r="66" ht="15.0" customHeight="1">
-      <c r="A66" s="31" t="s">
-        <v>360</v>
-      </c>
-      <c r="B66" s="33">
+      <c r="A66" s="32" t="s">
+        <v>361</v>
+      </c>
+      <c r="B66" s="34">
         <v>16.84</v>
       </c>
-      <c r="C66" s="33">
+      <c r="C66" s="34">
         <v>15.31</v>
       </c>
-      <c r="D66" s="33">
+      <c r="D66" s="34">
         <v>14.72</v>
       </c>
-      <c r="E66" s="33">
+      <c r="E66" s="34">
         <v>15.49</v>
       </c>
-      <c r="F66" s="33">
+      <c r="F66" s="34">
         <v>17.03</v>
       </c>
-      <c r="G66" s="33">
+      <c r="G66" s="34">
         <v>18.42</v>
       </c>
-      <c r="H66" s="33">
+      <c r="H66" s="34">
         <v>19.92</v>
       </c>
-      <c r="I66" s="33">
+      <c r="I66" s="34">
         <v>21.7</v>
       </c>
-      <c r="J66" s="33">
+      <c r="J66" s="34">
         <v>20.98</v>
       </c>
-      <c r="K66" s="33">
+      <c r="K66" s="34">
         <v>18.32</v>
       </c>
-      <c r="L66" s="33">
+      <c r="L66" s="34">
         <v>10.64</v>
       </c>
-      <c r="M66" s="33">
+      <c r="M66" s="34">
         <v>5.93</v>
       </c>
-      <c r="N66" s="33">
+      <c r="N66" s="34">
         <v>3.23</v>
       </c>
-      <c r="O66" s="33">
+      <c r="O66" s="34">
         <v>3.11</v>
       </c>
-      <c r="P66" s="33">
+      <c r="P66" s="34">
         <v>2.22</v>
       </c>
-      <c r="Q66" s="33">
+      <c r="Q66" s="34">
         <v>2.67</v>
       </c>
-      <c r="R66" s="33">
+      <c r="R66" s="34">
         <v>2.81</v>
       </c>
-      <c r="S66" s="33">
+      <c r="S66" s="34">
         <v>3.27</v>
       </c>
-      <c r="T66" s="33">
+      <c r="T66" s="34">
         <v>3.25</v>
       </c>
-      <c r="U66" s="33">
+      <c r="U66" s="34">
         <v>4.14</v>
       </c>
-      <c r="V66" s="33">
+      <c r="V66" s="34">
         <v>4.01</v>
       </c>
-      <c r="W66" s="35"/>
-      <c r="X66" s="35"/>
-      <c r="Y66" s="35"/>
-      <c r="Z66" s="35"/>
+      <c r="W66" s="36"/>
+      <c r="X66" s="36"/>
+      <c r="Y66" s="36"/>
+      <c r="Z66" s="36"/>
     </row>
     <row r="67" ht="15.0" customHeight="1">
-      <c r="A67" s="29" t="s">
-        <v>361</v>
-      </c>
-      <c r="B67" s="30"/>
-      <c r="C67" s="30"/>
-      <c r="D67" s="30"/>
-      <c r="E67" s="30"/>
-      <c r="F67" s="30"/>
-      <c r="G67" s="30"/>
-      <c r="H67" s="30"/>
-      <c r="I67" s="30"/>
-      <c r="J67" s="30"/>
-      <c r="K67" s="30"/>
-      <c r="L67" s="30"/>
-      <c r="M67" s="30"/>
-      <c r="N67" s="30"/>
-      <c r="O67" s="30"/>
-      <c r="P67" s="30"/>
-      <c r="Q67" s="30"/>
-      <c r="R67" s="30"/>
-      <c r="S67" s="30"/>
-      <c r="T67" s="30"/>
-      <c r="U67" s="30"/>
-      <c r="V67" s="30"/>
-      <c r="W67" s="30"/>
-      <c r="X67" s="30"/>
-      <c r="Y67" s="30"/>
-      <c r="Z67" s="30"/>
+      <c r="A67" s="30" t="s">
+        <v>362</v>
+      </c>
+      <c r="B67" s="31"/>
+      <c r="C67" s="31"/>
+      <c r="D67" s="31"/>
+      <c r="E67" s="31"/>
+      <c r="F67" s="31"/>
+      <c r="G67" s="31"/>
+      <c r="H67" s="31"/>
+      <c r="I67" s="31"/>
+      <c r="J67" s="31"/>
+      <c r="K67" s="31"/>
+      <c r="L67" s="31"/>
+      <c r="M67" s="31"/>
+      <c r="N67" s="31"/>
+      <c r="O67" s="31"/>
+      <c r="P67" s="31"/>
+      <c r="Q67" s="31"/>
+      <c r="R67" s="31"/>
+      <c r="S67" s="31"/>
+      <c r="T67" s="31"/>
+      <c r="U67" s="31"/>
+      <c r="V67" s="31"/>
+      <c r="W67" s="31"/>
+      <c r="X67" s="31"/>
+      <c r="Y67" s="31"/>
+      <c r="Z67" s="31"/>
     </row>
     <row r="68" ht="15.0" customHeight="1">
-      <c r="A68" s="31" t="s">
-        <v>362</v>
-      </c>
-      <c r="B68" s="33">
+      <c r="A68" s="32" t="s">
+        <v>363</v>
+      </c>
+      <c r="B68" s="34">
         <v>32.94</v>
       </c>
-      <c r="C68" s="32">
+      <c r="C68" s="33">
         <v>352.7</v>
       </c>
-      <c r="D68" s="32">
+      <c r="D68" s="33">
         <v>111.44</v>
       </c>
-      <c r="E68" s="33">
+      <c r="E68" s="34">
         <v>12.1</v>
       </c>
-      <c r="F68" s="33">
+      <c r="F68" s="34">
         <v>15.07</v>
       </c>
-      <c r="G68" s="33">
+      <c r="G68" s="34">
         <v>63.52</v>
       </c>
-      <c r="H68" s="33">
+      <c r="H68" s="34">
         <v>41.84</v>
       </c>
-      <c r="I68" s="33">
+      <c r="I68" s="34">
         <v>33.66</v>
       </c>
-      <c r="J68" s="33">
+      <c r="J68" s="34">
         <v>46.79</v>
       </c>
-      <c r="K68" s="33">
+      <c r="K68" s="34">
         <v>42.3</v>
       </c>
-      <c r="L68" s="32">
+      <c r="L68" s="33">
         <v>624.41</v>
       </c>
-      <c r="M68" s="33">
+      <c r="M68" s="34">
         <v>13.83</v>
       </c>
-      <c r="N68" s="33">
+      <c r="N68" s="34">
         <v>7.55</v>
       </c>
-      <c r="O68" s="33">
+      <c r="O68" s="34">
         <v>23.35</v>
       </c>
-      <c r="P68" s="33">
+      <c r="P68" s="34">
         <v>2.31</v>
       </c>
-      <c r="Q68" s="33">
+      <c r="Q68" s="34">
         <v>2.4</v>
       </c>
-      <c r="R68" s="34">
+      <c r="R68" s="35">
         <v>-0.08</v>
       </c>
-      <c r="S68" s="33">
+      <c r="S68" s="34">
         <v>5.58</v>
       </c>
-      <c r="T68" s="33">
+      <c r="T68" s="34">
         <v>4.61</v>
       </c>
-      <c r="U68" s="33">
+      <c r="U68" s="34">
         <v>4.66</v>
       </c>
-      <c r="V68" s="33">
+      <c r="V68" s="34">
         <v>2.97</v>
       </c>
-      <c r="W68" s="33">
+      <c r="W68" s="34">
         <v>3.44</v>
       </c>
-      <c r="X68" s="33">
+      <c r="X68" s="34">
         <v>7.19</v>
       </c>
-      <c r="Y68" s="33">
+      <c r="Y68" s="34">
         <v>11.16</v>
       </c>
-      <c r="Z68" s="35"/>
+      <c r="Z68" s="36"/>
     </row>
     <row r="69" ht="15.0" customHeight="1">
-      <c r="A69" s="31" t="s">
-        <v>363</v>
-      </c>
-      <c r="B69" s="33">
+      <c r="A69" s="32" t="s">
+        <v>364</v>
+      </c>
+      <c r="B69" s="34">
         <v>30.08</v>
       </c>
-      <c r="C69" s="33">
+      <c r="C69" s="34">
         <v>36.99</v>
       </c>
-      <c r="D69" s="33">
+      <c r="D69" s="34">
         <v>34.29</v>
       </c>
-      <c r="E69" s="33">
+      <c r="E69" s="34">
         <v>28.65</v>
       </c>
-      <c r="F69" s="33">
+      <c r="F69" s="34">
         <v>34.84</v>
       </c>
-      <c r="G69" s="33">
+      <c r="G69" s="34">
         <v>45.88</v>
       </c>
-      <c r="H69" s="33">
+      <c r="H69" s="34">
         <v>40.79</v>
       </c>
-      <c r="I69" s="33">
+      <c r="I69" s="34">
         <v>38.21</v>
       </c>
-      <c r="J69" s="33">
+      <c r="J69" s="34">
         <v>38.26</v>
       </c>
-      <c r="K69" s="33">
+      <c r="K69" s="34">
         <v>31.48</v>
       </c>
-      <c r="L69" s="33">
+      <c r="L69" s="34">
         <v>13.35</v>
       </c>
-      <c r="M69" s="33">
+      <c r="M69" s="34">
         <v>6.45</v>
       </c>
-      <c r="N69" s="33">
+      <c r="N69" s="34">
         <v>3.49</v>
       </c>
-      <c r="O69" s="33">
+      <c r="O69" s="34">
         <v>3.38</v>
       </c>
-      <c r="P69" s="33">
+      <c r="P69" s="34">
         <v>2.9</v>
       </c>
-      <c r="Q69" s="33">
+      <c r="Q69" s="34">
         <v>3.46</v>
       </c>
-      <c r="R69" s="33">
+      <c r="R69" s="34">
         <v>3.49</v>
       </c>
-      <c r="S69" s="33">
+      <c r="S69" s="34">
         <v>4.08</v>
       </c>
-      <c r="T69" s="33">
+      <c r="T69" s="34">
         <v>4.19</v>
       </c>
-      <c r="U69" s="33">
+      <c r="U69" s="34">
         <v>4.64</v>
       </c>
-      <c r="V69" s="33">
+      <c r="V69" s="34">
         <v>6.12</v>
       </c>
-      <c r="W69" s="35"/>
-      <c r="X69" s="35"/>
-      <c r="Y69" s="35"/>
-      <c r="Z69" s="35"/>
+      <c r="W69" s="36"/>
+      <c r="X69" s="36"/>
+      <c r="Y69" s="36"/>
+      <c r="Z69" s="36"/>
     </row>
     <row r="70" ht="15.0" customHeight="1">
-      <c r="A70" s="29" t="s">
-        <v>364</v>
-      </c>
-      <c r="B70" s="30"/>
-      <c r="C70" s="30"/>
-      <c r="D70" s="30"/>
-      <c r="E70" s="30"/>
-      <c r="F70" s="30"/>
-      <c r="G70" s="30"/>
-      <c r="H70" s="30"/>
-      <c r="I70" s="30"/>
-      <c r="J70" s="30"/>
-      <c r="K70" s="30"/>
-      <c r="L70" s="30"/>
-      <c r="M70" s="30"/>
-      <c r="N70" s="30"/>
-      <c r="O70" s="30"/>
-      <c r="P70" s="30"/>
-      <c r="Q70" s="30"/>
-      <c r="R70" s="30"/>
-      <c r="S70" s="30"/>
-      <c r="T70" s="30"/>
-      <c r="U70" s="30"/>
-      <c r="V70" s="30"/>
-      <c r="W70" s="30"/>
-      <c r="X70" s="30"/>
-      <c r="Y70" s="30"/>
-      <c r="Z70" s="30"/>
+      <c r="A70" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="B70" s="31"/>
+      <c r="C70" s="31"/>
+      <c r="D70" s="31"/>
+      <c r="E70" s="31"/>
+      <c r="F70" s="31"/>
+      <c r="G70" s="31"/>
+      <c r="H70" s="31"/>
+      <c r="I70" s="31"/>
+      <c r="J70" s="31"/>
+      <c r="K70" s="31"/>
+      <c r="L70" s="31"/>
+      <c r="M70" s="31"/>
+      <c r="N70" s="31"/>
+      <c r="O70" s="31"/>
+      <c r="P70" s="31"/>
+      <c r="Q70" s="31"/>
+      <c r="R70" s="31"/>
+      <c r="S70" s="31"/>
+      <c r="T70" s="31"/>
+      <c r="U70" s="31"/>
+      <c r="V70" s="31"/>
+      <c r="W70" s="31"/>
+      <c r="X70" s="31"/>
+      <c r="Y70" s="31"/>
+      <c r="Z70" s="31"/>
     </row>
     <row r="71" ht="15.0" customHeight="1">
-      <c r="A71" s="31" t="s">
-        <v>365</v>
-      </c>
-      <c r="B71" s="33">
+      <c r="A71" s="32" t="s">
+        <v>366</v>
+      </c>
+      <c r="B71" s="34">
         <v>32.94</v>
       </c>
-      <c r="C71" s="35"/>
-      <c r="D71" s="32">
+      <c r="C71" s="36"/>
+      <c r="D71" s="33">
         <v>121.6</v>
       </c>
-      <c r="E71" s="35"/>
-      <c r="F71" s="35"/>
-      <c r="G71" s="35"/>
-      <c r="H71" s="35"/>
-      <c r="I71" s="32">
+      <c r="E71" s="36"/>
+      <c r="F71" s="36"/>
+      <c r="G71" s="36"/>
+      <c r="H71" s="36"/>
+      <c r="I71" s="33">
         <v>518.44</v>
       </c>
-      <c r="J71" s="35"/>
-      <c r="K71" s="35"/>
-      <c r="L71" s="32">
+      <c r="J71" s="36"/>
+      <c r="K71" s="36"/>
+      <c r="L71" s="33">
         <v>624.41</v>
       </c>
-      <c r="M71" s="35"/>
-      <c r="N71" s="35"/>
-      <c r="O71" s="35"/>
-      <c r="P71" s="35"/>
-      <c r="Q71" s="33">
+      <c r="M71" s="36"/>
+      <c r="N71" s="36"/>
+      <c r="O71" s="36"/>
+      <c r="P71" s="36"/>
+      <c r="Q71" s="34">
         <v>2.4</v>
       </c>
-      <c r="R71" s="34">
+      <c r="R71" s="35">
         <v>-0.09</v>
       </c>
-      <c r="S71" s="33">
+      <c r="S71" s="34">
         <v>5.58</v>
       </c>
-      <c r="T71" s="33">
+      <c r="T71" s="34">
         <v>4.61</v>
       </c>
-      <c r="U71" s="33">
+      <c r="U71" s="34">
         <v>4.84</v>
       </c>
-      <c r="V71" s="33">
+      <c r="V71" s="34">
         <v>3.2</v>
       </c>
-      <c r="W71" s="33">
+      <c r="W71" s="34">
         <v>3.48</v>
       </c>
-      <c r="X71" s="33">
+      <c r="X71" s="34">
         <v>7.31</v>
       </c>
-      <c r="Y71" s="33">
+      <c r="Y71" s="34">
         <v>11.59</v>
       </c>
-      <c r="Z71" s="35"/>
+      <c r="Z71" s="36"/>
     </row>
     <row r="72" ht="15.0" customHeight="1">
-      <c r="A72" s="31" t="s">
-        <v>366</v>
-      </c>
-      <c r="B72" s="35"/>
-      <c r="C72" s="35"/>
-      <c r="D72" s="35"/>
-      <c r="E72" s="35"/>
-      <c r="F72" s="35"/>
-      <c r="G72" s="35"/>
-      <c r="H72" s="35"/>
-      <c r="I72" s="35"/>
-      <c r="J72" s="35"/>
-      <c r="K72" s="35"/>
-      <c r="L72" s="35"/>
-      <c r="M72" s="35"/>
-      <c r="N72" s="35"/>
-      <c r="O72" s="35"/>
-      <c r="P72" s="33">
+      <c r="A72" s="32" t="s">
+        <v>367</v>
+      </c>
+      <c r="B72" s="36"/>
+      <c r="C72" s="36"/>
+      <c r="D72" s="36"/>
+      <c r="E72" s="36"/>
+      <c r="F72" s="36"/>
+      <c r="G72" s="36"/>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" s="36"/>
+      <c r="K72" s="36"/>
+      <c r="L72" s="36"/>
+      <c r="M72" s="36"/>
+      <c r="N72" s="36"/>
+      <c r="O72" s="36"/>
+      <c r="P72" s="34">
         <v>3.71</v>
       </c>
-      <c r="Q72" s="33">
+      <c r="Q72" s="34">
         <v>3.51</v>
       </c>
-      <c r="R72" s="33">
+      <c r="R72" s="34">
         <v>3.61</v>
       </c>
-      <c r="S72" s="33">
+      <c r="S72" s="34">
         <v>4.2</v>
       </c>
-      <c r="T72" s="33">
+      <c r="T72" s="34">
         <v>4.33</v>
       </c>
-      <c r="U72" s="33">
+      <c r="U72" s="34">
         <v>4.83</v>
       </c>
-      <c r="V72" s="33">
+      <c r="V72" s="34">
         <v>7.06</v>
       </c>
-      <c r="W72" s="35"/>
-      <c r="X72" s="35"/>
-      <c r="Y72" s="35"/>
-      <c r="Z72" s="35"/>
+      <c r="W72" s="36"/>
+      <c r="X72" s="36"/>
+      <c r="Y72" s="36"/>
+      <c r="Z72" s="36"/>
     </row>
     <row r="73" ht="15.75" customHeight="1"/>
     <row r="74" ht="15.75" customHeight="1"/>
